--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DF7442-5A28-4002-8926-2EBCBADCECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC51294A-7E86-4297-AA6B-E397659BA9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5790" yWindow="1035" windowWidth="18660" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5894" uniqueCount="2028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5902" uniqueCount="2030">
   <si>
     <t>Upgrade_Table</t>
   </si>
@@ -6205,6 +6205,12 @@
   </si>
   <si>
     <t>수확기를 잡고 뒤로 끌었다 놓아 발사 · 마우스 좌우로 슬라이드 바 이동 · F/우클릭 배속(×1·×2·×4) · Esc 일시정지</t>
+  </si>
+  <si>
+    <t>수확 중단</t>
+  </si>
+  <si>
+    <t>수확이 도중에 중단되어 스테이지가 완료되지 않습니다.</t>
   </si>
 </sst>
 </file>
@@ -7089,46 +7095,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -7137,12 +7143,12 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7610,29 +7616,29 @@
   <sheetData>
     <row r="1" spans="2:44" ht="12" customHeight="1"/>
     <row r="2" spans="2:44">
-      <c r="B2" s="156" t="s">
+      <c r="B2" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-      <c r="R2" s="157"/>
-      <c r="S2" s="157"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="158"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155"/>
+      <c r="R2" s="155"/>
+      <c r="S2" s="155"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="156"/>
     </row>
     <row r="3" spans="2:44">
       <c r="B3" s="17"/>
@@ -7689,29 +7695,29 @@
       <c r="V4" s="14"/>
     </row>
     <row r="5" spans="2:44">
-      <c r="B5" s="156" t="s">
+      <c r="B5" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="157"/>
-      <c r="N5" s="157"/>
-      <c r="O5" s="157"/>
-      <c r="P5" s="157"/>
-      <c r="Q5" s="157"/>
-      <c r="R5" s="157"/>
-      <c r="S5" s="157"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="157"/>
-      <c r="V5" s="158"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="155"/>
+      <c r="Q5" s="155"/>
+      <c r="R5" s="155"/>
+      <c r="S5" s="155"/>
+      <c r="T5" s="155"/>
+      <c r="U5" s="155"/>
+      <c r="V5" s="156"/>
     </row>
     <row r="6" spans="2:44">
       <c r="B6" s="6"/>
@@ -7841,29 +7847,29 @@
     </row>
     <row r="10" spans="2:44" ht="8.1" customHeight="1"/>
     <row r="11" spans="2:44">
-      <c r="B11" s="156" t="s">
+      <c r="B11" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="157"/>
-      <c r="H11" s="157"/>
-      <c r="I11" s="157"/>
-      <c r="J11" s="157"/>
-      <c r="K11" s="157"/>
-      <c r="L11" s="157"/>
-      <c r="M11" s="157"/>
-      <c r="N11" s="157"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="157"/>
-      <c r="Q11" s="157"/>
-      <c r="R11" s="157"/>
-      <c r="S11" s="157"/>
-      <c r="T11" s="157"/>
-      <c r="U11" s="157"/>
-      <c r="V11" s="158"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="155"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="155"/>
+      <c r="G11" s="155"/>
+      <c r="H11" s="155"/>
+      <c r="I11" s="155"/>
+      <c r="J11" s="155"/>
+      <c r="K11" s="155"/>
+      <c r="L11" s="155"/>
+      <c r="M11" s="155"/>
+      <c r="N11" s="155"/>
+      <c r="O11" s="155"/>
+      <c r="P11" s="155"/>
+      <c r="Q11" s="155"/>
+      <c r="R11" s="155"/>
+      <c r="S11" s="155"/>
+      <c r="T11" s="155"/>
+      <c r="U11" s="155"/>
+      <c r="V11" s="156"/>
     </row>
     <row r="12" spans="2:44">
       <c r="B12" s="6"/>
@@ -8150,19 +8156,19 @@
       <c r="AF22" s="27"/>
     </row>
     <row r="23" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B23" s="159" t="s">
+      <c r="B23" s="157" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="146"/>
-      <c r="D23" s="146"/>
-      <c r="E23" s="146"/>
-      <c r="F23" s="146"/>
-      <c r="G23" s="146"/>
-      <c r="H23" s="161" t="s">
+      <c r="C23" s="144"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="144"/>
+      <c r="G23" s="144"/>
+      <c r="H23" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="146"/>
-      <c r="J23" s="146"/>
+      <c r="I23" s="144"/>
+      <c r="J23" s="144"/>
       <c r="K23" s="28" t="s">
         <v>68</v>
       </c>
@@ -8190,18 +8196,18 @@
     </row>
     <row r="24" spans="2:32" s="10" customFormat="1">
       <c r="B24" s="86"/>
-      <c r="C24" s="136" t="s">
+      <c r="C24" s="153" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="137"/>
-      <c r="E24" s="137"/>
-      <c r="F24" s="137"/>
-      <c r="G24" s="138"/>
-      <c r="H24" s="142" t="s">
+      <c r="D24" s="151"/>
+      <c r="E24" s="151"/>
+      <c r="F24" s="151"/>
+      <c r="G24" s="152"/>
+      <c r="H24" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="137"/>
-      <c r="J24" s="138"/>
+      <c r="I24" s="151"/>
+      <c r="J24" s="152"/>
       <c r="K24" s="34" t="s">
         <v>70</v>
       </c>
@@ -8229,14 +8235,14 @@
     </row>
     <row r="25" spans="2:32" s="10" customFormat="1">
       <c r="B25" s="22"/>
-      <c r="C25" s="139"/>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
-      <c r="G25" s="140"/>
-      <c r="H25" s="143"/>
-      <c r="I25" s="139"/>
-      <c r="J25" s="140"/>
+      <c r="C25" s="140"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="158"/>
+      <c r="I25" s="140"/>
+      <c r="J25" s="141"/>
       <c r="K25" s="19" t="s">
         <v>49</v>
       </c>
@@ -8258,18 +8264,18 @@
     </row>
     <row r="26" spans="2:32" s="10" customFormat="1">
       <c r="B26" s="22"/>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="139" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="141" t="s">
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="141"/>
+      <c r="H26" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="139"/>
-      <c r="J26" s="140"/>
+      <c r="I26" s="140"/>
+      <c r="J26" s="141"/>
       <c r="K26" s="19" t="s">
         <v>74</v>
       </c>
@@ -8289,18 +8295,18 @@
     </row>
     <row r="27" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B27" s="22"/>
-      <c r="C27" s="144" t="s">
+      <c r="C27" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="139"/>
-      <c r="G27" s="140"/>
-      <c r="H27" s="141" t="s">
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="141"/>
+      <c r="H27" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I27" s="139"/>
-      <c r="J27" s="140"/>
+      <c r="I27" s="140"/>
+      <c r="J27" s="141"/>
       <c r="K27" s="19" t="s">
         <v>75</v>
       </c>
@@ -8320,18 +8326,18 @@
     </row>
     <row r="28" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B28" s="22"/>
-      <c r="C28" s="144" t="s">
+      <c r="C28" s="139" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="139"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="141" t="s">
+      <c r="D28" s="140"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I28" s="139"/>
-      <c r="J28" s="140"/>
+      <c r="I28" s="140"/>
+      <c r="J28" s="141"/>
       <c r="K28" s="19" t="s">
         <v>77</v>
       </c>
@@ -8351,18 +8357,18 @@
     </row>
     <row r="29" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B29" s="22"/>
-      <c r="C29" s="144" t="s">
+      <c r="C29" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="140"/>
-      <c r="H29" s="141" t="s">
+      <c r="D29" s="140"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I29" s="139"/>
-      <c r="J29" s="140"/>
+      <c r="I29" s="140"/>
+      <c r="J29" s="141"/>
       <c r="K29" s="19" t="s">
         <v>78</v>
       </c>
@@ -8382,18 +8388,18 @@
     </row>
     <row r="30" spans="2:32" s="10" customFormat="1">
       <c r="B30" s="22"/>
-      <c r="C30" s="144" t="s">
+      <c r="C30" s="139" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="139"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="139"/>
-      <c r="G30" s="140"/>
-      <c r="H30" s="141" t="s">
+      <c r="D30" s="140"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="140"/>
+      <c r="G30" s="141"/>
+      <c r="H30" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I30" s="139"/>
-      <c r="J30" s="140"/>
+      <c r="I30" s="140"/>
+      <c r="J30" s="141"/>
       <c r="K30" s="120" t="s">
         <v>421</v>
       </c>
@@ -8413,18 +8419,18 @@
     </row>
     <row r="31" spans="2:32" s="10" customFormat="1">
       <c r="B31" s="22"/>
-      <c r="C31" s="144" t="s">
+      <c r="C31" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="140"/>
-      <c r="H31" s="141" t="s">
+      <c r="D31" s="140"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="140"/>
+      <c r="G31" s="141"/>
+      <c r="H31" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I31" s="139"/>
-      <c r="J31" s="140"/>
+      <c r="I31" s="140"/>
+      <c r="J31" s="141"/>
       <c r="K31" s="19" t="s">
         <v>80</v>
       </c>
@@ -8444,18 +8450,18 @@
     </row>
     <row r="32" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B32" s="75"/>
-      <c r="C32" s="160" t="s">
+      <c r="C32" s="145" t="s">
         <v>422</v>
       </c>
-      <c r="D32" s="149"/>
-      <c r="E32" s="149"/>
-      <c r="F32" s="149"/>
-      <c r="G32" s="150"/>
-      <c r="H32" s="148" t="s">
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="137"/>
+      <c r="G32" s="138"/>
+      <c r="H32" s="136" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="149"/>
-      <c r="J32" s="150"/>
+      <c r="I32" s="137"/>
+      <c r="J32" s="138"/>
       <c r="K32" s="81" t="s">
         <v>82</v>
       </c>
@@ -8517,19 +8523,19 @@
       <c r="AF33" s="27"/>
     </row>
     <row r="34" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B34" s="145" t="s">
+      <c r="B34" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="146"/>
-      <c r="D34" s="146"/>
-      <c r="E34" s="146"/>
-      <c r="F34" s="146"/>
-      <c r="G34" s="147"/>
-      <c r="H34" s="145" t="s">
+      <c r="C34" s="144"/>
+      <c r="D34" s="144"/>
+      <c r="E34" s="144"/>
+      <c r="F34" s="144"/>
+      <c r="G34" s="149"/>
+      <c r="H34" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I34" s="146"/>
-      <c r="J34" s="147"/>
+      <c r="I34" s="144"/>
+      <c r="J34" s="149"/>
       <c r="K34" s="28" t="s">
         <v>68</v>
       </c>
@@ -8557,18 +8563,18 @@
     </row>
     <row r="35" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B35" s="86"/>
-      <c r="C35" s="136" t="s">
+      <c r="C35" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="137"/>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="138"/>
-      <c r="H35" s="142" t="s">
+      <c r="D35" s="151"/>
+      <c r="E35" s="151"/>
+      <c r="F35" s="151"/>
+      <c r="G35" s="152"/>
+      <c r="H35" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="I35" s="137"/>
-      <c r="J35" s="138"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="152"/>
       <c r="K35" s="34" t="s">
         <v>84</v>
       </c>
@@ -8596,18 +8602,18 @@
     </row>
     <row r="36" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B36" s="75"/>
-      <c r="C36" s="160" t="s">
+      <c r="C36" s="145" t="s">
         <v>423</v>
       </c>
-      <c r="D36" s="149"/>
-      <c r="E36" s="149"/>
-      <c r="F36" s="149"/>
-      <c r="G36" s="150"/>
-      <c r="H36" s="148" t="s">
+      <c r="D36" s="137"/>
+      <c r="E36" s="137"/>
+      <c r="F36" s="137"/>
+      <c r="G36" s="138"/>
+      <c r="H36" s="136" t="s">
         <v>69</v>
       </c>
-      <c r="I36" s="149"/>
-      <c r="J36" s="150"/>
+      <c r="I36" s="137"/>
+      <c r="J36" s="138"/>
       <c r="K36" s="81" t="s">
         <v>85</v>
       </c>
@@ -8669,19 +8675,19 @@
       <c r="AF37" s="92"/>
     </row>
     <row r="38" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B38" s="145" t="s">
+      <c r="B38" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="146"/>
-      <c r="D38" s="146"/>
-      <c r="E38" s="146"/>
-      <c r="F38" s="146"/>
-      <c r="G38" s="147"/>
-      <c r="H38" s="145" t="s">
+      <c r="C38" s="144"/>
+      <c r="D38" s="144"/>
+      <c r="E38" s="144"/>
+      <c r="F38" s="144"/>
+      <c r="G38" s="149"/>
+      <c r="H38" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="146"/>
-      <c r="J38" s="147"/>
+      <c r="I38" s="144"/>
+      <c r="J38" s="149"/>
       <c r="K38" s="28" t="s">
         <v>68</v>
       </c>
@@ -8709,18 +8715,18 @@
     </row>
     <row r="39" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B39" s="21"/>
-      <c r="C39" s="144" t="s">
+      <c r="C39" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="139"/>
-      <c r="E39" s="139"/>
-      <c r="F39" s="139"/>
-      <c r="G39" s="140"/>
-      <c r="H39" s="141" t="s">
+      <c r="D39" s="140"/>
+      <c r="E39" s="140"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="141"/>
+      <c r="H39" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I39" s="139"/>
-      <c r="J39" s="140"/>
+      <c r="I39" s="140"/>
+      <c r="J39" s="141"/>
       <c r="K39" s="19" t="s">
         <v>86</v>
       </c>
@@ -8740,18 +8746,18 @@
     </row>
     <row r="40" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B40" s="22"/>
-      <c r="C40" s="144" t="s">
+      <c r="C40" s="139" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="139"/>
-      <c r="E40" s="139"/>
-      <c r="F40" s="139"/>
-      <c r="G40" s="140"/>
-      <c r="H40" s="141" t="s">
+      <c r="D40" s="140"/>
+      <c r="E40" s="140"/>
+      <c r="F40" s="140"/>
+      <c r="G40" s="141"/>
+      <c r="H40" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I40" s="139"/>
-      <c r="J40" s="140"/>
+      <c r="I40" s="140"/>
+      <c r="J40" s="141"/>
       <c r="K40" s="19" t="s">
         <v>88</v>
       </c>
@@ -8771,18 +8777,18 @@
     </row>
     <row r="41" spans="2:32" s="10" customFormat="1">
       <c r="B41" s="22"/>
-      <c r="C41" s="144" t="s">
+      <c r="C41" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="139"/>
-      <c r="E41" s="139"/>
-      <c r="F41" s="139"/>
-      <c r="G41" s="140"/>
-      <c r="H41" s="141" t="s">
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="140"/>
+      <c r="G41" s="141"/>
+      <c r="H41" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="139"/>
-      <c r="J41" s="140"/>
+      <c r="I41" s="140"/>
+      <c r="J41" s="141"/>
       <c r="K41" s="19" t="s">
         <v>89</v>
       </c>
@@ -8802,18 +8808,18 @@
     </row>
     <row r="42" spans="2:32" s="10" customFormat="1">
       <c r="B42" s="22"/>
-      <c r="C42" s="144" t="s">
+      <c r="C42" s="139" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="139"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="140"/>
-      <c r="H42" s="141" t="s">
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="141"/>
+      <c r="H42" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I42" s="139"/>
-      <c r="J42" s="140"/>
+      <c r="I42" s="140"/>
+      <c r="J42" s="141"/>
       <c r="K42" s="19" t="s">
         <v>91</v>
       </c>
@@ -8833,18 +8839,18 @@
     </row>
     <row r="43" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B43" s="75"/>
-      <c r="C43" s="152" t="s">
+      <c r="C43" s="142" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="149"/>
-      <c r="E43" s="149"/>
-      <c r="F43" s="149"/>
-      <c r="G43" s="150"/>
-      <c r="H43" s="148" t="s">
+      <c r="D43" s="137"/>
+      <c r="E43" s="137"/>
+      <c r="F43" s="137"/>
+      <c r="G43" s="138"/>
+      <c r="H43" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="149"/>
-      <c r="J43" s="150"/>
+      <c r="I43" s="137"/>
+      <c r="J43" s="138"/>
       <c r="K43" s="81" t="s">
         <v>92</v>
       </c>
@@ -8906,19 +8912,19 @@
       <c r="AF44" s="27"/>
     </row>
     <row r="45" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B45" s="145" t="s">
+      <c r="B45" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="146"/>
-      <c r="D45" s="146"/>
-      <c r="E45" s="146"/>
-      <c r="F45" s="146"/>
-      <c r="G45" s="147"/>
-      <c r="H45" s="153" t="s">
+      <c r="C45" s="144"/>
+      <c r="D45" s="144"/>
+      <c r="E45" s="144"/>
+      <c r="F45" s="144"/>
+      <c r="G45" s="149"/>
+      <c r="H45" s="159" t="s">
         <v>67</v>
       </c>
-      <c r="I45" s="154"/>
-      <c r="J45" s="155"/>
+      <c r="I45" s="160"/>
+      <c r="J45" s="161"/>
       <c r="K45" s="83" t="s">
         <v>68</v>
       </c>
@@ -8946,18 +8952,18 @@
     </row>
     <row r="46" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B46" s="21"/>
-      <c r="C46" s="144" t="s">
+      <c r="C46" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="139"/>
-      <c r="E46" s="139"/>
-      <c r="F46" s="139"/>
-      <c r="G46" s="140"/>
-      <c r="H46" s="142" t="s">
+      <c r="D46" s="140"/>
+      <c r="E46" s="140"/>
+      <c r="F46" s="140"/>
+      <c r="G46" s="141"/>
+      <c r="H46" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="I46" s="137"/>
-      <c r="J46" s="138"/>
+      <c r="I46" s="151"/>
+      <c r="J46" s="152"/>
       <c r="K46" s="19" t="s">
         <v>93</v>
       </c>
@@ -8977,18 +8983,18 @@
     </row>
     <row r="47" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B47" s="22"/>
-      <c r="C47" s="144" t="s">
+      <c r="C47" s="139" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="139"/>
-      <c r="E47" s="139"/>
-      <c r="F47" s="139"/>
-      <c r="G47" s="140"/>
-      <c r="H47" s="141" t="s">
+      <c r="D47" s="140"/>
+      <c r="E47" s="140"/>
+      <c r="F47" s="140"/>
+      <c r="G47" s="141"/>
+      <c r="H47" s="146" t="s">
         <v>81</v>
       </c>
-      <c r="I47" s="139"/>
-      <c r="J47" s="140"/>
+      <c r="I47" s="140"/>
+      <c r="J47" s="141"/>
       <c r="K47" s="19" t="s">
         <v>95</v>
       </c>
@@ -9008,14 +9014,14 @@
     </row>
     <row r="48" spans="2:32" s="10" customFormat="1">
       <c r="B48" s="22"/>
-      <c r="C48" s="139"/>
-      <c r="D48" s="139"/>
-      <c r="E48" s="139"/>
-      <c r="F48" s="139"/>
-      <c r="G48" s="140"/>
-      <c r="H48" s="143"/>
-      <c r="I48" s="139"/>
-      <c r="J48" s="140"/>
+      <c r="C48" s="140"/>
+      <c r="D48" s="140"/>
+      <c r="E48" s="140"/>
+      <c r="F48" s="140"/>
+      <c r="G48" s="141"/>
+      <c r="H48" s="158"/>
+      <c r="I48" s="140"/>
+      <c r="J48" s="141"/>
       <c r="K48" s="19" t="s">
         <v>49</v>
       </c>
@@ -9037,14 +9043,14 @@
     </row>
     <row r="49" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B49" s="22"/>
-      <c r="C49" s="139"/>
-      <c r="D49" s="139"/>
-      <c r="E49" s="139"/>
-      <c r="F49" s="139"/>
-      <c r="G49" s="140"/>
-      <c r="H49" s="143"/>
-      <c r="I49" s="139"/>
-      <c r="J49" s="140"/>
+      <c r="C49" s="140"/>
+      <c r="D49" s="140"/>
+      <c r="E49" s="140"/>
+      <c r="F49" s="140"/>
+      <c r="G49" s="141"/>
+      <c r="H49" s="158"/>
+      <c r="I49" s="140"/>
+      <c r="J49" s="141"/>
       <c r="K49" s="19" t="s">
         <v>49</v>
       </c>
@@ -9101,19 +9107,19 @@
       <c r="AG50" s="92"/>
     </row>
     <row r="51" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B51" s="145" t="s">
+      <c r="B51" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="146"/>
-      <c r="D51" s="146"/>
-      <c r="E51" s="146"/>
-      <c r="F51" s="146"/>
-      <c r="G51" s="147"/>
-      <c r="H51" s="145" t="s">
+      <c r="C51" s="144"/>
+      <c r="D51" s="144"/>
+      <c r="E51" s="144"/>
+      <c r="F51" s="144"/>
+      <c r="G51" s="149"/>
+      <c r="H51" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I51" s="146"/>
-      <c r="J51" s="147"/>
+      <c r="I51" s="144"/>
+      <c r="J51" s="149"/>
       <c r="K51" s="28" t="s">
         <v>68</v>
       </c>
@@ -9142,18 +9148,18 @@
     </row>
     <row r="52" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B52" s="21"/>
-      <c r="C52" s="144" t="s">
+      <c r="C52" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="139"/>
-      <c r="E52" s="139"/>
-      <c r="F52" s="139"/>
-      <c r="G52" s="140"/>
-      <c r="H52" s="141" t="s">
+      <c r="D52" s="140"/>
+      <c r="E52" s="140"/>
+      <c r="F52" s="140"/>
+      <c r="G52" s="141"/>
+      <c r="H52" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I52" s="139"/>
-      <c r="J52" s="140"/>
+      <c r="I52" s="140"/>
+      <c r="J52" s="141"/>
       <c r="K52" s="19" t="s">
         <v>99</v>
       </c>
@@ -9173,18 +9179,18 @@
     </row>
     <row r="53" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B53" s="22"/>
-      <c r="C53" s="144" t="s">
+      <c r="C53" s="139" t="s">
         <v>100</v>
       </c>
-      <c r="D53" s="139"/>
-      <c r="E53" s="139"/>
-      <c r="F53" s="139"/>
-      <c r="G53" s="140"/>
-      <c r="H53" s="141" t="s">
+      <c r="D53" s="140"/>
+      <c r="E53" s="140"/>
+      <c r="F53" s="140"/>
+      <c r="G53" s="141"/>
+      <c r="H53" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I53" s="139"/>
-      <c r="J53" s="140"/>
+      <c r="I53" s="140"/>
+      <c r="J53" s="141"/>
       <c r="K53" s="19" t="s">
         <v>101</v>
       </c>
@@ -9204,18 +9210,18 @@
     </row>
     <row r="54" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B54" s="75"/>
-      <c r="C54" s="152" t="s">
+      <c r="C54" s="142" t="s">
         <v>102</v>
       </c>
-      <c r="D54" s="149"/>
-      <c r="E54" s="149"/>
-      <c r="F54" s="149"/>
-      <c r="G54" s="150"/>
-      <c r="H54" s="148" t="s">
+      <c r="D54" s="137"/>
+      <c r="E54" s="137"/>
+      <c r="F54" s="137"/>
+      <c r="G54" s="138"/>
+      <c r="H54" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="I54" s="149"/>
-      <c r="J54" s="150"/>
+      <c r="I54" s="137"/>
+      <c r="J54" s="138"/>
       <c r="K54" s="81" t="s">
         <v>103</v>
       </c>
@@ -9279,19 +9285,19 @@
       <c r="AG55" s="92"/>
     </row>
     <row r="56" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B56" s="145" t="s">
+      <c r="B56" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="146"/>
-      <c r="D56" s="146"/>
-      <c r="E56" s="146"/>
-      <c r="F56" s="146"/>
-      <c r="G56" s="147"/>
-      <c r="H56" s="145" t="s">
+      <c r="C56" s="144"/>
+      <c r="D56" s="144"/>
+      <c r="E56" s="144"/>
+      <c r="F56" s="144"/>
+      <c r="G56" s="149"/>
+      <c r="H56" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I56" s="146"/>
-      <c r="J56" s="147"/>
+      <c r="I56" s="144"/>
+      <c r="J56" s="149"/>
       <c r="K56" s="28" t="s">
         <v>68</v>
       </c>
@@ -9320,18 +9326,18 @@
     </row>
     <row r="57" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B57" s="21"/>
-      <c r="C57" s="144" t="s">
+      <c r="C57" s="139" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="139"/>
-      <c r="E57" s="139"/>
-      <c r="F57" s="139"/>
-      <c r="G57" s="140"/>
-      <c r="H57" s="141" t="s">
+      <c r="D57" s="140"/>
+      <c r="E57" s="140"/>
+      <c r="F57" s="140"/>
+      <c r="G57" s="141"/>
+      <c r="H57" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I57" s="139"/>
-      <c r="J57" s="140"/>
+      <c r="I57" s="140"/>
+      <c r="J57" s="141"/>
       <c r="K57" s="19" t="s">
         <v>104</v>
       </c>
@@ -9351,18 +9357,18 @@
     </row>
     <row r="58" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B58" s="22"/>
-      <c r="C58" s="144" t="s">
+      <c r="C58" s="139" t="s">
         <v>105</v>
       </c>
-      <c r="D58" s="139"/>
-      <c r="E58" s="139"/>
-      <c r="F58" s="139"/>
-      <c r="G58" s="140"/>
-      <c r="H58" s="141" t="s">
+      <c r="D58" s="140"/>
+      <c r="E58" s="140"/>
+      <c r="F58" s="140"/>
+      <c r="G58" s="141"/>
+      <c r="H58" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I58" s="139"/>
-      <c r="J58" s="140"/>
+      <c r="I58" s="140"/>
+      <c r="J58" s="141"/>
       <c r="K58" s="19" t="s">
         <v>106</v>
       </c>
@@ -9382,18 +9388,18 @@
     </row>
     <row r="59" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B59" s="22"/>
-      <c r="C59" s="144" t="s">
+      <c r="C59" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="140"/>
-      <c r="H59" s="141" t="s">
+      <c r="D59" s="140"/>
+      <c r="E59" s="140"/>
+      <c r="F59" s="140"/>
+      <c r="G59" s="141"/>
+      <c r="H59" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I59" s="139"/>
-      <c r="J59" s="140"/>
+      <c r="I59" s="140"/>
+      <c r="J59" s="141"/>
       <c r="K59" s="19" t="s">
         <v>107</v>
       </c>
@@ -9413,18 +9419,18 @@
     </row>
     <row r="60" spans="2:33" s="10" customFormat="1">
       <c r="B60" s="22"/>
-      <c r="C60" s="144" t="s">
+      <c r="C60" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="D60" s="139"/>
-      <c r="E60" s="139"/>
-      <c r="F60" s="139"/>
-      <c r="G60" s="140"/>
-      <c r="H60" s="141" t="s">
+      <c r="D60" s="140"/>
+      <c r="E60" s="140"/>
+      <c r="F60" s="140"/>
+      <c r="G60" s="141"/>
+      <c r="H60" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I60" s="139"/>
-      <c r="J60" s="140"/>
+      <c r="I60" s="140"/>
+      <c r="J60" s="141"/>
       <c r="K60" s="19" t="s">
         <v>109</v>
       </c>
@@ -9444,18 +9450,18 @@
     </row>
     <row r="61" spans="2:33" s="10" customFormat="1">
       <c r="B61" s="22"/>
-      <c r="C61" s="144" t="s">
+      <c r="C61" s="139" t="s">
         <v>110</v>
       </c>
-      <c r="D61" s="139"/>
-      <c r="E61" s="139"/>
-      <c r="F61" s="139"/>
-      <c r="G61" s="140"/>
-      <c r="H61" s="141" t="s">
+      <c r="D61" s="140"/>
+      <c r="E61" s="140"/>
+      <c r="F61" s="140"/>
+      <c r="G61" s="141"/>
+      <c r="H61" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I61" s="139"/>
-      <c r="J61" s="140"/>
+      <c r="I61" s="140"/>
+      <c r="J61" s="141"/>
       <c r="K61" s="19" t="s">
         <v>111</v>
       </c>
@@ -9475,18 +9481,18 @@
     </row>
     <row r="62" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B62" s="75"/>
-      <c r="C62" s="152" t="s">
+      <c r="C62" s="142" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="149"/>
-      <c r="E62" s="149"/>
-      <c r="F62" s="149"/>
-      <c r="G62" s="150"/>
-      <c r="H62" s="148" t="s">
+      <c r="D62" s="137"/>
+      <c r="E62" s="137"/>
+      <c r="F62" s="137"/>
+      <c r="G62" s="138"/>
+      <c r="H62" s="136" t="s">
         <v>81</v>
       </c>
-      <c r="I62" s="149"/>
-      <c r="J62" s="150"/>
+      <c r="I62" s="137"/>
+      <c r="J62" s="138"/>
       <c r="K62" s="81" t="s">
         <v>113</v>
       </c>
@@ -9550,19 +9556,19 @@
       <c r="AG63" s="92"/>
     </row>
     <row r="64" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B64" s="145" t="s">
+      <c r="B64" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="146"/>
-      <c r="D64" s="146"/>
-      <c r="E64" s="146"/>
-      <c r="F64" s="146"/>
-      <c r="G64" s="147"/>
-      <c r="H64" s="145" t="s">
+      <c r="C64" s="144"/>
+      <c r="D64" s="144"/>
+      <c r="E64" s="144"/>
+      <c r="F64" s="144"/>
+      <c r="G64" s="149"/>
+      <c r="H64" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I64" s="146"/>
-      <c r="J64" s="147"/>
+      <c r="I64" s="144"/>
+      <c r="J64" s="149"/>
       <c r="K64" s="83" t="s">
         <v>68</v>
       </c>
@@ -9591,18 +9597,18 @@
     </row>
     <row r="65" spans="2:33">
       <c r="B65" s="21"/>
-      <c r="C65" s="144" t="s">
+      <c r="C65" s="139" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="151"/>
-      <c r="E65" s="151"/>
-      <c r="F65" s="151"/>
-      <c r="G65" s="140"/>
-      <c r="H65" s="142" t="s">
+      <c r="D65" s="147"/>
+      <c r="E65" s="147"/>
+      <c r="F65" s="147"/>
+      <c r="G65" s="141"/>
+      <c r="H65" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="I65" s="137"/>
-      <c r="J65" s="138"/>
+      <c r="I65" s="151"/>
+      <c r="J65" s="152"/>
       <c r="K65" s="19" t="s">
         <v>115</v>
       </c>
@@ -9622,18 +9628,18 @@
     </row>
     <row r="66" spans="2:33">
       <c r="B66" s="22"/>
-      <c r="C66" s="144" t="s">
+      <c r="C66" s="139" t="s">
         <v>116</v>
       </c>
-      <c r="D66" s="151"/>
-      <c r="E66" s="151"/>
-      <c r="F66" s="151"/>
-      <c r="G66" s="140"/>
-      <c r="H66" s="141" t="s">
+      <c r="D66" s="147"/>
+      <c r="E66" s="147"/>
+      <c r="F66" s="147"/>
+      <c r="G66" s="141"/>
+      <c r="H66" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I66" s="151"/>
-      <c r="J66" s="140"/>
+      <c r="I66" s="147"/>
+      <c r="J66" s="141"/>
       <c r="K66" s="19" t="s">
         <v>117</v>
       </c>
@@ -9653,18 +9659,18 @@
     </row>
     <row r="67" spans="2:33">
       <c r="B67" s="22"/>
-      <c r="C67" s="144" t="s">
+      <c r="C67" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="D67" s="151"/>
-      <c r="E67" s="151"/>
-      <c r="F67" s="151"/>
-      <c r="G67" s="140"/>
-      <c r="H67" s="141" t="s">
+      <c r="D67" s="147"/>
+      <c r="E67" s="147"/>
+      <c r="F67" s="147"/>
+      <c r="G67" s="141"/>
+      <c r="H67" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I67" s="151"/>
-      <c r="J67" s="140"/>
+      <c r="I67" s="147"/>
+      <c r="J67" s="141"/>
       <c r="K67" s="19" t="s">
         <v>118</v>
       </c>
@@ -9684,18 +9690,18 @@
     </row>
     <row r="68" spans="2:33">
       <c r="B68" s="22"/>
-      <c r="C68" s="144" t="s">
+      <c r="C68" s="139" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="151"/>
-      <c r="E68" s="151"/>
-      <c r="F68" s="151"/>
-      <c r="G68" s="140"/>
-      <c r="H68" s="141" t="s">
+      <c r="D68" s="147"/>
+      <c r="E68" s="147"/>
+      <c r="F68" s="147"/>
+      <c r="G68" s="141"/>
+      <c r="H68" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I68" s="151"/>
-      <c r="J68" s="140"/>
+      <c r="I68" s="147"/>
+      <c r="J68" s="141"/>
       <c r="K68" s="19" t="s">
         <v>120</v>
       </c>
@@ -9715,18 +9721,18 @@
     </row>
     <row r="69" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B69" s="75"/>
-      <c r="C69" s="152" t="s">
+      <c r="C69" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="D69" s="149"/>
-      <c r="E69" s="149"/>
-      <c r="F69" s="149"/>
-      <c r="G69" s="150"/>
-      <c r="H69" s="148" t="s">
+      <c r="D69" s="137"/>
+      <c r="E69" s="137"/>
+      <c r="F69" s="137"/>
+      <c r="G69" s="138"/>
+      <c r="H69" s="136" t="s">
         <v>69</v>
       </c>
-      <c r="I69" s="149"/>
-      <c r="J69" s="150"/>
+      <c r="I69" s="137"/>
+      <c r="J69" s="138"/>
       <c r="K69" s="81" t="s">
         <v>122</v>
       </c>
@@ -9790,19 +9796,19 @@
       <c r="AG70" s="94"/>
     </row>
     <row r="71" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B71" s="145" t="s">
+      <c r="B71" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="146"/>
-      <c r="D71" s="146"/>
-      <c r="E71" s="146"/>
-      <c r="F71" s="146"/>
-      <c r="G71" s="147"/>
-      <c r="H71" s="145" t="s">
+      <c r="C71" s="144"/>
+      <c r="D71" s="144"/>
+      <c r="E71" s="144"/>
+      <c r="F71" s="144"/>
+      <c r="G71" s="149"/>
+      <c r="H71" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I71" s="146"/>
-      <c r="J71" s="147"/>
+      <c r="I71" s="144"/>
+      <c r="J71" s="149"/>
       <c r="K71" s="83" t="s">
         <v>68</v>
       </c>
@@ -9831,18 +9837,18 @@
     </row>
     <row r="72" spans="2:33">
       <c r="B72" s="21"/>
-      <c r="C72" s="144" t="s">
+      <c r="C72" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="151"/>
-      <c r="E72" s="151"/>
-      <c r="F72" s="151"/>
-      <c r="G72" s="140"/>
-      <c r="H72" s="142" t="s">
+      <c r="D72" s="147"/>
+      <c r="E72" s="147"/>
+      <c r="F72" s="147"/>
+      <c r="G72" s="141"/>
+      <c r="H72" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="I72" s="137"/>
-      <c r="J72" s="138"/>
+      <c r="I72" s="151"/>
+      <c r="J72" s="152"/>
       <c r="K72" s="19" t="s">
         <v>123</v>
       </c>
@@ -9862,18 +9868,18 @@
     </row>
     <row r="73" spans="2:33">
       <c r="B73" s="22"/>
-      <c r="C73" s="144" t="s">
+      <c r="C73" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="D73" s="151"/>
-      <c r="E73" s="151"/>
-      <c r="F73" s="151"/>
-      <c r="G73" s="140"/>
-      <c r="H73" s="141" t="s">
+      <c r="D73" s="147"/>
+      <c r="E73" s="147"/>
+      <c r="F73" s="147"/>
+      <c r="G73" s="141"/>
+      <c r="H73" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I73" s="151"/>
-      <c r="J73" s="140"/>
+      <c r="I73" s="147"/>
+      <c r="J73" s="141"/>
       <c r="K73" s="19" t="s">
         <v>124</v>
       </c>
@@ -9893,18 +9899,18 @@
     </row>
     <row r="74" spans="2:33">
       <c r="B74" s="22"/>
-      <c r="C74" s="144" t="s">
+      <c r="C74" s="139" t="s">
         <v>125</v>
       </c>
-      <c r="D74" s="151"/>
-      <c r="E74" s="151"/>
-      <c r="F74" s="151"/>
-      <c r="G74" s="140"/>
-      <c r="H74" s="141" t="s">
+      <c r="D74" s="147"/>
+      <c r="E74" s="147"/>
+      <c r="F74" s="147"/>
+      <c r="G74" s="141"/>
+      <c r="H74" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I74" s="151"/>
-      <c r="J74" s="140"/>
+      <c r="I74" s="147"/>
+      <c r="J74" s="141"/>
       <c r="K74" s="19" t="s">
         <v>126</v>
       </c>
@@ -9924,18 +9930,18 @@
     </row>
     <row r="75" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B75" s="75"/>
-      <c r="C75" s="152" t="s">
+      <c r="C75" s="142" t="s">
         <v>127</v>
       </c>
-      <c r="D75" s="149"/>
-      <c r="E75" s="149"/>
-      <c r="F75" s="149"/>
-      <c r="G75" s="150"/>
-      <c r="H75" s="148" t="s">
+      <c r="D75" s="137"/>
+      <c r="E75" s="137"/>
+      <c r="F75" s="137"/>
+      <c r="G75" s="138"/>
+      <c r="H75" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="I75" s="149"/>
-      <c r="J75" s="150"/>
+      <c r="I75" s="137"/>
+      <c r="J75" s="138"/>
       <c r="K75" s="81" t="s">
         <v>128</v>
       </c>
@@ -9999,19 +10005,19 @@
       <c r="AG76" s="94"/>
     </row>
     <row r="77" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B77" s="145" t="s">
+      <c r="B77" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C77" s="146"/>
-      <c r="D77" s="146"/>
-      <c r="E77" s="146"/>
-      <c r="F77" s="146"/>
-      <c r="G77" s="147"/>
-      <c r="H77" s="145" t="s">
+      <c r="C77" s="144"/>
+      <c r="D77" s="144"/>
+      <c r="E77" s="144"/>
+      <c r="F77" s="144"/>
+      <c r="G77" s="149"/>
+      <c r="H77" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I77" s="146"/>
-      <c r="J77" s="147"/>
+      <c r="I77" s="144"/>
+      <c r="J77" s="149"/>
       <c r="K77" s="83" t="s">
         <v>68</v>
       </c>
@@ -10040,18 +10046,18 @@
     </row>
     <row r="78" spans="2:33">
       <c r="B78" s="21"/>
-      <c r="C78" s="144" t="s">
+      <c r="C78" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="151"/>
-      <c r="E78" s="151"/>
-      <c r="F78" s="151"/>
-      <c r="G78" s="140"/>
-      <c r="H78" s="142" t="s">
+      <c r="D78" s="147"/>
+      <c r="E78" s="147"/>
+      <c r="F78" s="147"/>
+      <c r="G78" s="141"/>
+      <c r="H78" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="I78" s="137"/>
-      <c r="J78" s="138"/>
+      <c r="I78" s="151"/>
+      <c r="J78" s="152"/>
       <c r="K78" s="19" t="s">
         <v>129</v>
       </c>
@@ -10071,18 +10077,18 @@
     </row>
     <row r="79" spans="2:33">
       <c r="B79" s="22"/>
-      <c r="C79" s="144" t="s">
+      <c r="C79" s="139" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="151"/>
-      <c r="E79" s="151"/>
-      <c r="F79" s="151"/>
-      <c r="G79" s="140"/>
-      <c r="H79" s="141" t="s">
+      <c r="D79" s="147"/>
+      <c r="E79" s="147"/>
+      <c r="F79" s="147"/>
+      <c r="G79" s="141"/>
+      <c r="H79" s="146" t="s">
         <v>131</v>
       </c>
-      <c r="I79" s="151"/>
-      <c r="J79" s="140"/>
+      <c r="I79" s="147"/>
+      <c r="J79" s="141"/>
       <c r="K79" s="19" t="s">
         <v>132</v>
       </c>
@@ -10102,18 +10108,18 @@
     </row>
     <row r="80" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B80" s="75"/>
-      <c r="C80" s="152" t="s">
+      <c r="C80" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="D80" s="149"/>
-      <c r="E80" s="149"/>
-      <c r="F80" s="149"/>
-      <c r="G80" s="150"/>
-      <c r="H80" s="148" t="s">
+      <c r="D80" s="137"/>
+      <c r="E80" s="137"/>
+      <c r="F80" s="137"/>
+      <c r="G80" s="138"/>
+      <c r="H80" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="I80" s="149"/>
-      <c r="J80" s="150"/>
+      <c r="I80" s="137"/>
+      <c r="J80" s="138"/>
       <c r="K80" s="81" t="s">
         <v>134</v>
       </c>
@@ -10224,6 +10230,87 @@
     </row>
   </sheetData>
   <mergeCells count="97">
+    <mergeCell ref="C24:G25"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="H24:J25"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="H69:J69"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="H66:J66"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="H64:J64"/>
+    <mergeCell ref="H60:J60"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="B11:V11"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B5:V5"/>
+    <mergeCell ref="H47:J49"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C47:G49"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="H65:J65"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="H36:J36"/>
     <mergeCell ref="H80:J80"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="H62:J62"/>
@@ -10240,87 +10327,6 @@
     <mergeCell ref="H74:J74"/>
     <mergeCell ref="H56:J56"/>
     <mergeCell ref="H68:J68"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="H79:J79"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H78:J78"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="H65:J65"/>
-    <mergeCell ref="H71:J71"/>
-    <mergeCell ref="H75:J75"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C47:G49"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B2:V2"/>
-    <mergeCell ref="B11:V11"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B5:V5"/>
-    <mergeCell ref="H47:J49"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="H51:J51"/>
-    <mergeCell ref="H69:J69"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="H66:J66"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="H64:J64"/>
-    <mergeCell ref="H60:J60"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="C24:G25"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="H24:J25"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:J26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10329,7 +10335,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F1133"/>
+  <dimension ref="A1:F1135"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.75" style="2" bestFit="1" customWidth="1"/>
@@ -32995,6 +33001,46 @@
         <v>816</v>
       </c>
       <c r="F1133" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:6">
+      <c r="A1134">
+        <v>900907</v>
+      </c>
+      <c r="B1134" s="2">
+        <v>90907</v>
+      </c>
+      <c r="C1134" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1134" s="130" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E1134" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1134" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:6">
+      <c r="A1135">
+        <v>900908</v>
+      </c>
+      <c r="B1135" s="2">
+        <v>90908</v>
+      </c>
+      <c r="C1135" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1135" s="130" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E1135" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1135" s="130" t="s">
         <v>816</v>
       </c>
     </row>
@@ -34919,10 +34965,10 @@
       <c r="B2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
       <c r="G2" s="163"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -34932,10 +34978,10 @@
       <c r="M2" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="146"/>
-      <c r="O2" s="146"/>
-      <c r="P2" s="146"/>
-      <c r="Q2" s="147"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="144"/>
+      <c r="Q2" s="149"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
       <c r="T2" s="11"/>
@@ -34943,10 +34989,10 @@
       <c r="V2" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="W2" s="146"/>
-      <c r="X2" s="146"/>
-      <c r="Y2" s="146"/>
-      <c r="Z2" s="147"/>
+      <c r="W2" s="144"/>
+      <c r="X2" s="144"/>
+      <c r="Y2" s="144"/>
+      <c r="Z2" s="149"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
       <c r="AC2" s="10"/>
@@ -35065,10 +35111,10 @@
       <c r="V5" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="W5" s="146"/>
-      <c r="X5" s="146"/>
-      <c r="Y5" s="146"/>
-      <c r="Z5" s="147"/>
+      <c r="W5" s="144"/>
+      <c r="X5" s="144"/>
+      <c r="Y5" s="144"/>
+      <c r="Z5" s="149"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="10"/>
@@ -35114,10 +35160,10 @@
       <c r="B7" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="146"/>
-      <c r="D7" s="146"/>
-      <c r="E7" s="146"/>
-      <c r="F7" s="147"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="149"/>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -35126,10 +35172,10 @@
       <c r="L7" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="146"/>
-      <c r="N7" s="146"/>
-      <c r="O7" s="146"/>
-      <c r="P7" s="147"/>
+      <c r="M7" s="144"/>
+      <c r="N7" s="144"/>
+      <c r="O7" s="144"/>
+      <c r="P7" s="149"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
@@ -35338,10 +35384,10 @@
       <c r="AB14" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="AC14" s="146"/>
-      <c r="AD14" s="146"/>
-      <c r="AE14" s="146"/>
-      <c r="AF14" s="147"/>
+      <c r="AC14" s="144"/>
+      <c r="AD14" s="144"/>
+      <c r="AE14" s="144"/>
+      <c r="AF14" s="149"/>
       <c r="AG14" s="100"/>
       <c r="AH14" s="45"/>
       <c r="AI14" s="12"/>
@@ -35415,10 +35461,10 @@
       <c r="AB17" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="AC17" s="146"/>
-      <c r="AD17" s="146"/>
-      <c r="AE17" s="146"/>
-      <c r="AF17" s="147"/>
+      <c r="AC17" s="144"/>
+      <c r="AD17" s="144"/>
+      <c r="AE17" s="144"/>
+      <c r="AF17" s="149"/>
       <c r="AG17" s="102"/>
       <c r="AH17" s="38"/>
       <c r="AI17" s="10"/>
@@ -35536,10 +35582,10 @@
       <c r="AB21" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="AC21" s="146"/>
-      <c r="AD21" s="146"/>
-      <c r="AE21" s="146"/>
-      <c r="AF21" s="147"/>
+      <c r="AC21" s="144"/>
+      <c r="AD21" s="144"/>
+      <c r="AE21" s="144"/>
+      <c r="AF21" s="149"/>
       <c r="AG21" s="116"/>
       <c r="AH21" s="117"/>
     </row>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC51294A-7E86-4297-AA6B-E397659BA9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2B0286-FB77-4361-8633-03F8937EB5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5790" yWindow="1035" windowWidth="18660" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5902" uniqueCount="2030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5998" uniqueCount="2054">
   <si>
     <t>Upgrade_Table</t>
   </si>
@@ -5118,9 +5118,6 @@
     <t>버섯 빨리 자라게 하기</t>
   </si>
   <si>
-    <t>세계수 나무에서 자라고 있는 버섯이 모두 지금 다 자라요. &lt;color=#8a6a4a&gt;(남은 시간 합 {0}분마다 균사석 1개)&lt;/color&gt;</t>
-  </si>
-  <si>
     <t>{0} 남은 시간 {1}</t>
   </si>
   <si>
@@ -6211,6 +6208,82 @@
   </si>
   <si>
     <t>수확이 도중에 중단되어 스테이지가 완료되지 않습니다.</t>
+  </si>
+  <si>
+    <t>장착 칸이 다 찼어요 ({0}/{1}). 다른 수확기를 먼저 꺼 주세요</t>
+  </si>
+  <si>
+    <t>칸 없음</t>
+  </si>
+  <si>
+    <t>장착 {0}</t>
+  </si>
+  <si>
+    <t>엔딩</t>
+  </si>
+  <si>
+    <t>버섯 도감 {0}종 완성!</t>
+  </si>
+  <si>
+    <t>화면을 누르면 계속해요</t>
+  </si>
+  <si>
+    <t>세계수 나무에서 자라고 있는 버섯이 모두 지금 다 자라요. &lt;color=#8a6a4a&gt;(남은 시간 합 {0}분마다 한 판 수입만큼 골드)&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>직접 타격</t>
+  </si>
+  <si>
+    <t>{0} 칼날</t>
+  </si>
+  <si>
+    <t>젤리 버섯 안</t>
+  </si>
+  <si>
+    <t>{0} 베기</t>
+  </si>
+  <si>
+    <t>{0} 울림</t>
+  </si>
+  <si>
+    <t>불꽃</t>
+  </si>
+  <si>
+    <t>분열로 생긴 소형 수확기</t>
+  </si>
+  <si>
+    <t>분신 수확기 (스킬)</t>
+  </si>
+  <si>
+    <t>기타</t>
+  </si>
+  <si>
+    <t>데미지 통계</t>
+  </si>
+  <si>
+    <t>총 피해 {0}</t>
+  </si>
+  <si>
+    <t>피해 비율</t>
+  </si>
+  <si>
+    <t>피해</t>
+  </si>
+  <si>
+    <t>타격</t>
+  </si>
+  <si>
+    <t>처치</t>
+  </si>
+  <si>
+    <t>스킬·능력별</t>
+  </si>
+  <si>
+    <t>수확기별</t>
+  </si>
+  <si>
+    <t>화면을 누르면 닫혀요</t>
   </si>
 </sst>
 </file>
@@ -7095,46 +7168,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -7143,12 +7216,12 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7616,29 +7689,29 @@
   <sheetData>
     <row r="1" spans="2:44" ht="12" customHeight="1"/>
     <row r="2" spans="2:44">
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="155"/>
-      <c r="Q2" s="155"/>
-      <c r="R2" s="155"/>
-      <c r="S2" s="155"/>
-      <c r="T2" s="155"/>
-      <c r="U2" s="155"/>
-      <c r="V2" s="156"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="157"/>
+      <c r="U2" s="157"/>
+      <c r="V2" s="158"/>
     </row>
     <row r="3" spans="2:44">
       <c r="B3" s="17"/>
@@ -7695,29 +7768,29 @@
       <c r="V4" s="14"/>
     </row>
     <row r="5" spans="2:44">
-      <c r="B5" s="154" t="s">
+      <c r="B5" s="156" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="155"/>
-      <c r="K5" s="155"/>
-      <c r="L5" s="155"/>
-      <c r="M5" s="155"/>
-      <c r="N5" s="155"/>
-      <c r="O5" s="155"/>
-      <c r="P5" s="155"/>
-      <c r="Q5" s="155"/>
-      <c r="R5" s="155"/>
-      <c r="S5" s="155"/>
-      <c r="T5" s="155"/>
-      <c r="U5" s="155"/>
-      <c r="V5" s="156"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="157"/>
+      <c r="G5" s="157"/>
+      <c r="H5" s="157"/>
+      <c r="I5" s="157"/>
+      <c r="J5" s="157"/>
+      <c r="K5" s="157"/>
+      <c r="L5" s="157"/>
+      <c r="M5" s="157"/>
+      <c r="N5" s="157"/>
+      <c r="O5" s="157"/>
+      <c r="P5" s="157"/>
+      <c r="Q5" s="157"/>
+      <c r="R5" s="157"/>
+      <c r="S5" s="157"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="157"/>
+      <c r="V5" s="158"/>
     </row>
     <row r="6" spans="2:44">
       <c r="B6" s="6"/>
@@ -7847,29 +7920,29 @@
     </row>
     <row r="10" spans="2:44" ht="8.1" customHeight="1"/>
     <row r="11" spans="2:44">
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="156" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155"/>
-      <c r="E11" s="155"/>
-      <c r="F11" s="155"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="155"/>
-      <c r="I11" s="155"/>
-      <c r="J11" s="155"/>
-      <c r="K11" s="155"/>
-      <c r="L11" s="155"/>
-      <c r="M11" s="155"/>
-      <c r="N11" s="155"/>
-      <c r="O11" s="155"/>
-      <c r="P11" s="155"/>
-      <c r="Q11" s="155"/>
-      <c r="R11" s="155"/>
-      <c r="S11" s="155"/>
-      <c r="T11" s="155"/>
-      <c r="U11" s="155"/>
-      <c r="V11" s="156"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="157"/>
+      <c r="F11" s="157"/>
+      <c r="G11" s="157"/>
+      <c r="H11" s="157"/>
+      <c r="I11" s="157"/>
+      <c r="J11" s="157"/>
+      <c r="K11" s="157"/>
+      <c r="L11" s="157"/>
+      <c r="M11" s="157"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="157"/>
+      <c r="Q11" s="157"/>
+      <c r="R11" s="157"/>
+      <c r="S11" s="157"/>
+      <c r="T11" s="157"/>
+      <c r="U11" s="157"/>
+      <c r="V11" s="158"/>
     </row>
     <row r="12" spans="2:44">
       <c r="B12" s="6"/>
@@ -8156,19 +8229,19 @@
       <c r="AF22" s="27"/>
     </row>
     <row r="23" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B23" s="157" t="s">
+      <c r="B23" s="159" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="144"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="143" t="s">
+      <c r="C23" s="146"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="146"/>
+      <c r="H23" s="161" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="144"/>
-      <c r="J23" s="144"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="146"/>
       <c r="K23" s="28" t="s">
         <v>68</v>
       </c>
@@ -8196,18 +8269,18 @@
     </row>
     <row r="24" spans="2:32" s="10" customFormat="1">
       <c r="B24" s="86"/>
-      <c r="C24" s="153" t="s">
+      <c r="C24" s="136" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="151"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
-      <c r="H24" s="150" t="s">
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="137"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="151"/>
-      <c r="J24" s="152"/>
+      <c r="I24" s="137"/>
+      <c r="J24" s="138"/>
       <c r="K24" s="34" t="s">
         <v>70</v>
       </c>
@@ -8235,14 +8308,14 @@
     </row>
     <row r="25" spans="2:32" s="10" customFormat="1">
       <c r="B25" s="22"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="140"/>
-      <c r="G25" s="141"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="140"/>
-      <c r="J25" s="141"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="139"/>
+      <c r="J25" s="140"/>
       <c r="K25" s="19" t="s">
         <v>49</v>
       </c>
@@ -8264,18 +8337,18 @@
     </row>
     <row r="26" spans="2:32" s="10" customFormat="1">
       <c r="B26" s="22"/>
-      <c r="C26" s="139" t="s">
+      <c r="C26" s="144" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="141"/>
-      <c r="H26" s="146" t="s">
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="140"/>
-      <c r="J26" s="141"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="140"/>
       <c r="K26" s="19" t="s">
         <v>74</v>
       </c>
@@ -8295,18 +8368,18 @@
     </row>
     <row r="27" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B27" s="22"/>
-      <c r="C27" s="139" t="s">
+      <c r="C27" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="140"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
-      <c r="G27" s="141"/>
-      <c r="H27" s="146" t="s">
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I27" s="140"/>
-      <c r="J27" s="141"/>
+      <c r="I27" s="139"/>
+      <c r="J27" s="140"/>
       <c r="K27" s="19" t="s">
         <v>75</v>
       </c>
@@ -8326,18 +8399,18 @@
     </row>
     <row r="28" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B28" s="22"/>
-      <c r="C28" s="139" t="s">
+      <c r="C28" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="140"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="141"/>
-      <c r="H28" s="146" t="s">
+      <c r="D28" s="139"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="139"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I28" s="140"/>
-      <c r="J28" s="141"/>
+      <c r="I28" s="139"/>
+      <c r="J28" s="140"/>
       <c r="K28" s="19" t="s">
         <v>77</v>
       </c>
@@ -8357,18 +8430,18 @@
     </row>
     <row r="29" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B29" s="22"/>
-      <c r="C29" s="139" t="s">
+      <c r="C29" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="140"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="140"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="146" t="s">
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I29" s="140"/>
-      <c r="J29" s="141"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="140"/>
       <c r="K29" s="19" t="s">
         <v>78</v>
       </c>
@@ -8388,18 +8461,18 @@
     </row>
     <row r="30" spans="2:32" s="10" customFormat="1">
       <c r="B30" s="22"/>
-      <c r="C30" s="139" t="s">
+      <c r="C30" s="144" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="140"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="140"/>
-      <c r="G30" s="141"/>
-      <c r="H30" s="146" t="s">
+      <c r="D30" s="139"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I30" s="140"/>
-      <c r="J30" s="141"/>
+      <c r="I30" s="139"/>
+      <c r="J30" s="140"/>
       <c r="K30" s="120" t="s">
         <v>421</v>
       </c>
@@ -8419,18 +8492,18 @@
     </row>
     <row r="31" spans="2:32" s="10" customFormat="1">
       <c r="B31" s="22"/>
-      <c r="C31" s="139" t="s">
+      <c r="C31" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="140"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="141"/>
-      <c r="H31" s="146" t="s">
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I31" s="140"/>
-      <c r="J31" s="141"/>
+      <c r="I31" s="139"/>
+      <c r="J31" s="140"/>
       <c r="K31" s="19" t="s">
         <v>80</v>
       </c>
@@ -8450,18 +8523,18 @@
     </row>
     <row r="32" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B32" s="75"/>
-      <c r="C32" s="145" t="s">
+      <c r="C32" s="160" t="s">
         <v>422</v>
       </c>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="138"/>
-      <c r="H32" s="136" t="s">
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
+      <c r="F32" s="149"/>
+      <c r="G32" s="150"/>
+      <c r="H32" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="137"/>
-      <c r="J32" s="138"/>
+      <c r="I32" s="149"/>
+      <c r="J32" s="150"/>
       <c r="K32" s="81" t="s">
         <v>82</v>
       </c>
@@ -8523,19 +8596,19 @@
       <c r="AF33" s="27"/>
     </row>
     <row r="34" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B34" s="148" t="s">
+      <c r="B34" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="144"/>
-      <c r="D34" s="144"/>
-      <c r="E34" s="144"/>
-      <c r="F34" s="144"/>
-      <c r="G34" s="149"/>
-      <c r="H34" s="148" t="s">
+      <c r="C34" s="146"/>
+      <c r="D34" s="146"/>
+      <c r="E34" s="146"/>
+      <c r="F34" s="146"/>
+      <c r="G34" s="147"/>
+      <c r="H34" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I34" s="144"/>
-      <c r="J34" s="149"/>
+      <c r="I34" s="146"/>
+      <c r="J34" s="147"/>
       <c r="K34" s="28" t="s">
         <v>68</v>
       </c>
@@ -8563,18 +8636,18 @@
     </row>
     <row r="35" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B35" s="86"/>
-      <c r="C35" s="153" t="s">
+      <c r="C35" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
-      <c r="G35" s="152"/>
-      <c r="H35" s="150" t="s">
+      <c r="D35" s="137"/>
+      <c r="E35" s="137"/>
+      <c r="F35" s="137"/>
+      <c r="G35" s="138"/>
+      <c r="H35" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I35" s="151"/>
-      <c r="J35" s="152"/>
+      <c r="I35" s="137"/>
+      <c r="J35" s="138"/>
       <c r="K35" s="34" t="s">
         <v>84</v>
       </c>
@@ -8602,18 +8675,18 @@
     </row>
     <row r="36" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B36" s="75"/>
-      <c r="C36" s="145" t="s">
+      <c r="C36" s="160" t="s">
         <v>423</v>
       </c>
-      <c r="D36" s="137"/>
-      <c r="E36" s="137"/>
-      <c r="F36" s="137"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="136" t="s">
+      <c r="D36" s="149"/>
+      <c r="E36" s="149"/>
+      <c r="F36" s="149"/>
+      <c r="G36" s="150"/>
+      <c r="H36" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="I36" s="137"/>
-      <c r="J36" s="138"/>
+      <c r="I36" s="149"/>
+      <c r="J36" s="150"/>
       <c r="K36" s="81" t="s">
         <v>85</v>
       </c>
@@ -8675,19 +8748,19 @@
       <c r="AF37" s="92"/>
     </row>
     <row r="38" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B38" s="148" t="s">
+      <c r="B38" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="144"/>
-      <c r="D38" s="144"/>
-      <c r="E38" s="144"/>
-      <c r="F38" s="144"/>
-      <c r="G38" s="149"/>
-      <c r="H38" s="148" t="s">
+      <c r="C38" s="146"/>
+      <c r="D38" s="146"/>
+      <c r="E38" s="146"/>
+      <c r="F38" s="146"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="144"/>
-      <c r="J38" s="149"/>
+      <c r="I38" s="146"/>
+      <c r="J38" s="147"/>
       <c r="K38" s="28" t="s">
         <v>68</v>
       </c>
@@ -8715,18 +8788,18 @@
     </row>
     <row r="39" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B39" s="21"/>
-      <c r="C39" s="139" t="s">
+      <c r="C39" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="140"/>
-      <c r="E39" s="140"/>
-      <c r="F39" s="140"/>
-      <c r="G39" s="141"/>
-      <c r="H39" s="146" t="s">
+      <c r="D39" s="139"/>
+      <c r="E39" s="139"/>
+      <c r="F39" s="139"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I39" s="140"/>
-      <c r="J39" s="141"/>
+      <c r="I39" s="139"/>
+      <c r="J39" s="140"/>
       <c r="K39" s="19" t="s">
         <v>86</v>
       </c>
@@ -8746,18 +8819,18 @@
     </row>
     <row r="40" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B40" s="22"/>
-      <c r="C40" s="139" t="s">
+      <c r="C40" s="144" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="140"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="140"/>
-      <c r="G40" s="141"/>
-      <c r="H40" s="146" t="s">
+      <c r="D40" s="139"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="139"/>
+      <c r="G40" s="140"/>
+      <c r="H40" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I40" s="140"/>
-      <c r="J40" s="141"/>
+      <c r="I40" s="139"/>
+      <c r="J40" s="140"/>
       <c r="K40" s="19" t="s">
         <v>88</v>
       </c>
@@ -8777,18 +8850,18 @@
     </row>
     <row r="41" spans="2:32" s="10" customFormat="1">
       <c r="B41" s="22"/>
-      <c r="C41" s="139" t="s">
+      <c r="C41" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="140"/>
-      <c r="E41" s="140"/>
-      <c r="F41" s="140"/>
-      <c r="G41" s="141"/>
-      <c r="H41" s="146" t="s">
+      <c r="D41" s="139"/>
+      <c r="E41" s="139"/>
+      <c r="F41" s="139"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="140"/>
-      <c r="J41" s="141"/>
+      <c r="I41" s="139"/>
+      <c r="J41" s="140"/>
       <c r="K41" s="19" t="s">
         <v>89</v>
       </c>
@@ -8808,18 +8881,18 @@
     </row>
     <row r="42" spans="2:32" s="10" customFormat="1">
       <c r="B42" s="22"/>
-      <c r="C42" s="139" t="s">
+      <c r="C42" s="144" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="140"/>
-      <c r="E42" s="140"/>
-      <c r="F42" s="140"/>
-      <c r="G42" s="141"/>
-      <c r="H42" s="146" t="s">
+      <c r="D42" s="139"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I42" s="140"/>
-      <c r="J42" s="141"/>
+      <c r="I42" s="139"/>
+      <c r="J42" s="140"/>
       <c r="K42" s="19" t="s">
         <v>91</v>
       </c>
@@ -8839,18 +8912,18 @@
     </row>
     <row r="43" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B43" s="75"/>
-      <c r="C43" s="142" t="s">
+      <c r="C43" s="152" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="137"/>
-      <c r="E43" s="137"/>
-      <c r="F43" s="137"/>
-      <c r="G43" s="138"/>
-      <c r="H43" s="136" t="s">
+      <c r="D43" s="149"/>
+      <c r="E43" s="149"/>
+      <c r="F43" s="149"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="137"/>
-      <c r="J43" s="138"/>
+      <c r="I43" s="149"/>
+      <c r="J43" s="150"/>
       <c r="K43" s="81" t="s">
         <v>92</v>
       </c>
@@ -8912,19 +8985,19 @@
       <c r="AF44" s="27"/>
     </row>
     <row r="45" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B45" s="148" t="s">
+      <c r="B45" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="144"/>
-      <c r="D45" s="144"/>
-      <c r="E45" s="144"/>
-      <c r="F45" s="144"/>
-      <c r="G45" s="149"/>
-      <c r="H45" s="159" t="s">
+      <c r="C45" s="146"/>
+      <c r="D45" s="146"/>
+      <c r="E45" s="146"/>
+      <c r="F45" s="146"/>
+      <c r="G45" s="147"/>
+      <c r="H45" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="I45" s="160"/>
-      <c r="J45" s="161"/>
+      <c r="I45" s="154"/>
+      <c r="J45" s="155"/>
       <c r="K45" s="83" t="s">
         <v>68</v>
       </c>
@@ -8952,18 +9025,18 @@
     </row>
     <row r="46" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B46" s="21"/>
-      <c r="C46" s="139" t="s">
+      <c r="C46" s="144" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="140"/>
-      <c r="E46" s="140"/>
-      <c r="F46" s="140"/>
-      <c r="G46" s="141"/>
-      <c r="H46" s="150" t="s">
+      <c r="D46" s="139"/>
+      <c r="E46" s="139"/>
+      <c r="F46" s="139"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="I46" s="151"/>
-      <c r="J46" s="152"/>
+      <c r="I46" s="137"/>
+      <c r="J46" s="138"/>
       <c r="K46" s="19" t="s">
         <v>93</v>
       </c>
@@ -8983,18 +9056,18 @@
     </row>
     <row r="47" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B47" s="22"/>
-      <c r="C47" s="139" t="s">
+      <c r="C47" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="140"/>
-      <c r="E47" s="140"/>
-      <c r="F47" s="140"/>
-      <c r="G47" s="141"/>
-      <c r="H47" s="146" t="s">
+      <c r="D47" s="139"/>
+      <c r="E47" s="139"/>
+      <c r="F47" s="139"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="141" t="s">
         <v>81</v>
       </c>
-      <c r="I47" s="140"/>
-      <c r="J47" s="141"/>
+      <c r="I47" s="139"/>
+      <c r="J47" s="140"/>
       <c r="K47" s="19" t="s">
         <v>95</v>
       </c>
@@ -9014,14 +9087,14 @@
     </row>
     <row r="48" spans="2:32" s="10" customFormat="1">
       <c r="B48" s="22"/>
-      <c r="C48" s="140"/>
-      <c r="D48" s="140"/>
-      <c r="E48" s="140"/>
-      <c r="F48" s="140"/>
-      <c r="G48" s="141"/>
-      <c r="H48" s="158"/>
-      <c r="I48" s="140"/>
-      <c r="J48" s="141"/>
+      <c r="C48" s="139"/>
+      <c r="D48" s="139"/>
+      <c r="E48" s="139"/>
+      <c r="F48" s="139"/>
+      <c r="G48" s="140"/>
+      <c r="H48" s="143"/>
+      <c r="I48" s="139"/>
+      <c r="J48" s="140"/>
       <c r="K48" s="19" t="s">
         <v>49</v>
       </c>
@@ -9043,14 +9116,14 @@
     </row>
     <row r="49" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B49" s="22"/>
-      <c r="C49" s="140"/>
-      <c r="D49" s="140"/>
-      <c r="E49" s="140"/>
-      <c r="F49" s="140"/>
-      <c r="G49" s="141"/>
-      <c r="H49" s="158"/>
-      <c r="I49" s="140"/>
-      <c r="J49" s="141"/>
+      <c r="C49" s="139"/>
+      <c r="D49" s="139"/>
+      <c r="E49" s="139"/>
+      <c r="F49" s="139"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="143"/>
+      <c r="I49" s="139"/>
+      <c r="J49" s="140"/>
       <c r="K49" s="19" t="s">
         <v>49</v>
       </c>
@@ -9107,19 +9180,19 @@
       <c r="AG50" s="92"/>
     </row>
     <row r="51" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B51" s="148" t="s">
+      <c r="B51" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="144"/>
-      <c r="D51" s="144"/>
-      <c r="E51" s="144"/>
-      <c r="F51" s="144"/>
-      <c r="G51" s="149"/>
-      <c r="H51" s="148" t="s">
+      <c r="C51" s="146"/>
+      <c r="D51" s="146"/>
+      <c r="E51" s="146"/>
+      <c r="F51" s="146"/>
+      <c r="G51" s="147"/>
+      <c r="H51" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I51" s="144"/>
-      <c r="J51" s="149"/>
+      <c r="I51" s="146"/>
+      <c r="J51" s="147"/>
       <c r="K51" s="28" t="s">
         <v>68</v>
       </c>
@@ -9148,18 +9221,18 @@
     </row>
     <row r="52" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B52" s="21"/>
-      <c r="C52" s="139" t="s">
+      <c r="C52" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="140"/>
-      <c r="E52" s="140"/>
-      <c r="F52" s="140"/>
-      <c r="G52" s="141"/>
-      <c r="H52" s="146" t="s">
+      <c r="D52" s="139"/>
+      <c r="E52" s="139"/>
+      <c r="F52" s="139"/>
+      <c r="G52" s="140"/>
+      <c r="H52" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I52" s="140"/>
-      <c r="J52" s="141"/>
+      <c r="I52" s="139"/>
+      <c r="J52" s="140"/>
       <c r="K52" s="19" t="s">
         <v>99</v>
       </c>
@@ -9179,18 +9252,18 @@
     </row>
     <row r="53" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B53" s="22"/>
-      <c r="C53" s="139" t="s">
+      <c r="C53" s="144" t="s">
         <v>100</v>
       </c>
-      <c r="D53" s="140"/>
-      <c r="E53" s="140"/>
-      <c r="F53" s="140"/>
-      <c r="G53" s="141"/>
-      <c r="H53" s="146" t="s">
+      <c r="D53" s="139"/>
+      <c r="E53" s="139"/>
+      <c r="F53" s="139"/>
+      <c r="G53" s="140"/>
+      <c r="H53" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I53" s="140"/>
-      <c r="J53" s="141"/>
+      <c r="I53" s="139"/>
+      <c r="J53" s="140"/>
       <c r="K53" s="19" t="s">
         <v>101</v>
       </c>
@@ -9210,18 +9283,18 @@
     </row>
     <row r="54" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B54" s="75"/>
-      <c r="C54" s="142" t="s">
+      <c r="C54" s="152" t="s">
         <v>102</v>
       </c>
-      <c r="D54" s="137"/>
-      <c r="E54" s="137"/>
-      <c r="F54" s="137"/>
-      <c r="G54" s="138"/>
-      <c r="H54" s="136" t="s">
+      <c r="D54" s="149"/>
+      <c r="E54" s="149"/>
+      <c r="F54" s="149"/>
+      <c r="G54" s="150"/>
+      <c r="H54" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I54" s="137"/>
-      <c r="J54" s="138"/>
+      <c r="I54" s="149"/>
+      <c r="J54" s="150"/>
       <c r="K54" s="81" t="s">
         <v>103</v>
       </c>
@@ -9285,19 +9358,19 @@
       <c r="AG55" s="92"/>
     </row>
     <row r="56" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B56" s="148" t="s">
+      <c r="B56" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="144"/>
-      <c r="D56" s="144"/>
-      <c r="E56" s="144"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="149"/>
-      <c r="H56" s="148" t="s">
+      <c r="C56" s="146"/>
+      <c r="D56" s="146"/>
+      <c r="E56" s="146"/>
+      <c r="F56" s="146"/>
+      <c r="G56" s="147"/>
+      <c r="H56" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I56" s="144"/>
-      <c r="J56" s="149"/>
+      <c r="I56" s="146"/>
+      <c r="J56" s="147"/>
       <c r="K56" s="28" t="s">
         <v>68</v>
       </c>
@@ -9326,18 +9399,18 @@
     </row>
     <row r="57" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B57" s="21"/>
-      <c r="C57" s="139" t="s">
+      <c r="C57" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="140"/>
-      <c r="E57" s="140"/>
-      <c r="F57" s="140"/>
-      <c r="G57" s="141"/>
-      <c r="H57" s="146" t="s">
+      <c r="D57" s="139"/>
+      <c r="E57" s="139"/>
+      <c r="F57" s="139"/>
+      <c r="G57" s="140"/>
+      <c r="H57" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I57" s="140"/>
-      <c r="J57" s="141"/>
+      <c r="I57" s="139"/>
+      <c r="J57" s="140"/>
       <c r="K57" s="19" t="s">
         <v>104</v>
       </c>
@@ -9357,18 +9430,18 @@
     </row>
     <row r="58" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B58" s="22"/>
-      <c r="C58" s="139" t="s">
+      <c r="C58" s="144" t="s">
         <v>105</v>
       </c>
-      <c r="D58" s="140"/>
-      <c r="E58" s="140"/>
-      <c r="F58" s="140"/>
-      <c r="G58" s="141"/>
-      <c r="H58" s="146" t="s">
+      <c r="D58" s="139"/>
+      <c r="E58" s="139"/>
+      <c r="F58" s="139"/>
+      <c r="G58" s="140"/>
+      <c r="H58" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I58" s="140"/>
-      <c r="J58" s="141"/>
+      <c r="I58" s="139"/>
+      <c r="J58" s="140"/>
       <c r="K58" s="19" t="s">
         <v>106</v>
       </c>
@@ -9388,18 +9461,18 @@
     </row>
     <row r="59" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B59" s="22"/>
-      <c r="C59" s="139" t="s">
+      <c r="C59" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="140"/>
-      <c r="E59" s="140"/>
-      <c r="F59" s="140"/>
-      <c r="G59" s="141"/>
-      <c r="H59" s="146" t="s">
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="140"/>
+      <c r="H59" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I59" s="140"/>
-      <c r="J59" s="141"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="140"/>
       <c r="K59" s="19" t="s">
         <v>107</v>
       </c>
@@ -9419,18 +9492,18 @@
     </row>
     <row r="60" spans="2:33" s="10" customFormat="1">
       <c r="B60" s="22"/>
-      <c r="C60" s="139" t="s">
+      <c r="C60" s="144" t="s">
         <v>108</v>
       </c>
-      <c r="D60" s="140"/>
-      <c r="E60" s="140"/>
-      <c r="F60" s="140"/>
-      <c r="G60" s="141"/>
-      <c r="H60" s="146" t="s">
+      <c r="D60" s="139"/>
+      <c r="E60" s="139"/>
+      <c r="F60" s="139"/>
+      <c r="G60" s="140"/>
+      <c r="H60" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I60" s="140"/>
-      <c r="J60" s="141"/>
+      <c r="I60" s="139"/>
+      <c r="J60" s="140"/>
       <c r="K60" s="19" t="s">
         <v>109</v>
       </c>
@@ -9450,18 +9523,18 @@
     </row>
     <row r="61" spans="2:33" s="10" customFormat="1">
       <c r="B61" s="22"/>
-      <c r="C61" s="139" t="s">
+      <c r="C61" s="144" t="s">
         <v>110</v>
       </c>
-      <c r="D61" s="140"/>
-      <c r="E61" s="140"/>
-      <c r="F61" s="140"/>
-      <c r="G61" s="141"/>
-      <c r="H61" s="146" t="s">
+      <c r="D61" s="139"/>
+      <c r="E61" s="139"/>
+      <c r="F61" s="139"/>
+      <c r="G61" s="140"/>
+      <c r="H61" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I61" s="140"/>
-      <c r="J61" s="141"/>
+      <c r="I61" s="139"/>
+      <c r="J61" s="140"/>
       <c r="K61" s="19" t="s">
         <v>111</v>
       </c>
@@ -9481,18 +9554,18 @@
     </row>
     <row r="62" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B62" s="75"/>
-      <c r="C62" s="142" t="s">
+      <c r="C62" s="152" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="137"/>
-      <c r="E62" s="137"/>
-      <c r="F62" s="137"/>
-      <c r="G62" s="138"/>
-      <c r="H62" s="136" t="s">
+      <c r="D62" s="149"/>
+      <c r="E62" s="149"/>
+      <c r="F62" s="149"/>
+      <c r="G62" s="150"/>
+      <c r="H62" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I62" s="137"/>
-      <c r="J62" s="138"/>
+      <c r="I62" s="149"/>
+      <c r="J62" s="150"/>
       <c r="K62" s="81" t="s">
         <v>113</v>
       </c>
@@ -9556,19 +9629,19 @@
       <c r="AG63" s="92"/>
     </row>
     <row r="64" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B64" s="148" t="s">
+      <c r="B64" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="144"/>
-      <c r="D64" s="144"/>
-      <c r="E64" s="144"/>
-      <c r="F64" s="144"/>
-      <c r="G64" s="149"/>
-      <c r="H64" s="148" t="s">
+      <c r="C64" s="146"/>
+      <c r="D64" s="146"/>
+      <c r="E64" s="146"/>
+      <c r="F64" s="146"/>
+      <c r="G64" s="147"/>
+      <c r="H64" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I64" s="144"/>
-      <c r="J64" s="149"/>
+      <c r="I64" s="146"/>
+      <c r="J64" s="147"/>
       <c r="K64" s="83" t="s">
         <v>68</v>
       </c>
@@ -9597,18 +9670,18 @@
     </row>
     <row r="65" spans="2:33">
       <c r="B65" s="21"/>
-      <c r="C65" s="139" t="s">
+      <c r="C65" s="144" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="147"/>
-      <c r="E65" s="147"/>
-      <c r="F65" s="147"/>
-      <c r="G65" s="141"/>
-      <c r="H65" s="150" t="s">
+      <c r="D65" s="151"/>
+      <c r="E65" s="151"/>
+      <c r="F65" s="151"/>
+      <c r="G65" s="140"/>
+      <c r="H65" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I65" s="151"/>
-      <c r="J65" s="152"/>
+      <c r="I65" s="137"/>
+      <c r="J65" s="138"/>
       <c r="K65" s="19" t="s">
         <v>115</v>
       </c>
@@ -9628,18 +9701,18 @@
     </row>
     <row r="66" spans="2:33">
       <c r="B66" s="22"/>
-      <c r="C66" s="139" t="s">
+      <c r="C66" s="144" t="s">
         <v>116</v>
       </c>
-      <c r="D66" s="147"/>
-      <c r="E66" s="147"/>
-      <c r="F66" s="147"/>
-      <c r="G66" s="141"/>
-      <c r="H66" s="146" t="s">
+      <c r="D66" s="151"/>
+      <c r="E66" s="151"/>
+      <c r="F66" s="151"/>
+      <c r="G66" s="140"/>
+      <c r="H66" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I66" s="147"/>
-      <c r="J66" s="141"/>
+      <c r="I66" s="151"/>
+      <c r="J66" s="140"/>
       <c r="K66" s="19" t="s">
         <v>117</v>
       </c>
@@ -9659,18 +9732,18 @@
     </row>
     <row r="67" spans="2:33">
       <c r="B67" s="22"/>
-      <c r="C67" s="139" t="s">
+      <c r="C67" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D67" s="147"/>
-      <c r="E67" s="147"/>
-      <c r="F67" s="147"/>
-      <c r="G67" s="141"/>
-      <c r="H67" s="146" t="s">
+      <c r="D67" s="151"/>
+      <c r="E67" s="151"/>
+      <c r="F67" s="151"/>
+      <c r="G67" s="140"/>
+      <c r="H67" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I67" s="147"/>
-      <c r="J67" s="141"/>
+      <c r="I67" s="151"/>
+      <c r="J67" s="140"/>
       <c r="K67" s="19" t="s">
         <v>118</v>
       </c>
@@ -9690,18 +9763,18 @@
     </row>
     <row r="68" spans="2:33">
       <c r="B68" s="22"/>
-      <c r="C68" s="139" t="s">
+      <c r="C68" s="144" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="147"/>
-      <c r="E68" s="147"/>
-      <c r="F68" s="147"/>
-      <c r="G68" s="141"/>
-      <c r="H68" s="146" t="s">
+      <c r="D68" s="151"/>
+      <c r="E68" s="151"/>
+      <c r="F68" s="151"/>
+      <c r="G68" s="140"/>
+      <c r="H68" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I68" s="147"/>
-      <c r="J68" s="141"/>
+      <c r="I68" s="151"/>
+      <c r="J68" s="140"/>
       <c r="K68" s="19" t="s">
         <v>120</v>
       </c>
@@ -9721,18 +9794,18 @@
     </row>
     <row r="69" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B69" s="75"/>
-      <c r="C69" s="142" t="s">
+      <c r="C69" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="D69" s="137"/>
-      <c r="E69" s="137"/>
-      <c r="F69" s="137"/>
-      <c r="G69" s="138"/>
-      <c r="H69" s="136" t="s">
+      <c r="D69" s="149"/>
+      <c r="E69" s="149"/>
+      <c r="F69" s="149"/>
+      <c r="G69" s="150"/>
+      <c r="H69" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="I69" s="137"/>
-      <c r="J69" s="138"/>
+      <c r="I69" s="149"/>
+      <c r="J69" s="150"/>
       <c r="K69" s="81" t="s">
         <v>122</v>
       </c>
@@ -9796,19 +9869,19 @@
       <c r="AG70" s="94"/>
     </row>
     <row r="71" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B71" s="148" t="s">
+      <c r="B71" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="144"/>
-      <c r="D71" s="144"/>
-      <c r="E71" s="144"/>
-      <c r="F71" s="144"/>
-      <c r="G71" s="149"/>
-      <c r="H71" s="148" t="s">
+      <c r="C71" s="146"/>
+      <c r="D71" s="146"/>
+      <c r="E71" s="146"/>
+      <c r="F71" s="146"/>
+      <c r="G71" s="147"/>
+      <c r="H71" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I71" s="144"/>
-      <c r="J71" s="149"/>
+      <c r="I71" s="146"/>
+      <c r="J71" s="147"/>
       <c r="K71" s="83" t="s">
         <v>68</v>
       </c>
@@ -9837,18 +9910,18 @@
     </row>
     <row r="72" spans="2:33">
       <c r="B72" s="21"/>
-      <c r="C72" s="139" t="s">
+      <c r="C72" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="147"/>
-      <c r="E72" s="147"/>
-      <c r="F72" s="147"/>
-      <c r="G72" s="141"/>
-      <c r="H72" s="150" t="s">
+      <c r="D72" s="151"/>
+      <c r="E72" s="151"/>
+      <c r="F72" s="151"/>
+      <c r="G72" s="140"/>
+      <c r="H72" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I72" s="151"/>
-      <c r="J72" s="152"/>
+      <c r="I72" s="137"/>
+      <c r="J72" s="138"/>
       <c r="K72" s="19" t="s">
         <v>123</v>
       </c>
@@ -9868,18 +9941,18 @@
     </row>
     <row r="73" spans="2:33">
       <c r="B73" s="22"/>
-      <c r="C73" s="139" t="s">
+      <c r="C73" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D73" s="147"/>
-      <c r="E73" s="147"/>
-      <c r="F73" s="147"/>
-      <c r="G73" s="141"/>
-      <c r="H73" s="146" t="s">
+      <c r="D73" s="151"/>
+      <c r="E73" s="151"/>
+      <c r="F73" s="151"/>
+      <c r="G73" s="140"/>
+      <c r="H73" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I73" s="147"/>
-      <c r="J73" s="141"/>
+      <c r="I73" s="151"/>
+      <c r="J73" s="140"/>
       <c r="K73" s="19" t="s">
         <v>124</v>
       </c>
@@ -9899,18 +9972,18 @@
     </row>
     <row r="74" spans="2:33">
       <c r="B74" s="22"/>
-      <c r="C74" s="139" t="s">
+      <c r="C74" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="D74" s="147"/>
-      <c r="E74" s="147"/>
-      <c r="F74" s="147"/>
-      <c r="G74" s="141"/>
-      <c r="H74" s="146" t="s">
+      <c r="D74" s="151"/>
+      <c r="E74" s="151"/>
+      <c r="F74" s="151"/>
+      <c r="G74" s="140"/>
+      <c r="H74" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I74" s="147"/>
-      <c r="J74" s="141"/>
+      <c r="I74" s="151"/>
+      <c r="J74" s="140"/>
       <c r="K74" s="19" t="s">
         <v>126</v>
       </c>
@@ -9930,18 +10003,18 @@
     </row>
     <row r="75" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B75" s="75"/>
-      <c r="C75" s="142" t="s">
+      <c r="C75" s="152" t="s">
         <v>127</v>
       </c>
-      <c r="D75" s="137"/>
-      <c r="E75" s="137"/>
-      <c r="F75" s="137"/>
-      <c r="G75" s="138"/>
-      <c r="H75" s="136" t="s">
+      <c r="D75" s="149"/>
+      <c r="E75" s="149"/>
+      <c r="F75" s="149"/>
+      <c r="G75" s="150"/>
+      <c r="H75" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I75" s="137"/>
-      <c r="J75" s="138"/>
+      <c r="I75" s="149"/>
+      <c r="J75" s="150"/>
       <c r="K75" s="81" t="s">
         <v>128</v>
       </c>
@@ -10005,19 +10078,19 @@
       <c r="AG76" s="94"/>
     </row>
     <row r="77" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B77" s="148" t="s">
+      <c r="B77" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C77" s="144"/>
-      <c r="D77" s="144"/>
-      <c r="E77" s="144"/>
-      <c r="F77" s="144"/>
-      <c r="G77" s="149"/>
-      <c r="H77" s="148" t="s">
+      <c r="C77" s="146"/>
+      <c r="D77" s="146"/>
+      <c r="E77" s="146"/>
+      <c r="F77" s="146"/>
+      <c r="G77" s="147"/>
+      <c r="H77" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I77" s="144"/>
-      <c r="J77" s="149"/>
+      <c r="I77" s="146"/>
+      <c r="J77" s="147"/>
       <c r="K77" s="83" t="s">
         <v>68</v>
       </c>
@@ -10046,18 +10119,18 @@
     </row>
     <row r="78" spans="2:33">
       <c r="B78" s="21"/>
-      <c r="C78" s="139" t="s">
+      <c r="C78" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="147"/>
-      <c r="E78" s="147"/>
-      <c r="F78" s="147"/>
-      <c r="G78" s="141"/>
-      <c r="H78" s="150" t="s">
+      <c r="D78" s="151"/>
+      <c r="E78" s="151"/>
+      <c r="F78" s="151"/>
+      <c r="G78" s="140"/>
+      <c r="H78" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="I78" s="151"/>
-      <c r="J78" s="152"/>
+      <c r="I78" s="137"/>
+      <c r="J78" s="138"/>
       <c r="K78" s="19" t="s">
         <v>129</v>
       </c>
@@ -10077,18 +10150,18 @@
     </row>
     <row r="79" spans="2:33">
       <c r="B79" s="22"/>
-      <c r="C79" s="139" t="s">
+      <c r="C79" s="144" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="147"/>
-      <c r="E79" s="147"/>
-      <c r="F79" s="147"/>
-      <c r="G79" s="141"/>
-      <c r="H79" s="146" t="s">
+      <c r="D79" s="151"/>
+      <c r="E79" s="151"/>
+      <c r="F79" s="151"/>
+      <c r="G79" s="140"/>
+      <c r="H79" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="I79" s="147"/>
-      <c r="J79" s="141"/>
+      <c r="I79" s="151"/>
+      <c r="J79" s="140"/>
       <c r="K79" s="19" t="s">
         <v>132</v>
       </c>
@@ -10108,18 +10181,18 @@
     </row>
     <row r="80" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B80" s="75"/>
-      <c r="C80" s="142" t="s">
+      <c r="C80" s="152" t="s">
         <v>133</v>
       </c>
-      <c r="D80" s="137"/>
-      <c r="E80" s="137"/>
-      <c r="F80" s="137"/>
-      <c r="G80" s="138"/>
-      <c r="H80" s="136" t="s">
+      <c r="D80" s="149"/>
+      <c r="E80" s="149"/>
+      <c r="F80" s="149"/>
+      <c r="G80" s="150"/>
+      <c r="H80" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I80" s="137"/>
-      <c r="J80" s="138"/>
+      <c r="I80" s="149"/>
+      <c r="J80" s="150"/>
       <c r="K80" s="81" t="s">
         <v>134</v>
       </c>
@@ -10158,7 +10231,7 @@
     </row>
     <row r="84" spans="2:3">
       <c r="B84" s="135" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="C84" s="68" t="s">
         <v>137</v>
@@ -10166,7 +10239,7 @@
     </row>
     <row r="85" spans="2:3">
       <c r="B85" s="135" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="C85" s="68" t="s">
         <v>138</v>
@@ -10174,7 +10247,7 @@
     </row>
     <row r="86" spans="2:3">
       <c r="B86" s="135" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="C86" s="68" t="s">
         <v>139</v>
@@ -10182,7 +10255,7 @@
     </row>
     <row r="87" spans="2:3">
       <c r="B87" s="135" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="C87" s="68" t="s">
         <v>140</v>
@@ -10190,52 +10263,121 @@
     </row>
     <row r="88" spans="2:3">
       <c r="B88" s="135" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="89" spans="2:3">
       <c r="B89" s="135" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="90" spans="2:3">
       <c r="B90" s="135" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="91" spans="2:3">
       <c r="B91" s="135" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="92" spans="2:3">
       <c r="B92" s="135" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="93" spans="2:3">
       <c r="B93" s="135" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="94" spans="2:3">
       <c r="B94" s="135" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="95" spans="2:3">
       <c r="B95" s="135" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="97">
-    <mergeCell ref="C24:G25"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="H24:J25"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="H65:J65"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C47:G49"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="B11:V11"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B5:V5"/>
+    <mergeCell ref="H47:J49"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="H40:J40"/>
     <mergeCell ref="H51:J51"/>
     <mergeCell ref="H69:J69"/>
     <mergeCell ref="C29:G29"/>
@@ -10252,81 +10394,12 @@
     <mergeCell ref="C62:G62"/>
     <mergeCell ref="H32:J32"/>
     <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B2:V2"/>
-    <mergeCell ref="B11:V11"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B5:V5"/>
-    <mergeCell ref="H47:J49"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C47:G49"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="H79:J79"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H78:J78"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="H65:J65"/>
-    <mergeCell ref="H71:J71"/>
-    <mergeCell ref="H75:J75"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="C24:G25"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="H24:J25"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:J26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10335,7 +10408,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F1135"/>
+  <dimension ref="A1:F1159"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.75" style="2" bestFit="1" customWidth="1"/>
@@ -13135,7 +13208,7 @@
         <v>966</v>
       </c>
       <c r="D140" s="130" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E140" s="130" t="s">
         <v>816</v>
@@ -13155,7 +13228,7 @@
         <v>967</v>
       </c>
       <c r="D141" s="130" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E141" s="130" t="s">
         <v>816</v>
@@ -13175,7 +13248,7 @@
         <v>968</v>
       </c>
       <c r="D142" s="130" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="E142" s="130" t="s">
         <v>816</v>
@@ -13195,7 +13268,7 @@
         <v>969</v>
       </c>
       <c r="D143" s="130" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="E143" s="130" t="s">
         <v>816</v>
@@ -13215,7 +13288,7 @@
         <v>970</v>
       </c>
       <c r="D144" s="130" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E144" s="130" t="s">
         <v>816</v>
@@ -26235,7 +26308,7 @@
         <v>815</v>
       </c>
       <c r="D795" s="130" t="s">
-        <v>1669</v>
+        <v>2035</v>
       </c>
       <c r="E795" s="130" t="s">
         <v>816</v>
@@ -26255,7 +26328,7 @@
         <v>815</v>
       </c>
       <c r="D796" s="130" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="E796" s="130" t="s">
         <v>816</v>
@@ -26275,7 +26348,7 @@
         <v>815</v>
       </c>
       <c r="D797" s="130" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="E797" s="130" t="s">
         <v>816</v>
@@ -26295,7 +26368,7 @@
         <v>815</v>
       </c>
       <c r="D798" s="130" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="E798" s="130" t="s">
         <v>816</v>
@@ -26315,7 +26388,7 @@
         <v>815</v>
       </c>
       <c r="D799" s="130" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="E799" s="130" t="s">
         <v>816</v>
@@ -26335,7 +26408,7 @@
         <v>815</v>
       </c>
       <c r="D800" s="130" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="E800" s="130" t="s">
         <v>816</v>
@@ -26355,7 +26428,7 @@
         <v>815</v>
       </c>
       <c r="D801" s="130" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="E801" s="130" t="s">
         <v>816</v>
@@ -26375,7 +26448,7 @@
         <v>815</v>
       </c>
       <c r="D802" s="130" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="E802" s="130" t="s">
         <v>816</v>
@@ -26395,7 +26468,7 @@
         <v>815</v>
       </c>
       <c r="D803" s="130" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="E803" s="130" t="s">
         <v>816</v>
@@ -26415,7 +26488,7 @@
         <v>815</v>
       </c>
       <c r="D804" s="130" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="E804" s="130" t="s">
         <v>816</v>
@@ -26435,7 +26508,7 @@
         <v>815</v>
       </c>
       <c r="D805" s="130" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="E805" s="130" t="s">
         <v>816</v>
@@ -26455,7 +26528,7 @@
         <v>815</v>
       </c>
       <c r="D806" s="130" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="E806" s="130" t="s">
         <v>816</v>
@@ -26475,7 +26548,7 @@
         <v>815</v>
       </c>
       <c r="D807" s="130" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="E807" s="130" t="s">
         <v>816</v>
@@ -26495,7 +26568,7 @@
         <v>815</v>
       </c>
       <c r="D808" s="130" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="E808" s="130" t="s">
         <v>816</v>
@@ -26515,7 +26588,7 @@
         <v>815</v>
       </c>
       <c r="D809" s="130" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="E809" s="130" t="s">
         <v>816</v>
@@ -26535,7 +26608,7 @@
         <v>815</v>
       </c>
       <c r="D810" s="130" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="E810" s="130" t="s">
         <v>816</v>
@@ -26555,7 +26628,7 @@
         <v>815</v>
       </c>
       <c r="D811" s="130" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="E811" s="130" t="s">
         <v>816</v>
@@ -26575,7 +26648,7 @@
         <v>815</v>
       </c>
       <c r="D812" s="130" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="E812" s="130" t="s">
         <v>816</v>
@@ -26595,7 +26668,7 @@
         <v>815</v>
       </c>
       <c r="D813" s="130" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E813" s="130" t="s">
         <v>816</v>
@@ -26615,7 +26688,7 @@
         <v>815</v>
       </c>
       <c r="D814" s="130" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="E814" s="130" t="s">
         <v>816</v>
@@ -26635,7 +26708,7 @@
         <v>815</v>
       </c>
       <c r="D815" s="130" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="E815" s="130" t="s">
         <v>816</v>
@@ -26655,7 +26728,7 @@
         <v>815</v>
       </c>
       <c r="D816" s="130" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E816" s="130" t="s">
         <v>816</v>
@@ -26675,7 +26748,7 @@
         <v>815</v>
       </c>
       <c r="D817" s="130" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="E817" s="130" t="s">
         <v>816</v>
@@ -26695,7 +26768,7 @@
         <v>815</v>
       </c>
       <c r="D818" s="130" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="E818" s="130" t="s">
         <v>816</v>
@@ -26715,7 +26788,7 @@
         <v>815</v>
       </c>
       <c r="D819" s="130" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="E819" s="130" t="s">
         <v>816</v>
@@ -26735,7 +26808,7 @@
         <v>815</v>
       </c>
       <c r="D820" s="130" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="E820" s="130" t="s">
         <v>816</v>
@@ -26755,7 +26828,7 @@
         <v>815</v>
       </c>
       <c r="D821" s="130" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="E821" s="130" t="s">
         <v>816</v>
@@ -26775,7 +26848,7 @@
         <v>815</v>
       </c>
       <c r="D822" s="130" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="E822" s="130" t="s">
         <v>816</v>
@@ -26795,7 +26868,7 @@
         <v>815</v>
       </c>
       <c r="D823" s="130" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="E823" s="130" t="s">
         <v>816</v>
@@ -26815,7 +26888,7 @@
         <v>815</v>
       </c>
       <c r="D824" s="130" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="E824" s="130" t="s">
         <v>816</v>
@@ -26835,7 +26908,7 @@
         <v>815</v>
       </c>
       <c r="D825" s="130" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="E825" s="130" t="s">
         <v>816</v>
@@ -26855,7 +26928,7 @@
         <v>815</v>
       </c>
       <c r="D826" s="130" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="E826" s="130" t="s">
         <v>816</v>
@@ -26875,7 +26948,7 @@
         <v>815</v>
       </c>
       <c r="D827" s="130" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="E827" s="130" t="s">
         <v>816</v>
@@ -26895,7 +26968,7 @@
         <v>815</v>
       </c>
       <c r="D828" s="130" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="E828" s="130" t="s">
         <v>816</v>
@@ -26915,7 +26988,7 @@
         <v>815</v>
       </c>
       <c r="D829" s="130" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="E829" s="130" t="s">
         <v>816</v>
@@ -26935,7 +27008,7 @@
         <v>815</v>
       </c>
       <c r="D830" s="130" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="E830" s="130" t="s">
         <v>816</v>
@@ -26955,7 +27028,7 @@
         <v>815</v>
       </c>
       <c r="D831" s="130" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="E831" s="130" t="s">
         <v>816</v>
@@ -26975,7 +27048,7 @@
         <v>815</v>
       </c>
       <c r="D832" s="130" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="E832" s="130" t="s">
         <v>816</v>
@@ -26995,7 +27068,7 @@
         <v>815</v>
       </c>
       <c r="D833" s="130" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="E833" s="130" t="s">
         <v>816</v>
@@ -27015,7 +27088,7 @@
         <v>815</v>
       </c>
       <c r="D834" s="130" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E834" s="130" t="s">
         <v>816</v>
@@ -27035,7 +27108,7 @@
         <v>815</v>
       </c>
       <c r="D835" s="130" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="E835" s="130" t="s">
         <v>816</v>
@@ -27055,7 +27128,7 @@
         <v>815</v>
       </c>
       <c r="D836" s="130" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="E836" s="130" t="s">
         <v>816</v>
@@ -27075,7 +27148,7 @@
         <v>815</v>
       </c>
       <c r="D837" s="130" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="E837" s="130" t="s">
         <v>816</v>
@@ -27095,7 +27168,7 @@
         <v>815</v>
       </c>
       <c r="D838" s="130" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="E838" s="130" t="s">
         <v>816</v>
@@ -27115,7 +27188,7 @@
         <v>815</v>
       </c>
       <c r="D839" s="130" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="E839" s="130" t="s">
         <v>816</v>
@@ -27135,7 +27208,7 @@
         <v>815</v>
       </c>
       <c r="D840" s="130" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E840" s="130" t="s">
         <v>816</v>
@@ -27155,7 +27228,7 @@
         <v>815</v>
       </c>
       <c r="D841" s="130" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="E841" s="130" t="s">
         <v>816</v>
@@ -27175,7 +27248,7 @@
         <v>815</v>
       </c>
       <c r="D842" s="130" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="E842" s="130" t="s">
         <v>816</v>
@@ -27195,7 +27268,7 @@
         <v>815</v>
       </c>
       <c r="D843" s="130" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="E843" s="130" t="s">
         <v>816</v>
@@ -27215,7 +27288,7 @@
         <v>815</v>
       </c>
       <c r="D844" s="130" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E844" s="130" t="s">
         <v>816</v>
@@ -27235,7 +27308,7 @@
         <v>815</v>
       </c>
       <c r="D845" s="130" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="E845" s="130" t="s">
         <v>816</v>
@@ -27255,7 +27328,7 @@
         <v>815</v>
       </c>
       <c r="D846" s="130" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="E846" s="130" t="s">
         <v>816</v>
@@ -27275,7 +27348,7 @@
         <v>815</v>
       </c>
       <c r="D847" s="130" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="E847" s="130" t="s">
         <v>816</v>
@@ -27295,7 +27368,7 @@
         <v>815</v>
       </c>
       <c r="D848" s="130" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="E848" s="130" t="s">
         <v>816</v>
@@ -27315,7 +27388,7 @@
         <v>815</v>
       </c>
       <c r="D849" s="130" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="E849" s="130" t="s">
         <v>816</v>
@@ -27335,7 +27408,7 @@
         <v>815</v>
       </c>
       <c r="D850" s="130" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="E850" s="130" t="s">
         <v>816</v>
@@ -27355,7 +27428,7 @@
         <v>815</v>
       </c>
       <c r="D851" s="130" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="E851" s="130" t="s">
         <v>816</v>
@@ -27375,7 +27448,7 @@
         <v>815</v>
       </c>
       <c r="D852" s="130" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="E852" s="130" t="s">
         <v>816</v>
@@ -27395,7 +27468,7 @@
         <v>815</v>
       </c>
       <c r="D853" s="130" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="E853" s="130" t="s">
         <v>816</v>
@@ -27415,7 +27488,7 @@
         <v>815</v>
       </c>
       <c r="D854" s="130" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="E854" s="130" t="s">
         <v>816</v>
@@ -27435,7 +27508,7 @@
         <v>815</v>
       </c>
       <c r="D855" s="130" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="E855" s="130" t="s">
         <v>816</v>
@@ -27455,7 +27528,7 @@
         <v>815</v>
       </c>
       <c r="D856" s="130" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="E856" s="130" t="s">
         <v>816</v>
@@ -27475,7 +27548,7 @@
         <v>815</v>
       </c>
       <c r="D857" s="130" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="E857" s="130" t="s">
         <v>816</v>
@@ -27495,7 +27568,7 @@
         <v>815</v>
       </c>
       <c r="D858" s="130" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="E858" s="130" t="s">
         <v>816</v>
@@ -27515,7 +27588,7 @@
         <v>815</v>
       </c>
       <c r="D859" s="130" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="E859" s="130" t="s">
         <v>816</v>
@@ -27535,7 +27608,7 @@
         <v>815</v>
       </c>
       <c r="D860" s="130" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="E860" s="130" t="s">
         <v>816</v>
@@ -27555,7 +27628,7 @@
         <v>815</v>
       </c>
       <c r="D861" s="130" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="E861" s="130" t="s">
         <v>816</v>
@@ -27575,7 +27648,7 @@
         <v>815</v>
       </c>
       <c r="D862" s="130" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="E862" s="130" t="s">
         <v>816</v>
@@ -27595,7 +27668,7 @@
         <v>815</v>
       </c>
       <c r="D863" s="130" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="E863" s="130" t="s">
         <v>816</v>
@@ -27615,7 +27688,7 @@
         <v>815</v>
       </c>
       <c r="D864" s="130" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="E864" s="130" t="s">
         <v>816</v>
@@ -27635,7 +27708,7 @@
         <v>815</v>
       </c>
       <c r="D865" s="130" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="E865" s="130" t="s">
         <v>816</v>
@@ -27655,7 +27728,7 @@
         <v>815</v>
       </c>
       <c r="D866" s="130" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="E866" s="130" t="s">
         <v>816</v>
@@ -27675,7 +27748,7 @@
         <v>815</v>
       </c>
       <c r="D867" s="130" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="E867" s="130" t="s">
         <v>816</v>
@@ -27695,7 +27768,7 @@
         <v>815</v>
       </c>
       <c r="D868" s="130" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="E868" s="130" t="s">
         <v>816</v>
@@ -27715,7 +27788,7 @@
         <v>815</v>
       </c>
       <c r="D869" s="130" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="E869" s="130" t="s">
         <v>816</v>
@@ -27735,7 +27808,7 @@
         <v>815</v>
       </c>
       <c r="D870" s="130" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="E870" s="130" t="s">
         <v>816</v>
@@ -27755,7 +27828,7 @@
         <v>815</v>
       </c>
       <c r="D871" s="130" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="E871" s="130" t="s">
         <v>816</v>
@@ -27775,7 +27848,7 @@
         <v>815</v>
       </c>
       <c r="D872" s="130" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="E872" s="130" t="s">
         <v>816</v>
@@ -27795,7 +27868,7 @@
         <v>815</v>
       </c>
       <c r="D873" s="130" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="E873" s="130" t="s">
         <v>816</v>
@@ -27815,7 +27888,7 @@
         <v>815</v>
       </c>
       <c r="D874" s="130" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="E874" s="130" t="s">
         <v>816</v>
@@ -27835,7 +27908,7 @@
         <v>815</v>
       </c>
       <c r="D875" s="130" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="E875" s="130" t="s">
         <v>816</v>
@@ -27855,7 +27928,7 @@
         <v>815</v>
       </c>
       <c r="D876" s="130" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="E876" s="130" t="s">
         <v>816</v>
@@ -27875,7 +27948,7 @@
         <v>815</v>
       </c>
       <c r="D877" s="130" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="E877" s="130" t="s">
         <v>816</v>
@@ -27895,7 +27968,7 @@
         <v>815</v>
       </c>
       <c r="D878" s="130" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="E878" s="130" t="s">
         <v>816</v>
@@ -27915,7 +27988,7 @@
         <v>815</v>
       </c>
       <c r="D879" s="130" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="E879" s="130" t="s">
         <v>816</v>
@@ -27935,7 +28008,7 @@
         <v>815</v>
       </c>
       <c r="D880" s="130" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="E880" s="130" t="s">
         <v>816</v>
@@ -27955,7 +28028,7 @@
         <v>815</v>
       </c>
       <c r="D881" s="130" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="E881" s="130" t="s">
         <v>816</v>
@@ -27975,7 +28048,7 @@
         <v>815</v>
       </c>
       <c r="D882" s="130" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="E882" s="130" t="s">
         <v>816</v>
@@ -27995,7 +28068,7 @@
         <v>815</v>
       </c>
       <c r="D883" s="130" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="E883" s="130" t="s">
         <v>816</v>
@@ -28015,7 +28088,7 @@
         <v>815</v>
       </c>
       <c r="D884" s="130" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="E884" s="130" t="s">
         <v>816</v>
@@ -28035,7 +28108,7 @@
         <v>815</v>
       </c>
       <c r="D885" s="130" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="E885" s="130" t="s">
         <v>816</v>
@@ -28055,7 +28128,7 @@
         <v>815</v>
       </c>
       <c r="D886" s="130" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="E886" s="130" t="s">
         <v>816</v>
@@ -28075,7 +28148,7 @@
         <v>815</v>
       </c>
       <c r="D887" s="130" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="E887" s="130" t="s">
         <v>816</v>
@@ -28095,7 +28168,7 @@
         <v>815</v>
       </c>
       <c r="D888" s="130" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="E888" s="130" t="s">
         <v>816</v>
@@ -28115,7 +28188,7 @@
         <v>815</v>
       </c>
       <c r="D889" s="130" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="E889" s="130" t="s">
         <v>816</v>
@@ -28135,7 +28208,7 @@
         <v>815</v>
       </c>
       <c r="D890" s="130" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="E890" s="130" t="s">
         <v>816</v>
@@ -28155,7 +28228,7 @@
         <v>815</v>
       </c>
       <c r="D891" s="130" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="E891" s="130" t="s">
         <v>816</v>
@@ -28175,7 +28248,7 @@
         <v>815</v>
       </c>
       <c r="D892" s="130" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="E892" s="130" t="s">
         <v>816</v>
@@ -28195,7 +28268,7 @@
         <v>815</v>
       </c>
       <c r="D893" s="130" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="E893" s="130" t="s">
         <v>816</v>
@@ -28215,7 +28288,7 @@
         <v>815</v>
       </c>
       <c r="D894" s="130" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="E894" s="130" t="s">
         <v>816</v>
@@ -28235,7 +28308,7 @@
         <v>815</v>
       </c>
       <c r="D895" s="130" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="E895" s="130" t="s">
         <v>816</v>
@@ -28255,7 +28328,7 @@
         <v>815</v>
       </c>
       <c r="D896" s="130" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="E896" s="130" t="s">
         <v>816</v>
@@ -28275,7 +28348,7 @@
         <v>815</v>
       </c>
       <c r="D897" s="130" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="E897" s="130" t="s">
         <v>816</v>
@@ -28295,7 +28368,7 @@
         <v>815</v>
       </c>
       <c r="D898" s="130" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="E898" s="130" t="s">
         <v>816</v>
@@ -28315,7 +28388,7 @@
         <v>815</v>
       </c>
       <c r="D899" s="130" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="E899" s="130" t="s">
         <v>816</v>
@@ -28335,7 +28408,7 @@
         <v>815</v>
       </c>
       <c r="D900" s="130" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="E900" s="130" t="s">
         <v>816</v>
@@ -28355,7 +28428,7 @@
         <v>815</v>
       </c>
       <c r="D901" s="130" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="E901" s="130" t="s">
         <v>816</v>
@@ -28375,7 +28448,7 @@
         <v>815</v>
       </c>
       <c r="D902" s="130" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="E902" s="130" t="s">
         <v>816</v>
@@ -28395,7 +28468,7 @@
         <v>815</v>
       </c>
       <c r="D903" s="130" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="E903" s="130" t="s">
         <v>816</v>
@@ -28415,7 +28488,7 @@
         <v>815</v>
       </c>
       <c r="D904" s="130" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="E904" s="130" t="s">
         <v>816</v>
@@ -28435,7 +28508,7 @@
         <v>815</v>
       </c>
       <c r="D905" s="130" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="E905" s="130" t="s">
         <v>816</v>
@@ -28455,7 +28528,7 @@
         <v>815</v>
       </c>
       <c r="D906" s="130" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="E906" s="130" t="s">
         <v>816</v>
@@ -28475,7 +28548,7 @@
         <v>815</v>
       </c>
       <c r="D907" s="130" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="E907" s="130" t="s">
         <v>816</v>
@@ -28495,7 +28568,7 @@
         <v>815</v>
       </c>
       <c r="D908" s="130" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="E908" s="130" t="s">
         <v>816</v>
@@ -28515,7 +28588,7 @@
         <v>815</v>
       </c>
       <c r="D909" s="130" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="E909" s="130" t="s">
         <v>816</v>
@@ -28535,7 +28608,7 @@
         <v>815</v>
       </c>
       <c r="D910" s="130" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="E910" s="130" t="s">
         <v>816</v>
@@ -28555,7 +28628,7 @@
         <v>815</v>
       </c>
       <c r="D911" s="130" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="E911" s="130" t="s">
         <v>816</v>
@@ -28575,7 +28648,7 @@
         <v>815</v>
       </c>
       <c r="D912" s="130" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="E912" s="130" t="s">
         <v>816</v>
@@ -28595,7 +28668,7 @@
         <v>815</v>
       </c>
       <c r="D913" s="130" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="E913" s="130" t="s">
         <v>816</v>
@@ -28615,7 +28688,7 @@
         <v>815</v>
       </c>
       <c r="D914" s="130" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="E914" s="130" t="s">
         <v>816</v>
@@ -28635,7 +28708,7 @@
         <v>815</v>
       </c>
       <c r="D915" s="130" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="E915" s="130" t="s">
         <v>816</v>
@@ -28655,7 +28728,7 @@
         <v>815</v>
       </c>
       <c r="D916" s="130" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="E916" s="130" t="s">
         <v>816</v>
@@ -28675,7 +28748,7 @@
         <v>815</v>
       </c>
       <c r="D917" s="130" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="E917" s="130" t="s">
         <v>816</v>
@@ -28695,7 +28768,7 @@
         <v>815</v>
       </c>
       <c r="D918" s="130" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="E918" s="130" t="s">
         <v>816</v>
@@ -28715,7 +28788,7 @@
         <v>815</v>
       </c>
       <c r="D919" s="130" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="E919" s="130" t="s">
         <v>816</v>
@@ -28735,7 +28808,7 @@
         <v>815</v>
       </c>
       <c r="D920" s="130" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="E920" s="130" t="s">
         <v>816</v>
@@ -28755,7 +28828,7 @@
         <v>815</v>
       </c>
       <c r="D921" s="130" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="E921" s="130" t="s">
         <v>816</v>
@@ -28775,7 +28848,7 @@
         <v>815</v>
       </c>
       <c r="D922" s="130" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="E922" s="130" t="s">
         <v>816</v>
@@ -28795,7 +28868,7 @@
         <v>815</v>
       </c>
       <c r="D923" s="130" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="E923" s="130" t="s">
         <v>816</v>
@@ -28815,7 +28888,7 @@
         <v>815</v>
       </c>
       <c r="D924" s="130" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="E924" s="130" t="s">
         <v>816</v>
@@ -28835,7 +28908,7 @@
         <v>815</v>
       </c>
       <c r="D925" s="130" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="E925" s="130" t="s">
         <v>816</v>
@@ -28855,7 +28928,7 @@
         <v>815</v>
       </c>
       <c r="D926" s="130" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="E926" s="130" t="s">
         <v>816</v>
@@ -28875,7 +28948,7 @@
         <v>815</v>
       </c>
       <c r="D927" s="130" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="E927" s="130" t="s">
         <v>816</v>
@@ -28895,7 +28968,7 @@
         <v>815</v>
       </c>
       <c r="D928" s="130" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="E928" s="130" t="s">
         <v>816</v>
@@ -28915,7 +28988,7 @@
         <v>815</v>
       </c>
       <c r="D929" s="130" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="E929" s="130" t="s">
         <v>816</v>
@@ -28935,7 +29008,7 @@
         <v>815</v>
       </c>
       <c r="D930" s="130" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="E930" s="130" t="s">
         <v>816</v>
@@ -28955,7 +29028,7 @@
         <v>815</v>
       </c>
       <c r="D931" s="130" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E931" s="130" t="s">
         <v>816</v>
@@ -28975,7 +29048,7 @@
         <v>815</v>
       </c>
       <c r="D932" s="130" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="E932" s="130" t="s">
         <v>816</v>
@@ -28995,7 +29068,7 @@
         <v>815</v>
       </c>
       <c r="D933" s="130" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="E933" s="130" t="s">
         <v>816</v>
@@ -29015,7 +29088,7 @@
         <v>815</v>
       </c>
       <c r="D934" s="130" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="E934" s="130" t="s">
         <v>816</v>
@@ -29035,7 +29108,7 @@
         <v>815</v>
       </c>
       <c r="D935" s="130" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="E935" s="130" t="s">
         <v>816</v>
@@ -29055,7 +29128,7 @@
         <v>815</v>
       </c>
       <c r="D936" s="130" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="E936" s="130" t="s">
         <v>816</v>
@@ -29075,7 +29148,7 @@
         <v>815</v>
       </c>
       <c r="D937" s="130" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="E937" s="130" t="s">
         <v>816</v>
@@ -29095,7 +29168,7 @@
         <v>815</v>
       </c>
       <c r="D938" s="130" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="E938" s="130" t="s">
         <v>816</v>
@@ -29115,7 +29188,7 @@
         <v>815</v>
       </c>
       <c r="D939" s="130" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="E939" s="130" t="s">
         <v>816</v>
@@ -29135,7 +29208,7 @@
         <v>815</v>
       </c>
       <c r="D940" s="130" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="E940" s="130" t="s">
         <v>816</v>
@@ -29155,7 +29228,7 @@
         <v>815</v>
       </c>
       <c r="D941" s="130" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="E941" s="130" t="s">
         <v>816</v>
@@ -29175,7 +29248,7 @@
         <v>815</v>
       </c>
       <c r="D942" s="130" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="E942" s="130" t="s">
         <v>816</v>
@@ -29195,7 +29268,7 @@
         <v>815</v>
       </c>
       <c r="D943" s="130" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="E943" s="130" t="s">
         <v>816</v>
@@ -29215,7 +29288,7 @@
         <v>815</v>
       </c>
       <c r="D944" s="130" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E944" s="130" t="s">
         <v>816</v>
@@ -29235,7 +29308,7 @@
         <v>815</v>
       </c>
       <c r="D945" s="133" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="E945" s="130" t="s">
         <v>816</v>
@@ -29255,7 +29328,7 @@
         <v>815</v>
       </c>
       <c r="D946" s="130" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="E946" s="130" t="s">
         <v>816</v>
@@ -29295,7 +29368,7 @@
         <v>815</v>
       </c>
       <c r="D948" s="130" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="E948" s="130" t="s">
         <v>816</v>
@@ -29315,7 +29388,7 @@
         <v>815</v>
       </c>
       <c r="D949" s="130" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="E949" s="130" t="s">
         <v>816</v>
@@ -29335,7 +29408,7 @@
         <v>815</v>
       </c>
       <c r="D950" s="130" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="E950" s="130" t="s">
         <v>816</v>
@@ -29355,7 +29428,7 @@
         <v>815</v>
       </c>
       <c r="D951" s="130" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="E951" s="130" t="s">
         <v>816</v>
@@ -29375,7 +29448,7 @@
         <v>815</v>
       </c>
       <c r="D952" s="130" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="E952" s="130" t="s">
         <v>816</v>
@@ -29395,7 +29468,7 @@
         <v>815</v>
       </c>
       <c r="D953" s="130" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="E953" s="130" t="s">
         <v>816</v>
@@ -29415,7 +29488,7 @@
         <v>815</v>
       </c>
       <c r="D954" s="130" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="E954" s="130" t="s">
         <v>816</v>
@@ -29435,7 +29508,7 @@
         <v>815</v>
       </c>
       <c r="D955" s="130" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="E955" s="130" t="s">
         <v>816</v>
@@ -29455,7 +29528,7 @@
         <v>815</v>
       </c>
       <c r="D956" s="130" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="E956" s="130" t="s">
         <v>816</v>
@@ -29495,7 +29568,7 @@
         <v>815</v>
       </c>
       <c r="D958" s="130" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="E958" s="130" t="s">
         <v>816</v>
@@ -29515,7 +29588,7 @@
         <v>815</v>
       </c>
       <c r="D959" s="130" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="E959" s="130" t="s">
         <v>816</v>
@@ -29535,7 +29608,7 @@
         <v>815</v>
       </c>
       <c r="D960" s="130" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="E960" s="130" t="s">
         <v>816</v>
@@ -29555,7 +29628,7 @@
         <v>815</v>
       </c>
       <c r="D961" s="130" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="E961" s="130" t="s">
         <v>816</v>
@@ -29575,7 +29648,7 @@
         <v>815</v>
       </c>
       <c r="D962" s="130" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="E962" s="130" t="s">
         <v>816</v>
@@ -29595,7 +29668,7 @@
         <v>815</v>
       </c>
       <c r="D963" s="130" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E963" s="130" t="s">
         <v>816</v>
@@ -29615,7 +29688,7 @@
         <v>815</v>
       </c>
       <c r="D964" s="130" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="E964" s="130" t="s">
         <v>816</v>
@@ -29635,7 +29708,7 @@
         <v>815</v>
       </c>
       <c r="D965" s="130" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="E965" s="130" t="s">
         <v>816</v>
@@ -29655,7 +29728,7 @@
         <v>815</v>
       </c>
       <c r="D966" s="130" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="E966" s="130" t="s">
         <v>816</v>
@@ -29675,7 +29748,7 @@
         <v>815</v>
       </c>
       <c r="D967" s="130" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="E967" s="130" t="s">
         <v>816</v>
@@ -29695,7 +29768,7 @@
         <v>815</v>
       </c>
       <c r="D968" s="133" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="E968" s="130" t="s">
         <v>816</v>
@@ -29715,7 +29788,7 @@
         <v>815</v>
       </c>
       <c r="D969" s="130" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="E969" s="130" t="s">
         <v>816</v>
@@ -29735,7 +29808,7 @@
         <v>815</v>
       </c>
       <c r="D970" s="130" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="E970" s="130" t="s">
         <v>816</v>
@@ -29755,7 +29828,7 @@
         <v>815</v>
       </c>
       <c r="D971" s="130" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="E971" s="130" t="s">
         <v>816</v>
@@ -29775,7 +29848,7 @@
         <v>815</v>
       </c>
       <c r="D972" s="130" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="E972" s="130" t="s">
         <v>816</v>
@@ -29795,7 +29868,7 @@
         <v>815</v>
       </c>
       <c r="D973" s="130" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="E973" s="130" t="s">
         <v>816</v>
@@ -29815,7 +29888,7 @@
         <v>815</v>
       </c>
       <c r="D974" s="130" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="E974" s="130" t="s">
         <v>816</v>
@@ -29835,7 +29908,7 @@
         <v>815</v>
       </c>
       <c r="D975" s="130" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="E975" s="130" t="s">
         <v>816</v>
@@ -29855,7 +29928,7 @@
         <v>815</v>
       </c>
       <c r="D976" s="130" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="E976" s="130" t="s">
         <v>816</v>
@@ -29875,7 +29948,7 @@
         <v>815</v>
       </c>
       <c r="D977" s="130" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="E977" s="130" t="s">
         <v>816</v>
@@ -29895,7 +29968,7 @@
         <v>815</v>
       </c>
       <c r="D978" s="130" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="E978" s="130" t="s">
         <v>816</v>
@@ -29915,7 +29988,7 @@
         <v>815</v>
       </c>
       <c r="D979" s="130" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="E979" s="130" t="s">
         <v>816</v>
@@ -29935,7 +30008,7 @@
         <v>815</v>
       </c>
       <c r="D980" s="130" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="E980" s="130" t="s">
         <v>816</v>
@@ -29955,7 +30028,7 @@
         <v>815</v>
       </c>
       <c r="D981" s="130" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="E981" s="130" t="s">
         <v>816</v>
@@ -29975,7 +30048,7 @@
         <v>815</v>
       </c>
       <c r="D982" s="130" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="E982" s="130" t="s">
         <v>816</v>
@@ -29995,7 +30068,7 @@
         <v>815</v>
       </c>
       <c r="D983" s="130" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="E983" s="130" t="s">
         <v>816</v>
@@ -30015,7 +30088,7 @@
         <v>815</v>
       </c>
       <c r="D984" s="130" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="E984" s="130" t="s">
         <v>816</v>
@@ -30035,7 +30108,7 @@
         <v>815</v>
       </c>
       <c r="D985" s="130" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="E985" s="130" t="s">
         <v>816</v>
@@ -30055,7 +30128,7 @@
         <v>815</v>
       </c>
       <c r="D986" s="130" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="E986" s="130" t="s">
         <v>816</v>
@@ -30075,7 +30148,7 @@
         <v>815</v>
       </c>
       <c r="D987" s="130" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="E987" s="130" t="s">
         <v>816</v>
@@ -30095,7 +30168,7 @@
         <v>815</v>
       </c>
       <c r="D988" s="130" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="E988" s="130" t="s">
         <v>816</v>
@@ -30115,7 +30188,7 @@
         <v>815</v>
       </c>
       <c r="D989" s="130" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="E989" s="130" t="s">
         <v>816</v>
@@ -30135,7 +30208,7 @@
         <v>815</v>
       </c>
       <c r="D990" s="130" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="E990" s="130" t="s">
         <v>816</v>
@@ -30155,7 +30228,7 @@
         <v>815</v>
       </c>
       <c r="D991" s="130" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="E991" s="130" t="s">
         <v>816</v>
@@ -30175,7 +30248,7 @@
         <v>815</v>
       </c>
       <c r="D992" s="130" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="E992" s="130" t="s">
         <v>816</v>
@@ -30195,7 +30268,7 @@
         <v>815</v>
       </c>
       <c r="D993" s="130" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="E993" s="130" t="s">
         <v>816</v>
@@ -30215,7 +30288,7 @@
         <v>815</v>
       </c>
       <c r="D994" s="130" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="E994" s="130" t="s">
         <v>816</v>
@@ -30235,7 +30308,7 @@
         <v>815</v>
       </c>
       <c r="D995" s="130" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="E995" s="130" t="s">
         <v>816</v>
@@ -30255,7 +30328,7 @@
         <v>815</v>
       </c>
       <c r="D996" s="130" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="E996" s="130" t="s">
         <v>816</v>
@@ -30275,7 +30348,7 @@
         <v>815</v>
       </c>
       <c r="D997" s="130" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="E997" s="130" t="s">
         <v>816</v>
@@ -30295,7 +30368,7 @@
         <v>815</v>
       </c>
       <c r="D998" s="130" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="E998" s="130" t="s">
         <v>816</v>
@@ -30315,7 +30388,7 @@
         <v>815</v>
       </c>
       <c r="D999" s="130" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="E999" s="130" t="s">
         <v>816</v>
@@ -30335,7 +30408,7 @@
         <v>815</v>
       </c>
       <c r="D1000" s="130" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="E1000" s="130" t="s">
         <v>816</v>
@@ -30355,7 +30428,7 @@
         <v>815</v>
       </c>
       <c r="D1001" s="130" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="E1001" s="130" t="s">
         <v>816</v>
@@ -30375,7 +30448,7 @@
         <v>815</v>
       </c>
       <c r="D1002" s="130" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="E1002" s="130" t="s">
         <v>816</v>
@@ -30395,7 +30468,7 @@
         <v>815</v>
       </c>
       <c r="D1003" s="130" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="E1003" s="130" t="s">
         <v>816</v>
@@ -30415,7 +30488,7 @@
         <v>815</v>
       </c>
       <c r="D1004" s="130" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="E1004" s="130" t="s">
         <v>816</v>
@@ -30435,7 +30508,7 @@
         <v>815</v>
       </c>
       <c r="D1005" s="130" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="E1005" s="130" t="s">
         <v>816</v>
@@ -30455,7 +30528,7 @@
         <v>815</v>
       </c>
       <c r="D1006" s="130" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="E1006" s="130" t="s">
         <v>816</v>
@@ -30475,7 +30548,7 @@
         <v>815</v>
       </c>
       <c r="D1007" s="130" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="E1007" s="130" t="s">
         <v>816</v>
@@ -30495,7 +30568,7 @@
         <v>815</v>
       </c>
       <c r="D1008" s="130" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="E1008" s="130" t="s">
         <v>816</v>
@@ -30515,7 +30588,7 @@
         <v>815</v>
       </c>
       <c r="D1009" s="130" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="E1009" s="130" t="s">
         <v>816</v>
@@ -30535,7 +30608,7 @@
         <v>815</v>
       </c>
       <c r="D1010" s="130" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="E1010" s="130" t="s">
         <v>816</v>
@@ -30555,7 +30628,7 @@
         <v>815</v>
       </c>
       <c r="D1011" s="130" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="E1011" s="130" t="s">
         <v>816</v>
@@ -30575,7 +30648,7 @@
         <v>815</v>
       </c>
       <c r="D1012" s="130" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="E1012" s="130" t="s">
         <v>816</v>
@@ -30595,7 +30668,7 @@
         <v>815</v>
       </c>
       <c r="D1013" s="130" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E1013" s="130" t="s">
         <v>816</v>
@@ -30615,7 +30688,7 @@
         <v>815</v>
       </c>
       <c r="D1014" s="130" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="E1014" s="130" t="s">
         <v>816</v>
@@ -30635,7 +30708,7 @@
         <v>815</v>
       </c>
       <c r="D1015" s="130" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="E1015" s="130" t="s">
         <v>816</v>
@@ -30655,7 +30728,7 @@
         <v>815</v>
       </c>
       <c r="D1016" s="130" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="E1016" s="130" t="s">
         <v>816</v>
@@ -30675,7 +30748,7 @@
         <v>815</v>
       </c>
       <c r="D1017" s="130" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="E1017" s="130" t="s">
         <v>816</v>
@@ -30695,7 +30768,7 @@
         <v>815</v>
       </c>
       <c r="D1018" s="130" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="E1018" s="130" t="s">
         <v>816</v>
@@ -30715,7 +30788,7 @@
         <v>815</v>
       </c>
       <c r="D1019" s="130" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E1019" s="130" t="s">
         <v>816</v>
@@ -30735,7 +30808,7 @@
         <v>815</v>
       </c>
       <c r="D1020" s="130" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="E1020" s="130" t="s">
         <v>816</v>
@@ -30755,7 +30828,7 @@
         <v>815</v>
       </c>
       <c r="D1021" s="130" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="E1021" s="130" t="s">
         <v>816</v>
@@ -30775,7 +30848,7 @@
         <v>815</v>
       </c>
       <c r="D1022" s="130" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="E1022" s="130" t="s">
         <v>816</v>
@@ -30795,7 +30868,7 @@
         <v>815</v>
       </c>
       <c r="D1023" s="130" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="E1023" s="130" t="s">
         <v>816</v>
@@ -30815,7 +30888,7 @@
         <v>815</v>
       </c>
       <c r="D1024" s="130" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="E1024" s="130" t="s">
         <v>816</v>
@@ -30835,7 +30908,7 @@
         <v>815</v>
       </c>
       <c r="D1025" s="130" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="E1025" s="130" t="s">
         <v>816</v>
@@ -30855,7 +30928,7 @@
         <v>815</v>
       </c>
       <c r="D1026" s="130" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1026" s="130" t="s">
         <v>816</v>
@@ -30875,7 +30948,7 @@
         <v>815</v>
       </c>
       <c r="D1027" s="130" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="E1027" s="130" t="s">
         <v>816</v>
@@ -30895,7 +30968,7 @@
         <v>815</v>
       </c>
       <c r="D1028" s="130" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="E1028" s="130" t="s">
         <v>816</v>
@@ -30915,7 +30988,7 @@
         <v>815</v>
       </c>
       <c r="D1029" s="130" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="E1029" s="130" t="s">
         <v>816</v>
@@ -30935,7 +31008,7 @@
         <v>815</v>
       </c>
       <c r="D1030" s="130" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="E1030" s="130" t="s">
         <v>816</v>
@@ -30955,7 +31028,7 @@
         <v>815</v>
       </c>
       <c r="D1031" s="130" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="E1031" s="130" t="s">
         <v>816</v>
@@ -30975,7 +31048,7 @@
         <v>815</v>
       </c>
       <c r="D1032" s="130" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="E1032" s="130" t="s">
         <v>816</v>
@@ -30995,7 +31068,7 @@
         <v>815</v>
       </c>
       <c r="D1033" s="130" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="E1033" s="130" t="s">
         <v>816</v>
@@ -31015,7 +31088,7 @@
         <v>815</v>
       </c>
       <c r="D1034" s="130" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="E1034" s="130" t="s">
         <v>816</v>
@@ -31035,7 +31108,7 @@
         <v>815</v>
       </c>
       <c r="D1035" s="130" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="E1035" s="130" t="s">
         <v>816</v>
@@ -31055,7 +31128,7 @@
         <v>815</v>
       </c>
       <c r="D1036" s="130" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="E1036" s="130" t="s">
         <v>816</v>
@@ -31075,7 +31148,7 @@
         <v>815</v>
       </c>
       <c r="D1037" s="130" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="E1037" s="130" t="s">
         <v>816</v>
@@ -31115,7 +31188,7 @@
         <v>815</v>
       </c>
       <c r="D1039" s="130" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="E1039" s="130" t="s">
         <v>816</v>
@@ -31155,7 +31228,7 @@
         <v>815</v>
       </c>
       <c r="D1041" s="130" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="E1041" s="130" t="s">
         <v>816</v>
@@ -31175,7 +31248,7 @@
         <v>815</v>
       </c>
       <c r="D1042" s="130" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="E1042" s="130" t="s">
         <v>816</v>
@@ -31195,7 +31268,7 @@
         <v>815</v>
       </c>
       <c r="D1043" s="130" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="E1043" s="130" t="s">
         <v>816</v>
@@ -31215,7 +31288,7 @@
         <v>815</v>
       </c>
       <c r="D1044" s="130" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="E1044" s="130" t="s">
         <v>816</v>
@@ -31235,7 +31308,7 @@
         <v>815</v>
       </c>
       <c r="D1045" s="130" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="E1045" s="130" t="s">
         <v>816</v>
@@ -31255,7 +31328,7 @@
         <v>815</v>
       </c>
       <c r="D1046" s="130" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="E1046" s="130" t="s">
         <v>816</v>
@@ -31275,7 +31348,7 @@
         <v>815</v>
       </c>
       <c r="D1047" s="130" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="E1047" s="130" t="s">
         <v>816</v>
@@ -31295,7 +31368,7 @@
         <v>815</v>
       </c>
       <c r="D1048" s="130" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="E1048" s="130" t="s">
         <v>816</v>
@@ -31315,7 +31388,7 @@
         <v>815</v>
       </c>
       <c r="D1049" s="130" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="E1049" s="130" t="s">
         <v>816</v>
@@ -31335,7 +31408,7 @@
         <v>815</v>
       </c>
       <c r="D1050" s="130" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="E1050" s="130" t="s">
         <v>816</v>
@@ -31355,7 +31428,7 @@
         <v>815</v>
       </c>
       <c r="D1051" s="130" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E1051" s="130" t="s">
         <v>816</v>
@@ -31375,7 +31448,7 @@
         <v>815</v>
       </c>
       <c r="D1052" s="130" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="E1052" s="130" t="s">
         <v>816</v>
@@ -31395,7 +31468,7 @@
         <v>815</v>
       </c>
       <c r="D1053" s="130" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="E1053" s="130" t="s">
         <v>816</v>
@@ -31415,7 +31488,7 @@
         <v>815</v>
       </c>
       <c r="D1054" s="130" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="E1054" s="130" t="s">
         <v>816</v>
@@ -31435,7 +31508,7 @@
         <v>815</v>
       </c>
       <c r="D1055" s="133" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="E1055" s="130" t="s">
         <v>816</v>
@@ -31455,7 +31528,7 @@
         <v>815</v>
       </c>
       <c r="D1056" s="130" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="E1056" s="130" t="s">
         <v>816</v>
@@ -31475,7 +31548,7 @@
         <v>815</v>
       </c>
       <c r="D1057" s="130" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="E1057" s="130" t="s">
         <v>816</v>
@@ -31495,7 +31568,7 @@
         <v>815</v>
       </c>
       <c r="D1058" s="130" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="E1058" s="130" t="s">
         <v>816</v>
@@ -31515,7 +31588,7 @@
         <v>815</v>
       </c>
       <c r="D1059" s="130" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="E1059" s="130" t="s">
         <v>816</v>
@@ -31535,7 +31608,7 @@
         <v>815</v>
       </c>
       <c r="D1060" s="130" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="E1060" s="130" t="s">
         <v>816</v>
@@ -31555,7 +31628,7 @@
         <v>815</v>
       </c>
       <c r="D1061" s="130" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="E1061" s="130" t="s">
         <v>816</v>
@@ -31575,7 +31648,7 @@
         <v>815</v>
       </c>
       <c r="D1062" s="130" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="E1062" s="130" t="s">
         <v>816</v>
@@ -31595,7 +31668,7 @@
         <v>815</v>
       </c>
       <c r="D1063" s="130" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="E1063" s="130" t="s">
         <v>816</v>
@@ -31615,7 +31688,7 @@
         <v>815</v>
       </c>
       <c r="D1064" s="130" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="E1064" s="130" t="s">
         <v>816</v>
@@ -31635,7 +31708,7 @@
         <v>815</v>
       </c>
       <c r="D1065" s="130" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="E1065" s="130" t="s">
         <v>816</v>
@@ -31655,7 +31728,7 @@
         <v>815</v>
       </c>
       <c r="D1066" s="130" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="E1066" s="130" t="s">
         <v>816</v>
@@ -31675,7 +31748,7 @@
         <v>815</v>
       </c>
       <c r="D1067" s="130" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="E1067" s="130" t="s">
         <v>816</v>
@@ -31695,7 +31768,7 @@
         <v>815</v>
       </c>
       <c r="D1068" s="130" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="E1068" s="130" t="s">
         <v>816</v>
@@ -31715,7 +31788,7 @@
         <v>815</v>
       </c>
       <c r="D1069" s="130" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="E1069" s="130" t="s">
         <v>816</v>
@@ -31735,7 +31808,7 @@
         <v>815</v>
       </c>
       <c r="D1070" s="130" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="E1070" s="130" t="s">
         <v>816</v>
@@ -31755,7 +31828,7 @@
         <v>815</v>
       </c>
       <c r="D1071" s="130" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="E1071" s="130" t="s">
         <v>816</v>
@@ -31775,7 +31848,7 @@
         <v>815</v>
       </c>
       <c r="D1072" s="130" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E1072" s="130" t="s">
         <v>816</v>
@@ -31795,7 +31868,7 @@
         <v>815</v>
       </c>
       <c r="D1073" s="130" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="E1073" s="130" t="s">
         <v>816</v>
@@ -31815,7 +31888,7 @@
         <v>815</v>
       </c>
       <c r="D1074" s="130" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="E1074" s="130" t="s">
         <v>816</v>
@@ -31835,7 +31908,7 @@
         <v>815</v>
       </c>
       <c r="D1075" s="130" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="E1075" s="130" t="s">
         <v>816</v>
@@ -31855,7 +31928,7 @@
         <v>815</v>
       </c>
       <c r="D1076" s="130" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="E1076" s="130" t="s">
         <v>816</v>
@@ -31875,7 +31948,7 @@
         <v>815</v>
       </c>
       <c r="D1077" s="130" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="E1077" s="130" t="s">
         <v>816</v>
@@ -31895,7 +31968,7 @@
         <v>815</v>
       </c>
       <c r="D1078" s="130" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="E1078" s="130" t="s">
         <v>816</v>
@@ -31915,7 +31988,7 @@
         <v>815</v>
       </c>
       <c r="D1079" s="130" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="E1079" s="130" t="s">
         <v>816</v>
@@ -31935,7 +32008,7 @@
         <v>815</v>
       </c>
       <c r="D1080" s="130" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="E1080" s="130" t="s">
         <v>816</v>
@@ -31955,7 +32028,7 @@
         <v>815</v>
       </c>
       <c r="D1081" s="130" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="E1081" s="130" t="s">
         <v>816</v>
@@ -31975,7 +32048,7 @@
         <v>815</v>
       </c>
       <c r="D1082" s="130" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="E1082" s="130" t="s">
         <v>816</v>
@@ -31995,7 +32068,7 @@
         <v>815</v>
       </c>
       <c r="D1083" s="134" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="E1083" s="130" t="s">
         <v>816</v>
@@ -32015,7 +32088,7 @@
         <v>815</v>
       </c>
       <c r="D1084" s="130" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="E1084" s="130" t="s">
         <v>816</v>
@@ -32095,7 +32168,7 @@
         <v>815</v>
       </c>
       <c r="D1088" s="130" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="E1088" s="130" t="s">
         <v>816</v>
@@ -32115,7 +32188,7 @@
         <v>815</v>
       </c>
       <c r="D1089" s="130" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="E1089" s="130" t="s">
         <v>816</v>
@@ -32135,7 +32208,7 @@
         <v>815</v>
       </c>
       <c r="D1090" s="130" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="E1090" s="130" t="s">
         <v>816</v>
@@ -32155,7 +32228,7 @@
         <v>815</v>
       </c>
       <c r="D1091" s="130" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="E1091" s="130" t="s">
         <v>816</v>
@@ -32175,7 +32248,7 @@
         <v>815</v>
       </c>
       <c r="D1092" s="130" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="E1092" s="130" t="s">
         <v>816</v>
@@ -32195,7 +32268,7 @@
         <v>815</v>
       </c>
       <c r="D1093" s="130" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="E1093" s="130" t="s">
         <v>816</v>
@@ -32235,7 +32308,7 @@
         <v>815</v>
       </c>
       <c r="D1095" s="130" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="E1095" s="130" t="s">
         <v>816</v>
@@ -32255,7 +32328,7 @@
         <v>815</v>
       </c>
       <c r="D1096" s="130" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="E1096" s="130" t="s">
         <v>816</v>
@@ -32275,7 +32348,7 @@
         <v>815</v>
       </c>
       <c r="D1097" s="130" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="E1097" s="130" t="s">
         <v>816</v>
@@ -32295,7 +32368,7 @@
         <v>815</v>
       </c>
       <c r="D1098" s="130" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="E1098" s="130" t="s">
         <v>816</v>
@@ -32315,7 +32388,7 @@
         <v>815</v>
       </c>
       <c r="D1099" s="130" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="E1099" s="130" t="s">
         <v>816</v>
@@ -32335,7 +32408,7 @@
         <v>815</v>
       </c>
       <c r="D1100" s="130" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="E1100" s="130" t="s">
         <v>816</v>
@@ -32355,7 +32428,7 @@
         <v>815</v>
       </c>
       <c r="D1101" s="130" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E1101" s="130" t="s">
         <v>816</v>
@@ -32375,7 +32448,7 @@
         <v>815</v>
       </c>
       <c r="D1102" s="130" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="E1102" s="130" t="s">
         <v>816</v>
@@ -32395,7 +32468,7 @@
         <v>815</v>
       </c>
       <c r="D1103" s="130" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="E1103" s="130" t="s">
         <v>816</v>
@@ -32415,7 +32488,7 @@
         <v>815</v>
       </c>
       <c r="D1104" s="130" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="E1104" s="130" t="s">
         <v>816</v>
@@ -32435,7 +32508,7 @@
         <v>815</v>
       </c>
       <c r="D1105" s="130" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="E1105" s="130" t="s">
         <v>816</v>
@@ -32455,7 +32528,7 @@
         <v>815</v>
       </c>
       <c r="D1106" s="130" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="E1106" s="130" t="s">
         <v>816</v>
@@ -32475,7 +32548,7 @@
         <v>815</v>
       </c>
       <c r="D1107" s="130" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="E1107" s="130" t="s">
         <v>816</v>
@@ -32495,7 +32568,7 @@
         <v>815</v>
       </c>
       <c r="D1108" s="130" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="E1108" s="130" t="s">
         <v>816</v>
@@ -32515,7 +32588,7 @@
         <v>815</v>
       </c>
       <c r="D1109" s="130" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="E1109" s="130" t="s">
         <v>816</v>
@@ -32535,7 +32608,7 @@
         <v>815</v>
       </c>
       <c r="D1110" s="130" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="E1110" s="130" t="s">
         <v>816</v>
@@ -32555,7 +32628,7 @@
         <v>815</v>
       </c>
       <c r="D1111" s="130" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="E1111" s="130" t="s">
         <v>816</v>
@@ -32575,7 +32648,7 @@
         <v>815</v>
       </c>
       <c r="D1112" s="130" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="E1112" s="130" t="s">
         <v>816</v>
@@ -32595,7 +32668,7 @@
         <v>815</v>
       </c>
       <c r="D1113" s="130" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="E1113" s="130" t="s">
         <v>816</v>
@@ -32615,7 +32688,7 @@
         <v>815</v>
       </c>
       <c r="D1114" s="130" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="E1114" s="130" t="s">
         <v>816</v>
@@ -32635,7 +32708,7 @@
         <v>815</v>
       </c>
       <c r="D1115" s="130" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="E1115" s="130" t="s">
         <v>816</v>
@@ -32655,7 +32728,7 @@
         <v>815</v>
       </c>
       <c r="D1116" s="130" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="E1116" s="130" t="s">
         <v>816</v>
@@ -32675,7 +32748,7 @@
         <v>815</v>
       </c>
       <c r="D1117" s="130" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="E1117" s="130" t="s">
         <v>816</v>
@@ -32695,7 +32768,7 @@
         <v>815</v>
       </c>
       <c r="D1118" s="130" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="E1118" s="130" t="s">
         <v>816</v>
@@ -32715,7 +32788,7 @@
         <v>815</v>
       </c>
       <c r="D1119" s="130" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="E1119" s="130" t="s">
         <v>816</v>
@@ -32735,7 +32808,7 @@
         <v>815</v>
       </c>
       <c r="D1120" s="130" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1120" s="130" t="s">
         <v>816</v>
@@ -32755,7 +32828,7 @@
         <v>815</v>
       </c>
       <c r="D1121" s="130" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="E1121" s="130" t="s">
         <v>816</v>
@@ -32775,7 +32848,7 @@
         <v>815</v>
       </c>
       <c r="D1122" s="130" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="E1122" s="130" t="s">
         <v>816</v>
@@ -32795,7 +32868,7 @@
         <v>815</v>
       </c>
       <c r="D1123" s="130" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="E1123" s="130" t="s">
         <v>816</v>
@@ -32815,7 +32888,7 @@
         <v>815</v>
       </c>
       <c r="D1124" s="130" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="E1124" s="130" t="s">
         <v>816</v>
@@ -32835,7 +32908,7 @@
         <v>815</v>
       </c>
       <c r="D1125" s="130" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="E1125" s="130" t="s">
         <v>816</v>
@@ -32855,7 +32928,7 @@
         <v>815</v>
       </c>
       <c r="D1126" s="130" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="E1126" s="130" t="s">
         <v>816</v>
@@ -32872,10 +32945,10 @@
         <v>21032</v>
       </c>
       <c r="C1127" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D1127" s="130" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="E1127" s="133" t="s">
         <v>816</v>
@@ -32892,10 +32965,10 @@
         <v>21032</v>
       </c>
       <c r="C1128" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D1128" s="130" t="s">
         <v>2010</v>
-      </c>
-      <c r="D1128" s="130" t="s">
-        <v>2011</v>
       </c>
       <c r="E1128" s="133" t="s">
         <v>816</v>
@@ -32912,10 +32985,10 @@
         <v>23032</v>
       </c>
       <c r="C1129" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D1129" s="130" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="E1129" s="133" t="s">
         <v>816</v>
@@ -32932,10 +33005,10 @@
         <v>23032</v>
       </c>
       <c r="C1130" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D1130" s="130" t="s">
         <v>2013</v>
-      </c>
-      <c r="D1130" s="130" t="s">
-        <v>2014</v>
       </c>
       <c r="E1130" s="133" t="s">
         <v>816</v>
@@ -32955,7 +33028,7 @@
         <v>815</v>
       </c>
       <c r="D1131" s="130" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1131" s="130" t="s">
         <v>816</v>
@@ -32975,7 +33048,7 @@
         <v>815</v>
       </c>
       <c r="D1132" s="130" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E1132" s="130" t="s">
         <v>816</v>
@@ -32995,7 +33068,7 @@
         <v>815</v>
       </c>
       <c r="D1133" s="130" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E1133" s="130" t="s">
         <v>816</v>
@@ -33015,7 +33088,7 @@
         <v>815</v>
       </c>
       <c r="D1134" s="130" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E1134" s="130" t="s">
         <v>816</v>
@@ -33035,12 +33108,492 @@
         <v>815</v>
       </c>
       <c r="D1135" s="130" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E1135" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1135" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:6">
+      <c r="A1136">
+        <v>900909</v>
+      </c>
+      <c r="B1136" s="2">
+        <v>90909</v>
+      </c>
+      <c r="C1136" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1136" s="130" t="s">
         <v>2029</v>
       </c>
-      <c r="E1135" s="130" t="s">
-        <v>816</v>
-      </c>
-      <c r="F1135" s="130" t="s">
+      <c r="E1136" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1136" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:6">
+      <c r="A1137">
+        <v>900910</v>
+      </c>
+      <c r="B1137" s="2">
+        <v>90910</v>
+      </c>
+      <c r="C1137" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1137" s="130" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E1137" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1137" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:6">
+      <c r="A1138">
+        <v>900911</v>
+      </c>
+      <c r="B1138" s="2">
+        <v>90911</v>
+      </c>
+      <c r="C1138" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1138" s="130" t="s">
+        <v>2031</v>
+      </c>
+      <c r="E1138" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1138" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:6">
+      <c r="A1139">
+        <v>900912</v>
+      </c>
+      <c r="B1139" s="2">
+        <v>90912</v>
+      </c>
+      <c r="C1139" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1139" s="130" t="s">
+        <v>2032</v>
+      </c>
+      <c r="E1139" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1139" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:6">
+      <c r="A1140">
+        <v>900913</v>
+      </c>
+      <c r="B1140" s="2">
+        <v>90913</v>
+      </c>
+      <c r="C1140" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1140" s="130" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E1140" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1140" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:6">
+      <c r="A1141">
+        <v>900914</v>
+      </c>
+      <c r="B1141" s="2">
+        <v>90914</v>
+      </c>
+      <c r="C1141" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1141" s="130" t="s">
+        <v>2034</v>
+      </c>
+      <c r="E1141" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1141" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:6">
+      <c r="A1142">
+        <v>900915</v>
+      </c>
+      <c r="B1142" s="2">
+        <v>90915</v>
+      </c>
+      <c r="C1142" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1142" s="130" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E1142" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1142" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:6">
+      <c r="A1143">
+        <v>900916</v>
+      </c>
+      <c r="B1143" s="2">
+        <v>90916</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1143" s="130" t="s">
+        <v>2037</v>
+      </c>
+      <c r="E1143" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1143" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:6">
+      <c r="A1144">
+        <v>900917</v>
+      </c>
+      <c r="B1144" s="2">
+        <v>90917</v>
+      </c>
+      <c r="C1144" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1144" s="130" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E1144" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1144" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:6">
+      <c r="A1145">
+        <v>900918</v>
+      </c>
+      <c r="B1145" s="2">
+        <v>90918</v>
+      </c>
+      <c r="C1145" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1145" s="130" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E1145" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1145" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:6">
+      <c r="A1146">
+        <v>900919</v>
+      </c>
+      <c r="B1146" s="2">
+        <v>90919</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1146" s="130" t="s">
+        <v>2040</v>
+      </c>
+      <c r="E1146" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1146" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:6">
+      <c r="A1147">
+        <v>900920</v>
+      </c>
+      <c r="B1147" s="2">
+        <v>90920</v>
+      </c>
+      <c r="C1147" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1147" s="130" t="s">
+        <v>2041</v>
+      </c>
+      <c r="E1147" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1147" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:6">
+      <c r="A1148">
+        <v>900921</v>
+      </c>
+      <c r="B1148" s="2">
+        <v>90921</v>
+      </c>
+      <c r="C1148" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1148" s="130" t="s">
+        <v>2042</v>
+      </c>
+      <c r="E1148" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1148" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:6">
+      <c r="A1149">
+        <v>900922</v>
+      </c>
+      <c r="B1149" s="2">
+        <v>90922</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1149" s="130" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E1149" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1149" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:6">
+      <c r="A1150">
+        <v>900923</v>
+      </c>
+      <c r="B1150" s="2">
+        <v>90923</v>
+      </c>
+      <c r="C1150" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1150" s="130" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E1150" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1150" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:6">
+      <c r="A1151">
+        <v>900924</v>
+      </c>
+      <c r="B1151" s="2">
+        <v>90924</v>
+      </c>
+      <c r="C1151" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1151" s="130" t="s">
+        <v>2045</v>
+      </c>
+      <c r="E1151" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1151" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:6">
+      <c r="A1152">
+        <v>900925</v>
+      </c>
+      <c r="B1152" s="2">
+        <v>90925</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1152" s="130" t="s">
+        <v>2046</v>
+      </c>
+      <c r="E1152" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1152" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:6">
+      <c r="A1153">
+        <v>900926</v>
+      </c>
+      <c r="B1153" s="2">
+        <v>90926</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1153" s="130" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E1153" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1153" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:6">
+      <c r="A1154">
+        <v>900927</v>
+      </c>
+      <c r="B1154" s="2">
+        <v>90927</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1154" s="130" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1154" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1154" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:6">
+      <c r="A1155">
+        <v>900928</v>
+      </c>
+      <c r="B1155" s="2">
+        <v>90928</v>
+      </c>
+      <c r="C1155" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1155" s="130" t="s">
+        <v>2049</v>
+      </c>
+      <c r="E1155" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1155" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:6">
+      <c r="A1156">
+        <v>900929</v>
+      </c>
+      <c r="B1156" s="2">
+        <v>90929</v>
+      </c>
+      <c r="C1156" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1156" s="130" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E1156" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1156" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:6">
+      <c r="A1157">
+        <v>900930</v>
+      </c>
+      <c r="B1157" s="2">
+        <v>90930</v>
+      </c>
+      <c r="C1157" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1157" s="130" t="s">
+        <v>2051</v>
+      </c>
+      <c r="E1157" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1157" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:6">
+      <c r="A1158">
+        <v>900931</v>
+      </c>
+      <c r="B1158" s="2">
+        <v>90931</v>
+      </c>
+      <c r="C1158" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1158" s="130" t="s">
+        <v>2052</v>
+      </c>
+      <c r="E1158" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1158" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:6">
+      <c r="A1159">
+        <v>900932</v>
+      </c>
+      <c r="B1159" s="2">
+        <v>90932</v>
+      </c>
+      <c r="C1159" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1159" s="130" t="s">
+        <v>2053</v>
+      </c>
+      <c r="E1159" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1159" s="130" t="s">
         <v>816</v>
       </c>
     </row>
@@ -34965,10 +35518,10 @@
       <c r="B2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
       <c r="G2" s="163"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -34978,10 +35531,10 @@
       <c r="M2" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="149"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="147"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
       <c r="T2" s="11"/>
@@ -34989,10 +35542,10 @@
       <c r="V2" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="W2" s="144"/>
-      <c r="X2" s="144"/>
-      <c r="Y2" s="144"/>
-      <c r="Z2" s="149"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="146"/>
+      <c r="Y2" s="146"/>
+      <c r="Z2" s="147"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
       <c r="AC2" s="10"/>
@@ -35111,10 +35664,10 @@
       <c r="V5" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="W5" s="144"/>
-      <c r="X5" s="144"/>
-      <c r="Y5" s="144"/>
-      <c r="Z5" s="149"/>
+      <c r="W5" s="146"/>
+      <c r="X5" s="146"/>
+      <c r="Y5" s="146"/>
+      <c r="Z5" s="147"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="10"/>
@@ -35160,10 +35713,10 @@
       <c r="B7" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="144"/>
-      <c r="D7" s="144"/>
-      <c r="E7" s="144"/>
-      <c r="F7" s="149"/>
+      <c r="C7" s="146"/>
+      <c r="D7" s="146"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="147"/>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -35172,10 +35725,10 @@
       <c r="L7" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="144"/>
-      <c r="N7" s="144"/>
-      <c r="O7" s="144"/>
-      <c r="P7" s="149"/>
+      <c r="M7" s="146"/>
+      <c r="N7" s="146"/>
+      <c r="O7" s="146"/>
+      <c r="P7" s="147"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
@@ -35384,10 +35937,10 @@
       <c r="AB14" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="AC14" s="144"/>
-      <c r="AD14" s="144"/>
-      <c r="AE14" s="144"/>
-      <c r="AF14" s="149"/>
+      <c r="AC14" s="146"/>
+      <c r="AD14" s="146"/>
+      <c r="AE14" s="146"/>
+      <c r="AF14" s="147"/>
       <c r="AG14" s="100"/>
       <c r="AH14" s="45"/>
       <c r="AI14" s="12"/>
@@ -35461,10 +36014,10 @@
       <c r="AB17" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="AC17" s="144"/>
-      <c r="AD17" s="144"/>
-      <c r="AE17" s="144"/>
-      <c r="AF17" s="149"/>
+      <c r="AC17" s="146"/>
+      <c r="AD17" s="146"/>
+      <c r="AE17" s="146"/>
+      <c r="AF17" s="147"/>
       <c r="AG17" s="102"/>
       <c r="AH17" s="38"/>
       <c r="AI17" s="10"/>
@@ -35582,10 +36135,10 @@
       <c r="AB21" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="AC21" s="144"/>
-      <c r="AD21" s="144"/>
-      <c r="AE21" s="144"/>
-      <c r="AF21" s="149"/>
+      <c r="AC21" s="146"/>
+      <c r="AD21" s="146"/>
+      <c r="AE21" s="146"/>
+      <c r="AF21" s="147"/>
       <c r="AG21" s="116"/>
       <c r="AH21" s="117"/>
     </row>
@@ -36390,7 +36943,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -36571,24 +37124,24 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B23">
         <v>0.05</v>
       </c>
       <c r="C23" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B24">
         <v>5.5</v>
       </c>
       <c r="C24" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
   </sheetData>
@@ -42205,10 +42758,10 @@
         <v>11032</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>2005</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>2006</v>
       </c>
       <c r="D91" s="2">
         <v>21032</v>
@@ -42267,10 +42820,10 @@
         <v>13032</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>2007</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>2008</v>
       </c>
       <c r="D92" s="2">
         <v>23032</v>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BB3913-FD7D-4A02-AAD7-0D8E3308EAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBF2F06-1097-4685-9A42-C0AC5C5204CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="570" windowWidth="18900" windowHeight="13410" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5790" yWindow="1035" windowWidth="18660" windowHeight="13995" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9798" uniqueCount="7731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9846" uniqueCount="7755">
   <si>
     <t>Upgrade_Table</t>
   </si>
@@ -26579,6 +26579,94 @@
   </si>
   <si>
     <t>{0} готово! Поставь на Мировое древо в разделе "Украшение"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>균사 트리 강화</t>
+  </si>
+  <si>
+    <t>날씨</t>
+  </si>
+  <si>
+    <t>보스 도전 버튼</t>
+  </si>
+  <si>
+    <t>새 기능이 열렸어요: {0}</t>
+  </si>
+  <si>
+    <t>수확기를 잡고 아래로 당겼다 놓으면 버섯을 향해 날아가요!</t>
+  </si>
+  <si>
+    <t>첫 강화를 사 보세요! 밝게 빛나는 노드를 누르세요</t>
+  </si>
+  <si>
+    <t>강해졌어요! 다시 수확하러 가 볼까요?</t>
+  </si>
+  <si>
+    <t>수확하러 가서 첫 스테이지를 마쳐 보세요!</t>
+  </si>
+  <si>
+    <t>Mycelium Tree Upgrades</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>菌糸ツリー強化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weather</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天気</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss Challenge Button</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ボス挑戦ボタン</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>New feature unlocked: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新しい機能が解放されました:{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grab the Harvester, pull it down, and let go to send it flying at the mushroom!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>収穫機をつかんで下に引いて離すと、キノコに向かって飛んでいくよ!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buy your first upgrade! Tap the glowing node</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>はじめての強化を買ってみよう!光っているノードを押してね</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You got stronger! Ready to go harvest again?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>強くなったね!もう一度収穫に行こうか?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Go harvest and clear the first stage!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>収穫に行って、最初のステージをクリアしよう!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -30704,7 +30792,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H1422"/>
+  <dimension ref="A1:H1430"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.75" style="2" bestFit="1" customWidth="1"/>
@@ -67396,6 +67484,214 @@
       </c>
       <c r="H1422" s="130" t="s">
         <v>7717</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:8">
+      <c r="A1423">
+        <v>901196</v>
+      </c>
+      <c r="B1423" s="2">
+        <v>91196</v>
+      </c>
+      <c r="C1423" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1423" s="130" t="s">
+        <v>7731</v>
+      </c>
+      <c r="E1423" s="130" t="s">
+        <v>7739</v>
+      </c>
+      <c r="F1423" s="130" t="s">
+        <v>7740</v>
+      </c>
+      <c r="G1423" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1423" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:8">
+      <c r="A1424">
+        <v>901197</v>
+      </c>
+      <c r="B1424" s="2">
+        <v>91197</v>
+      </c>
+      <c r="C1424" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1424" s="130" t="s">
+        <v>7732</v>
+      </c>
+      <c r="E1424" s="130" t="s">
+        <v>7741</v>
+      </c>
+      <c r="F1424" s="130" t="s">
+        <v>7742</v>
+      </c>
+      <c r="G1424" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1424" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:8">
+      <c r="A1425">
+        <v>901198</v>
+      </c>
+      <c r="B1425" s="2">
+        <v>91198</v>
+      </c>
+      <c r="C1425" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1425" s="130" t="s">
+        <v>7733</v>
+      </c>
+      <c r="E1425" s="130" t="s">
+        <v>7743</v>
+      </c>
+      <c r="F1425" s="130" t="s">
+        <v>7744</v>
+      </c>
+      <c r="G1425" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1425" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:8">
+      <c r="A1426">
+        <v>901199</v>
+      </c>
+      <c r="B1426" s="2">
+        <v>91199</v>
+      </c>
+      <c r="C1426" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1426" s="130" t="s">
+        <v>7734</v>
+      </c>
+      <c r="E1426" s="130" t="s">
+        <v>7745</v>
+      </c>
+      <c r="F1426" s="130" t="s">
+        <v>7746</v>
+      </c>
+      <c r="G1426" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1426" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:8">
+      <c r="A1427">
+        <v>901200</v>
+      </c>
+      <c r="B1427" s="2">
+        <v>91200</v>
+      </c>
+      <c r="C1427" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1427" s="130" t="s">
+        <v>7735</v>
+      </c>
+      <c r="E1427" s="130" t="s">
+        <v>7747</v>
+      </c>
+      <c r="F1427" s="130" t="s">
+        <v>7748</v>
+      </c>
+      <c r="G1427" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1427" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:8">
+      <c r="A1428">
+        <v>901201</v>
+      </c>
+      <c r="B1428" s="2">
+        <v>91201</v>
+      </c>
+      <c r="C1428" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1428" s="130" t="s">
+        <v>7736</v>
+      </c>
+      <c r="E1428" s="130" t="s">
+        <v>7749</v>
+      </c>
+      <c r="F1428" s="130" t="s">
+        <v>7750</v>
+      </c>
+      <c r="G1428" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1428" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:8">
+      <c r="A1429">
+        <v>901202</v>
+      </c>
+      <c r="B1429" s="2">
+        <v>91202</v>
+      </c>
+      <c r="C1429" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1429" s="130" t="s">
+        <v>7737</v>
+      </c>
+      <c r="E1429" s="130" t="s">
+        <v>7751</v>
+      </c>
+      <c r="F1429" s="130" t="s">
+        <v>7752</v>
+      </c>
+      <c r="G1429" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1429" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:8">
+      <c r="A1430">
+        <v>901203</v>
+      </c>
+      <c r="B1430" s="2">
+        <v>91203</v>
+      </c>
+      <c r="C1430" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1430" s="130" t="s">
+        <v>7738</v>
+      </c>
+      <c r="E1430" s="130" t="s">
+        <v>7753</v>
+      </c>
+      <c r="F1430" s="130" t="s">
+        <v>7754</v>
+      </c>
+      <c r="G1430" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1430" s="130" t="s">
+        <v>816</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBF2F06-1097-4685-9A42-C0AC5C5204CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A8BBAE-F033-478E-90D4-D4528F65E15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5790" yWindow="1035" windowWidth="18660" windowHeight="13995" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27552,46 +27552,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -27600,12 +27600,12 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -28073,29 +28073,29 @@
   <sheetData>
     <row r="1" spans="2:44" ht="12" customHeight="1"/>
     <row r="2" spans="2:44">
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="155"/>
-      <c r="Q2" s="155"/>
-      <c r="R2" s="155"/>
-      <c r="S2" s="155"/>
-      <c r="T2" s="155"/>
-      <c r="U2" s="155"/>
-      <c r="V2" s="156"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="157"/>
+      <c r="U2" s="157"/>
+      <c r="V2" s="158"/>
     </row>
     <row r="3" spans="2:44">
       <c r="B3" s="17"/>
@@ -28152,29 +28152,29 @@
       <c r="V4" s="14"/>
     </row>
     <row r="5" spans="2:44">
-      <c r="B5" s="154" t="s">
+      <c r="B5" s="156" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="155"/>
-      <c r="K5" s="155"/>
-      <c r="L5" s="155"/>
-      <c r="M5" s="155"/>
-      <c r="N5" s="155"/>
-      <c r="O5" s="155"/>
-      <c r="P5" s="155"/>
-      <c r="Q5" s="155"/>
-      <c r="R5" s="155"/>
-      <c r="S5" s="155"/>
-      <c r="T5" s="155"/>
-      <c r="U5" s="155"/>
-      <c r="V5" s="156"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="157"/>
+      <c r="G5" s="157"/>
+      <c r="H5" s="157"/>
+      <c r="I5" s="157"/>
+      <c r="J5" s="157"/>
+      <c r="K5" s="157"/>
+      <c r="L5" s="157"/>
+      <c r="M5" s="157"/>
+      <c r="N5" s="157"/>
+      <c r="O5" s="157"/>
+      <c r="P5" s="157"/>
+      <c r="Q5" s="157"/>
+      <c r="R5" s="157"/>
+      <c r="S5" s="157"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="157"/>
+      <c r="V5" s="158"/>
     </row>
     <row r="6" spans="2:44">
       <c r="B6" s="6"/>
@@ -28304,29 +28304,29 @@
     </row>
     <row r="10" spans="2:44" ht="8.1" customHeight="1"/>
     <row r="11" spans="2:44">
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="156" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155"/>
-      <c r="E11" s="155"/>
-      <c r="F11" s="155"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="155"/>
-      <c r="I11" s="155"/>
-      <c r="J11" s="155"/>
-      <c r="K11" s="155"/>
-      <c r="L11" s="155"/>
-      <c r="M11" s="155"/>
-      <c r="N11" s="155"/>
-      <c r="O11" s="155"/>
-      <c r="P11" s="155"/>
-      <c r="Q11" s="155"/>
-      <c r="R11" s="155"/>
-      <c r="S11" s="155"/>
-      <c r="T11" s="155"/>
-      <c r="U11" s="155"/>
-      <c r="V11" s="156"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="157"/>
+      <c r="F11" s="157"/>
+      <c r="G11" s="157"/>
+      <c r="H11" s="157"/>
+      <c r="I11" s="157"/>
+      <c r="J11" s="157"/>
+      <c r="K11" s="157"/>
+      <c r="L11" s="157"/>
+      <c r="M11" s="157"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="157"/>
+      <c r="Q11" s="157"/>
+      <c r="R11" s="157"/>
+      <c r="S11" s="157"/>
+      <c r="T11" s="157"/>
+      <c r="U11" s="157"/>
+      <c r="V11" s="158"/>
     </row>
     <row r="12" spans="2:44">
       <c r="B12" s="6"/>
@@ -28613,19 +28613,19 @@
       <c r="AF22" s="27"/>
     </row>
     <row r="23" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B23" s="157" t="s">
+      <c r="B23" s="159" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="144"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="143" t="s">
+      <c r="C23" s="146"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="146"/>
+      <c r="H23" s="161" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="144"/>
-      <c r="J23" s="144"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="146"/>
       <c r="K23" s="28" t="s">
         <v>68</v>
       </c>
@@ -28653,18 +28653,18 @@
     </row>
     <row r="24" spans="2:32" s="10" customFormat="1">
       <c r="B24" s="86"/>
-      <c r="C24" s="153" t="s">
+      <c r="C24" s="136" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="151"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
-      <c r="H24" s="150" t="s">
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="137"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="151"/>
-      <c r="J24" s="152"/>
+      <c r="I24" s="137"/>
+      <c r="J24" s="138"/>
       <c r="K24" s="34" t="s">
         <v>70</v>
       </c>
@@ -28692,14 +28692,14 @@
     </row>
     <row r="25" spans="2:32" s="10" customFormat="1">
       <c r="B25" s="22"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="140"/>
-      <c r="G25" s="141"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="140"/>
-      <c r="J25" s="141"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="139"/>
+      <c r="J25" s="140"/>
       <c r="K25" s="19" t="s">
         <v>49</v>
       </c>
@@ -28721,18 +28721,18 @@
     </row>
     <row r="26" spans="2:32" s="10" customFormat="1">
       <c r="B26" s="22"/>
-      <c r="C26" s="139" t="s">
+      <c r="C26" s="144" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="141"/>
-      <c r="H26" s="146" t="s">
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="140"/>
-      <c r="J26" s="141"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="140"/>
       <c r="K26" s="19" t="s">
         <v>74</v>
       </c>
@@ -28752,18 +28752,18 @@
     </row>
     <row r="27" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B27" s="22"/>
-      <c r="C27" s="139" t="s">
+      <c r="C27" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="140"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
-      <c r="G27" s="141"/>
-      <c r="H27" s="146" t="s">
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I27" s="140"/>
-      <c r="J27" s="141"/>
+      <c r="I27" s="139"/>
+      <c r="J27" s="140"/>
       <c r="K27" s="19" t="s">
         <v>75</v>
       </c>
@@ -28783,18 +28783,18 @@
     </row>
     <row r="28" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B28" s="22"/>
-      <c r="C28" s="139" t="s">
+      <c r="C28" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="140"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="141"/>
-      <c r="H28" s="146" t="s">
+      <c r="D28" s="139"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="139"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I28" s="140"/>
-      <c r="J28" s="141"/>
+      <c r="I28" s="139"/>
+      <c r="J28" s="140"/>
       <c r="K28" s="19" t="s">
         <v>77</v>
       </c>
@@ -28814,18 +28814,18 @@
     </row>
     <row r="29" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B29" s="22"/>
-      <c r="C29" s="139" t="s">
+      <c r="C29" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="140"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="140"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="146" t="s">
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I29" s="140"/>
-      <c r="J29" s="141"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="140"/>
       <c r="K29" s="19" t="s">
         <v>78</v>
       </c>
@@ -28845,18 +28845,18 @@
     </row>
     <row r="30" spans="2:32" s="10" customFormat="1">
       <c r="B30" s="22"/>
-      <c r="C30" s="139" t="s">
+      <c r="C30" s="144" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="140"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="140"/>
-      <c r="G30" s="141"/>
-      <c r="H30" s="146" t="s">
+      <c r="D30" s="139"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I30" s="140"/>
-      <c r="J30" s="141"/>
+      <c r="I30" s="139"/>
+      <c r="J30" s="140"/>
       <c r="K30" s="120" t="s">
         <v>421</v>
       </c>
@@ -28876,18 +28876,18 @@
     </row>
     <row r="31" spans="2:32" s="10" customFormat="1">
       <c r="B31" s="22"/>
-      <c r="C31" s="139" t="s">
+      <c r="C31" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="140"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="141"/>
-      <c r="H31" s="146" t="s">
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I31" s="140"/>
-      <c r="J31" s="141"/>
+      <c r="I31" s="139"/>
+      <c r="J31" s="140"/>
       <c r="K31" s="19" t="s">
         <v>80</v>
       </c>
@@ -28907,18 +28907,18 @@
     </row>
     <row r="32" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B32" s="75"/>
-      <c r="C32" s="145" t="s">
+      <c r="C32" s="160" t="s">
         <v>422</v>
       </c>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="138"/>
-      <c r="H32" s="136" t="s">
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
+      <c r="F32" s="149"/>
+      <c r="G32" s="150"/>
+      <c r="H32" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="137"/>
-      <c r="J32" s="138"/>
+      <c r="I32" s="149"/>
+      <c r="J32" s="150"/>
       <c r="K32" s="81" t="s">
         <v>82</v>
       </c>
@@ -28980,19 +28980,19 @@
       <c r="AF33" s="27"/>
     </row>
     <row r="34" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B34" s="148" t="s">
+      <c r="B34" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="144"/>
-      <c r="D34" s="144"/>
-      <c r="E34" s="144"/>
-      <c r="F34" s="144"/>
-      <c r="G34" s="149"/>
-      <c r="H34" s="148" t="s">
+      <c r="C34" s="146"/>
+      <c r="D34" s="146"/>
+      <c r="E34" s="146"/>
+      <c r="F34" s="146"/>
+      <c r="G34" s="147"/>
+      <c r="H34" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I34" s="144"/>
-      <c r="J34" s="149"/>
+      <c r="I34" s="146"/>
+      <c r="J34" s="147"/>
       <c r="K34" s="28" t="s">
         <v>68</v>
       </c>
@@ -29020,18 +29020,18 @@
     </row>
     <row r="35" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B35" s="86"/>
-      <c r="C35" s="153" t="s">
+      <c r="C35" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
-      <c r="G35" s="152"/>
-      <c r="H35" s="150" t="s">
+      <c r="D35" s="137"/>
+      <c r="E35" s="137"/>
+      <c r="F35" s="137"/>
+      <c r="G35" s="138"/>
+      <c r="H35" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I35" s="151"/>
-      <c r="J35" s="152"/>
+      <c r="I35" s="137"/>
+      <c r="J35" s="138"/>
       <c r="K35" s="34" t="s">
         <v>84</v>
       </c>
@@ -29059,18 +29059,18 @@
     </row>
     <row r="36" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B36" s="75"/>
-      <c r="C36" s="145" t="s">
+      <c r="C36" s="160" t="s">
         <v>423</v>
       </c>
-      <c r="D36" s="137"/>
-      <c r="E36" s="137"/>
-      <c r="F36" s="137"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="136" t="s">
+      <c r="D36" s="149"/>
+      <c r="E36" s="149"/>
+      <c r="F36" s="149"/>
+      <c r="G36" s="150"/>
+      <c r="H36" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="I36" s="137"/>
-      <c r="J36" s="138"/>
+      <c r="I36" s="149"/>
+      <c r="J36" s="150"/>
       <c r="K36" s="81" t="s">
         <v>85</v>
       </c>
@@ -29132,19 +29132,19 @@
       <c r="AF37" s="92"/>
     </row>
     <row r="38" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B38" s="148" t="s">
+      <c r="B38" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="144"/>
-      <c r="D38" s="144"/>
-      <c r="E38" s="144"/>
-      <c r="F38" s="144"/>
-      <c r="G38" s="149"/>
-      <c r="H38" s="148" t="s">
+      <c r="C38" s="146"/>
+      <c r="D38" s="146"/>
+      <c r="E38" s="146"/>
+      <c r="F38" s="146"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="144"/>
-      <c r="J38" s="149"/>
+      <c r="I38" s="146"/>
+      <c r="J38" s="147"/>
       <c r="K38" s="28" t="s">
         <v>68</v>
       </c>
@@ -29172,18 +29172,18 @@
     </row>
     <row r="39" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B39" s="21"/>
-      <c r="C39" s="139" t="s">
+      <c r="C39" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="140"/>
-      <c r="E39" s="140"/>
-      <c r="F39" s="140"/>
-      <c r="G39" s="141"/>
-      <c r="H39" s="146" t="s">
+      <c r="D39" s="139"/>
+      <c r="E39" s="139"/>
+      <c r="F39" s="139"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I39" s="140"/>
-      <c r="J39" s="141"/>
+      <c r="I39" s="139"/>
+      <c r="J39" s="140"/>
       <c r="K39" s="19" t="s">
         <v>86</v>
       </c>
@@ -29203,18 +29203,18 @@
     </row>
     <row r="40" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B40" s="22"/>
-      <c r="C40" s="139" t="s">
+      <c r="C40" s="144" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="140"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="140"/>
-      <c r="G40" s="141"/>
-      <c r="H40" s="146" t="s">
+      <c r="D40" s="139"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="139"/>
+      <c r="G40" s="140"/>
+      <c r="H40" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I40" s="140"/>
-      <c r="J40" s="141"/>
+      <c r="I40" s="139"/>
+      <c r="J40" s="140"/>
       <c r="K40" s="19" t="s">
         <v>88</v>
       </c>
@@ -29234,18 +29234,18 @@
     </row>
     <row r="41" spans="2:32" s="10" customFormat="1">
       <c r="B41" s="22"/>
-      <c r="C41" s="139" t="s">
+      <c r="C41" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="140"/>
-      <c r="E41" s="140"/>
-      <c r="F41" s="140"/>
-      <c r="G41" s="141"/>
-      <c r="H41" s="146" t="s">
+      <c r="D41" s="139"/>
+      <c r="E41" s="139"/>
+      <c r="F41" s="139"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="140"/>
-      <c r="J41" s="141"/>
+      <c r="I41" s="139"/>
+      <c r="J41" s="140"/>
       <c r="K41" s="19" t="s">
         <v>89</v>
       </c>
@@ -29265,18 +29265,18 @@
     </row>
     <row r="42" spans="2:32" s="10" customFormat="1">
       <c r="B42" s="22"/>
-      <c r="C42" s="139" t="s">
+      <c r="C42" s="144" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="140"/>
-      <c r="E42" s="140"/>
-      <c r="F42" s="140"/>
-      <c r="G42" s="141"/>
-      <c r="H42" s="146" t="s">
+      <c r="D42" s="139"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I42" s="140"/>
-      <c r="J42" s="141"/>
+      <c r="I42" s="139"/>
+      <c r="J42" s="140"/>
       <c r="K42" s="19" t="s">
         <v>91</v>
       </c>
@@ -29296,18 +29296,18 @@
     </row>
     <row r="43" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B43" s="75"/>
-      <c r="C43" s="142" t="s">
+      <c r="C43" s="152" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="137"/>
-      <c r="E43" s="137"/>
-      <c r="F43" s="137"/>
-      <c r="G43" s="138"/>
-      <c r="H43" s="136" t="s">
+      <c r="D43" s="149"/>
+      <c r="E43" s="149"/>
+      <c r="F43" s="149"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="137"/>
-      <c r="J43" s="138"/>
+      <c r="I43" s="149"/>
+      <c r="J43" s="150"/>
       <c r="K43" s="81" t="s">
         <v>92</v>
       </c>
@@ -29369,19 +29369,19 @@
       <c r="AF44" s="27"/>
     </row>
     <row r="45" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B45" s="148" t="s">
+      <c r="B45" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="144"/>
-      <c r="D45" s="144"/>
-      <c r="E45" s="144"/>
-      <c r="F45" s="144"/>
-      <c r="G45" s="149"/>
-      <c r="H45" s="159" t="s">
+      <c r="C45" s="146"/>
+      <c r="D45" s="146"/>
+      <c r="E45" s="146"/>
+      <c r="F45" s="146"/>
+      <c r="G45" s="147"/>
+      <c r="H45" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="I45" s="160"/>
-      <c r="J45" s="161"/>
+      <c r="I45" s="154"/>
+      <c r="J45" s="155"/>
       <c r="K45" s="83" t="s">
         <v>68</v>
       </c>
@@ -29409,18 +29409,18 @@
     </row>
     <row r="46" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B46" s="21"/>
-      <c r="C46" s="139" t="s">
+      <c r="C46" s="144" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="140"/>
-      <c r="E46" s="140"/>
-      <c r="F46" s="140"/>
-      <c r="G46" s="141"/>
-      <c r="H46" s="150" t="s">
+      <c r="D46" s="139"/>
+      <c r="E46" s="139"/>
+      <c r="F46" s="139"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="I46" s="151"/>
-      <c r="J46" s="152"/>
+      <c r="I46" s="137"/>
+      <c r="J46" s="138"/>
       <c r="K46" s="19" t="s">
         <v>93</v>
       </c>
@@ -29440,18 +29440,18 @@
     </row>
     <row r="47" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B47" s="22"/>
-      <c r="C47" s="139" t="s">
+      <c r="C47" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="140"/>
-      <c r="E47" s="140"/>
-      <c r="F47" s="140"/>
-      <c r="G47" s="141"/>
-      <c r="H47" s="146" t="s">
+      <c r="D47" s="139"/>
+      <c r="E47" s="139"/>
+      <c r="F47" s="139"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="141" t="s">
         <v>81</v>
       </c>
-      <c r="I47" s="140"/>
-      <c r="J47" s="141"/>
+      <c r="I47" s="139"/>
+      <c r="J47" s="140"/>
       <c r="K47" s="19" t="s">
         <v>95</v>
       </c>
@@ -29471,14 +29471,14 @@
     </row>
     <row r="48" spans="2:32" s="10" customFormat="1">
       <c r="B48" s="22"/>
-      <c r="C48" s="140"/>
-      <c r="D48" s="140"/>
-      <c r="E48" s="140"/>
-      <c r="F48" s="140"/>
-      <c r="G48" s="141"/>
-      <c r="H48" s="158"/>
-      <c r="I48" s="140"/>
-      <c r="J48" s="141"/>
+      <c r="C48" s="139"/>
+      <c r="D48" s="139"/>
+      <c r="E48" s="139"/>
+      <c r="F48" s="139"/>
+      <c r="G48" s="140"/>
+      <c r="H48" s="143"/>
+      <c r="I48" s="139"/>
+      <c r="J48" s="140"/>
       <c r="K48" s="19" t="s">
         <v>49</v>
       </c>
@@ -29500,14 +29500,14 @@
     </row>
     <row r="49" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B49" s="22"/>
-      <c r="C49" s="140"/>
-      <c r="D49" s="140"/>
-      <c r="E49" s="140"/>
-      <c r="F49" s="140"/>
-      <c r="G49" s="141"/>
-      <c r="H49" s="158"/>
-      <c r="I49" s="140"/>
-      <c r="J49" s="141"/>
+      <c r="C49" s="139"/>
+      <c r="D49" s="139"/>
+      <c r="E49" s="139"/>
+      <c r="F49" s="139"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="143"/>
+      <c r="I49" s="139"/>
+      <c r="J49" s="140"/>
       <c r="K49" s="19" t="s">
         <v>49</v>
       </c>
@@ -29564,19 +29564,19 @@
       <c r="AG50" s="92"/>
     </row>
     <row r="51" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B51" s="148" t="s">
+      <c r="B51" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="144"/>
-      <c r="D51" s="144"/>
-      <c r="E51" s="144"/>
-      <c r="F51" s="144"/>
-      <c r="G51" s="149"/>
-      <c r="H51" s="148" t="s">
+      <c r="C51" s="146"/>
+      <c r="D51" s="146"/>
+      <c r="E51" s="146"/>
+      <c r="F51" s="146"/>
+      <c r="G51" s="147"/>
+      <c r="H51" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I51" s="144"/>
-      <c r="J51" s="149"/>
+      <c r="I51" s="146"/>
+      <c r="J51" s="147"/>
       <c r="K51" s="28" t="s">
         <v>68</v>
       </c>
@@ -29605,18 +29605,18 @@
     </row>
     <row r="52" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B52" s="21"/>
-      <c r="C52" s="139" t="s">
+      <c r="C52" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="140"/>
-      <c r="E52" s="140"/>
-      <c r="F52" s="140"/>
-      <c r="G52" s="141"/>
-      <c r="H52" s="146" t="s">
+      <c r="D52" s="139"/>
+      <c r="E52" s="139"/>
+      <c r="F52" s="139"/>
+      <c r="G52" s="140"/>
+      <c r="H52" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I52" s="140"/>
-      <c r="J52" s="141"/>
+      <c r="I52" s="139"/>
+      <c r="J52" s="140"/>
       <c r="K52" s="19" t="s">
         <v>99</v>
       </c>
@@ -29636,18 +29636,18 @@
     </row>
     <row r="53" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B53" s="22"/>
-      <c r="C53" s="139" t="s">
+      <c r="C53" s="144" t="s">
         <v>100</v>
       </c>
-      <c r="D53" s="140"/>
-      <c r="E53" s="140"/>
-      <c r="F53" s="140"/>
-      <c r="G53" s="141"/>
-      <c r="H53" s="146" t="s">
+      <c r="D53" s="139"/>
+      <c r="E53" s="139"/>
+      <c r="F53" s="139"/>
+      <c r="G53" s="140"/>
+      <c r="H53" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I53" s="140"/>
-      <c r="J53" s="141"/>
+      <c r="I53" s="139"/>
+      <c r="J53" s="140"/>
       <c r="K53" s="19" t="s">
         <v>101</v>
       </c>
@@ -29667,18 +29667,18 @@
     </row>
     <row r="54" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B54" s="75"/>
-      <c r="C54" s="142" t="s">
+      <c r="C54" s="152" t="s">
         <v>102</v>
       </c>
-      <c r="D54" s="137"/>
-      <c r="E54" s="137"/>
-      <c r="F54" s="137"/>
-      <c r="G54" s="138"/>
-      <c r="H54" s="136" t="s">
+      <c r="D54" s="149"/>
+      <c r="E54" s="149"/>
+      <c r="F54" s="149"/>
+      <c r="G54" s="150"/>
+      <c r="H54" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I54" s="137"/>
-      <c r="J54" s="138"/>
+      <c r="I54" s="149"/>
+      <c r="J54" s="150"/>
       <c r="K54" s="81" t="s">
         <v>103</v>
       </c>
@@ -29742,19 +29742,19 @@
       <c r="AG55" s="92"/>
     </row>
     <row r="56" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B56" s="148" t="s">
+      <c r="B56" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="144"/>
-      <c r="D56" s="144"/>
-      <c r="E56" s="144"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="149"/>
-      <c r="H56" s="148" t="s">
+      <c r="C56" s="146"/>
+      <c r="D56" s="146"/>
+      <c r="E56" s="146"/>
+      <c r="F56" s="146"/>
+      <c r="G56" s="147"/>
+      <c r="H56" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I56" s="144"/>
-      <c r="J56" s="149"/>
+      <c r="I56" s="146"/>
+      <c r="J56" s="147"/>
       <c r="K56" s="28" t="s">
         <v>68</v>
       </c>
@@ -29783,18 +29783,18 @@
     </row>
     <row r="57" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B57" s="21"/>
-      <c r="C57" s="139" t="s">
+      <c r="C57" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="140"/>
-      <c r="E57" s="140"/>
-      <c r="F57" s="140"/>
-      <c r="G57" s="141"/>
-      <c r="H57" s="146" t="s">
+      <c r="D57" s="139"/>
+      <c r="E57" s="139"/>
+      <c r="F57" s="139"/>
+      <c r="G57" s="140"/>
+      <c r="H57" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I57" s="140"/>
-      <c r="J57" s="141"/>
+      <c r="I57" s="139"/>
+      <c r="J57" s="140"/>
       <c r="K57" s="19" t="s">
         <v>104</v>
       </c>
@@ -29814,18 +29814,18 @@
     </row>
     <row r="58" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B58" s="22"/>
-      <c r="C58" s="139" t="s">
+      <c r="C58" s="144" t="s">
         <v>105</v>
       </c>
-      <c r="D58" s="140"/>
-      <c r="E58" s="140"/>
-      <c r="F58" s="140"/>
-      <c r="G58" s="141"/>
-      <c r="H58" s="146" t="s">
+      <c r="D58" s="139"/>
+      <c r="E58" s="139"/>
+      <c r="F58" s="139"/>
+      <c r="G58" s="140"/>
+      <c r="H58" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I58" s="140"/>
-      <c r="J58" s="141"/>
+      <c r="I58" s="139"/>
+      <c r="J58" s="140"/>
       <c r="K58" s="19" t="s">
         <v>106</v>
       </c>
@@ -29845,18 +29845,18 @@
     </row>
     <row r="59" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B59" s="22"/>
-      <c r="C59" s="139" t="s">
+      <c r="C59" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="140"/>
-      <c r="E59" s="140"/>
-      <c r="F59" s="140"/>
-      <c r="G59" s="141"/>
-      <c r="H59" s="146" t="s">
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="140"/>
+      <c r="H59" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I59" s="140"/>
-      <c r="J59" s="141"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="140"/>
       <c r="K59" s="19" t="s">
         <v>107</v>
       </c>
@@ -29876,18 +29876,18 @@
     </row>
     <row r="60" spans="2:33" s="10" customFormat="1">
       <c r="B60" s="22"/>
-      <c r="C60" s="139" t="s">
+      <c r="C60" s="144" t="s">
         <v>108</v>
       </c>
-      <c r="D60" s="140"/>
-      <c r="E60" s="140"/>
-      <c r="F60" s="140"/>
-      <c r="G60" s="141"/>
-      <c r="H60" s="146" t="s">
+      <c r="D60" s="139"/>
+      <c r="E60" s="139"/>
+      <c r="F60" s="139"/>
+      <c r="G60" s="140"/>
+      <c r="H60" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I60" s="140"/>
-      <c r="J60" s="141"/>
+      <c r="I60" s="139"/>
+      <c r="J60" s="140"/>
       <c r="K60" s="19" t="s">
         <v>109</v>
       </c>
@@ -29907,18 +29907,18 @@
     </row>
     <row r="61" spans="2:33" s="10" customFormat="1">
       <c r="B61" s="22"/>
-      <c r="C61" s="139" t="s">
+      <c r="C61" s="144" t="s">
         <v>110</v>
       </c>
-      <c r="D61" s="140"/>
-      <c r="E61" s="140"/>
-      <c r="F61" s="140"/>
-      <c r="G61" s="141"/>
-      <c r="H61" s="146" t="s">
+      <c r="D61" s="139"/>
+      <c r="E61" s="139"/>
+      <c r="F61" s="139"/>
+      <c r="G61" s="140"/>
+      <c r="H61" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I61" s="140"/>
-      <c r="J61" s="141"/>
+      <c r="I61" s="139"/>
+      <c r="J61" s="140"/>
       <c r="K61" s="19" t="s">
         <v>111</v>
       </c>
@@ -29938,18 +29938,18 @@
     </row>
     <row r="62" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B62" s="75"/>
-      <c r="C62" s="142" t="s">
+      <c r="C62" s="152" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="137"/>
-      <c r="E62" s="137"/>
-      <c r="F62" s="137"/>
-      <c r="G62" s="138"/>
-      <c r="H62" s="136" t="s">
+      <c r="D62" s="149"/>
+      <c r="E62" s="149"/>
+      <c r="F62" s="149"/>
+      <c r="G62" s="150"/>
+      <c r="H62" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I62" s="137"/>
-      <c r="J62" s="138"/>
+      <c r="I62" s="149"/>
+      <c r="J62" s="150"/>
       <c r="K62" s="81" t="s">
         <v>113</v>
       </c>
@@ -30013,19 +30013,19 @@
       <c r="AG63" s="92"/>
     </row>
     <row r="64" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B64" s="148" t="s">
+      <c r="B64" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="144"/>
-      <c r="D64" s="144"/>
-      <c r="E64" s="144"/>
-      <c r="F64" s="144"/>
-      <c r="G64" s="149"/>
-      <c r="H64" s="148" t="s">
+      <c r="C64" s="146"/>
+      <c r="D64" s="146"/>
+      <c r="E64" s="146"/>
+      <c r="F64" s="146"/>
+      <c r="G64" s="147"/>
+      <c r="H64" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I64" s="144"/>
-      <c r="J64" s="149"/>
+      <c r="I64" s="146"/>
+      <c r="J64" s="147"/>
       <c r="K64" s="83" t="s">
         <v>68</v>
       </c>
@@ -30054,18 +30054,18 @@
     </row>
     <row r="65" spans="2:33">
       <c r="B65" s="21"/>
-      <c r="C65" s="139" t="s">
+      <c r="C65" s="144" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="147"/>
-      <c r="E65" s="147"/>
-      <c r="F65" s="147"/>
-      <c r="G65" s="141"/>
-      <c r="H65" s="150" t="s">
+      <c r="D65" s="151"/>
+      <c r="E65" s="151"/>
+      <c r="F65" s="151"/>
+      <c r="G65" s="140"/>
+      <c r="H65" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I65" s="151"/>
-      <c r="J65" s="152"/>
+      <c r="I65" s="137"/>
+      <c r="J65" s="138"/>
       <c r="K65" s="19" t="s">
         <v>115</v>
       </c>
@@ -30085,18 +30085,18 @@
     </row>
     <row r="66" spans="2:33">
       <c r="B66" s="22"/>
-      <c r="C66" s="139" t="s">
+      <c r="C66" s="144" t="s">
         <v>116</v>
       </c>
-      <c r="D66" s="147"/>
-      <c r="E66" s="147"/>
-      <c r="F66" s="147"/>
-      <c r="G66" s="141"/>
-      <c r="H66" s="146" t="s">
+      <c r="D66" s="151"/>
+      <c r="E66" s="151"/>
+      <c r="F66" s="151"/>
+      <c r="G66" s="140"/>
+      <c r="H66" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I66" s="147"/>
-      <c r="J66" s="141"/>
+      <c r="I66" s="151"/>
+      <c r="J66" s="140"/>
       <c r="K66" s="19" t="s">
         <v>117</v>
       </c>
@@ -30116,18 +30116,18 @@
     </row>
     <row r="67" spans="2:33">
       <c r="B67" s="22"/>
-      <c r="C67" s="139" t="s">
+      <c r="C67" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D67" s="147"/>
-      <c r="E67" s="147"/>
-      <c r="F67" s="147"/>
-      <c r="G67" s="141"/>
-      <c r="H67" s="146" t="s">
+      <c r="D67" s="151"/>
+      <c r="E67" s="151"/>
+      <c r="F67" s="151"/>
+      <c r="G67" s="140"/>
+      <c r="H67" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I67" s="147"/>
-      <c r="J67" s="141"/>
+      <c r="I67" s="151"/>
+      <c r="J67" s="140"/>
       <c r="K67" s="19" t="s">
         <v>118</v>
       </c>
@@ -30147,18 +30147,18 @@
     </row>
     <row r="68" spans="2:33">
       <c r="B68" s="22"/>
-      <c r="C68" s="139" t="s">
+      <c r="C68" s="144" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="147"/>
-      <c r="E68" s="147"/>
-      <c r="F68" s="147"/>
-      <c r="G68" s="141"/>
-      <c r="H68" s="146" t="s">
+      <c r="D68" s="151"/>
+      <c r="E68" s="151"/>
+      <c r="F68" s="151"/>
+      <c r="G68" s="140"/>
+      <c r="H68" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I68" s="147"/>
-      <c r="J68" s="141"/>
+      <c r="I68" s="151"/>
+      <c r="J68" s="140"/>
       <c r="K68" s="19" t="s">
         <v>120</v>
       </c>
@@ -30178,18 +30178,18 @@
     </row>
     <row r="69" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B69" s="75"/>
-      <c r="C69" s="142" t="s">
+      <c r="C69" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="D69" s="137"/>
-      <c r="E69" s="137"/>
-      <c r="F69" s="137"/>
-      <c r="G69" s="138"/>
-      <c r="H69" s="136" t="s">
+      <c r="D69" s="149"/>
+      <c r="E69" s="149"/>
+      <c r="F69" s="149"/>
+      <c r="G69" s="150"/>
+      <c r="H69" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="I69" s="137"/>
-      <c r="J69" s="138"/>
+      <c r="I69" s="149"/>
+      <c r="J69" s="150"/>
       <c r="K69" s="81" t="s">
         <v>122</v>
       </c>
@@ -30253,19 +30253,19 @@
       <c r="AG70" s="94"/>
     </row>
     <row r="71" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B71" s="148" t="s">
+      <c r="B71" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="144"/>
-      <c r="D71" s="144"/>
-      <c r="E71" s="144"/>
-      <c r="F71" s="144"/>
-      <c r="G71" s="149"/>
-      <c r="H71" s="148" t="s">
+      <c r="C71" s="146"/>
+      <c r="D71" s="146"/>
+      <c r="E71" s="146"/>
+      <c r="F71" s="146"/>
+      <c r="G71" s="147"/>
+      <c r="H71" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I71" s="144"/>
-      <c r="J71" s="149"/>
+      <c r="I71" s="146"/>
+      <c r="J71" s="147"/>
       <c r="K71" s="83" t="s">
         <v>68</v>
       </c>
@@ -30294,18 +30294,18 @@
     </row>
     <row r="72" spans="2:33">
       <c r="B72" s="21"/>
-      <c r="C72" s="139" t="s">
+      <c r="C72" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="147"/>
-      <c r="E72" s="147"/>
-      <c r="F72" s="147"/>
-      <c r="G72" s="141"/>
-      <c r="H72" s="150" t="s">
+      <c r="D72" s="151"/>
+      <c r="E72" s="151"/>
+      <c r="F72" s="151"/>
+      <c r="G72" s="140"/>
+      <c r="H72" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I72" s="151"/>
-      <c r="J72" s="152"/>
+      <c r="I72" s="137"/>
+      <c r="J72" s="138"/>
       <c r="K72" s="19" t="s">
         <v>123</v>
       </c>
@@ -30325,18 +30325,18 @@
     </row>
     <row r="73" spans="2:33">
       <c r="B73" s="22"/>
-      <c r="C73" s="139" t="s">
+      <c r="C73" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D73" s="147"/>
-      <c r="E73" s="147"/>
-      <c r="F73" s="147"/>
-      <c r="G73" s="141"/>
-      <c r="H73" s="146" t="s">
+      <c r="D73" s="151"/>
+      <c r="E73" s="151"/>
+      <c r="F73" s="151"/>
+      <c r="G73" s="140"/>
+      <c r="H73" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I73" s="147"/>
-      <c r="J73" s="141"/>
+      <c r="I73" s="151"/>
+      <c r="J73" s="140"/>
       <c r="K73" s="19" t="s">
         <v>124</v>
       </c>
@@ -30356,18 +30356,18 @@
     </row>
     <row r="74" spans="2:33">
       <c r="B74" s="22"/>
-      <c r="C74" s="139" t="s">
+      <c r="C74" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="D74" s="147"/>
-      <c r="E74" s="147"/>
-      <c r="F74" s="147"/>
-      <c r="G74" s="141"/>
-      <c r="H74" s="146" t="s">
+      <c r="D74" s="151"/>
+      <c r="E74" s="151"/>
+      <c r="F74" s="151"/>
+      <c r="G74" s="140"/>
+      <c r="H74" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I74" s="147"/>
-      <c r="J74" s="141"/>
+      <c r="I74" s="151"/>
+      <c r="J74" s="140"/>
       <c r="K74" s="19" t="s">
         <v>126</v>
       </c>
@@ -30387,18 +30387,18 @@
     </row>
     <row r="75" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B75" s="75"/>
-      <c r="C75" s="142" t="s">
+      <c r="C75" s="152" t="s">
         <v>127</v>
       </c>
-      <c r="D75" s="137"/>
-      <c r="E75" s="137"/>
-      <c r="F75" s="137"/>
-      <c r="G75" s="138"/>
-      <c r="H75" s="136" t="s">
+      <c r="D75" s="149"/>
+      <c r="E75" s="149"/>
+      <c r="F75" s="149"/>
+      <c r="G75" s="150"/>
+      <c r="H75" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I75" s="137"/>
-      <c r="J75" s="138"/>
+      <c r="I75" s="149"/>
+      <c r="J75" s="150"/>
       <c r="K75" s="81" t="s">
         <v>128</v>
       </c>
@@ -30462,19 +30462,19 @@
       <c r="AG76" s="94"/>
     </row>
     <row r="77" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B77" s="148" t="s">
+      <c r="B77" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C77" s="144"/>
-      <c r="D77" s="144"/>
-      <c r="E77" s="144"/>
-      <c r="F77" s="144"/>
-      <c r="G77" s="149"/>
-      <c r="H77" s="148" t="s">
+      <c r="C77" s="146"/>
+      <c r="D77" s="146"/>
+      <c r="E77" s="146"/>
+      <c r="F77" s="146"/>
+      <c r="G77" s="147"/>
+      <c r="H77" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I77" s="144"/>
-      <c r="J77" s="149"/>
+      <c r="I77" s="146"/>
+      <c r="J77" s="147"/>
       <c r="K77" s="83" t="s">
         <v>68</v>
       </c>
@@ -30503,18 +30503,18 @@
     </row>
     <row r="78" spans="2:33">
       <c r="B78" s="21"/>
-      <c r="C78" s="139" t="s">
+      <c r="C78" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="147"/>
-      <c r="E78" s="147"/>
-      <c r="F78" s="147"/>
-      <c r="G78" s="141"/>
-      <c r="H78" s="150" t="s">
+      <c r="D78" s="151"/>
+      <c r="E78" s="151"/>
+      <c r="F78" s="151"/>
+      <c r="G78" s="140"/>
+      <c r="H78" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="I78" s="151"/>
-      <c r="J78" s="152"/>
+      <c r="I78" s="137"/>
+      <c r="J78" s="138"/>
       <c r="K78" s="19" t="s">
         <v>129</v>
       </c>
@@ -30534,18 +30534,18 @@
     </row>
     <row r="79" spans="2:33">
       <c r="B79" s="22"/>
-      <c r="C79" s="139" t="s">
+      <c r="C79" s="144" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="147"/>
-      <c r="E79" s="147"/>
-      <c r="F79" s="147"/>
-      <c r="G79" s="141"/>
-      <c r="H79" s="146" t="s">
+      <c r="D79" s="151"/>
+      <c r="E79" s="151"/>
+      <c r="F79" s="151"/>
+      <c r="G79" s="140"/>
+      <c r="H79" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="I79" s="147"/>
-      <c r="J79" s="141"/>
+      <c r="I79" s="151"/>
+      <c r="J79" s="140"/>
       <c r="K79" s="19" t="s">
         <v>132</v>
       </c>
@@ -30565,18 +30565,18 @@
     </row>
     <row r="80" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B80" s="75"/>
-      <c r="C80" s="142" t="s">
+      <c r="C80" s="152" t="s">
         <v>133</v>
       </c>
-      <c r="D80" s="137"/>
-      <c r="E80" s="137"/>
-      <c r="F80" s="137"/>
-      <c r="G80" s="138"/>
-      <c r="H80" s="136" t="s">
+      <c r="D80" s="149"/>
+      <c r="E80" s="149"/>
+      <c r="F80" s="149"/>
+      <c r="G80" s="150"/>
+      <c r="H80" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I80" s="137"/>
-      <c r="J80" s="138"/>
+      <c r="I80" s="149"/>
+      <c r="J80" s="150"/>
       <c r="K80" s="81" t="s">
         <v>134</v>
       </c>
@@ -30687,12 +30687,81 @@
     </row>
   </sheetData>
   <mergeCells count="97">
-    <mergeCell ref="C24:G25"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="H24:J25"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="H65:J65"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C47:G49"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="B11:V11"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B5:V5"/>
+    <mergeCell ref="H47:J49"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="H40:J40"/>
     <mergeCell ref="H51:J51"/>
     <mergeCell ref="H69:J69"/>
     <mergeCell ref="C29:G29"/>
@@ -30709,81 +30778,12 @@
     <mergeCell ref="C62:G62"/>
     <mergeCell ref="H32:J32"/>
     <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B2:V2"/>
-    <mergeCell ref="B11:V11"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B5:V5"/>
-    <mergeCell ref="H47:J49"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C47:G49"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="H79:J79"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H78:J78"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="H65:J65"/>
-    <mergeCell ref="H71:J71"/>
-    <mergeCell ref="H75:J75"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="C24:G25"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="H24:J25"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:J26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -69615,10 +69615,10 @@
       <c r="B2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
       <c r="G2" s="163"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -69628,10 +69628,10 @@
       <c r="M2" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="149"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="147"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
       <c r="T2" s="11"/>
@@ -69639,10 +69639,10 @@
       <c r="V2" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="W2" s="144"/>
-      <c r="X2" s="144"/>
-      <c r="Y2" s="144"/>
-      <c r="Z2" s="149"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="146"/>
+      <c r="Y2" s="146"/>
+      <c r="Z2" s="147"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
       <c r="AC2" s="10"/>
@@ -69761,10 +69761,10 @@
       <c r="V5" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="W5" s="144"/>
-      <c r="X5" s="144"/>
-      <c r="Y5" s="144"/>
-      <c r="Z5" s="149"/>
+      <c r="W5" s="146"/>
+      <c r="X5" s="146"/>
+      <c r="Y5" s="146"/>
+      <c r="Z5" s="147"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="10"/>
@@ -69810,10 +69810,10 @@
       <c r="B7" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="144"/>
-      <c r="D7" s="144"/>
-      <c r="E7" s="144"/>
-      <c r="F7" s="149"/>
+      <c r="C7" s="146"/>
+      <c r="D7" s="146"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="147"/>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -69822,10 +69822,10 @@
       <c r="L7" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="144"/>
-      <c r="N7" s="144"/>
-      <c r="O7" s="144"/>
-      <c r="P7" s="149"/>
+      <c r="M7" s="146"/>
+      <c r="N7" s="146"/>
+      <c r="O7" s="146"/>
+      <c r="P7" s="147"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
@@ -70034,10 +70034,10 @@
       <c r="AB14" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="AC14" s="144"/>
-      <c r="AD14" s="144"/>
-      <c r="AE14" s="144"/>
-      <c r="AF14" s="149"/>
+      <c r="AC14" s="146"/>
+      <c r="AD14" s="146"/>
+      <c r="AE14" s="146"/>
+      <c r="AF14" s="147"/>
       <c r="AG14" s="100"/>
       <c r="AH14" s="45"/>
       <c r="AI14" s="12"/>
@@ -70111,10 +70111,10 @@
       <c r="AB17" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="AC17" s="144"/>
-      <c r="AD17" s="144"/>
-      <c r="AE17" s="144"/>
-      <c r="AF17" s="149"/>
+      <c r="AC17" s="146"/>
+      <c r="AD17" s="146"/>
+      <c r="AE17" s="146"/>
+      <c r="AF17" s="147"/>
       <c r="AG17" s="102"/>
       <c r="AH17" s="38"/>
       <c r="AI17" s="10"/>
@@ -70232,10 +70232,10 @@
       <c r="AB21" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="AC21" s="144"/>
-      <c r="AD21" s="144"/>
-      <c r="AE21" s="144"/>
-      <c r="AF21" s="149"/>
+      <c r="AC21" s="146"/>
+      <c r="AD21" s="146"/>
+      <c r="AE21" s="146"/>
+      <c r="AF21" s="147"/>
       <c r="AG21" s="116"/>
       <c r="AH21" s="117"/>
     </row>
@@ -71048,7 +71048,7 @@
         <v>781</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
         <v>782</v>
@@ -71363,7 +71363,7 @@
         <v>754</v>
       </c>
       <c r="H4">
-        <v>0.21</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush-r3\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F6CACE-7DB9-4689-A4D7-1D0045D82701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A588FA7-6C26-41C5-B6D1-94C71F224D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4500" yWindow="570" windowWidth="18900" windowHeight="13410" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27568,46 +27568,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -27616,12 +27616,12 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -28089,29 +28089,29 @@
   <sheetData>
     <row r="1" spans="2:44" ht="12" customHeight="1"/>
     <row r="2" spans="2:44">
-      <c r="B2" s="156" t="s">
+      <c r="B2" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-      <c r="R2" s="157"/>
-      <c r="S2" s="157"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="158"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155"/>
+      <c r="R2" s="155"/>
+      <c r="S2" s="155"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="156"/>
     </row>
     <row r="3" spans="2:44">
       <c r="B3" s="17"/>
@@ -28168,29 +28168,29 @@
       <c r="V4" s="14"/>
     </row>
     <row r="5" spans="2:44">
-      <c r="B5" s="156" t="s">
+      <c r="B5" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="157"/>
-      <c r="N5" s="157"/>
-      <c r="O5" s="157"/>
-      <c r="P5" s="157"/>
-      <c r="Q5" s="157"/>
-      <c r="R5" s="157"/>
-      <c r="S5" s="157"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="157"/>
-      <c r="V5" s="158"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="155"/>
+      <c r="Q5" s="155"/>
+      <c r="R5" s="155"/>
+      <c r="S5" s="155"/>
+      <c r="T5" s="155"/>
+      <c r="U5" s="155"/>
+      <c r="V5" s="156"/>
     </row>
     <row r="6" spans="2:44">
       <c r="B6" s="6"/>
@@ -28320,29 +28320,29 @@
     </row>
     <row r="10" spans="2:44" ht="8.1" customHeight="1"/>
     <row r="11" spans="2:44">
-      <c r="B11" s="156" t="s">
+      <c r="B11" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="157"/>
-      <c r="H11" s="157"/>
-      <c r="I11" s="157"/>
-      <c r="J11" s="157"/>
-      <c r="K11" s="157"/>
-      <c r="L11" s="157"/>
-      <c r="M11" s="157"/>
-      <c r="N11" s="157"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="157"/>
-      <c r="Q11" s="157"/>
-      <c r="R11" s="157"/>
-      <c r="S11" s="157"/>
-      <c r="T11" s="157"/>
-      <c r="U11" s="157"/>
-      <c r="V11" s="158"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="155"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="155"/>
+      <c r="G11" s="155"/>
+      <c r="H11" s="155"/>
+      <c r="I11" s="155"/>
+      <c r="J11" s="155"/>
+      <c r="K11" s="155"/>
+      <c r="L11" s="155"/>
+      <c r="M11" s="155"/>
+      <c r="N11" s="155"/>
+      <c r="O11" s="155"/>
+      <c r="P11" s="155"/>
+      <c r="Q11" s="155"/>
+      <c r="R11" s="155"/>
+      <c r="S11" s="155"/>
+      <c r="T11" s="155"/>
+      <c r="U11" s="155"/>
+      <c r="V11" s="156"/>
     </row>
     <row r="12" spans="2:44">
       <c r="B12" s="6"/>
@@ -28629,19 +28629,19 @@
       <c r="AF22" s="27"/>
     </row>
     <row r="23" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B23" s="159" t="s">
+      <c r="B23" s="157" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="146"/>
-      <c r="D23" s="146"/>
-      <c r="E23" s="146"/>
-      <c r="F23" s="146"/>
-      <c r="G23" s="146"/>
-      <c r="H23" s="161" t="s">
+      <c r="C23" s="144"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="144"/>
+      <c r="G23" s="144"/>
+      <c r="H23" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="146"/>
-      <c r="J23" s="146"/>
+      <c r="I23" s="144"/>
+      <c r="J23" s="144"/>
       <c r="K23" s="28" t="s">
         <v>68</v>
       </c>
@@ -28669,18 +28669,18 @@
     </row>
     <row r="24" spans="2:32" s="10" customFormat="1">
       <c r="B24" s="86"/>
-      <c r="C24" s="136" t="s">
+      <c r="C24" s="153" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="137"/>
-      <c r="E24" s="137"/>
-      <c r="F24" s="137"/>
-      <c r="G24" s="138"/>
-      <c r="H24" s="142" t="s">
+      <c r="D24" s="151"/>
+      <c r="E24" s="151"/>
+      <c r="F24" s="151"/>
+      <c r="G24" s="152"/>
+      <c r="H24" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="137"/>
-      <c r="J24" s="138"/>
+      <c r="I24" s="151"/>
+      <c r="J24" s="152"/>
       <c r="K24" s="34" t="s">
         <v>70</v>
       </c>
@@ -28708,14 +28708,14 @@
     </row>
     <row r="25" spans="2:32" s="10" customFormat="1">
       <c r="B25" s="22"/>
-      <c r="C25" s="139"/>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
-      <c r="G25" s="140"/>
-      <c r="H25" s="143"/>
-      <c r="I25" s="139"/>
-      <c r="J25" s="140"/>
+      <c r="C25" s="140"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="158"/>
+      <c r="I25" s="140"/>
+      <c r="J25" s="141"/>
       <c r="K25" s="19" t="s">
         <v>49</v>
       </c>
@@ -28737,18 +28737,18 @@
     </row>
     <row r="26" spans="2:32" s="10" customFormat="1">
       <c r="B26" s="22"/>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="139" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="141" t="s">
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="141"/>
+      <c r="H26" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="139"/>
-      <c r="J26" s="140"/>
+      <c r="I26" s="140"/>
+      <c r="J26" s="141"/>
       <c r="K26" s="19" t="s">
         <v>74</v>
       </c>
@@ -28768,18 +28768,18 @@
     </row>
     <row r="27" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B27" s="22"/>
-      <c r="C27" s="144" t="s">
+      <c r="C27" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="139"/>
-      <c r="G27" s="140"/>
-      <c r="H27" s="141" t="s">
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="141"/>
+      <c r="H27" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I27" s="139"/>
-      <c r="J27" s="140"/>
+      <c r="I27" s="140"/>
+      <c r="J27" s="141"/>
       <c r="K27" s="19" t="s">
         <v>75</v>
       </c>
@@ -28799,18 +28799,18 @@
     </row>
     <row r="28" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B28" s="22"/>
-      <c r="C28" s="144" t="s">
+      <c r="C28" s="139" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="139"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="141" t="s">
+      <c r="D28" s="140"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I28" s="139"/>
-      <c r="J28" s="140"/>
+      <c r="I28" s="140"/>
+      <c r="J28" s="141"/>
       <c r="K28" s="19" t="s">
         <v>77</v>
       </c>
@@ -28830,18 +28830,18 @@
     </row>
     <row r="29" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B29" s="22"/>
-      <c r="C29" s="144" t="s">
+      <c r="C29" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="140"/>
-      <c r="H29" s="141" t="s">
+      <c r="D29" s="140"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I29" s="139"/>
-      <c r="J29" s="140"/>
+      <c r="I29" s="140"/>
+      <c r="J29" s="141"/>
       <c r="K29" s="19" t="s">
         <v>78</v>
       </c>
@@ -28861,18 +28861,18 @@
     </row>
     <row r="30" spans="2:32" s="10" customFormat="1">
       <c r="B30" s="22"/>
-      <c r="C30" s="144" t="s">
+      <c r="C30" s="139" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="139"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="139"/>
-      <c r="G30" s="140"/>
-      <c r="H30" s="141" t="s">
+      <c r="D30" s="140"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="140"/>
+      <c r="G30" s="141"/>
+      <c r="H30" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I30" s="139"/>
-      <c r="J30" s="140"/>
+      <c r="I30" s="140"/>
+      <c r="J30" s="141"/>
       <c r="K30" s="120" t="s">
         <v>421</v>
       </c>
@@ -28892,18 +28892,18 @@
     </row>
     <row r="31" spans="2:32" s="10" customFormat="1">
       <c r="B31" s="22"/>
-      <c r="C31" s="144" t="s">
+      <c r="C31" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="140"/>
-      <c r="H31" s="141" t="s">
+      <c r="D31" s="140"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="140"/>
+      <c r="G31" s="141"/>
+      <c r="H31" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I31" s="139"/>
-      <c r="J31" s="140"/>
+      <c r="I31" s="140"/>
+      <c r="J31" s="141"/>
       <c r="K31" s="19" t="s">
         <v>80</v>
       </c>
@@ -28923,18 +28923,18 @@
     </row>
     <row r="32" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B32" s="75"/>
-      <c r="C32" s="160" t="s">
+      <c r="C32" s="145" t="s">
         <v>422</v>
       </c>
-      <c r="D32" s="149"/>
-      <c r="E32" s="149"/>
-      <c r="F32" s="149"/>
-      <c r="G32" s="150"/>
-      <c r="H32" s="148" t="s">
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="137"/>
+      <c r="G32" s="138"/>
+      <c r="H32" s="136" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="149"/>
-      <c r="J32" s="150"/>
+      <c r="I32" s="137"/>
+      <c r="J32" s="138"/>
       <c r="K32" s="81" t="s">
         <v>82</v>
       </c>
@@ -28996,19 +28996,19 @@
       <c r="AF33" s="27"/>
     </row>
     <row r="34" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B34" s="145" t="s">
+      <c r="B34" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="146"/>
-      <c r="D34" s="146"/>
-      <c r="E34" s="146"/>
-      <c r="F34" s="146"/>
-      <c r="G34" s="147"/>
-      <c r="H34" s="145" t="s">
+      <c r="C34" s="144"/>
+      <c r="D34" s="144"/>
+      <c r="E34" s="144"/>
+      <c r="F34" s="144"/>
+      <c r="G34" s="149"/>
+      <c r="H34" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I34" s="146"/>
-      <c r="J34" s="147"/>
+      <c r="I34" s="144"/>
+      <c r="J34" s="149"/>
       <c r="K34" s="28" t="s">
         <v>68</v>
       </c>
@@ -29036,18 +29036,18 @@
     </row>
     <row r="35" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B35" s="86"/>
-      <c r="C35" s="136" t="s">
+      <c r="C35" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="137"/>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="138"/>
-      <c r="H35" s="142" t="s">
+      <c r="D35" s="151"/>
+      <c r="E35" s="151"/>
+      <c r="F35" s="151"/>
+      <c r="G35" s="152"/>
+      <c r="H35" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="I35" s="137"/>
-      <c r="J35" s="138"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="152"/>
       <c r="K35" s="34" t="s">
         <v>84</v>
       </c>
@@ -29075,18 +29075,18 @@
     </row>
     <row r="36" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B36" s="75"/>
-      <c r="C36" s="160" t="s">
+      <c r="C36" s="145" t="s">
         <v>423</v>
       </c>
-      <c r="D36" s="149"/>
-      <c r="E36" s="149"/>
-      <c r="F36" s="149"/>
-      <c r="G36" s="150"/>
-      <c r="H36" s="148" t="s">
+      <c r="D36" s="137"/>
+      <c r="E36" s="137"/>
+      <c r="F36" s="137"/>
+      <c r="G36" s="138"/>
+      <c r="H36" s="136" t="s">
         <v>69</v>
       </c>
-      <c r="I36" s="149"/>
-      <c r="J36" s="150"/>
+      <c r="I36" s="137"/>
+      <c r="J36" s="138"/>
       <c r="K36" s="81" t="s">
         <v>85</v>
       </c>
@@ -29148,19 +29148,19 @@
       <c r="AF37" s="92"/>
     </row>
     <row r="38" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B38" s="145" t="s">
+      <c r="B38" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="146"/>
-      <c r="D38" s="146"/>
-      <c r="E38" s="146"/>
-      <c r="F38" s="146"/>
-      <c r="G38" s="147"/>
-      <c r="H38" s="145" t="s">
+      <c r="C38" s="144"/>
+      <c r="D38" s="144"/>
+      <c r="E38" s="144"/>
+      <c r="F38" s="144"/>
+      <c r="G38" s="149"/>
+      <c r="H38" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="146"/>
-      <c r="J38" s="147"/>
+      <c r="I38" s="144"/>
+      <c r="J38" s="149"/>
       <c r="K38" s="28" t="s">
         <v>68</v>
       </c>
@@ -29188,18 +29188,18 @@
     </row>
     <row r="39" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B39" s="21"/>
-      <c r="C39" s="144" t="s">
+      <c r="C39" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="139"/>
-      <c r="E39" s="139"/>
-      <c r="F39" s="139"/>
-      <c r="G39" s="140"/>
-      <c r="H39" s="141" t="s">
+      <c r="D39" s="140"/>
+      <c r="E39" s="140"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="141"/>
+      <c r="H39" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I39" s="139"/>
-      <c r="J39" s="140"/>
+      <c r="I39" s="140"/>
+      <c r="J39" s="141"/>
       <c r="K39" s="19" t="s">
         <v>86</v>
       </c>
@@ -29219,18 +29219,18 @@
     </row>
     <row r="40" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B40" s="22"/>
-      <c r="C40" s="144" t="s">
+      <c r="C40" s="139" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="139"/>
-      <c r="E40" s="139"/>
-      <c r="F40" s="139"/>
-      <c r="G40" s="140"/>
-      <c r="H40" s="141" t="s">
+      <c r="D40" s="140"/>
+      <c r="E40" s="140"/>
+      <c r="F40" s="140"/>
+      <c r="G40" s="141"/>
+      <c r="H40" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I40" s="139"/>
-      <c r="J40" s="140"/>
+      <c r="I40" s="140"/>
+      <c r="J40" s="141"/>
       <c r="K40" s="19" t="s">
         <v>88</v>
       </c>
@@ -29250,18 +29250,18 @@
     </row>
     <row r="41" spans="2:32" s="10" customFormat="1">
       <c r="B41" s="22"/>
-      <c r="C41" s="144" t="s">
+      <c r="C41" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="139"/>
-      <c r="E41" s="139"/>
-      <c r="F41" s="139"/>
-      <c r="G41" s="140"/>
-      <c r="H41" s="141" t="s">
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="140"/>
+      <c r="G41" s="141"/>
+      <c r="H41" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="139"/>
-      <c r="J41" s="140"/>
+      <c r="I41" s="140"/>
+      <c r="J41" s="141"/>
       <c r="K41" s="19" t="s">
         <v>89</v>
       </c>
@@ -29281,18 +29281,18 @@
     </row>
     <row r="42" spans="2:32" s="10" customFormat="1">
       <c r="B42" s="22"/>
-      <c r="C42" s="144" t="s">
+      <c r="C42" s="139" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="139"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="140"/>
-      <c r="H42" s="141" t="s">
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="141"/>
+      <c r="H42" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I42" s="139"/>
-      <c r="J42" s="140"/>
+      <c r="I42" s="140"/>
+      <c r="J42" s="141"/>
       <c r="K42" s="19" t="s">
         <v>91</v>
       </c>
@@ -29312,18 +29312,18 @@
     </row>
     <row r="43" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B43" s="75"/>
-      <c r="C43" s="152" t="s">
+      <c r="C43" s="142" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="149"/>
-      <c r="E43" s="149"/>
-      <c r="F43" s="149"/>
-      <c r="G43" s="150"/>
-      <c r="H43" s="148" t="s">
+      <c r="D43" s="137"/>
+      <c r="E43" s="137"/>
+      <c r="F43" s="137"/>
+      <c r="G43" s="138"/>
+      <c r="H43" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="149"/>
-      <c r="J43" s="150"/>
+      <c r="I43" s="137"/>
+      <c r="J43" s="138"/>
       <c r="K43" s="81" t="s">
         <v>92</v>
       </c>
@@ -29385,19 +29385,19 @@
       <c r="AF44" s="27"/>
     </row>
     <row r="45" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B45" s="145" t="s">
+      <c r="B45" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="146"/>
-      <c r="D45" s="146"/>
-      <c r="E45" s="146"/>
-      <c r="F45" s="146"/>
-      <c r="G45" s="147"/>
-      <c r="H45" s="153" t="s">
+      <c r="C45" s="144"/>
+      <c r="D45" s="144"/>
+      <c r="E45" s="144"/>
+      <c r="F45" s="144"/>
+      <c r="G45" s="149"/>
+      <c r="H45" s="159" t="s">
         <v>67</v>
       </c>
-      <c r="I45" s="154"/>
-      <c r="J45" s="155"/>
+      <c r="I45" s="160"/>
+      <c r="J45" s="161"/>
       <c r="K45" s="83" t="s">
         <v>68</v>
       </c>
@@ -29425,18 +29425,18 @@
     </row>
     <row r="46" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B46" s="21"/>
-      <c r="C46" s="144" t="s">
+      <c r="C46" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="139"/>
-      <c r="E46" s="139"/>
-      <c r="F46" s="139"/>
-      <c r="G46" s="140"/>
-      <c r="H46" s="142" t="s">
+      <c r="D46" s="140"/>
+      <c r="E46" s="140"/>
+      <c r="F46" s="140"/>
+      <c r="G46" s="141"/>
+      <c r="H46" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="I46" s="137"/>
-      <c r="J46" s="138"/>
+      <c r="I46" s="151"/>
+      <c r="J46" s="152"/>
       <c r="K46" s="19" t="s">
         <v>93</v>
       </c>
@@ -29456,18 +29456,18 @@
     </row>
     <row r="47" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B47" s="22"/>
-      <c r="C47" s="144" t="s">
+      <c r="C47" s="139" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="139"/>
-      <c r="E47" s="139"/>
-      <c r="F47" s="139"/>
-      <c r="G47" s="140"/>
-      <c r="H47" s="141" t="s">
+      <c r="D47" s="140"/>
+      <c r="E47" s="140"/>
+      <c r="F47" s="140"/>
+      <c r="G47" s="141"/>
+      <c r="H47" s="146" t="s">
         <v>81</v>
       </c>
-      <c r="I47" s="139"/>
-      <c r="J47" s="140"/>
+      <c r="I47" s="140"/>
+      <c r="J47" s="141"/>
       <c r="K47" s="19" t="s">
         <v>95</v>
       </c>
@@ -29487,14 +29487,14 @@
     </row>
     <row r="48" spans="2:32" s="10" customFormat="1">
       <c r="B48" s="22"/>
-      <c r="C48" s="139"/>
-      <c r="D48" s="139"/>
-      <c r="E48" s="139"/>
-      <c r="F48" s="139"/>
-      <c r="G48" s="140"/>
-      <c r="H48" s="143"/>
-      <c r="I48" s="139"/>
-      <c r="J48" s="140"/>
+      <c r="C48" s="140"/>
+      <c r="D48" s="140"/>
+      <c r="E48" s="140"/>
+      <c r="F48" s="140"/>
+      <c r="G48" s="141"/>
+      <c r="H48" s="158"/>
+      <c r="I48" s="140"/>
+      <c r="J48" s="141"/>
       <c r="K48" s="19" t="s">
         <v>49</v>
       </c>
@@ -29516,14 +29516,14 @@
     </row>
     <row r="49" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B49" s="22"/>
-      <c r="C49" s="139"/>
-      <c r="D49" s="139"/>
-      <c r="E49" s="139"/>
-      <c r="F49" s="139"/>
-      <c r="G49" s="140"/>
-      <c r="H49" s="143"/>
-      <c r="I49" s="139"/>
-      <c r="J49" s="140"/>
+      <c r="C49" s="140"/>
+      <c r="D49" s="140"/>
+      <c r="E49" s="140"/>
+      <c r="F49" s="140"/>
+      <c r="G49" s="141"/>
+      <c r="H49" s="158"/>
+      <c r="I49" s="140"/>
+      <c r="J49" s="141"/>
       <c r="K49" s="19" t="s">
         <v>49</v>
       </c>
@@ -29580,19 +29580,19 @@
       <c r="AG50" s="92"/>
     </row>
     <row r="51" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B51" s="145" t="s">
+      <c r="B51" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="146"/>
-      <c r="D51" s="146"/>
-      <c r="E51" s="146"/>
-      <c r="F51" s="146"/>
-      <c r="G51" s="147"/>
-      <c r="H51" s="145" t="s">
+      <c r="C51" s="144"/>
+      <c r="D51" s="144"/>
+      <c r="E51" s="144"/>
+      <c r="F51" s="144"/>
+      <c r="G51" s="149"/>
+      <c r="H51" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I51" s="146"/>
-      <c r="J51" s="147"/>
+      <c r="I51" s="144"/>
+      <c r="J51" s="149"/>
       <c r="K51" s="28" t="s">
         <v>68</v>
       </c>
@@ -29621,18 +29621,18 @@
     </row>
     <row r="52" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B52" s="21"/>
-      <c r="C52" s="144" t="s">
+      <c r="C52" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="139"/>
-      <c r="E52" s="139"/>
-      <c r="F52" s="139"/>
-      <c r="G52" s="140"/>
-      <c r="H52" s="141" t="s">
+      <c r="D52" s="140"/>
+      <c r="E52" s="140"/>
+      <c r="F52" s="140"/>
+      <c r="G52" s="141"/>
+      <c r="H52" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I52" s="139"/>
-      <c r="J52" s="140"/>
+      <c r="I52" s="140"/>
+      <c r="J52" s="141"/>
       <c r="K52" s="19" t="s">
         <v>99</v>
       </c>
@@ -29652,18 +29652,18 @@
     </row>
     <row r="53" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B53" s="22"/>
-      <c r="C53" s="144" t="s">
+      <c r="C53" s="139" t="s">
         <v>100</v>
       </c>
-      <c r="D53" s="139"/>
-      <c r="E53" s="139"/>
-      <c r="F53" s="139"/>
-      <c r="G53" s="140"/>
-      <c r="H53" s="141" t="s">
+      <c r="D53" s="140"/>
+      <c r="E53" s="140"/>
+      <c r="F53" s="140"/>
+      <c r="G53" s="141"/>
+      <c r="H53" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I53" s="139"/>
-      <c r="J53" s="140"/>
+      <c r="I53" s="140"/>
+      <c r="J53" s="141"/>
       <c r="K53" s="19" t="s">
         <v>101</v>
       </c>
@@ -29683,18 +29683,18 @@
     </row>
     <row r="54" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B54" s="75"/>
-      <c r="C54" s="152" t="s">
+      <c r="C54" s="142" t="s">
         <v>102</v>
       </c>
-      <c r="D54" s="149"/>
-      <c r="E54" s="149"/>
-      <c r="F54" s="149"/>
-      <c r="G54" s="150"/>
-      <c r="H54" s="148" t="s">
+      <c r="D54" s="137"/>
+      <c r="E54" s="137"/>
+      <c r="F54" s="137"/>
+      <c r="G54" s="138"/>
+      <c r="H54" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="I54" s="149"/>
-      <c r="J54" s="150"/>
+      <c r="I54" s="137"/>
+      <c r="J54" s="138"/>
       <c r="K54" s="81" t="s">
         <v>103</v>
       </c>
@@ -29758,19 +29758,19 @@
       <c r="AG55" s="92"/>
     </row>
     <row r="56" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B56" s="145" t="s">
+      <c r="B56" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="146"/>
-      <c r="D56" s="146"/>
-      <c r="E56" s="146"/>
-      <c r="F56" s="146"/>
-      <c r="G56" s="147"/>
-      <c r="H56" s="145" t="s">
+      <c r="C56" s="144"/>
+      <c r="D56" s="144"/>
+      <c r="E56" s="144"/>
+      <c r="F56" s="144"/>
+      <c r="G56" s="149"/>
+      <c r="H56" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I56" s="146"/>
-      <c r="J56" s="147"/>
+      <c r="I56" s="144"/>
+      <c r="J56" s="149"/>
       <c r="K56" s="28" t="s">
         <v>68</v>
       </c>
@@ -29799,18 +29799,18 @@
     </row>
     <row r="57" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B57" s="21"/>
-      <c r="C57" s="144" t="s">
+      <c r="C57" s="139" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="139"/>
-      <c r="E57" s="139"/>
-      <c r="F57" s="139"/>
-      <c r="G57" s="140"/>
-      <c r="H57" s="141" t="s">
+      <c r="D57" s="140"/>
+      <c r="E57" s="140"/>
+      <c r="F57" s="140"/>
+      <c r="G57" s="141"/>
+      <c r="H57" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I57" s="139"/>
-      <c r="J57" s="140"/>
+      <c r="I57" s="140"/>
+      <c r="J57" s="141"/>
       <c r="K57" s="19" t="s">
         <v>104</v>
       </c>
@@ -29830,18 +29830,18 @@
     </row>
     <row r="58" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B58" s="22"/>
-      <c r="C58" s="144" t="s">
+      <c r="C58" s="139" t="s">
         <v>105</v>
       </c>
-      <c r="D58" s="139"/>
-      <c r="E58" s="139"/>
-      <c r="F58" s="139"/>
-      <c r="G58" s="140"/>
-      <c r="H58" s="141" t="s">
+      <c r="D58" s="140"/>
+      <c r="E58" s="140"/>
+      <c r="F58" s="140"/>
+      <c r="G58" s="141"/>
+      <c r="H58" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I58" s="139"/>
-      <c r="J58" s="140"/>
+      <c r="I58" s="140"/>
+      <c r="J58" s="141"/>
       <c r="K58" s="19" t="s">
         <v>106</v>
       </c>
@@ -29861,18 +29861,18 @@
     </row>
     <row r="59" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B59" s="22"/>
-      <c r="C59" s="144" t="s">
+      <c r="C59" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="140"/>
-      <c r="H59" s="141" t="s">
+      <c r="D59" s="140"/>
+      <c r="E59" s="140"/>
+      <c r="F59" s="140"/>
+      <c r="G59" s="141"/>
+      <c r="H59" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I59" s="139"/>
-      <c r="J59" s="140"/>
+      <c r="I59" s="140"/>
+      <c r="J59" s="141"/>
       <c r="K59" s="19" t="s">
         <v>107</v>
       </c>
@@ -29892,18 +29892,18 @@
     </row>
     <row r="60" spans="2:33" s="10" customFormat="1">
       <c r="B60" s="22"/>
-      <c r="C60" s="144" t="s">
+      <c r="C60" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="D60" s="139"/>
-      <c r="E60" s="139"/>
-      <c r="F60" s="139"/>
-      <c r="G60" s="140"/>
-      <c r="H60" s="141" t="s">
+      <c r="D60" s="140"/>
+      <c r="E60" s="140"/>
+      <c r="F60" s="140"/>
+      <c r="G60" s="141"/>
+      <c r="H60" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I60" s="139"/>
-      <c r="J60" s="140"/>
+      <c r="I60" s="140"/>
+      <c r="J60" s="141"/>
       <c r="K60" s="19" t="s">
         <v>109</v>
       </c>
@@ -29923,18 +29923,18 @@
     </row>
     <row r="61" spans="2:33" s="10" customFormat="1">
       <c r="B61" s="22"/>
-      <c r="C61" s="144" t="s">
+      <c r="C61" s="139" t="s">
         <v>110</v>
       </c>
-      <c r="D61" s="139"/>
-      <c r="E61" s="139"/>
-      <c r="F61" s="139"/>
-      <c r="G61" s="140"/>
-      <c r="H61" s="141" t="s">
+      <c r="D61" s="140"/>
+      <c r="E61" s="140"/>
+      <c r="F61" s="140"/>
+      <c r="G61" s="141"/>
+      <c r="H61" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I61" s="139"/>
-      <c r="J61" s="140"/>
+      <c r="I61" s="140"/>
+      <c r="J61" s="141"/>
       <c r="K61" s="19" t="s">
         <v>111</v>
       </c>
@@ -29954,18 +29954,18 @@
     </row>
     <row r="62" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B62" s="75"/>
-      <c r="C62" s="152" t="s">
+      <c r="C62" s="142" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="149"/>
-      <c r="E62" s="149"/>
-      <c r="F62" s="149"/>
-      <c r="G62" s="150"/>
-      <c r="H62" s="148" t="s">
+      <c r="D62" s="137"/>
+      <c r="E62" s="137"/>
+      <c r="F62" s="137"/>
+      <c r="G62" s="138"/>
+      <c r="H62" s="136" t="s">
         <v>81</v>
       </c>
-      <c r="I62" s="149"/>
-      <c r="J62" s="150"/>
+      <c r="I62" s="137"/>
+      <c r="J62" s="138"/>
       <c r="K62" s="81" t="s">
         <v>113</v>
       </c>
@@ -30029,19 +30029,19 @@
       <c r="AG63" s="92"/>
     </row>
     <row r="64" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B64" s="145" t="s">
+      <c r="B64" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="146"/>
-      <c r="D64" s="146"/>
-      <c r="E64" s="146"/>
-      <c r="F64" s="146"/>
-      <c r="G64" s="147"/>
-      <c r="H64" s="145" t="s">
+      <c r="C64" s="144"/>
+      <c r="D64" s="144"/>
+      <c r="E64" s="144"/>
+      <c r="F64" s="144"/>
+      <c r="G64" s="149"/>
+      <c r="H64" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I64" s="146"/>
-      <c r="J64" s="147"/>
+      <c r="I64" s="144"/>
+      <c r="J64" s="149"/>
       <c r="K64" s="83" t="s">
         <v>68</v>
       </c>
@@ -30070,18 +30070,18 @@
     </row>
     <row r="65" spans="2:33">
       <c r="B65" s="21"/>
-      <c r="C65" s="144" t="s">
+      <c r="C65" s="139" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="151"/>
-      <c r="E65" s="151"/>
-      <c r="F65" s="151"/>
-      <c r="G65" s="140"/>
-      <c r="H65" s="142" t="s">
+      <c r="D65" s="147"/>
+      <c r="E65" s="147"/>
+      <c r="F65" s="147"/>
+      <c r="G65" s="141"/>
+      <c r="H65" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="I65" s="137"/>
-      <c r="J65" s="138"/>
+      <c r="I65" s="151"/>
+      <c r="J65" s="152"/>
       <c r="K65" s="19" t="s">
         <v>115</v>
       </c>
@@ -30101,18 +30101,18 @@
     </row>
     <row r="66" spans="2:33">
       <c r="B66" s="22"/>
-      <c r="C66" s="144" t="s">
+      <c r="C66" s="139" t="s">
         <v>116</v>
       </c>
-      <c r="D66" s="151"/>
-      <c r="E66" s="151"/>
-      <c r="F66" s="151"/>
-      <c r="G66" s="140"/>
-      <c r="H66" s="141" t="s">
+      <c r="D66" s="147"/>
+      <c r="E66" s="147"/>
+      <c r="F66" s="147"/>
+      <c r="G66" s="141"/>
+      <c r="H66" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I66" s="151"/>
-      <c r="J66" s="140"/>
+      <c r="I66" s="147"/>
+      <c r="J66" s="141"/>
       <c r="K66" s="19" t="s">
         <v>117</v>
       </c>
@@ -30132,18 +30132,18 @@
     </row>
     <row r="67" spans="2:33">
       <c r="B67" s="22"/>
-      <c r="C67" s="144" t="s">
+      <c r="C67" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="D67" s="151"/>
-      <c r="E67" s="151"/>
-      <c r="F67" s="151"/>
-      <c r="G67" s="140"/>
-      <c r="H67" s="141" t="s">
+      <c r="D67" s="147"/>
+      <c r="E67" s="147"/>
+      <c r="F67" s="147"/>
+      <c r="G67" s="141"/>
+      <c r="H67" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I67" s="151"/>
-      <c r="J67" s="140"/>
+      <c r="I67" s="147"/>
+      <c r="J67" s="141"/>
       <c r="K67" s="19" t="s">
         <v>118</v>
       </c>
@@ -30163,18 +30163,18 @@
     </row>
     <row r="68" spans="2:33">
       <c r="B68" s="22"/>
-      <c r="C68" s="144" t="s">
+      <c r="C68" s="139" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="151"/>
-      <c r="E68" s="151"/>
-      <c r="F68" s="151"/>
-      <c r="G68" s="140"/>
-      <c r="H68" s="141" t="s">
+      <c r="D68" s="147"/>
+      <c r="E68" s="147"/>
+      <c r="F68" s="147"/>
+      <c r="G68" s="141"/>
+      <c r="H68" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I68" s="151"/>
-      <c r="J68" s="140"/>
+      <c r="I68" s="147"/>
+      <c r="J68" s="141"/>
       <c r="K68" s="19" t="s">
         <v>120</v>
       </c>
@@ -30194,18 +30194,18 @@
     </row>
     <row r="69" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B69" s="75"/>
-      <c r="C69" s="152" t="s">
+      <c r="C69" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="D69" s="149"/>
-      <c r="E69" s="149"/>
-      <c r="F69" s="149"/>
-      <c r="G69" s="150"/>
-      <c r="H69" s="148" t="s">
+      <c r="D69" s="137"/>
+      <c r="E69" s="137"/>
+      <c r="F69" s="137"/>
+      <c r="G69" s="138"/>
+      <c r="H69" s="136" t="s">
         <v>69</v>
       </c>
-      <c r="I69" s="149"/>
-      <c r="J69" s="150"/>
+      <c r="I69" s="137"/>
+      <c r="J69" s="138"/>
       <c r="K69" s="81" t="s">
         <v>122</v>
       </c>
@@ -30269,19 +30269,19 @@
       <c r="AG70" s="94"/>
     </row>
     <row r="71" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B71" s="145" t="s">
+      <c r="B71" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="146"/>
-      <c r="D71" s="146"/>
-      <c r="E71" s="146"/>
-      <c r="F71" s="146"/>
-      <c r="G71" s="147"/>
-      <c r="H71" s="145" t="s">
+      <c r="C71" s="144"/>
+      <c r="D71" s="144"/>
+      <c r="E71" s="144"/>
+      <c r="F71" s="144"/>
+      <c r="G71" s="149"/>
+      <c r="H71" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I71" s="146"/>
-      <c r="J71" s="147"/>
+      <c r="I71" s="144"/>
+      <c r="J71" s="149"/>
       <c r="K71" s="83" t="s">
         <v>68</v>
       </c>
@@ -30310,18 +30310,18 @@
     </row>
     <row r="72" spans="2:33">
       <c r="B72" s="21"/>
-      <c r="C72" s="144" t="s">
+      <c r="C72" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="151"/>
-      <c r="E72" s="151"/>
-      <c r="F72" s="151"/>
-      <c r="G72" s="140"/>
-      <c r="H72" s="142" t="s">
+      <c r="D72" s="147"/>
+      <c r="E72" s="147"/>
+      <c r="F72" s="147"/>
+      <c r="G72" s="141"/>
+      <c r="H72" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="I72" s="137"/>
-      <c r="J72" s="138"/>
+      <c r="I72" s="151"/>
+      <c r="J72" s="152"/>
       <c r="K72" s="19" t="s">
         <v>123</v>
       </c>
@@ -30341,18 +30341,18 @@
     </row>
     <row r="73" spans="2:33">
       <c r="B73" s="22"/>
-      <c r="C73" s="144" t="s">
+      <c r="C73" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="D73" s="151"/>
-      <c r="E73" s="151"/>
-      <c r="F73" s="151"/>
-      <c r="G73" s="140"/>
-      <c r="H73" s="141" t="s">
+      <c r="D73" s="147"/>
+      <c r="E73" s="147"/>
+      <c r="F73" s="147"/>
+      <c r="G73" s="141"/>
+      <c r="H73" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I73" s="151"/>
-      <c r="J73" s="140"/>
+      <c r="I73" s="147"/>
+      <c r="J73" s="141"/>
       <c r="K73" s="19" t="s">
         <v>124</v>
       </c>
@@ -30372,18 +30372,18 @@
     </row>
     <row r="74" spans="2:33">
       <c r="B74" s="22"/>
-      <c r="C74" s="144" t="s">
+      <c r="C74" s="139" t="s">
         <v>125</v>
       </c>
-      <c r="D74" s="151"/>
-      <c r="E74" s="151"/>
-      <c r="F74" s="151"/>
-      <c r="G74" s="140"/>
-      <c r="H74" s="141" t="s">
+      <c r="D74" s="147"/>
+      <c r="E74" s="147"/>
+      <c r="F74" s="147"/>
+      <c r="G74" s="141"/>
+      <c r="H74" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I74" s="151"/>
-      <c r="J74" s="140"/>
+      <c r="I74" s="147"/>
+      <c r="J74" s="141"/>
       <c r="K74" s="19" t="s">
         <v>126</v>
       </c>
@@ -30403,18 +30403,18 @@
     </row>
     <row r="75" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B75" s="75"/>
-      <c r="C75" s="152" t="s">
+      <c r="C75" s="142" t="s">
         <v>127</v>
       </c>
-      <c r="D75" s="149"/>
-      <c r="E75" s="149"/>
-      <c r="F75" s="149"/>
-      <c r="G75" s="150"/>
-      <c r="H75" s="148" t="s">
+      <c r="D75" s="137"/>
+      <c r="E75" s="137"/>
+      <c r="F75" s="137"/>
+      <c r="G75" s="138"/>
+      <c r="H75" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="I75" s="149"/>
-      <c r="J75" s="150"/>
+      <c r="I75" s="137"/>
+      <c r="J75" s="138"/>
       <c r="K75" s="81" t="s">
         <v>128</v>
       </c>
@@ -30478,19 +30478,19 @@
       <c r="AG76" s="94"/>
     </row>
     <row r="77" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B77" s="145" t="s">
+      <c r="B77" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C77" s="146"/>
-      <c r="D77" s="146"/>
-      <c r="E77" s="146"/>
-      <c r="F77" s="146"/>
-      <c r="G77" s="147"/>
-      <c r="H77" s="145" t="s">
+      <c r="C77" s="144"/>
+      <c r="D77" s="144"/>
+      <c r="E77" s="144"/>
+      <c r="F77" s="144"/>
+      <c r="G77" s="149"/>
+      <c r="H77" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I77" s="146"/>
-      <c r="J77" s="147"/>
+      <c r="I77" s="144"/>
+      <c r="J77" s="149"/>
       <c r="K77" s="83" t="s">
         <v>68</v>
       </c>
@@ -30519,18 +30519,18 @@
     </row>
     <row r="78" spans="2:33">
       <c r="B78" s="21"/>
-      <c r="C78" s="144" t="s">
+      <c r="C78" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="151"/>
-      <c r="E78" s="151"/>
-      <c r="F78" s="151"/>
-      <c r="G78" s="140"/>
-      <c r="H78" s="142" t="s">
+      <c r="D78" s="147"/>
+      <c r="E78" s="147"/>
+      <c r="F78" s="147"/>
+      <c r="G78" s="141"/>
+      <c r="H78" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="I78" s="137"/>
-      <c r="J78" s="138"/>
+      <c r="I78" s="151"/>
+      <c r="J78" s="152"/>
       <c r="K78" s="19" t="s">
         <v>129</v>
       </c>
@@ -30550,18 +30550,18 @@
     </row>
     <row r="79" spans="2:33">
       <c r="B79" s="22"/>
-      <c r="C79" s="144" t="s">
+      <c r="C79" s="139" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="151"/>
-      <c r="E79" s="151"/>
-      <c r="F79" s="151"/>
-      <c r="G79" s="140"/>
-      <c r="H79" s="141" t="s">
+      <c r="D79" s="147"/>
+      <c r="E79" s="147"/>
+      <c r="F79" s="147"/>
+      <c r="G79" s="141"/>
+      <c r="H79" s="146" t="s">
         <v>131</v>
       </c>
-      <c r="I79" s="151"/>
-      <c r="J79" s="140"/>
+      <c r="I79" s="147"/>
+      <c r="J79" s="141"/>
       <c r="K79" s="19" t="s">
         <v>132</v>
       </c>
@@ -30581,18 +30581,18 @@
     </row>
     <row r="80" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B80" s="75"/>
-      <c r="C80" s="152" t="s">
+      <c r="C80" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="D80" s="149"/>
-      <c r="E80" s="149"/>
-      <c r="F80" s="149"/>
-      <c r="G80" s="150"/>
-      <c r="H80" s="148" t="s">
+      <c r="D80" s="137"/>
+      <c r="E80" s="137"/>
+      <c r="F80" s="137"/>
+      <c r="G80" s="138"/>
+      <c r="H80" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="I80" s="149"/>
-      <c r="J80" s="150"/>
+      <c r="I80" s="137"/>
+      <c r="J80" s="138"/>
       <c r="K80" s="81" t="s">
         <v>134</v>
       </c>
@@ -30703,6 +30703,87 @@
     </row>
   </sheetData>
   <mergeCells count="97">
+    <mergeCell ref="C24:G25"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="H24:J25"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="H69:J69"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="H66:J66"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="H64:J64"/>
+    <mergeCell ref="H60:J60"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="B11:V11"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B5:V5"/>
+    <mergeCell ref="H47:J49"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C47:G49"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="H65:J65"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="H36:J36"/>
     <mergeCell ref="H80:J80"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="H62:J62"/>
@@ -30719,87 +30800,6 @@
     <mergeCell ref="H74:J74"/>
     <mergeCell ref="H56:J56"/>
     <mergeCell ref="H68:J68"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="H79:J79"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H78:J78"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="H65:J65"/>
-    <mergeCell ref="H71:J71"/>
-    <mergeCell ref="H75:J75"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C47:G49"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B2:V2"/>
-    <mergeCell ref="B11:V11"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B5:V5"/>
-    <mergeCell ref="H47:J49"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="H51:J51"/>
-    <mergeCell ref="H69:J69"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="H66:J66"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="H64:J64"/>
-    <mergeCell ref="H60:J60"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="C24:G25"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="H24:J25"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:J26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -69671,10 +69671,10 @@
       <c r="B2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
       <c r="G2" s="163"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -69684,10 +69684,10 @@
       <c r="M2" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="146"/>
-      <c r="O2" s="146"/>
-      <c r="P2" s="146"/>
-      <c r="Q2" s="147"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="144"/>
+      <c r="Q2" s="149"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
       <c r="T2" s="11"/>
@@ -69695,10 +69695,10 @@
       <c r="V2" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="W2" s="146"/>
-      <c r="X2" s="146"/>
-      <c r="Y2" s="146"/>
-      <c r="Z2" s="147"/>
+      <c r="W2" s="144"/>
+      <c r="X2" s="144"/>
+      <c r="Y2" s="144"/>
+      <c r="Z2" s="149"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
       <c r="AC2" s="10"/>
@@ -69817,10 +69817,10 @@
       <c r="V5" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="W5" s="146"/>
-      <c r="X5" s="146"/>
-      <c r="Y5" s="146"/>
-      <c r="Z5" s="147"/>
+      <c r="W5" s="144"/>
+      <c r="X5" s="144"/>
+      <c r="Y5" s="144"/>
+      <c r="Z5" s="149"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="10"/>
@@ -69866,10 +69866,10 @@
       <c r="B7" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="146"/>
-      <c r="D7" s="146"/>
-      <c r="E7" s="146"/>
-      <c r="F7" s="147"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="149"/>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -69878,10 +69878,10 @@
       <c r="L7" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="146"/>
-      <c r="N7" s="146"/>
-      <c r="O7" s="146"/>
-      <c r="P7" s="147"/>
+      <c r="M7" s="144"/>
+      <c r="N7" s="144"/>
+      <c r="O7" s="144"/>
+      <c r="P7" s="149"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
@@ -70090,10 +70090,10 @@
       <c r="AB14" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="AC14" s="146"/>
-      <c r="AD14" s="146"/>
-      <c r="AE14" s="146"/>
-      <c r="AF14" s="147"/>
+      <c r="AC14" s="144"/>
+      <c r="AD14" s="144"/>
+      <c r="AE14" s="144"/>
+      <c r="AF14" s="149"/>
       <c r="AG14" s="100"/>
       <c r="AH14" s="45"/>
       <c r="AI14" s="12"/>
@@ -70167,10 +70167,10 @@
       <c r="AB17" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="AC17" s="146"/>
-      <c r="AD17" s="146"/>
-      <c r="AE17" s="146"/>
-      <c r="AF17" s="147"/>
+      <c r="AC17" s="144"/>
+      <c r="AD17" s="144"/>
+      <c r="AE17" s="144"/>
+      <c r="AF17" s="149"/>
       <c r="AG17" s="102"/>
       <c r="AH17" s="38"/>
       <c r="AI17" s="10"/>
@@ -70288,10 +70288,10 @@
       <c r="AB21" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="AC21" s="146"/>
-      <c r="AD21" s="146"/>
-      <c r="AE21" s="146"/>
-      <c r="AF21" s="147"/>
+      <c r="AC21" s="144"/>
+      <c r="AD21" s="144"/>
+      <c r="AE21" s="144"/>
+      <c r="AF21" s="149"/>
       <c r="AG21" s="116"/>
       <c r="AH21" s="117"/>
     </row>
@@ -71104,7 +71104,7 @@
         <v>781</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>782</v>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A8BBAE-F033-478E-90D4-D4528F65E15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529870C9-7E70-4ACB-982F-C2B8467411F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5790" yWindow="1035" windowWidth="18660" windowHeight="13995" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9846" uniqueCount="7755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10554" uniqueCount="8347">
   <si>
     <t>Upgrade_Table</t>
   </si>
@@ -26667,6 +26667,2256 @@
   </si>
   <si>
     <t>収穫に行って、最初のステージをクリアしよう!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세계수 월드 뷰. 비우면 씬에서 찾는다</t>
+  </si>
+  <si>
+    <t>수확석</t>
+  </si>
+  <si>
+    <t>돌아가기</t>
+  </si>
+  <si>
+    <t>세계수가 {0}단계({1})가 되면 열려요</t>
+  </si>
+  <si>
+    <t>{0}을(를) 데려오려면 {1}{2}이 필요해요 (지금 {3})</t>
+  </si>
+  <si>
+    <t>한 번 더 누르면 {0}{1}으로 {2}을(를) 데려와요</t>
+  </si>
+  <si>
+    <t>{0}이(가) 세계수에 왔어요!</t>
+  </si>
+  <si>
+    <t>Lv 업에 {0}{1}이 필요해요</t>
+  </si>
+  <si>
+    <t>{0}은(는) 마지막 진화까지 마쳤어요 {1}</t>
+  </si>
+  <si>
+    <t>세계수가 {0}단계({1})가 되면 ★{2} 진화가 열려요</t>
+  </si>
+  <si>
+    <t>Lv.{0}이 되면 진화할 수 있어요 (지금 Lv.{1})</t>
+  </si>
+  <si>
+    <t>★{0} 진화에 {1}{2}이 필요해요 (지금 {3})</t>
+  </si>
+  <si>
+    <t>한 번 더 누르면 {0}{1}으로 ★{2} 진화해요</t>
+  </si>
+  <si>
+    <t>{0} 진화! {1}</t>
+  </si>
+  <si>
+    <t>라운드를 그리는 월드 뷰 (Prefabs/Round 프리팹을 쓰는 RoundView)</t>
+  </si>
+  <si>
+    <t>1920×1080 기준 캔버스 영역. 비우면 화면 전체를 1920×1080으로 본다</t>
+  </si>
+  <si>
+    <t>지금 끝내기</t>
+  </si>
+  <si>
+    <t>1920×1080 기준 캔버스 영역 (화면 → 스테이지 좌표). 비우면 화면 전체를 1920×1080으로 본다</t>
+  </si>
+  <si>
+    <t>세계수 · {0}단계 {1}</t>
+  </si>
+  <si>
+    <t>나이테 Lv.{0}/{1}</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;나이테&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>나무버섯 성장 +{0}</t>
+  </si>
+  <si>
+    <t>슬롯 {0}→{1} · 장식 {2}→{3}</t>
+  </si>
+  <si>
+    <t>{0} 해금</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;공물&lt;/b&gt;  창고 버섯 {0}개 → 경험치 +{1}</t>
+  </si>
+  <si>
+    <t>선호 ×2: {0}</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;아르카나 세계수&lt;/b&gt; · 최종 단계</t>
+  </si>
+  <si>
+    <t>수확</t>
+  </si>
+  <si>
+    <t>보따리 최대 {0}</t>
+  </si>
+  <si>
+    <t>시간당 {0}  {1}</t>
+  </si>
+  <si>
+    <t>{0} {1}단계</t>
+  </si>
+  <si>
+    <t>세계수의 가호</t>
+  </si>
+  <si>
+    <t>라운드 영구 적용</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}단계 {1}&lt;/b&gt;  {2}</t>
+  </si>
+  <si>
+    <t>나이테 Lv.{0} 필요</t>
+  </si>
+  <si>
+    <t>세계수 {0}단계 {1}! · 가호: {2}</t>
+  </si>
+  <si>
+    <t>{0} 합류 가능</t>
+  </si>
+  <si>
+    <t>바칠 버섯 없음</t>
+  </si>
+  <si>
+    <t>공물 · 경험치 +{0}</t>
+  </si>
+  <si>
+    <t>진화 가능!</t>
+  </si>
+  <si>
+    <t>Lv 합계 {0}: 장식 슬롯 +1</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;구역&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>선호 구역 수확 +50% · 빈 구역은 수확 안 함</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt;  세계수 {1}단계 해금</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt;  합류 가능</t>
+  </si>
+  <si>
+    <t>데려오기 {0}</t>
+  </si>
+  <si>
+    <t>{0} · 수확 ×{1}</t>
+  </si>
+  <si>
+    <t>쉬는 중 · 선호 {0}</t>
+  </si>
+  <si>
+    <t>진화 필요</t>
+  </si>
+  <si>
+    <t>진화 최대</t>
+  </si>
+  <si>
+    <t>★{0} · {1}단계</t>
+  </si>
+  <si>
+    <t>진화 ★{0} {1}</t>
+  </si>
+  <si>
+    <t>보상 {0} · 호감도 +{1} · 매일 3개</t>
+  </si>
+  <si>
+    <t>아직 부탁 없음</t>
+  </si>
+  <si>
+    <t>이번 주 {0}/{1}</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;꼬마의 상자&lt;/b&gt;  {0}</t>
+  </si>
+  <si>
+    <t>{0} 합류!</t>
+  </si>
+  <si>
+    <t>★{1} 진화: 세계수 {0}단계 필요</t>
+  </si>
+  <si>
+    <t>Lv.{0} 필요</t>
+  </si>
+  <si>
+    <t>반짝반짝… 진화했어!</t>
+  </si>
+  <si>
+    <t>{0} 진화 ★{1}! {2}</t>
+  </si>
+  <si>
+    <t>선물할 버섯 없음</t>
+  </si>
+  <si>
+    <t>{0}에게 {1} ×{2}</t>
+  </si>
+  <si>
+    <t>버섯 부족</t>
+  </si>
+  <si>
+    <t>부탁 완료 · {0}+{1}</t>
+  </si>
+  <si>
+    <t>도감 {0}/{1}종</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;공방 잠김&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>세계수 장식 제작</t>
+  </si>
+  <si>
+    <t>제작 중</t>
+  </si>
+  <si>
+    <t>슬롯 {0}/{1} · 즉시 완료 오늘 {2}회</t>
+  </si>
+  <si>
+    <t>제작 중인 장식 없음</t>
+  </si>
+  <si>
+    <t>레시피</t>
+  </si>
+  <si>
+    <t>합류하면 열림: {0}</t>
+  </si>
+  <si>
+    <t>보유 ★{0}</t>
+  </si>
+  <si>
+    <t>제작 {0}</t>
+  </si>
+  <si>
+    <t>제작 슬롯 가득</t>
+  </si>
+  <si>
+    <t>공방 미해금</t>
+  </si>
+  <si>
+    <t>{0} 제작 시작 · {1}</t>
+  </si>
+  <si>
+    <t>{0} 완성! · 강화 재료 +1</t>
+  </si>
+  <si>
+    <t>이미 완성</t>
+  </si>
+  <si>
+    <t>오늘 즉시 완료 소진</t>
+  </si>
+  <si>
+    <t>아름다움</t>
+  </si>
+  <si>
+    <t>보유 장식 합계</t>
+  </si>
+  <si>
+    <t>{0}점 · 최대</t>
+  </si>
+  <si>
+    <t>{0}/{1}점</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;아름다움 {0}점&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>다음 {0}점: {1}</t>
+  </si>
+  <si>
+    <t>장식 슬롯</t>
+  </si>
+  <si>
+    <t>{0}칸</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;슬롯 {0}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>빈 슬롯</t>
+  </si>
+  <si>
+    <t>보유 장식 없음 · 공방에서 제작</t>
+  </si>
+  <si>
+    <t>세트 효과</t>
+  </si>
+  <si>
+    <t>같은 꼬마 장식 3종: 수확 +{0} · 특별 보너스 +1단계</t>
+  </si>
+  <si>
+    <t>보유 장식</t>
+  </si>
+  <si>
+    <t>{0}종</t>
+  </si>
+  <si>
+    <t>첫 배치! {0} · {1}+{2} · {3} 호감도 +{4}</t>
+  </si>
+  <si>
+    <t>강화 재료 부족 (같은 장식 1개)</t>
+  </si>
+  <si>
+    <t>Buttons (비우면 이름으로 찾음)</t>
+  </si>
+  <si>
+    <t>Panels (비워도 됨)</t>
+  </si>
+  <si>
+    <t>정말 초기화하시겠습니까?</t>
+  </si>
+  <si>
+    <t>예</t>
+  </si>
+  <si>
+    <t>아니오</t>
+  </si>
+  <si>
+    <t>닫기</t>
+  </si>
+  <si>
+    <t>설정</t>
+  </si>
+  <si>
+    <t>으앗!</t>
+  </si>
+  <si>
+    <t>높다~!</t>
+  </si>
+  <si>
+    <t>내려 줘~</t>
+  </si>
+  <si>
+    <t>와아!</t>
+  </si>
+  <si>
+    <t>어디 가?</t>
+  </si>
+  <si>
+    <t>아야!</t>
+  </si>
+  <si>
+    <t>콩!</t>
+  </si>
+  <si>
+    <t>휴~</t>
+  </si>
+  <si>
+    <t>다시 해 줘!</t>
+  </si>
+  <si>
+    <t>여기 좋다~</t>
+  </si>
+  <si>
+    <t>높은 데 최고!</t>
+  </si>
+  <si>
+    <t>냠냠 버섯 냄새</t>
+  </si>
+  <si>
+    <t>바람 시원해~</t>
+  </si>
+  <si>
+    <t>World Tree world view. If empty, finds it in the scene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹のワールドビュー。空なら、シーンから探します</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Мировой вид Мирового древа. Если пусто, ищется в сцене</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Світовий вигляд Світового дерева. Якщо порожньо, шукається в сцені</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Harvest Stone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>収穫石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Камень урожая</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Камінь урожаю</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Back</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>もどる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Назад</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Opens when the World Tree reaches Tier {0} ({1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹が{0}段階({1})になると開きます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Откроется, когда Мировое древо достигнет стадии {0} ({1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Відкриється, коли Світове дерево досягне ярусу {0} ({1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bringing {0} needs {1}{2} (now {3})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}を連れてくるには{1}{2}が必要です (今 {3})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Чтобы привести {0}, нужно {1}{2} (сейчас {3})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Щоб привести {0}, потрібно {1}{2} (зараз {3})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Press again to bring {2} over for {0}{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>もう一度押すと、{0}{1}で{2}を連れてきます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Нажми ещё раз, чтобы привести {2} за {0}{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Натисни ще раз, щоб привести {2} за {0}{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} came to the World Tree!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}が世界樹に来たよ!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} теперь на Мировом древе!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} тепер на Світовому дереві!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level Up needs {0}{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lvアップに{0}{1}が必要です</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Для повышения ур. нужно {0}{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Для підвищення рів. потрібно {0}{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} has reached its final evolution {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}は最後の進化まで終わりました {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} достиг финальной эволюции {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} досягнув фінальної еволюції {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★{2} Evolution opens when the World Tree reaches Tier {0} ({1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹が{0}段階({1})になると★{2}進化が開きます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Эволюция ★{2} откроется, когда Мировое древо достигнет стадии {0} ({1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Еволюція ★{2} відкриється, коли Світове дерево досягне ярусу {0} ({1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can evolve at Lv.{0} (now Lv.{1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lv.{0}になると進化できます (今 Lv.{1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Эволюция доступна с Ур.{0} (сейчас Ур.{1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Еволюція доступна з рів. {0} (зараз рів. {1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★{0} Evolution needs {1}{2} (now {3})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★{0}進化には{1}{2}が必要です (今 {3})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Для эволюции ★{0} нужно {1}{2} (сейчас {3})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Для еволюції ★{0} потрібно {1}{2} (зараз {3})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Press again to evolve to ★{2} for {0}{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>もう一度押すと、{0}{1}で★{2}に進化します</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Нажми ещё раз: эволюция до ★{2} за {0}{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Натисни ще раз: еволюція до ★{2} за {0}{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} evolved! {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}が進化! {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}: эволюция! {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}: еволюція! {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>World view that draws rounds (RoundView using the Prefabs/Round prefab)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ラウンドを描くワールドビュー (Prefabs/Roundプレハブを使うRoundView)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Мировой вид, рисующий раунды (RoundView на префабе Prefabs/Round)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Світовий вигляд, що малює раунди (RoundView на префабі Prefabs/Round)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Canvas area based on 1920×1080. If empty, the whole screen is treated as 1920×1080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1920×1080基準のキャンバス領域。空なら、画面全体を1920×1080として扱います</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Область холста на основе 1920×1080. Если пусто, весь экран считается 1920×1080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Область полотна на основі 1920×1080. Якщо порожньо, увесь екран вважається 1920×1080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>End Now</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今すぐ終わる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Завершить сейчас</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Завершити зараз</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Canvas area based on 1920×1080 (screen → stage coordinates). If empty, the whole screen is treated as 1920×1080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1920×1080基準のキャンバス領域 (画面 → ステージ座標)。空なら、画面全体を1920×1080として扱います</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Область холста на основе 1920×1080 (экран → координаты этапа). Если пусто, весь экран считается 1920×1080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Область полотна на основі 1920×1080 (екран → координати етапу). Якщо порожньо, увесь екран вважається 1920×1080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>World Tree · Tier {0} {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Мировое древо · стадия {0}: {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Світове дерево · ярус {0}: {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tree Rings Lv.{0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年輪 Lv.{0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Годовые кольца Ур.{0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Річні кільця: рів. {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Tree Rings&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;年輪&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Годовые кольца&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Річні кільця&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tree Mushroom growth +{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ツリーキノコの成長 +{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Рост древесных грибов +{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ріст деревних грибів +{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slots {0}→{1} · Decor {2}→{3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Слоты {0}→{1} · Украшения {2}→{3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Слоти {0}→{1} · Декор {2}→{3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} unlocked</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}解放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}: открыто</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}: відкрито</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Offering&lt;/b&gt;  {0} Granary mushrooms → EXP +{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;お供え&lt;/b&gt;  倉庫のキノコ {0}個 → 経験値 +{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Подношение&lt;/b&gt;  Грибов из кладовой: {0} → Опыт +{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Дар&lt;/b&gt;  грибів у коморі: {0} → досвід +{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Preferred ×2: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好み ×2:{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Любимое ×2: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Улюблене ×2: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Arcana World Tree&lt;/b&gt; · Final Tier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Мировое древо Аркана&lt;/b&gt; · финальная стадия</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Світове дерево Аркани&lt;/b&gt; · фінальний ярус</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Harvest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>収穫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Сбор</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Збір</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basket max {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふろしき最大 {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Корзина макс. {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Макс. у кошику: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Per hour {0}  {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1時間あたり {0}  {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>В час {0}  {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>За годину {0}  {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} Tier {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} {1}段階</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}: стадия {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}: ярус {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>World Tree's Blessing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹の加護</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Благословение Мирового древа</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Благословення Світового дерева</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Permanent in rounds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ラウンドにずっと適用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Действует в раундах постоянно</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Постійне в раундах</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Tier {0} {1}&lt;/b&gt;  {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}段階 {1}&lt;/b&gt;  {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Стадия {0}: {1}&lt;/b&gt;  {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Ярус {0}: {1}&lt;/b&gt;  {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tree Rings Lv.{0} needed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年輪 Lv.{0}が必要です</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Нужны годовые кольца Ур.{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Потрібні річні кільця: рів. {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>World Tree Tier {0} {1}! · Blessing: {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Мировое древо: стадия {0}, {1}! · Благословение: {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Світове дерево: ярус {0}, {1}! · Благословення: {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} can join</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}が仲間入りできます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} может присоединиться</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} може приєднатися</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No mushrooms to offer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お供えするキノコがありません</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Нет грибов для подношения</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Немає грибів для дару</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Offering · EXP +{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Подношение · Опыт +{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Дар · досвід +{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ready to evolve!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進化できる!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Можно эволюционировать!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Можна еволюціонувати!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total Lv {0}: Decor Slot +1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lv合計 {0}:飾りの枠 +1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Сумма ур. {0}: слот украшений +1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Сума рів. {0}: слот декору +1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Zone&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;エリア&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Зона&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Preferred zone harvest +50% · Empty zones aren't harvested</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Любимая зона: урожай +50% · пустые зоны не собираются</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Улюблена зона: врожай +50% · порожні зони не збирають</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt;  Unlocks at World Tree Tier {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt;  世界樹{1}段階で解放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt;  Откроется на стадии {1} Мирового древа</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt;  Відкриється на ярусі {1} Світового дерева</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt;  can join</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt;  仲間入りできます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt;  может присоединиться</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt;  може приєднатися</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bring {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>連れてくる {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Привести {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} · Harvest ×{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} · Урожай ×{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} · Врожай ×{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resting · Prefers {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Отдыхает · любимая: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Відпочиває · улюблена: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evolution needed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進化が必要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Нужна эволюция</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Потрібна еволюція</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max Evolution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進化最大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Макс. эволюция</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Макс. еволюція</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★{0} · Tier {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★{0} · стадия {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★{0} · ярус {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evolve ★{0} {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進化 ★{0} {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Эволюция ★{0} {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Еволюція ★{0} {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward {0} · Affection +{1} · 3 daily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Награда {0} · Привязанность +{1} · 3 в день</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Нагорода {0} · Прихильність +{1} · 3 на день</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No Favors yet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>まだお願いはありません</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Пока нет просьб</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Поки немає прохань</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>This week {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今週 {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>На этой неделе {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Цього тижня {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Little One's Box&lt;/b&gt;  {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;ちびの箱&lt;/b&gt;  {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Ящик малыша&lt;/b&gt;  {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Скринька малюка&lt;/b&gt;  {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} joined!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}が仲間入り!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} с нами!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} приєднується!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★{1} Evolution: World Tree Tier {0} needed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★{1}進化:世界樹{0}段階が必要です</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Эволюция ★{1}: нужна стадия {0} Мирового древа</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Еволюція ★{1}: потрібен ярус {0} Світового дерева</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lv.{0} needed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lv.{0}が必要です</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Нужен Ур.{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Потрібен рів. {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sparkle sparkle… I evolved!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>きらきら…進化したよ!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Блеск-блеск… Я эволюционировал!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Блиск-блиск… Я еволюціонував!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} evolved ★{1}! {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}が進化 ★{1}! {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}: эволюция ★{1}! {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}: еволюція ★{1}! {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No mushrooms to gift</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>プレゼントするキノコがありません</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Нет грибов для подарка</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Немає грибів для подарунка</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{1} ×{2} to {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}に{1} ×{2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Для {0}: {1} ×{2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not enough mushrooms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>キノコが足りません</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Не хватает грибов</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Бракує грибів</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Favor done · {0}+{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Просьба выполнена · {0}+{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Прохання виконано · {0}+{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Collection {0}/{1} species</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>図鑑 {0}/{1}種</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Атлас {0}/{1} видов</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Колекція {0}/{1} видів</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Workshop Locked&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;工房はロック中&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Мастерская закрыта&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Майстерня зачинена&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Craft World Tree Decor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹の飾りを作る</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Изготовление украшений для Мирового древа</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Виготовлення декору для Світового дерева</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crafting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Изготовление</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Виготовлення</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slots {0}/{1} · Instant finishes today: {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Слоты {0}/{1} · Мгновенно сегодня: {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Слоти {0}/{1} · Миттєвих завершень сьогодні: {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No decor being crafted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作中の飾りはありません</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Нет украшений в изготовлении</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Немає декору у виготовленні</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recipes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>レシピ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Рецепты</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Рецепти</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unlocks when it joins: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仲間入りすると解放:{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Откроется, когда присоединится: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Відкриється, коли приєднається: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Owned ★{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所持 ★{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Есть ★{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Є: ★{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Craft {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作 {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Создать {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Створити {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crafting slots full</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作枠がいっぱい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Слоты изготовления заняты</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Слоти виготовлення зайняті</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Workshop not unlocked</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工房は未解放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Мастерская не открыта</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Майстерня не відкрита</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Started crafting {0} · {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Началось изготовление: {0} · {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Розпочато виготовлення: {0} · {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} complete! · Upgrade material +1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} готово! · Материал для улучшения +1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} готово! · Матеріал для покращення +1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>もうできあがり</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant finishes used up today</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今日の即完了は使い切り</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Мгновенные завершения на сегодня закончились</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Миттєві завершення на сьогодні вичерпано</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Beauty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美しさ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Красота</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Краса</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Owned Decor Total</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持っている飾りの合計</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Сумма имеющихся украшений</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Сума наявного декору</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} pts · Max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} оч. · Макс.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} балів · Макс.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}/{1} pts</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}/{1}点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}/{1} оч.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}/{1} балів</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Beauty {0} pts&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;美しさ {0}点&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Красота: {0} оч.&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Краса: {0} балів&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Next at {0} pts: {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>次の{0}点:{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Следующее на {0} оч.: {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Наступне на {0} балів: {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decor Slots</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飾りの枠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Слоты украшений</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Слоти декору</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} slots</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}枠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Слотов: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Слотів: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Slot {0}&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;枠 {0}&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Слот {0}&lt;/b&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Empty Slot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空き枠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Пустой слот</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Порожній слот</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No decor owned · Craft at the Workshop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Нет украшений · Создай в Мастерской</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Немає декору · Створи в Майстерні</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set Effect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>セット効果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Эффект набора</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ефект набору</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 decor of the same Little One: Harvest +{0} · Special bonus +1 tier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 украшения одного малыша: урожай +{0} · особый бонус +1 уровень</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 декори одного малюка: врожай +{0} · особливий бонус +1 ступінь</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Owned Decor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持っている飾り</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Имеющиеся украшения</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Наявний декор</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} species</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}種</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} видов</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} видів</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>First placement! {0} · {1}+{2} · {3} Affection +{4}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Первая расстановка! {0} · {1}+{2} · {3} Привязанность +{4}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Перше розміщення! {0} · {1}+{2} · {3} Прихильність +{4}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not enough upgrade material (1 same decoration)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>強化材料が足りません (同じ飾り1個)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Не хватает материала для улучшения (1 такое же украшение)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Бракує матеріалу для покращення (1 такий самий декор)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buttons (looked up by name if empty)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buttons (空なら名前で探します)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buttons (если пусто, ищутся по имени)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buttons (якщо порожньо, шукаються за назвою)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panels (optional)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panels (空でもかまいません)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panels (можно оставить пустым)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panels (можна залишити порожнім)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Really reset?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本当に初期化しますか?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Точно сбросить?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Точно скинути?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>はい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Да</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Так</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いいえ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ні</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Close</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>閉じる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Закрыть</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Закрити</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Settings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Настройки</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Налаштування</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eep!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>わっ!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ой-ой!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>So high~!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高い〜!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Как высоко~!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Як високо~!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Put me down~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>おろして〜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Спусти меня~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Спусти мене~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wow!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>わあ!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ух ты!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Вау!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Where to?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>どこ行くの?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Куда?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Куди?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ouch!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いたっ!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ай!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonk!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ごん!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Бам!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phew~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふぅ〜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Уф~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Do it again!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>もう一回!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ещё раз!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ще раз!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I like it here~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ここ、いいな〜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Тут хорошо~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Тут добре~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>High places are the best!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高いところ最高!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Высота — это класс!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Висота — найкраще!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yum yum, mushroom smell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>むしゃむしゃ、キノコのにおい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ням-ням, пахнет грибами</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ням-ням, пахне грибами</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The breeze feels nice~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>風が気持ちいい〜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ветерок — прелесть~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Вітерець — краса~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹・{0}段階 {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枠 {0}→{1}・飾り {2}→{3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;アルカナ世界樹&lt;/b&gt;・最終段階</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹が{0}段階 {1}に!・加護:{2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お供え・経験値 +{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好きなエリアの収穫 +50%・誰もいないエリアは収穫しません</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}・収穫 ×{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お休み中・好み {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★{0}・{1}段階</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ごほうび {0}・好感度 +{1}・毎日3つ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お願い完了・{0}+{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枠 {0}/{1}・即完了 今日 {2}回</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}の制作を開始・{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}完成!・強化材料 +1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}点・最大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持っている飾りなし・工房で制作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同じちびの飾り3種:収穫 +{0}・特別ボーナス +1段階</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初めての配置! {0}・{1}+{2}・{3} 好感度 +{4}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Улучшения древа грибницы</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Покращення дерева грибниці</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Погода</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Кнопка вызова босса</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Кнопка виклику боса</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Открыта новая функция: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Відкрито нову функцію: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Схвати сборщика, потяни вниз и отпусти — он полетит к грибу!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Схопи збирача, потягни вниз і відпусти — він полетить до гриба!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Купи первое улучшение! Нажми на светящийся узел</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Купи перше покращення! Натисни на вузол, що світиться</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ты стал сильнее! Снова на сбор урожая?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ти став сильнішим! Знову на збір урожаю?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Отправляйся за урожаем и пройди первый этап!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Вирушай по врожай і пройди перший етап!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -30792,7 +33042,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H1430"/>
+  <dimension ref="A1:H1548"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.75" style="2" bestFit="1" customWidth="1"/>
@@ -67506,10 +69756,10 @@
         <v>7740</v>
       </c>
       <c r="G1423" s="130" t="s">
-        <v>816</v>
+        <v>8332</v>
       </c>
       <c r="H1423" s="130" t="s">
-        <v>816</v>
+        <v>8333</v>
       </c>
     </row>
     <row r="1424" spans="1:8">
@@ -67532,10 +69782,10 @@
         <v>7742</v>
       </c>
       <c r="G1424" s="130" t="s">
-        <v>816</v>
+        <v>8334</v>
       </c>
       <c r="H1424" s="130" t="s">
-        <v>816</v>
+        <v>8334</v>
       </c>
     </row>
     <row r="1425" spans="1:8">
@@ -67558,10 +69808,10 @@
         <v>7744</v>
       </c>
       <c r="G1425" s="130" t="s">
-        <v>816</v>
+        <v>8335</v>
       </c>
       <c r="H1425" s="130" t="s">
-        <v>816</v>
+        <v>8336</v>
       </c>
     </row>
     <row r="1426" spans="1:8">
@@ -67584,10 +69834,10 @@
         <v>7746</v>
       </c>
       <c r="G1426" s="130" t="s">
-        <v>816</v>
+        <v>8337</v>
       </c>
       <c r="H1426" s="130" t="s">
-        <v>816</v>
+        <v>8338</v>
       </c>
     </row>
     <row r="1427" spans="1:8">
@@ -67610,10 +69860,10 @@
         <v>7748</v>
       </c>
       <c r="G1427" s="130" t="s">
-        <v>816</v>
+        <v>8339</v>
       </c>
       <c r="H1427" s="130" t="s">
-        <v>816</v>
+        <v>8340</v>
       </c>
     </row>
     <row r="1428" spans="1:8">
@@ -67636,10 +69886,10 @@
         <v>7750</v>
       </c>
       <c r="G1428" s="130" t="s">
-        <v>816</v>
+        <v>8341</v>
       </c>
       <c r="H1428" s="130" t="s">
-        <v>816</v>
+        <v>8342</v>
       </c>
     </row>
     <row r="1429" spans="1:8">
@@ -67662,10 +69912,10 @@
         <v>7752</v>
       </c>
       <c r="G1429" s="130" t="s">
-        <v>816</v>
+        <v>8343</v>
       </c>
       <c r="H1429" s="130" t="s">
-        <v>816</v>
+        <v>8344</v>
       </c>
     </row>
     <row r="1430" spans="1:8">
@@ -67688,10 +69938,3078 @@
         <v>7754</v>
       </c>
       <c r="G1430" s="130" t="s">
-        <v>816</v>
+        <v>8345</v>
       </c>
       <c r="H1430" s="130" t="s">
-        <v>816</v>
+        <v>8346</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:8">
+      <c r="A1431">
+        <v>901204</v>
+      </c>
+      <c r="B1431" s="2">
+        <v>91204</v>
+      </c>
+      <c r="C1431" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1431" s="130" t="s">
+        <v>7755</v>
+      </c>
+      <c r="E1431" s="130" t="s">
+        <v>7873</v>
+      </c>
+      <c r="F1431" s="130" t="s">
+        <v>7874</v>
+      </c>
+      <c r="G1431" s="130" t="s">
+        <v>7875</v>
+      </c>
+      <c r="H1431" s="130" t="s">
+        <v>7876</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:8">
+      <c r="A1432">
+        <v>901205</v>
+      </c>
+      <c r="B1432" s="2">
+        <v>91205</v>
+      </c>
+      <c r="C1432" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1432" s="130" t="s">
+        <v>7756</v>
+      </c>
+      <c r="E1432" s="130" t="s">
+        <v>7877</v>
+      </c>
+      <c r="F1432" s="130" t="s">
+        <v>7878</v>
+      </c>
+      <c r="G1432" s="130" t="s">
+        <v>7879</v>
+      </c>
+      <c r="H1432" s="130" t="s">
+        <v>7880</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:8">
+      <c r="A1433">
+        <v>901206</v>
+      </c>
+      <c r="B1433" s="2">
+        <v>91206</v>
+      </c>
+      <c r="C1433" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1433" s="130" t="s">
+        <v>7757</v>
+      </c>
+      <c r="E1433" s="130" t="s">
+        <v>7881</v>
+      </c>
+      <c r="F1433" s="130" t="s">
+        <v>7882</v>
+      </c>
+      <c r="G1433" s="130" t="s">
+        <v>7883</v>
+      </c>
+      <c r="H1433" s="130" t="s">
+        <v>7883</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:8">
+      <c r="A1434">
+        <v>901207</v>
+      </c>
+      <c r="B1434" s="2">
+        <v>91207</v>
+      </c>
+      <c r="C1434" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1434" s="130" t="s">
+        <v>7758</v>
+      </c>
+      <c r="E1434" s="130" t="s">
+        <v>7884</v>
+      </c>
+      <c r="F1434" s="130" t="s">
+        <v>7885</v>
+      </c>
+      <c r="G1434" s="130" t="s">
+        <v>7886</v>
+      </c>
+      <c r="H1434" s="130" t="s">
+        <v>7887</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:8">
+      <c r="A1435">
+        <v>901208</v>
+      </c>
+      <c r="B1435" s="2">
+        <v>91208</v>
+      </c>
+      <c r="C1435" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1435" s="130" t="s">
+        <v>7759</v>
+      </c>
+      <c r="E1435" s="130" t="s">
+        <v>7888</v>
+      </c>
+      <c r="F1435" s="130" t="s">
+        <v>7889</v>
+      </c>
+      <c r="G1435" s="130" t="s">
+        <v>7890</v>
+      </c>
+      <c r="H1435" s="130" t="s">
+        <v>7891</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:8">
+      <c r="A1436">
+        <v>901209</v>
+      </c>
+      <c r="B1436" s="2">
+        <v>91209</v>
+      </c>
+      <c r="C1436" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1436" s="130" t="s">
+        <v>7760</v>
+      </c>
+      <c r="E1436" s="130" t="s">
+        <v>7892</v>
+      </c>
+      <c r="F1436" s="130" t="s">
+        <v>7893</v>
+      </c>
+      <c r="G1436" s="130" t="s">
+        <v>7894</v>
+      </c>
+      <c r="H1436" s="130" t="s">
+        <v>7895</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:8">
+      <c r="A1437">
+        <v>901210</v>
+      </c>
+      <c r="B1437" s="2">
+        <v>91210</v>
+      </c>
+      <c r="C1437" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1437" s="130" t="s">
+        <v>7761</v>
+      </c>
+      <c r="E1437" s="130" t="s">
+        <v>7896</v>
+      </c>
+      <c r="F1437" s="130" t="s">
+        <v>7897</v>
+      </c>
+      <c r="G1437" s="130" t="s">
+        <v>7898</v>
+      </c>
+      <c r="H1437" s="130" t="s">
+        <v>7899</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:8">
+      <c r="A1438">
+        <v>901211</v>
+      </c>
+      <c r="B1438" s="2">
+        <v>91211</v>
+      </c>
+      <c r="C1438" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1438" s="130" t="s">
+        <v>7762</v>
+      </c>
+      <c r="E1438" s="130" t="s">
+        <v>7900</v>
+      </c>
+      <c r="F1438" s="130" t="s">
+        <v>7901</v>
+      </c>
+      <c r="G1438" s="130" t="s">
+        <v>7902</v>
+      </c>
+      <c r="H1438" s="130" t="s">
+        <v>7903</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:8">
+      <c r="A1439">
+        <v>901212</v>
+      </c>
+      <c r="B1439" s="2">
+        <v>91212</v>
+      </c>
+      <c r="C1439" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1439" s="130" t="s">
+        <v>7763</v>
+      </c>
+      <c r="E1439" s="130" t="s">
+        <v>7904</v>
+      </c>
+      <c r="F1439" s="130" t="s">
+        <v>7905</v>
+      </c>
+      <c r="G1439" s="130" t="s">
+        <v>7906</v>
+      </c>
+      <c r="H1439" s="130" t="s">
+        <v>7907</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:8">
+      <c r="A1440">
+        <v>901213</v>
+      </c>
+      <c r="B1440" s="2">
+        <v>91213</v>
+      </c>
+      <c r="C1440" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1440" s="130" t="s">
+        <v>7764</v>
+      </c>
+      <c r="E1440" s="130" t="s">
+        <v>7908</v>
+      </c>
+      <c r="F1440" s="130" t="s">
+        <v>7909</v>
+      </c>
+      <c r="G1440" s="130" t="s">
+        <v>7910</v>
+      </c>
+      <c r="H1440" s="130" t="s">
+        <v>7911</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:8">
+      <c r="A1441">
+        <v>901214</v>
+      </c>
+      <c r="B1441" s="2">
+        <v>91214</v>
+      </c>
+      <c r="C1441" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1441" s="130" t="s">
+        <v>7765</v>
+      </c>
+      <c r="E1441" s="130" t="s">
+        <v>7912</v>
+      </c>
+      <c r="F1441" s="130" t="s">
+        <v>7913</v>
+      </c>
+      <c r="G1441" s="130" t="s">
+        <v>7914</v>
+      </c>
+      <c r="H1441" s="130" t="s">
+        <v>7915</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:8">
+      <c r="A1442">
+        <v>901215</v>
+      </c>
+      <c r="B1442" s="2">
+        <v>91215</v>
+      </c>
+      <c r="C1442" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1442" s="130" t="s">
+        <v>7766</v>
+      </c>
+      <c r="E1442" s="130" t="s">
+        <v>7916</v>
+      </c>
+      <c r="F1442" s="130" t="s">
+        <v>7917</v>
+      </c>
+      <c r="G1442" s="130" t="s">
+        <v>7918</v>
+      </c>
+      <c r="H1442" s="130" t="s">
+        <v>7919</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:8">
+      <c r="A1443">
+        <v>901216</v>
+      </c>
+      <c r="B1443" s="2">
+        <v>91216</v>
+      </c>
+      <c r="C1443" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1443" s="130" t="s">
+        <v>7767</v>
+      </c>
+      <c r="E1443" s="130" t="s">
+        <v>7920</v>
+      </c>
+      <c r="F1443" s="130" t="s">
+        <v>7921</v>
+      </c>
+      <c r="G1443" s="130" t="s">
+        <v>7922</v>
+      </c>
+      <c r="H1443" s="130" t="s">
+        <v>7923</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:8">
+      <c r="A1444">
+        <v>901217</v>
+      </c>
+      <c r="B1444" s="2">
+        <v>91217</v>
+      </c>
+      <c r="C1444" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1444" s="130" t="s">
+        <v>7768</v>
+      </c>
+      <c r="E1444" s="130" t="s">
+        <v>7924</v>
+      </c>
+      <c r="F1444" s="130" t="s">
+        <v>7925</v>
+      </c>
+      <c r="G1444" s="130" t="s">
+        <v>7926</v>
+      </c>
+      <c r="H1444" s="130" t="s">
+        <v>7927</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:8">
+      <c r="A1445">
+        <v>901218</v>
+      </c>
+      <c r="B1445" s="2">
+        <v>91218</v>
+      </c>
+      <c r="C1445" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1445" s="130" t="s">
+        <v>7769</v>
+      </c>
+      <c r="E1445" s="130" t="s">
+        <v>7928</v>
+      </c>
+      <c r="F1445" s="130" t="s">
+        <v>7929</v>
+      </c>
+      <c r="G1445" s="130" t="s">
+        <v>7930</v>
+      </c>
+      <c r="H1445" s="130" t="s">
+        <v>7931</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:8">
+      <c r="A1446">
+        <v>901219</v>
+      </c>
+      <c r="B1446" s="2">
+        <v>91219</v>
+      </c>
+      <c r="C1446" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1446" s="130" t="s">
+        <v>7770</v>
+      </c>
+      <c r="E1446" s="130" t="s">
+        <v>7932</v>
+      </c>
+      <c r="F1446" s="130" t="s">
+        <v>7933</v>
+      </c>
+      <c r="G1446" s="130" t="s">
+        <v>7934</v>
+      </c>
+      <c r="H1446" s="130" t="s">
+        <v>7935</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:8">
+      <c r="A1447">
+        <v>901220</v>
+      </c>
+      <c r="B1447" s="2">
+        <v>91220</v>
+      </c>
+      <c r="C1447" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1447" s="130" t="s">
+        <v>7771</v>
+      </c>
+      <c r="E1447" s="130" t="s">
+        <v>7936</v>
+      </c>
+      <c r="F1447" s="130" t="s">
+        <v>7937</v>
+      </c>
+      <c r="G1447" s="130" t="s">
+        <v>7938</v>
+      </c>
+      <c r="H1447" s="130" t="s">
+        <v>7939</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:8">
+      <c r="A1448">
+        <v>901221</v>
+      </c>
+      <c r="B1448" s="2">
+        <v>91221</v>
+      </c>
+      <c r="C1448" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1448" s="130" t="s">
+        <v>7772</v>
+      </c>
+      <c r="E1448" s="130" t="s">
+        <v>7940</v>
+      </c>
+      <c r="F1448" s="130" t="s">
+        <v>7941</v>
+      </c>
+      <c r="G1448" s="130" t="s">
+        <v>7942</v>
+      </c>
+      <c r="H1448" s="130" t="s">
+        <v>7943</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:8">
+      <c r="A1449">
+        <v>901222</v>
+      </c>
+      <c r="B1449" s="2">
+        <v>91222</v>
+      </c>
+      <c r="C1449" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1449" s="130" t="s">
+        <v>7773</v>
+      </c>
+      <c r="E1449" s="130" t="s">
+        <v>7944</v>
+      </c>
+      <c r="F1449" s="130" t="s">
+        <v>8314</v>
+      </c>
+      <c r="G1449" s="130" t="s">
+        <v>7945</v>
+      </c>
+      <c r="H1449" s="130" t="s">
+        <v>7946</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:8">
+      <c r="A1450">
+        <v>901223</v>
+      </c>
+      <c r="B1450" s="2">
+        <v>91223</v>
+      </c>
+      <c r="C1450" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1450" s="130" t="s">
+        <v>7774</v>
+      </c>
+      <c r="E1450" s="130" t="s">
+        <v>7947</v>
+      </c>
+      <c r="F1450" s="130" t="s">
+        <v>7948</v>
+      </c>
+      <c r="G1450" s="130" t="s">
+        <v>7949</v>
+      </c>
+      <c r="H1450" s="130" t="s">
+        <v>7950</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:8">
+      <c r="A1451">
+        <v>901224</v>
+      </c>
+      <c r="B1451" s="2">
+        <v>91224</v>
+      </c>
+      <c r="C1451" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1451" s="130" t="s">
+        <v>7775</v>
+      </c>
+      <c r="E1451" s="130" t="s">
+        <v>7951</v>
+      </c>
+      <c r="F1451" s="130" t="s">
+        <v>7952</v>
+      </c>
+      <c r="G1451" s="130" t="s">
+        <v>7953</v>
+      </c>
+      <c r="H1451" s="130" t="s">
+        <v>7954</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:8">
+      <c r="A1452">
+        <v>901225</v>
+      </c>
+      <c r="B1452" s="2">
+        <v>91225</v>
+      </c>
+      <c r="C1452" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1452" s="130" t="s">
+        <v>7776</v>
+      </c>
+      <c r="E1452" s="130" t="s">
+        <v>7955</v>
+      </c>
+      <c r="F1452" s="130" t="s">
+        <v>7956</v>
+      </c>
+      <c r="G1452" s="130" t="s">
+        <v>7957</v>
+      </c>
+      <c r="H1452" s="130" t="s">
+        <v>7958</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:8">
+      <c r="A1453">
+        <v>901226</v>
+      </c>
+      <c r="B1453" s="2">
+        <v>91226</v>
+      </c>
+      <c r="C1453" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1453" s="130" t="s">
+        <v>7777</v>
+      </c>
+      <c r="E1453" s="130" t="s">
+        <v>7959</v>
+      </c>
+      <c r="F1453" s="130" t="s">
+        <v>8315</v>
+      </c>
+      <c r="G1453" s="130" t="s">
+        <v>7960</v>
+      </c>
+      <c r="H1453" s="130" t="s">
+        <v>7961</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:8">
+      <c r="A1454">
+        <v>901227</v>
+      </c>
+      <c r="B1454" s="2">
+        <v>91227</v>
+      </c>
+      <c r="C1454" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1454" s="130" t="s">
+        <v>7778</v>
+      </c>
+      <c r="E1454" s="130" t="s">
+        <v>7962</v>
+      </c>
+      <c r="F1454" s="130" t="s">
+        <v>7963</v>
+      </c>
+      <c r="G1454" s="130" t="s">
+        <v>7964</v>
+      </c>
+      <c r="H1454" s="130" t="s">
+        <v>7965</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:8">
+      <c r="A1455">
+        <v>901228</v>
+      </c>
+      <c r="B1455" s="2">
+        <v>91228</v>
+      </c>
+      <c r="C1455" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1455" s="130" t="s">
+        <v>7779</v>
+      </c>
+      <c r="E1455" s="130" t="s">
+        <v>7966</v>
+      </c>
+      <c r="F1455" s="130" t="s">
+        <v>7967</v>
+      </c>
+      <c r="G1455" s="130" t="s">
+        <v>7968</v>
+      </c>
+      <c r="H1455" s="130" t="s">
+        <v>7969</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:8">
+      <c r="A1456">
+        <v>901229</v>
+      </c>
+      <c r="B1456" s="2">
+        <v>91229</v>
+      </c>
+      <c r="C1456" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1456" s="130" t="s">
+        <v>7780</v>
+      </c>
+      <c r="E1456" s="130" t="s">
+        <v>7970</v>
+      </c>
+      <c r="F1456" s="130" t="s">
+        <v>7971</v>
+      </c>
+      <c r="G1456" s="130" t="s">
+        <v>7972</v>
+      </c>
+      <c r="H1456" s="130" t="s">
+        <v>7973</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:8">
+      <c r="A1457">
+        <v>901230</v>
+      </c>
+      <c r="B1457" s="2">
+        <v>91230</v>
+      </c>
+      <c r="C1457" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1457" s="130" t="s">
+        <v>7781</v>
+      </c>
+      <c r="E1457" s="130" t="s">
+        <v>7974</v>
+      </c>
+      <c r="F1457" s="130" t="s">
+        <v>8316</v>
+      </c>
+      <c r="G1457" s="130" t="s">
+        <v>7975</v>
+      </c>
+      <c r="H1457" s="130" t="s">
+        <v>7976</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:8">
+      <c r="A1458">
+        <v>901231</v>
+      </c>
+      <c r="B1458" s="2">
+        <v>91231</v>
+      </c>
+      <c r="C1458" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1458" s="130" t="s">
+        <v>7782</v>
+      </c>
+      <c r="E1458" s="130" t="s">
+        <v>7977</v>
+      </c>
+      <c r="F1458" s="130" t="s">
+        <v>7978</v>
+      </c>
+      <c r="G1458" s="130" t="s">
+        <v>7979</v>
+      </c>
+      <c r="H1458" s="130" t="s">
+        <v>7980</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:8">
+      <c r="A1459">
+        <v>901232</v>
+      </c>
+      <c r="B1459" s="2">
+        <v>91232</v>
+      </c>
+      <c r="C1459" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1459" s="130" t="s">
+        <v>7783</v>
+      </c>
+      <c r="E1459" s="130" t="s">
+        <v>7981</v>
+      </c>
+      <c r="F1459" s="130" t="s">
+        <v>7982</v>
+      </c>
+      <c r="G1459" s="130" t="s">
+        <v>7983</v>
+      </c>
+      <c r="H1459" s="130" t="s">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:8">
+      <c r="A1460">
+        <v>901233</v>
+      </c>
+      <c r="B1460" s="2">
+        <v>91233</v>
+      </c>
+      <c r="C1460" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1460" s="130" t="s">
+        <v>7784</v>
+      </c>
+      <c r="E1460" s="130" t="s">
+        <v>7985</v>
+      </c>
+      <c r="F1460" s="130" t="s">
+        <v>7986</v>
+      </c>
+      <c r="G1460" s="130" t="s">
+        <v>7987</v>
+      </c>
+      <c r="H1460" s="130" t="s">
+        <v>7988</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:8">
+      <c r="A1461">
+        <v>901234</v>
+      </c>
+      <c r="B1461" s="2">
+        <v>91234</v>
+      </c>
+      <c r="C1461" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1461" s="130" t="s">
+        <v>7785</v>
+      </c>
+      <c r="E1461" s="130" t="s">
+        <v>7989</v>
+      </c>
+      <c r="F1461" s="130" t="s">
+        <v>7990</v>
+      </c>
+      <c r="G1461" s="130" t="s">
+        <v>7991</v>
+      </c>
+      <c r="H1461" s="130" t="s">
+        <v>7992</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:8">
+      <c r="A1462">
+        <v>901235</v>
+      </c>
+      <c r="B1462" s="2">
+        <v>91235</v>
+      </c>
+      <c r="C1462" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1462" s="130" t="s">
+        <v>7786</v>
+      </c>
+      <c r="E1462" s="130" t="s">
+        <v>7993</v>
+      </c>
+      <c r="F1462" s="130" t="s">
+        <v>7994</v>
+      </c>
+      <c r="G1462" s="130" t="s">
+        <v>7995</v>
+      </c>
+      <c r="H1462" s="130" t="s">
+        <v>7996</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:8">
+      <c r="A1463">
+        <v>901236</v>
+      </c>
+      <c r="B1463" s="2">
+        <v>91236</v>
+      </c>
+      <c r="C1463" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1463" s="130" t="s">
+        <v>7787</v>
+      </c>
+      <c r="E1463" s="130" t="s">
+        <v>7997</v>
+      </c>
+      <c r="F1463" s="130" t="s">
+        <v>7998</v>
+      </c>
+      <c r="G1463" s="130" t="s">
+        <v>7999</v>
+      </c>
+      <c r="H1463" s="130" t="s">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:8">
+      <c r="A1464">
+        <v>901237</v>
+      </c>
+      <c r="B1464" s="2">
+        <v>91237</v>
+      </c>
+      <c r="C1464" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1464" s="130" t="s">
+        <v>7788</v>
+      </c>
+      <c r="E1464" s="130" t="s">
+        <v>8001</v>
+      </c>
+      <c r="F1464" s="130" t="s">
+        <v>8002</v>
+      </c>
+      <c r="G1464" s="130" t="s">
+        <v>8003</v>
+      </c>
+      <c r="H1464" s="130" t="s">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:8">
+      <c r="A1465">
+        <v>901238</v>
+      </c>
+      <c r="B1465" s="2">
+        <v>91238</v>
+      </c>
+      <c r="C1465" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1465" s="130" t="s">
+        <v>7789</v>
+      </c>
+      <c r="E1465" s="130" t="s">
+        <v>8005</v>
+      </c>
+      <c r="F1465" s="130" t="s">
+        <v>8006</v>
+      </c>
+      <c r="G1465" s="130" t="s">
+        <v>8007</v>
+      </c>
+      <c r="H1465" s="130" t="s">
+        <v>8008</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:8">
+      <c r="A1466">
+        <v>901239</v>
+      </c>
+      <c r="B1466" s="2">
+        <v>91239</v>
+      </c>
+      <c r="C1466" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1466" s="130" t="s">
+        <v>7790</v>
+      </c>
+      <c r="E1466" s="130" t="s">
+        <v>8009</v>
+      </c>
+      <c r="F1466" s="130" t="s">
+        <v>8317</v>
+      </c>
+      <c r="G1466" s="130" t="s">
+        <v>8010</v>
+      </c>
+      <c r="H1466" s="130" t="s">
+        <v>8011</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:8">
+      <c r="A1467">
+        <v>901240</v>
+      </c>
+      <c r="B1467" s="2">
+        <v>91240</v>
+      </c>
+      <c r="C1467" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1467" s="130" t="s">
+        <v>7791</v>
+      </c>
+      <c r="E1467" s="130" t="s">
+        <v>8012</v>
+      </c>
+      <c r="F1467" s="130" t="s">
+        <v>8013</v>
+      </c>
+      <c r="G1467" s="130" t="s">
+        <v>8014</v>
+      </c>
+      <c r="H1467" s="130" t="s">
+        <v>8015</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:8">
+      <c r="A1468">
+        <v>901241</v>
+      </c>
+      <c r="B1468" s="2">
+        <v>91241</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1468" s="130" t="s">
+        <v>7792</v>
+      </c>
+      <c r="E1468" s="130" t="s">
+        <v>8016</v>
+      </c>
+      <c r="F1468" s="130" t="s">
+        <v>8017</v>
+      </c>
+      <c r="G1468" s="130" t="s">
+        <v>8018</v>
+      </c>
+      <c r="H1468" s="130" t="s">
+        <v>8019</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:8">
+      <c r="A1469">
+        <v>901242</v>
+      </c>
+      <c r="B1469" s="2">
+        <v>91242</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1469" s="130" t="s">
+        <v>7793</v>
+      </c>
+      <c r="E1469" s="130" t="s">
+        <v>8020</v>
+      </c>
+      <c r="F1469" s="130" t="s">
+        <v>8318</v>
+      </c>
+      <c r="G1469" s="130" t="s">
+        <v>8021</v>
+      </c>
+      <c r="H1469" s="130" t="s">
+        <v>8022</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:8">
+      <c r="A1470">
+        <v>901243</v>
+      </c>
+      <c r="B1470" s="2">
+        <v>91243</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1470" s="130" t="s">
+        <v>7794</v>
+      </c>
+      <c r="E1470" s="130" t="s">
+        <v>8023</v>
+      </c>
+      <c r="F1470" s="130" t="s">
+        <v>8024</v>
+      </c>
+      <c r="G1470" s="130" t="s">
+        <v>8025</v>
+      </c>
+      <c r="H1470" s="130" t="s">
+        <v>8026</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:8">
+      <c r="A1471">
+        <v>901244</v>
+      </c>
+      <c r="B1471" s="2">
+        <v>91244</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1471" s="130" t="s">
+        <v>7795</v>
+      </c>
+      <c r="E1471" s="130" t="s">
+        <v>8027</v>
+      </c>
+      <c r="F1471" s="130" t="s">
+        <v>8028</v>
+      </c>
+      <c r="G1471" s="130" t="s">
+        <v>8029</v>
+      </c>
+      <c r="H1471" s="130" t="s">
+        <v>8030</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:8">
+      <c r="A1472">
+        <v>901245</v>
+      </c>
+      <c r="B1472" s="2">
+        <v>91245</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1472" s="130" t="s">
+        <v>7796</v>
+      </c>
+      <c r="E1472" s="130" t="s">
+        <v>8031</v>
+      </c>
+      <c r="F1472" s="130" t="s">
+        <v>8032</v>
+      </c>
+      <c r="G1472" s="130" t="s">
+        <v>8033</v>
+      </c>
+      <c r="H1472" s="130" t="s">
+        <v>8033</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:8">
+      <c r="A1473">
+        <v>901246</v>
+      </c>
+      <c r="B1473" s="2">
+        <v>91246</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1473" s="130" t="s">
+        <v>7797</v>
+      </c>
+      <c r="E1473" s="130" t="s">
+        <v>8034</v>
+      </c>
+      <c r="F1473" s="130" t="s">
+        <v>8319</v>
+      </c>
+      <c r="G1473" s="130" t="s">
+        <v>8035</v>
+      </c>
+      <c r="H1473" s="130" t="s">
+        <v>8036</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:8">
+      <c r="A1474">
+        <v>901247</v>
+      </c>
+      <c r="B1474" s="2">
+        <v>91247</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1474" s="130" t="s">
+        <v>7798</v>
+      </c>
+      <c r="E1474" s="130" t="s">
+        <v>8037</v>
+      </c>
+      <c r="F1474" s="130" t="s">
+        <v>8038</v>
+      </c>
+      <c r="G1474" s="130" t="s">
+        <v>8039</v>
+      </c>
+      <c r="H1474" s="130" t="s">
+        <v>8040</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:8">
+      <c r="A1475">
+        <v>901248</v>
+      </c>
+      <c r="B1475" s="2">
+        <v>91248</v>
+      </c>
+      <c r="C1475" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1475" s="130" t="s">
+        <v>7799</v>
+      </c>
+      <c r="E1475" s="130" t="s">
+        <v>8041</v>
+      </c>
+      <c r="F1475" s="130" t="s">
+        <v>8042</v>
+      </c>
+      <c r="G1475" s="130" t="s">
+        <v>8043</v>
+      </c>
+      <c r="H1475" s="130" t="s">
+        <v>8044</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:8">
+      <c r="A1476">
+        <v>901249</v>
+      </c>
+      <c r="B1476" s="2">
+        <v>91249</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1476" s="130" t="s">
+        <v>7800</v>
+      </c>
+      <c r="E1476" s="130" t="s">
+        <v>8045</v>
+      </c>
+      <c r="F1476" s="130" t="s">
+        <v>8046</v>
+      </c>
+      <c r="G1476" s="130" t="s">
+        <v>8047</v>
+      </c>
+      <c r="H1476" s="130" t="s">
+        <v>8047</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:8">
+      <c r="A1477">
+        <v>901250</v>
+      </c>
+      <c r="B1477" s="2">
+        <v>91250</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1477" s="130" t="s">
+        <v>7801</v>
+      </c>
+      <c r="E1477" s="130" t="s">
+        <v>8048</v>
+      </c>
+      <c r="F1477" s="130" t="s">
+        <v>8320</v>
+      </c>
+      <c r="G1477" s="130" t="s">
+        <v>8049</v>
+      </c>
+      <c r="H1477" s="130" t="s">
+        <v>8050</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:8">
+      <c r="A1478">
+        <v>901251</v>
+      </c>
+      <c r="B1478" s="2">
+        <v>91251</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1478" s="130" t="s">
+        <v>7802</v>
+      </c>
+      <c r="E1478" s="130" t="s">
+        <v>8051</v>
+      </c>
+      <c r="F1478" s="130" t="s">
+        <v>8321</v>
+      </c>
+      <c r="G1478" s="130" t="s">
+        <v>8052</v>
+      </c>
+      <c r="H1478" s="130" t="s">
+        <v>8053</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:8">
+      <c r="A1479">
+        <v>901252</v>
+      </c>
+      <c r="B1479" s="2">
+        <v>91252</v>
+      </c>
+      <c r="C1479" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1479" s="130" t="s">
+        <v>7803</v>
+      </c>
+      <c r="E1479" s="130" t="s">
+        <v>8054</v>
+      </c>
+      <c r="F1479" s="130" t="s">
+        <v>8055</v>
+      </c>
+      <c r="G1479" s="130" t="s">
+        <v>8056</v>
+      </c>
+      <c r="H1479" s="130" t="s">
+        <v>8057</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:8">
+      <c r="A1480">
+        <v>901253</v>
+      </c>
+      <c r="B1480" s="2">
+        <v>91253</v>
+      </c>
+      <c r="C1480" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1480" s="130" t="s">
+        <v>7804</v>
+      </c>
+      <c r="E1480" s="130" t="s">
+        <v>8058</v>
+      </c>
+      <c r="F1480" s="130" t="s">
+        <v>8059</v>
+      </c>
+      <c r="G1480" s="130" t="s">
+        <v>8060</v>
+      </c>
+      <c r="H1480" s="130" t="s">
+        <v>8061</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:8">
+      <c r="A1481">
+        <v>901254</v>
+      </c>
+      <c r="B1481" s="2">
+        <v>91254</v>
+      </c>
+      <c r="C1481" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1481" s="130" t="s">
+        <v>7805</v>
+      </c>
+      <c r="E1481" s="130" t="s">
+        <v>8062</v>
+      </c>
+      <c r="F1481" s="130" t="s">
+        <v>8322</v>
+      </c>
+      <c r="G1481" s="130" t="s">
+        <v>8063</v>
+      </c>
+      <c r="H1481" s="130" t="s">
+        <v>8064</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:8">
+      <c r="A1482">
+        <v>901255</v>
+      </c>
+      <c r="B1482" s="2">
+        <v>91255</v>
+      </c>
+      <c r="C1482" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1482" s="130" t="s">
+        <v>7806</v>
+      </c>
+      <c r="E1482" s="130" t="s">
+        <v>8065</v>
+      </c>
+      <c r="F1482" s="130" t="s">
+        <v>8066</v>
+      </c>
+      <c r="G1482" s="130" t="s">
+        <v>8067</v>
+      </c>
+      <c r="H1482" s="130" t="s">
+        <v>8068</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:8">
+      <c r="A1483">
+        <v>901256</v>
+      </c>
+      <c r="B1483" s="2">
+        <v>91256</v>
+      </c>
+      <c r="C1483" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1483" s="130" t="s">
+        <v>7807</v>
+      </c>
+      <c r="E1483" s="130" t="s">
+        <v>8069</v>
+      </c>
+      <c r="F1483" s="130" t="s">
+        <v>8323</v>
+      </c>
+      <c r="G1483" s="130" t="s">
+        <v>8070</v>
+      </c>
+      <c r="H1483" s="130" t="s">
+        <v>8071</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:8">
+      <c r="A1484">
+        <v>901257</v>
+      </c>
+      <c r="B1484" s="2">
+        <v>91257</v>
+      </c>
+      <c r="C1484" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1484" s="130" t="s">
+        <v>7808</v>
+      </c>
+      <c r="E1484" s="130" t="s">
+        <v>8072</v>
+      </c>
+      <c r="F1484" s="130" t="s">
+        <v>8073</v>
+      </c>
+      <c r="G1484" s="130" t="s">
+        <v>8074</v>
+      </c>
+      <c r="H1484" s="130" t="s">
+        <v>8075</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:8">
+      <c r="A1485">
+        <v>901258</v>
+      </c>
+      <c r="B1485" s="2">
+        <v>91258</v>
+      </c>
+      <c r="C1485" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1485" s="130" t="s">
+        <v>7809</v>
+      </c>
+      <c r="E1485" s="130" t="s">
+        <v>8076</v>
+      </c>
+      <c r="F1485" s="130" t="s">
+        <v>8077</v>
+      </c>
+      <c r="G1485" s="130" t="s">
+        <v>8078</v>
+      </c>
+      <c r="H1485" s="130" t="s">
+        <v>8079</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:8">
+      <c r="A1486">
+        <v>901259</v>
+      </c>
+      <c r="B1486" s="2">
+        <v>91259</v>
+      </c>
+      <c r="C1486" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1486" s="130" t="s">
+        <v>7810</v>
+      </c>
+      <c r="E1486" s="130" t="s">
+        <v>8080</v>
+      </c>
+      <c r="F1486" s="130" t="s">
+        <v>8081</v>
+      </c>
+      <c r="G1486" s="130" t="s">
+        <v>8082</v>
+      </c>
+      <c r="H1486" s="130" t="s">
+        <v>8083</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:8">
+      <c r="A1487">
+        <v>901260</v>
+      </c>
+      <c r="B1487" s="2">
+        <v>91260</v>
+      </c>
+      <c r="C1487" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1487" s="130" t="s">
+        <v>7811</v>
+      </c>
+      <c r="E1487" s="130" t="s">
+        <v>8084</v>
+      </c>
+      <c r="F1487" s="130" t="s">
+        <v>8085</v>
+      </c>
+      <c r="G1487" s="130" t="s">
+        <v>8086</v>
+      </c>
+      <c r="H1487" s="130" t="s">
+        <v>8087</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:8">
+      <c r="A1488">
+        <v>901261</v>
+      </c>
+      <c r="B1488" s="2">
+        <v>91261</v>
+      </c>
+      <c r="C1488" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1488" s="130" t="s">
+        <v>7812</v>
+      </c>
+      <c r="E1488" s="130" t="s">
+        <v>8088</v>
+      </c>
+      <c r="F1488" s="130" t="s">
+        <v>8089</v>
+      </c>
+      <c r="G1488" s="130" t="s">
+        <v>8090</v>
+      </c>
+      <c r="H1488" s="130" t="s">
+        <v>8091</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:8">
+      <c r="A1489">
+        <v>901262</v>
+      </c>
+      <c r="B1489" s="2">
+        <v>91262</v>
+      </c>
+      <c r="C1489" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1489" s="130" t="s">
+        <v>7813</v>
+      </c>
+      <c r="E1489" s="130" t="s">
+        <v>8092</v>
+      </c>
+      <c r="F1489" s="130" t="s">
+        <v>8093</v>
+      </c>
+      <c r="G1489" s="130" t="s">
+        <v>8094</v>
+      </c>
+      <c r="H1489" s="130" t="s">
+        <v>8095</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:8">
+      <c r="A1490">
+        <v>901263</v>
+      </c>
+      <c r="B1490" s="2">
+        <v>91263</v>
+      </c>
+      <c r="C1490" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1490" s="130" t="s">
+        <v>7814</v>
+      </c>
+      <c r="E1490" s="130" t="s">
+        <v>8096</v>
+      </c>
+      <c r="F1490" s="130" t="s">
+        <v>8097</v>
+      </c>
+      <c r="G1490" s="130" t="s">
+        <v>8098</v>
+      </c>
+      <c r="H1490" s="130" t="s">
+        <v>8099</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:8">
+      <c r="A1491">
+        <v>901264</v>
+      </c>
+      <c r="B1491" s="2">
+        <v>91264</v>
+      </c>
+      <c r="C1491" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1491" s="130" t="s">
+        <v>7815</v>
+      </c>
+      <c r="E1491" s="130" t="s">
+        <v>8100</v>
+      </c>
+      <c r="F1491" s="130" t="s">
+        <v>8101</v>
+      </c>
+      <c r="G1491" s="130" t="s">
+        <v>8102</v>
+      </c>
+      <c r="H1491" s="130" t="s">
+        <v>8103</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:8">
+      <c r="A1492">
+        <v>901265</v>
+      </c>
+      <c r="B1492" s="2">
+        <v>91265</v>
+      </c>
+      <c r="C1492" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1492" s="130" t="s">
+        <v>7816</v>
+      </c>
+      <c r="E1492" s="130" t="s">
+        <v>8104</v>
+      </c>
+      <c r="F1492" s="130" t="s">
+        <v>8105</v>
+      </c>
+      <c r="G1492" s="130" t="s">
+        <v>8106</v>
+      </c>
+      <c r="H1492" s="130" t="s">
+        <v>8107</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:8">
+      <c r="A1493">
+        <v>901266</v>
+      </c>
+      <c r="B1493" s="2">
+        <v>91266</v>
+      </c>
+      <c r="C1493" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1493" s="130" t="s">
+        <v>7817</v>
+      </c>
+      <c r="E1493" s="130" t="s">
+        <v>8108</v>
+      </c>
+      <c r="F1493" s="130" t="s">
+        <v>8109</v>
+      </c>
+      <c r="G1493" s="130" t="s">
+        <v>8110</v>
+      </c>
+      <c r="H1493" s="130" t="s">
+        <v>8110</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:8">
+      <c r="A1494">
+        <v>901267</v>
+      </c>
+      <c r="B1494" s="2">
+        <v>91267</v>
+      </c>
+      <c r="C1494" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1494" s="130" t="s">
+        <v>7818</v>
+      </c>
+      <c r="E1494" s="130" t="s">
+        <v>8111</v>
+      </c>
+      <c r="F1494" s="130" t="s">
+        <v>8112</v>
+      </c>
+      <c r="G1494" s="130" t="s">
+        <v>8113</v>
+      </c>
+      <c r="H1494" s="130" t="s">
+        <v>8114</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:8">
+      <c r="A1495">
+        <v>901268</v>
+      </c>
+      <c r="B1495" s="2">
+        <v>91268</v>
+      </c>
+      <c r="C1495" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1495" s="130" t="s">
+        <v>7819</v>
+      </c>
+      <c r="E1495" s="130" t="s">
+        <v>8115</v>
+      </c>
+      <c r="F1495" s="130" t="s">
+        <v>8324</v>
+      </c>
+      <c r="G1495" s="130" t="s">
+        <v>8116</v>
+      </c>
+      <c r="H1495" s="130" t="s">
+        <v>8117</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:8">
+      <c r="A1496">
+        <v>901269</v>
+      </c>
+      <c r="B1496" s="2">
+        <v>91269</v>
+      </c>
+      <c r="C1496" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1496" s="130" t="s">
+        <v>7820</v>
+      </c>
+      <c r="E1496" s="130" t="s">
+        <v>8118</v>
+      </c>
+      <c r="F1496" s="130" t="s">
+        <v>8119</v>
+      </c>
+      <c r="G1496" s="130" t="s">
+        <v>8120</v>
+      </c>
+      <c r="H1496" s="130" t="s">
+        <v>8121</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:8">
+      <c r="A1497">
+        <v>901270</v>
+      </c>
+      <c r="B1497" s="2">
+        <v>91270</v>
+      </c>
+      <c r="C1497" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1497" s="130" t="s">
+        <v>7821</v>
+      </c>
+      <c r="E1497" s="130" t="s">
+        <v>8122</v>
+      </c>
+      <c r="F1497" s="130" t="s">
+        <v>8123</v>
+      </c>
+      <c r="G1497" s="130" t="s">
+        <v>8124</v>
+      </c>
+      <c r="H1497" s="130" t="s">
+        <v>8125</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:8">
+      <c r="A1498">
+        <v>901271</v>
+      </c>
+      <c r="B1498" s="2">
+        <v>91271</v>
+      </c>
+      <c r="C1498" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1498" s="130" t="s">
+        <v>7822</v>
+      </c>
+      <c r="E1498" s="130" t="s">
+        <v>8126</v>
+      </c>
+      <c r="F1498" s="130" t="s">
+        <v>8127</v>
+      </c>
+      <c r="G1498" s="130" t="s">
+        <v>8128</v>
+      </c>
+      <c r="H1498" s="130" t="s">
+        <v>8129</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:8">
+      <c r="A1499">
+        <v>901272</v>
+      </c>
+      <c r="B1499" s="2">
+        <v>91272</v>
+      </c>
+      <c r="C1499" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1499" s="130" t="s">
+        <v>7823</v>
+      </c>
+      <c r="E1499" s="130" t="s">
+        <v>8130</v>
+      </c>
+      <c r="F1499" s="130" t="s">
+        <v>8131</v>
+      </c>
+      <c r="G1499" s="130" t="s">
+        <v>8132</v>
+      </c>
+      <c r="H1499" s="130" t="s">
+        <v>8133</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:8">
+      <c r="A1500">
+        <v>901273</v>
+      </c>
+      <c r="B1500" s="2">
+        <v>91273</v>
+      </c>
+      <c r="C1500" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1500" s="130" t="s">
+        <v>7824</v>
+      </c>
+      <c r="E1500" s="130" t="s">
+        <v>8134</v>
+      </c>
+      <c r="F1500" s="130" t="s">
+        <v>8325</v>
+      </c>
+      <c r="G1500" s="130" t="s">
+        <v>8135</v>
+      </c>
+      <c r="H1500" s="130" t="s">
+        <v>8136</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:8">
+      <c r="A1501">
+        <v>901274</v>
+      </c>
+      <c r="B1501" s="2">
+        <v>91274</v>
+      </c>
+      <c r="C1501" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1501" s="130" t="s">
+        <v>7825</v>
+      </c>
+      <c r="E1501" s="130" t="s">
+        <v>8137</v>
+      </c>
+      <c r="F1501" s="130" t="s">
+        <v>8138</v>
+      </c>
+      <c r="G1501" s="130" t="s">
+        <v>8139</v>
+      </c>
+      <c r="H1501" s="130" t="s">
+        <v>8140</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:8">
+      <c r="A1502">
+        <v>901275</v>
+      </c>
+      <c r="B1502" s="2">
+        <v>91275</v>
+      </c>
+      <c r="C1502" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1502" s="130" t="s">
+        <v>7826</v>
+      </c>
+      <c r="E1502" s="130" t="s">
+        <v>8141</v>
+      </c>
+      <c r="F1502" s="130" t="s">
+        <v>8142</v>
+      </c>
+      <c r="G1502" s="130" t="s">
+        <v>8143</v>
+      </c>
+      <c r="H1502" s="130" t="s">
+        <v>8144</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:8">
+      <c r="A1503">
+        <v>901276</v>
+      </c>
+      <c r="B1503" s="2">
+        <v>91276</v>
+      </c>
+      <c r="C1503" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1503" s="130" t="s">
+        <v>7827</v>
+      </c>
+      <c r="E1503" s="130" t="s">
+        <v>8145</v>
+      </c>
+      <c r="F1503" s="130" t="s">
+        <v>8146</v>
+      </c>
+      <c r="G1503" s="130" t="s">
+        <v>8147</v>
+      </c>
+      <c r="H1503" s="130" t="s">
+        <v>8148</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:8">
+      <c r="A1504">
+        <v>901277</v>
+      </c>
+      <c r="B1504" s="2">
+        <v>91277</v>
+      </c>
+      <c r="C1504" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1504" s="130" t="s">
+        <v>7828</v>
+      </c>
+      <c r="E1504" s="130" t="s">
+        <v>8149</v>
+      </c>
+      <c r="F1504" s="130" t="s">
+        <v>8150</v>
+      </c>
+      <c r="G1504" s="130" t="s">
+        <v>8151</v>
+      </c>
+      <c r="H1504" s="130" t="s">
+        <v>8152</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:8">
+      <c r="A1505">
+        <v>901278</v>
+      </c>
+      <c r="B1505" s="2">
+        <v>91278</v>
+      </c>
+      <c r="C1505" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1505" s="130" t="s">
+        <v>7829</v>
+      </c>
+      <c r="E1505" s="130" t="s">
+        <v>8153</v>
+      </c>
+      <c r="F1505" s="130" t="s">
+        <v>8154</v>
+      </c>
+      <c r="G1505" s="130" t="s">
+        <v>8155</v>
+      </c>
+      <c r="H1505" s="130" t="s">
+        <v>8156</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:8">
+      <c r="A1506">
+        <v>901279</v>
+      </c>
+      <c r="B1506" s="2">
+        <v>91279</v>
+      </c>
+      <c r="C1506" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1506" s="130" t="s">
+        <v>7830</v>
+      </c>
+      <c r="E1506" s="130" t="s">
+        <v>8157</v>
+      </c>
+      <c r="F1506" s="130" t="s">
+        <v>8158</v>
+      </c>
+      <c r="G1506" s="130" t="s">
+        <v>8159</v>
+      </c>
+      <c r="H1506" s="130" t="s">
+        <v>8160</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:8">
+      <c r="A1507">
+        <v>901280</v>
+      </c>
+      <c r="B1507" s="2">
+        <v>91280</v>
+      </c>
+      <c r="C1507" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1507" s="130" t="s">
+        <v>7831</v>
+      </c>
+      <c r="E1507" s="130" t="s">
+        <v>8161</v>
+      </c>
+      <c r="F1507" s="130" t="s">
+        <v>8162</v>
+      </c>
+      <c r="G1507" s="130" t="s">
+        <v>8163</v>
+      </c>
+      <c r="H1507" s="130" t="s">
+        <v>8164</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:8">
+      <c r="A1508">
+        <v>901281</v>
+      </c>
+      <c r="B1508" s="2">
+        <v>91281</v>
+      </c>
+      <c r="C1508" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1508" s="130" t="s">
+        <v>7832</v>
+      </c>
+      <c r="E1508" s="130" t="s">
+        <v>8165</v>
+      </c>
+      <c r="F1508" s="130" t="s">
+        <v>8326</v>
+      </c>
+      <c r="G1508" s="130" t="s">
+        <v>8166</v>
+      </c>
+      <c r="H1508" s="130" t="s">
+        <v>8167</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:8">
+      <c r="A1509">
+        <v>901282</v>
+      </c>
+      <c r="B1509" s="2">
+        <v>91282</v>
+      </c>
+      <c r="C1509" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1509" s="130" t="s">
+        <v>7833</v>
+      </c>
+      <c r="E1509" s="130" t="s">
+        <v>8168</v>
+      </c>
+      <c r="F1509" s="130" t="s">
+        <v>8327</v>
+      </c>
+      <c r="G1509" s="130" t="s">
+        <v>8169</v>
+      </c>
+      <c r="H1509" s="130" t="s">
+        <v>8170</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:8">
+      <c r="A1510">
+        <v>901283</v>
+      </c>
+      <c r="B1510" s="2">
+        <v>91283</v>
+      </c>
+      <c r="C1510" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1510" s="130" t="s">
+        <v>7834</v>
+      </c>
+      <c r="E1510" s="130" t="s">
+        <v>6934</v>
+      </c>
+      <c r="F1510" s="130" t="s">
+        <v>8171</v>
+      </c>
+      <c r="G1510" s="130" t="s">
+        <v>7680</v>
+      </c>
+      <c r="H1510" s="130" t="s">
+        <v>7681</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:8">
+      <c r="A1511">
+        <v>901284</v>
+      </c>
+      <c r="B1511" s="2">
+        <v>91284</v>
+      </c>
+      <c r="C1511" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1511" s="130" t="s">
+        <v>7835</v>
+      </c>
+      <c r="E1511" s="130" t="s">
+        <v>8172</v>
+      </c>
+      <c r="F1511" s="130" t="s">
+        <v>8173</v>
+      </c>
+      <c r="G1511" s="130" t="s">
+        <v>8174</v>
+      </c>
+      <c r="H1511" s="130" t="s">
+        <v>8175</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:8">
+      <c r="A1512">
+        <v>901285</v>
+      </c>
+      <c r="B1512" s="2">
+        <v>91285</v>
+      </c>
+      <c r="C1512" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1512" s="130" t="s">
+        <v>7836</v>
+      </c>
+      <c r="E1512" s="130" t="s">
+        <v>8176</v>
+      </c>
+      <c r="F1512" s="130" t="s">
+        <v>8177</v>
+      </c>
+      <c r="G1512" s="130" t="s">
+        <v>8178</v>
+      </c>
+      <c r="H1512" s="130" t="s">
+        <v>8179</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:8">
+      <c r="A1513">
+        <v>901286</v>
+      </c>
+      <c r="B1513" s="2">
+        <v>91286</v>
+      </c>
+      <c r="C1513" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1513" s="130" t="s">
+        <v>7837</v>
+      </c>
+      <c r="E1513" s="130" t="s">
+        <v>8180</v>
+      </c>
+      <c r="F1513" s="130" t="s">
+        <v>8181</v>
+      </c>
+      <c r="G1513" s="130" t="s">
+        <v>8182</v>
+      </c>
+      <c r="H1513" s="130" t="s">
+        <v>8183</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:8">
+      <c r="A1514">
+        <v>901287</v>
+      </c>
+      <c r="B1514" s="2">
+        <v>91287</v>
+      </c>
+      <c r="C1514" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1514" s="130" t="s">
+        <v>7838</v>
+      </c>
+      <c r="E1514" s="130" t="s">
+        <v>8184</v>
+      </c>
+      <c r="F1514" s="130" t="s">
+        <v>8328</v>
+      </c>
+      <c r="G1514" s="130" t="s">
+        <v>8185</v>
+      </c>
+      <c r="H1514" s="130" t="s">
+        <v>8186</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:8">
+      <c r="A1515">
+        <v>901288</v>
+      </c>
+      <c r="B1515" s="2">
+        <v>91288</v>
+      </c>
+      <c r="C1515" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1515" s="130" t="s">
+        <v>7839</v>
+      </c>
+      <c r="E1515" s="130" t="s">
+        <v>8187</v>
+      </c>
+      <c r="F1515" s="130" t="s">
+        <v>8188</v>
+      </c>
+      <c r="G1515" s="130" t="s">
+        <v>8189</v>
+      </c>
+      <c r="H1515" s="130" t="s">
+        <v>8190</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:8">
+      <c r="A1516">
+        <v>901289</v>
+      </c>
+      <c r="B1516" s="2">
+        <v>91289</v>
+      </c>
+      <c r="C1516" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1516" s="130" t="s">
+        <v>7840</v>
+      </c>
+      <c r="E1516" s="130" t="s">
+        <v>8191</v>
+      </c>
+      <c r="F1516" s="130" t="s">
+        <v>8192</v>
+      </c>
+      <c r="G1516" s="130" t="s">
+        <v>8193</v>
+      </c>
+      <c r="H1516" s="130" t="s">
+        <v>8194</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:8">
+      <c r="A1517">
+        <v>901290</v>
+      </c>
+      <c r="B1517" s="2">
+        <v>91290</v>
+      </c>
+      <c r="C1517" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1517" s="130" t="s">
+        <v>7841</v>
+      </c>
+      <c r="E1517" s="130" t="s">
+        <v>8195</v>
+      </c>
+      <c r="F1517" s="130" t="s">
+        <v>8196</v>
+      </c>
+      <c r="G1517" s="130" t="s">
+        <v>8197</v>
+      </c>
+      <c r="H1517" s="130" t="s">
+        <v>8198</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:8">
+      <c r="A1518">
+        <v>901291</v>
+      </c>
+      <c r="B1518" s="2">
+        <v>91291</v>
+      </c>
+      <c r="C1518" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1518" s="130" t="s">
+        <v>7842</v>
+      </c>
+      <c r="E1518" s="130" t="s">
+        <v>8199</v>
+      </c>
+      <c r="F1518" s="130" t="s">
+        <v>8200</v>
+      </c>
+      <c r="G1518" s="130" t="s">
+        <v>8201</v>
+      </c>
+      <c r="H1518" s="130" t="s">
+        <v>8202</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:8">
+      <c r="A1519">
+        <v>901292</v>
+      </c>
+      <c r="B1519" s="2">
+        <v>91292</v>
+      </c>
+      <c r="C1519" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1519" s="130" t="s">
+        <v>7843</v>
+      </c>
+      <c r="E1519" s="130" t="s">
+        <v>8203</v>
+      </c>
+      <c r="F1519" s="130" t="s">
+        <v>8204</v>
+      </c>
+      <c r="G1519" s="130" t="s">
+        <v>8205</v>
+      </c>
+      <c r="H1519" s="130" t="s">
+        <v>8206</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:8">
+      <c r="A1520">
+        <v>901293</v>
+      </c>
+      <c r="B1520" s="2">
+        <v>91293</v>
+      </c>
+      <c r="C1520" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1520" s="130" t="s">
+        <v>7844</v>
+      </c>
+      <c r="E1520" s="130" t="s">
+        <v>8207</v>
+      </c>
+      <c r="F1520" s="130" t="s">
+        <v>8208</v>
+      </c>
+      <c r="G1520" s="130" t="s">
+        <v>8209</v>
+      </c>
+      <c r="H1520" s="130" t="s">
+        <v>8209</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:8">
+      <c r="A1521">
+        <v>901294</v>
+      </c>
+      <c r="B1521" s="2">
+        <v>91294</v>
+      </c>
+      <c r="C1521" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1521" s="130" t="s">
+        <v>7845</v>
+      </c>
+      <c r="E1521" s="130" t="s">
+        <v>8210</v>
+      </c>
+      <c r="F1521" s="130" t="s">
+        <v>8211</v>
+      </c>
+      <c r="G1521" s="130" t="s">
+        <v>8212</v>
+      </c>
+      <c r="H1521" s="130" t="s">
+        <v>8213</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:8">
+      <c r="A1522">
+        <v>901295</v>
+      </c>
+      <c r="B1522" s="2">
+        <v>91295</v>
+      </c>
+      <c r="C1522" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1522" s="130" t="s">
+        <v>7846</v>
+      </c>
+      <c r="E1522" s="130" t="s">
+        <v>8214</v>
+      </c>
+      <c r="F1522" s="130" t="s">
+        <v>8329</v>
+      </c>
+      <c r="G1522" s="130" t="s">
+        <v>8215</v>
+      </c>
+      <c r="H1522" s="130" t="s">
+        <v>8216</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:8">
+      <c r="A1523">
+        <v>901296</v>
+      </c>
+      <c r="B1523" s="2">
+        <v>91296</v>
+      </c>
+      <c r="C1523" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1523" s="130" t="s">
+        <v>7847</v>
+      </c>
+      <c r="E1523" s="130" t="s">
+        <v>8217</v>
+      </c>
+      <c r="F1523" s="130" t="s">
+        <v>8218</v>
+      </c>
+      <c r="G1523" s="130" t="s">
+        <v>8219</v>
+      </c>
+      <c r="H1523" s="130" t="s">
+        <v>8220</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:8">
+      <c r="A1524">
+        <v>901297</v>
+      </c>
+      <c r="B1524" s="2">
+        <v>91297</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1524" s="130" t="s">
+        <v>7848</v>
+      </c>
+      <c r="E1524" s="130" t="s">
+        <v>8221</v>
+      </c>
+      <c r="F1524" s="130" t="s">
+        <v>8330</v>
+      </c>
+      <c r="G1524" s="130" t="s">
+        <v>8222</v>
+      </c>
+      <c r="H1524" s="130" t="s">
+        <v>8223</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:8">
+      <c r="A1525">
+        <v>901298</v>
+      </c>
+      <c r="B1525" s="2">
+        <v>91298</v>
+      </c>
+      <c r="C1525" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1525" s="130" t="s">
+        <v>7849</v>
+      </c>
+      <c r="E1525" s="130" t="s">
+        <v>8224</v>
+      </c>
+      <c r="F1525" s="130" t="s">
+        <v>8225</v>
+      </c>
+      <c r="G1525" s="130" t="s">
+        <v>8226</v>
+      </c>
+      <c r="H1525" s="130" t="s">
+        <v>8227</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:8">
+      <c r="A1526">
+        <v>901299</v>
+      </c>
+      <c r="B1526" s="2">
+        <v>91299</v>
+      </c>
+      <c r="C1526" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1526" s="130" t="s">
+        <v>7850</v>
+      </c>
+      <c r="E1526" s="130" t="s">
+        <v>8228</v>
+      </c>
+      <c r="F1526" s="130" t="s">
+        <v>8229</v>
+      </c>
+      <c r="G1526" s="130" t="s">
+        <v>8230</v>
+      </c>
+      <c r="H1526" s="130" t="s">
+        <v>8231</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:8">
+      <c r="A1527">
+        <v>901300</v>
+      </c>
+      <c r="B1527" s="2">
+        <v>91300</v>
+      </c>
+      <c r="C1527" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1527" s="130" t="s">
+        <v>7851</v>
+      </c>
+      <c r="E1527" s="130" t="s">
+        <v>8232</v>
+      </c>
+      <c r="F1527" s="130" t="s">
+        <v>8331</v>
+      </c>
+      <c r="G1527" s="130" t="s">
+        <v>8233</v>
+      </c>
+      <c r="H1527" s="130" t="s">
+        <v>8234</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:8">
+      <c r="A1528">
+        <v>901301</v>
+      </c>
+      <c r="B1528" s="2">
+        <v>91301</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1528" s="130" t="s">
+        <v>7852</v>
+      </c>
+      <c r="E1528" s="130" t="s">
+        <v>8235</v>
+      </c>
+      <c r="F1528" s="130" t="s">
+        <v>8236</v>
+      </c>
+      <c r="G1528" s="130" t="s">
+        <v>8237</v>
+      </c>
+      <c r="H1528" s="130" t="s">
+        <v>8238</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:8">
+      <c r="A1529">
+        <v>901302</v>
+      </c>
+      <c r="B1529" s="2">
+        <v>91302</v>
+      </c>
+      <c r="C1529" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1529" s="130" t="s">
+        <v>7853</v>
+      </c>
+      <c r="E1529" s="130" t="s">
+        <v>8239</v>
+      </c>
+      <c r="F1529" s="130" t="s">
+        <v>8240</v>
+      </c>
+      <c r="G1529" s="130" t="s">
+        <v>8241</v>
+      </c>
+      <c r="H1529" s="130" t="s">
+        <v>8242</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:8">
+      <c r="A1530">
+        <v>901303</v>
+      </c>
+      <c r="B1530" s="2">
+        <v>91303</v>
+      </c>
+      <c r="C1530" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1530" s="130" t="s">
+        <v>7854</v>
+      </c>
+      <c r="E1530" s="130" t="s">
+        <v>8243</v>
+      </c>
+      <c r="F1530" s="130" t="s">
+        <v>8244</v>
+      </c>
+      <c r="G1530" s="130" t="s">
+        <v>8245</v>
+      </c>
+      <c r="H1530" s="130" t="s">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:8">
+      <c r="A1531">
+        <v>901304</v>
+      </c>
+      <c r="B1531" s="2">
+        <v>91304</v>
+      </c>
+      <c r="C1531" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1531" s="130" t="s">
+        <v>7855</v>
+      </c>
+      <c r="E1531" s="130" t="s">
+        <v>8247</v>
+      </c>
+      <c r="F1531" s="130" t="s">
+        <v>8248</v>
+      </c>
+      <c r="G1531" s="130" t="s">
+        <v>8249</v>
+      </c>
+      <c r="H1531" s="130" t="s">
+        <v>8250</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:8">
+      <c r="A1532">
+        <v>901305</v>
+      </c>
+      <c r="B1532" s="2">
+        <v>91305</v>
+      </c>
+      <c r="C1532" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1532" s="130" t="s">
+        <v>7856</v>
+      </c>
+      <c r="E1532" s="130" t="s">
+        <v>8251</v>
+      </c>
+      <c r="F1532" s="130" t="s">
+        <v>8252</v>
+      </c>
+      <c r="G1532" s="130" t="s">
+        <v>8253</v>
+      </c>
+      <c r="H1532" s="130" t="s">
+        <v>8254</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:8">
+      <c r="A1533">
+        <v>901306</v>
+      </c>
+      <c r="B1533" s="2">
+        <v>91306</v>
+      </c>
+      <c r="C1533" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1533" s="130" t="s">
+        <v>7857</v>
+      </c>
+      <c r="E1533" s="130" t="s">
+        <v>8255</v>
+      </c>
+      <c r="F1533" s="130" t="s">
+        <v>8256</v>
+      </c>
+      <c r="G1533" s="130" t="s">
+        <v>7492</v>
+      </c>
+      <c r="H1533" s="130" t="s">
+        <v>8257</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:8">
+      <c r="A1534">
+        <v>901307</v>
+      </c>
+      <c r="B1534" s="2">
+        <v>91307</v>
+      </c>
+      <c r="C1534" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1534" s="130" t="s">
+        <v>7858</v>
+      </c>
+      <c r="E1534" s="130" t="s">
+        <v>8258</v>
+      </c>
+      <c r="F1534" s="130" t="s">
+        <v>8259</v>
+      </c>
+      <c r="G1534" s="130" t="s">
+        <v>8260</v>
+      </c>
+      <c r="H1534" s="130" t="s">
+        <v>8261</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:8">
+      <c r="A1535">
+        <v>901308</v>
+      </c>
+      <c r="B1535" s="2">
+        <v>91308</v>
+      </c>
+      <c r="C1535" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1535" s="130" t="s">
+        <v>7859</v>
+      </c>
+      <c r="E1535" s="130" t="s">
+        <v>8262</v>
+      </c>
+      <c r="F1535" s="130" t="s">
+        <v>8263</v>
+      </c>
+      <c r="G1535" s="130" t="s">
+        <v>8264</v>
+      </c>
+      <c r="H1535" s="130" t="s">
+        <v>8265</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:8">
+      <c r="A1536">
+        <v>901309</v>
+      </c>
+      <c r="B1536" s="2">
+        <v>91309</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1536" s="130" t="s">
+        <v>7860</v>
+      </c>
+      <c r="E1536" s="130" t="s">
+        <v>8266</v>
+      </c>
+      <c r="F1536" s="130" t="s">
+        <v>8267</v>
+      </c>
+      <c r="G1536" s="130" t="s">
+        <v>8268</v>
+      </c>
+      <c r="H1536" s="130" t="s">
+        <v>8268</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:8">
+      <c r="A1537">
+        <v>901310</v>
+      </c>
+      <c r="B1537" s="2">
+        <v>91310</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1537" s="130" t="s">
+        <v>7861</v>
+      </c>
+      <c r="E1537" s="130" t="s">
+        <v>8269</v>
+      </c>
+      <c r="F1537" s="130" t="s">
+        <v>8270</v>
+      </c>
+      <c r="G1537" s="130" t="s">
+        <v>8271</v>
+      </c>
+      <c r="H1537" s="130" t="s">
+        <v>8272</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:8">
+      <c r="A1538">
+        <v>901311</v>
+      </c>
+      <c r="B1538" s="2">
+        <v>91311</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1538" s="130" t="s">
+        <v>7862</v>
+      </c>
+      <c r="E1538" s="130" t="s">
+        <v>8273</v>
+      </c>
+      <c r="F1538" s="130" t="s">
+        <v>8274</v>
+      </c>
+      <c r="G1538" s="130" t="s">
+        <v>8275</v>
+      </c>
+      <c r="H1538" s="130" t="s">
+        <v>8276</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:8">
+      <c r="A1539">
+        <v>901312</v>
+      </c>
+      <c r="B1539" s="2">
+        <v>91312</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1539" s="130" t="s">
+        <v>7863</v>
+      </c>
+      <c r="E1539" s="130" t="s">
+        <v>8277</v>
+      </c>
+      <c r="F1539" s="130" t="s">
+        <v>8278</v>
+      </c>
+      <c r="G1539" s="130" t="s">
+        <v>8279</v>
+      </c>
+      <c r="H1539" s="130" t="s">
+        <v>8280</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:8">
+      <c r="A1540">
+        <v>901313</v>
+      </c>
+      <c r="B1540" s="2">
+        <v>91313</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1540" s="130" t="s">
+        <v>7864</v>
+      </c>
+      <c r="E1540" s="130" t="s">
+        <v>8281</v>
+      </c>
+      <c r="F1540" s="130" t="s">
+        <v>8282</v>
+      </c>
+      <c r="G1540" s="130" t="s">
+        <v>8283</v>
+      </c>
+      <c r="H1540" s="130" t="s">
+        <v>8284</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:8">
+      <c r="A1541">
+        <v>901314</v>
+      </c>
+      <c r="B1541" s="2">
+        <v>91314</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1541" s="130" t="s">
+        <v>7865</v>
+      </c>
+      <c r="E1541" s="130" t="s">
+        <v>8285</v>
+      </c>
+      <c r="F1541" s="130" t="s">
+        <v>8286</v>
+      </c>
+      <c r="G1541" s="130" t="s">
+        <v>8287</v>
+      </c>
+      <c r="H1541" s="130" t="s">
+        <v>8287</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:8">
+      <c r="A1542">
+        <v>901315</v>
+      </c>
+      <c r="B1542" s="2">
+        <v>91315</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1542" s="130" t="s">
+        <v>7866</v>
+      </c>
+      <c r="E1542" s="130" t="s">
+        <v>8288</v>
+      </c>
+      <c r="F1542" s="130" t="s">
+        <v>8289</v>
+      </c>
+      <c r="G1542" s="130" t="s">
+        <v>8290</v>
+      </c>
+      <c r="H1542" s="130" t="s">
+        <v>8290</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:8">
+      <c r="A1543">
+        <v>901316</v>
+      </c>
+      <c r="B1543" s="2">
+        <v>91316</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1543" s="130" t="s">
+        <v>7867</v>
+      </c>
+      <c r="E1543" s="130" t="s">
+        <v>8291</v>
+      </c>
+      <c r="F1543" s="130" t="s">
+        <v>8292</v>
+      </c>
+      <c r="G1543" s="130" t="s">
+        <v>8293</v>
+      </c>
+      <c r="H1543" s="130" t="s">
+        <v>8293</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:8">
+      <c r="A1544">
+        <v>901317</v>
+      </c>
+      <c r="B1544" s="2">
+        <v>91317</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1544" s="130" t="s">
+        <v>7868</v>
+      </c>
+      <c r="E1544" s="130" t="s">
+        <v>8294</v>
+      </c>
+      <c r="F1544" s="130" t="s">
+        <v>8295</v>
+      </c>
+      <c r="G1544" s="130" t="s">
+        <v>8296</v>
+      </c>
+      <c r="H1544" s="130" t="s">
+        <v>8297</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:8">
+      <c r="A1545">
+        <v>901318</v>
+      </c>
+      <c r="B1545" s="2">
+        <v>91318</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1545" s="130" t="s">
+        <v>7869</v>
+      </c>
+      <c r="E1545" s="130" t="s">
+        <v>8298</v>
+      </c>
+      <c r="F1545" s="130" t="s">
+        <v>8299</v>
+      </c>
+      <c r="G1545" s="130" t="s">
+        <v>8300</v>
+      </c>
+      <c r="H1545" s="130" t="s">
+        <v>8301</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:8">
+      <c r="A1546">
+        <v>901319</v>
+      </c>
+      <c r="B1546" s="2">
+        <v>91319</v>
+      </c>
+      <c r="C1546" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1546" s="130" t="s">
+        <v>7870</v>
+      </c>
+      <c r="E1546" s="130" t="s">
+        <v>8302</v>
+      </c>
+      <c r="F1546" s="130" t="s">
+        <v>8303</v>
+      </c>
+      <c r="G1546" s="130" t="s">
+        <v>8304</v>
+      </c>
+      <c r="H1546" s="130" t="s">
+        <v>8305</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:8">
+      <c r="A1547">
+        <v>901320</v>
+      </c>
+      <c r="B1547" s="2">
+        <v>91320</v>
+      </c>
+      <c r="C1547" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1547" s="130" t="s">
+        <v>7871</v>
+      </c>
+      <c r="E1547" s="130" t="s">
+        <v>8306</v>
+      </c>
+      <c r="F1547" s="130" t="s">
+        <v>8307</v>
+      </c>
+      <c r="G1547" s="130" t="s">
+        <v>8308</v>
+      </c>
+      <c r="H1547" s="130" t="s">
+        <v>8309</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:8">
+      <c r="A1548">
+        <v>901321</v>
+      </c>
+      <c r="B1548" s="2">
+        <v>91321</v>
+      </c>
+      <c r="C1548" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1548" s="130" t="s">
+        <v>7872</v>
+      </c>
+      <c r="E1548" s="130" t="s">
+        <v>8310</v>
+      </c>
+      <c r="F1548" s="130" t="s">
+        <v>8311</v>
+      </c>
+      <c r="G1548" s="130" t="s">
+        <v>8312</v>
+      </c>
+      <c r="H1548" s="130" t="s">
+        <v>8313</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush-r3\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A588FA7-6C26-41C5-B6D1-94C71F224D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD62E5E6-2FC6-4EBC-9DEB-48B114A6A31F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4500" yWindow="570" windowWidth="18900" windowHeight="13410" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71419,7 +71419,7 @@
         <v>754</v>
       </c>
       <c r="H4">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -71445,7 +71445,7 @@
         <v>758</v>
       </c>
       <c r="H5">
-        <v>0.184</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -71471,7 +71471,7 @@
         <v>762</v>
       </c>
       <c r="H6">
-        <v>1.1299999999999999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -71497,7 +71497,7 @@
         <v>766</v>
       </c>
       <c r="H7">
-        <v>2.83</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -71523,7 +71523,7 @@
         <v>770</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -77409,13 +77409,13 @@
         <v>90008</v>
       </c>
       <c r="B11" s="1">
-        <v>390000</v>
+        <v>210000</v>
       </c>
       <c r="C11" s="1">
-        <v>1400000</v>
+        <v>770000</v>
       </c>
       <c r="D11" s="1">
-        <v>5300000</v>
+        <v>2900000</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -77438,13 +77438,13 @@
         <v>90009</v>
       </c>
       <c r="B12" s="1">
-        <v>680000</v>
+        <v>370000</v>
       </c>
       <c r="C12" s="1">
-        <v>2500000</v>
+        <v>1400000</v>
       </c>
       <c r="D12" s="1">
-        <v>9500000</v>
+        <v>5200000</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -77467,13 +77467,13 @@
         <v>90010</v>
       </c>
       <c r="B13" s="1">
-        <v>20000000</v>
+        <v>11000000</v>
       </c>
       <c r="C13" s="1">
-        <v>76000000</v>
+        <v>42000000</v>
       </c>
       <c r="D13" s="1">
-        <v>280000000</v>
+        <v>150000000</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -77496,13 +77496,13 @@
         <v>90011</v>
       </c>
       <c r="B14" s="1">
-        <v>35000000</v>
+        <v>19000000</v>
       </c>
       <c r="C14" s="1">
-        <v>130000000</v>
+        <v>72000000</v>
       </c>
       <c r="D14" s="1">
-        <v>490000000</v>
+        <v>270000000</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -77525,10 +77525,10 @@
         <v>90012</v>
       </c>
       <c r="B15" s="1">
-        <v>7500000</v>
+        <v>4100000</v>
       </c>
       <c r="C15" s="1">
-        <v>28000000</v>
+        <v>15000000</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -77554,10 +77554,10 @@
         <v>90013</v>
       </c>
       <c r="B16" s="1">
-        <v>24000000</v>
+        <v>13000000</v>
       </c>
       <c r="C16" s="1">
-        <v>91000000</v>
+        <v>50000000</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -77583,13 +77583,13 @@
         <v>90014</v>
       </c>
       <c r="B17" s="1">
-        <v>1300000</v>
+        <v>720000</v>
       </c>
       <c r="C17" s="1">
-        <v>4800000</v>
+        <v>2600000</v>
       </c>
       <c r="D17" s="1">
-        <v>17000000</v>
+        <v>9400000</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -77612,13 +77612,13 @@
         <v>90015</v>
       </c>
       <c r="B18" s="1">
-        <v>740000</v>
+        <v>410000</v>
       </c>
       <c r="C18" s="1">
-        <v>2400000</v>
+        <v>1300000</v>
       </c>
       <c r="D18" s="1">
-        <v>9100000</v>
+        <v>5000000</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -77641,13 +77641,13 @@
         <v>90016</v>
       </c>
       <c r="B19" s="1">
-        <v>1700000000</v>
+        <v>940000000</v>
       </c>
       <c r="C19" s="1">
-        <v>6400000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D19" s="1">
-        <v>24000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -77670,13 +77670,13 @@
         <v>90017</v>
       </c>
       <c r="B20" s="1">
-        <v>3000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="C20" s="1">
-        <v>11000000000</v>
+        <v>6100000000</v>
       </c>
       <c r="D20" s="1">
-        <v>41000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -77699,13 +77699,13 @@
         <v>90018</v>
       </c>
       <c r="B21" s="1">
-        <v>90000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="C21" s="1">
-        <v>340000000000</v>
+        <v>190000000000</v>
       </c>
       <c r="D21" s="1">
-        <v>1200000000000</v>
+        <v>660000000000</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -77728,13 +77728,13 @@
         <v>90019</v>
       </c>
       <c r="B22" s="1">
-        <v>150000000000</v>
+        <v>82000000000</v>
       </c>
       <c r="C22" s="1">
-        <v>570000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="D22" s="1">
-        <v>2100000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -77757,10 +77757,10 @@
         <v>90020</v>
       </c>
       <c r="B23" s="1">
-        <v>210000000000</v>
+        <v>120000000000</v>
       </c>
       <c r="C23" s="1">
-        <v>790000000000</v>
+        <v>430000000000</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -77786,10 +77786,10 @@
         <v>90021</v>
       </c>
       <c r="B24" s="1">
-        <v>210000000000</v>
+        <v>120000000000</v>
       </c>
       <c r="C24" s="1">
-        <v>790000000000</v>
+        <v>430000000000</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -77815,10 +77815,10 @@
         <v>90022</v>
       </c>
       <c r="B25" s="1">
-        <v>55000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="C25" s="1">
-        <v>210000000000</v>
+        <v>120000000000</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -77844,10 +77844,10 @@
         <v>90023</v>
       </c>
       <c r="B26" s="1">
-        <v>680000000000</v>
+        <v>370000000000</v>
       </c>
       <c r="C26" s="1">
-        <v>1100000000000</v>
+        <v>600000000000</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -78076,10 +78076,10 @@
         <v>90031</v>
       </c>
       <c r="B34" s="1">
-        <v>4400000</v>
+        <v>2400000</v>
       </c>
       <c r="C34" s="1">
-        <v>16000000</v>
+        <v>8800000</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
@@ -78105,10 +78105,10 @@
         <v>90032</v>
       </c>
       <c r="B35" s="1">
-        <v>24000000</v>
+        <v>13000000</v>
       </c>
       <c r="C35" s="1">
-        <v>91000000</v>
+        <v>50000000</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
@@ -78134,10 +78134,10 @@
         <v>90033</v>
       </c>
       <c r="B36" s="1">
-        <v>79000000000</v>
+        <v>43000000000</v>
       </c>
       <c r="C36" s="1">
-        <v>300000000000</v>
+        <v>160000000000</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
@@ -78163,10 +78163,10 @@
         <v>90034</v>
       </c>
       <c r="B37" s="1">
-        <v>110000000000</v>
+        <v>61000000000</v>
       </c>
       <c r="C37" s="1">
-        <v>410000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
@@ -78221,16 +78221,16 @@
         <v>90036</v>
       </c>
       <c r="B39" s="1">
-        <v>2000000</v>
+        <v>1100000</v>
       </c>
       <c r="C39" s="1">
-        <v>7500000</v>
+        <v>4100000</v>
       </c>
       <c r="D39" s="1">
-        <v>15000000</v>
+        <v>8300000</v>
       </c>
       <c r="E39">
-        <v>56000000</v>
+        <v>31000000</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -78250,16 +78250,16 @@
         <v>90037</v>
       </c>
       <c r="B40" s="1">
-        <v>79000000000</v>
+        <v>43000000000</v>
       </c>
       <c r="C40" s="1">
-        <v>300000000000</v>
+        <v>160000000000</v>
       </c>
       <c r="D40" s="1">
-        <v>600000000000</v>
+        <v>330000000000</v>
       </c>
       <c r="E40">
-        <v>2300000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -78279,16 +78279,16 @@
         <v>90038</v>
       </c>
       <c r="B41" s="1">
-        <v>16000000</v>
+        <v>8800000</v>
       </c>
       <c r="C41" s="1">
-        <v>60000000</v>
+        <v>33000000</v>
       </c>
       <c r="D41" s="1">
-        <v>230000000</v>
+        <v>130000000</v>
       </c>
       <c r="E41">
-        <v>630000000</v>
+        <v>350000000</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -78337,16 +78337,16 @@
         <v>90040</v>
       </c>
       <c r="B43" s="1">
-        <v>680000000000</v>
+        <v>370000000000</v>
       </c>
       <c r="C43" s="1">
-        <v>1100000000000</v>
+        <v>600000000000</v>
       </c>
       <c r="D43" s="1">
-        <v>1100000000000</v>
+        <v>600000000000</v>
       </c>
       <c r="E43">
-        <v>3200000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -78366,16 +78366,16 @@
         <v>90041</v>
       </c>
       <c r="B44" s="1">
-        <v>14000000</v>
+        <v>7700000</v>
       </c>
       <c r="C44" s="1">
-        <v>55000000</v>
+        <v>30000000</v>
       </c>
       <c r="D44" s="1">
-        <v>120000000</v>
+        <v>66000000</v>
       </c>
       <c r="E44">
-        <v>450000000</v>
+        <v>250000000</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -78395,16 +78395,16 @@
         <v>90042</v>
       </c>
       <c r="B45" s="1">
-        <v>1400000000000</v>
+        <v>770000000000</v>
       </c>
       <c r="C45" s="1">
-        <v>1600000000000</v>
+        <v>880000000000</v>
       </c>
       <c r="D45" s="1">
-        <v>1600000000000</v>
+        <v>880000000000</v>
       </c>
       <c r="E45">
-        <v>4300000000000</v>
+        <v>2400000000000</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -78424,16 +78424,16 @@
         <v>90043</v>
       </c>
       <c r="B46" s="1">
-        <v>1600000000000</v>
+        <v>880000000000</v>
       </c>
       <c r="C46" s="1">
-        <v>1800000000000</v>
+        <v>990000000000</v>
       </c>
       <c r="D46" s="1">
-        <v>1800000000000</v>
+        <v>990000000000</v>
       </c>
       <c r="E46">
-        <v>4400000000000</v>
+        <v>2400000000000</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -78453,16 +78453,16 @@
         <v>90044</v>
       </c>
       <c r="B47" s="1">
-        <v>1100000000000</v>
+        <v>600000000000</v>
       </c>
       <c r="C47" s="1">
-        <v>1400000000000</v>
+        <v>770000000000</v>
       </c>
       <c r="D47" s="1">
-        <v>1400000000000</v>
+        <v>770000000000</v>
       </c>
       <c r="E47">
-        <v>3600000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -78511,16 +78511,16 @@
         <v>90046</v>
       </c>
       <c r="B49" s="1">
-        <v>48000</v>
+        <v>26000</v>
       </c>
       <c r="C49" s="1">
-        <v>95000</v>
+        <v>52000</v>
       </c>
       <c r="D49" s="1">
-        <v>150000</v>
+        <v>82000</v>
       </c>
       <c r="E49">
-        <v>570000</v>
+        <v>310000</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -78569,16 +78569,16 @@
         <v>90048</v>
       </c>
       <c r="B51" s="1">
-        <v>34000000</v>
+        <v>19000000</v>
       </c>
       <c r="C51" s="1">
-        <v>68000000</v>
+        <v>37000000</v>
       </c>
       <c r="D51" s="1">
-        <v>110000000</v>
+        <v>61000000</v>
       </c>
       <c r="E51">
-        <v>410000000</v>
+        <v>230000000</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -78598,16 +78598,16 @@
         <v>90049</v>
       </c>
       <c r="B52" s="1">
-        <v>2200000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="C52" s="1">
-        <v>2300000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="D52" s="1">
-        <v>2500000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="E52">
-        <v>7500000000000</v>
+        <v>4100000000000</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -78627,10 +78627,10 @@
         <v>90050</v>
       </c>
       <c r="B53" s="1">
-        <v>59000000</v>
+        <v>32000000</v>
       </c>
       <c r="C53" s="1">
-        <v>190000000</v>
+        <v>100000000</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
@@ -78801,16 +78801,16 @@
         <v>90056</v>
       </c>
       <c r="B59" s="1">
-        <v>25000</v>
+        <v>14000</v>
       </c>
       <c r="C59" s="1">
-        <v>95000</v>
+        <v>52000</v>
       </c>
       <c r="D59" s="1">
-        <v>360000</v>
+        <v>200000</v>
       </c>
       <c r="E59">
-        <v>1300000</v>
+        <v>720000</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -78830,7 +78830,7 @@
         <v>90057</v>
       </c>
       <c r="B60" s="2">
-        <v>110000000</v>
+        <v>61000000</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -78859,13 +78859,13 @@
         <v>90058</v>
       </c>
       <c r="B61" s="2">
-        <v>4900000</v>
+        <v>2700000</v>
       </c>
       <c r="C61" s="2">
-        <v>18000000</v>
+        <v>9900000</v>
       </c>
       <c r="D61" s="2">
-        <v>68000000</v>
+        <v>37000000</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -78888,10 +78888,10 @@
         <v>90059</v>
       </c>
       <c r="B62" s="2">
-        <v>25000000</v>
+        <v>14000000</v>
       </c>
       <c r="C62" s="2">
-        <v>95000000</v>
+        <v>52000000</v>
       </c>
       <c r="D62" s="2">
         <v>0</v>
@@ -78917,13 +78917,13 @@
         <v>90060</v>
       </c>
       <c r="B63" s="2">
-        <v>1900000</v>
+        <v>1000000</v>
       </c>
       <c r="C63" s="2">
-        <v>7100000</v>
+        <v>3900000</v>
       </c>
       <c r="D63" s="2">
-        <v>27000000</v>
+        <v>15000000</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -78946,10 +78946,10 @@
         <v>90061</v>
       </c>
       <c r="B64" s="2">
-        <v>4400000</v>
+        <v>2400000</v>
       </c>
       <c r="C64" s="2">
-        <v>16000000</v>
+        <v>8800000</v>
       </c>
       <c r="D64" s="2">
         <v>0</v>
@@ -78975,10 +78975,10 @@
         <v>90062</v>
       </c>
       <c r="B65" s="2">
-        <v>29000000</v>
+        <v>16000000</v>
       </c>
       <c r="C65" s="2">
-        <v>110000000</v>
+        <v>61000000</v>
       </c>
       <c r="D65" s="2">
         <v>0</v>
@@ -79004,16 +79004,16 @@
         <v>90063</v>
       </c>
       <c r="B66" s="2">
-        <v>37000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="C66" s="2">
-        <v>140000000000</v>
+        <v>77000000000</v>
       </c>
       <c r="D66" s="2">
-        <v>240000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="E66">
-        <v>900000000000</v>
+        <v>500000000000</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -79033,13 +79033,13 @@
         <v>90064</v>
       </c>
       <c r="B67" s="2">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="C67" s="2">
-        <v>50000</v>
+        <v>28000</v>
       </c>
       <c r="D67" s="2">
-        <v>120000</v>
+        <v>66000</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -79062,13 +79062,13 @@
         <v>90065</v>
       </c>
       <c r="B68" s="2">
-        <v>32000</v>
+        <v>18000</v>
       </c>
       <c r="C68" s="2">
-        <v>79000</v>
+        <v>43000</v>
       </c>
       <c r="D68" s="2">
-        <v>200000</v>
+        <v>110000</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -79091,13 +79091,13 @@
         <v>90066</v>
       </c>
       <c r="B69" s="2">
-        <v>48000</v>
+        <v>26000</v>
       </c>
       <c r="C69" s="2">
-        <v>120000</v>
+        <v>66000</v>
       </c>
       <c r="D69" s="2">
-        <v>330000</v>
+        <v>180000</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -79120,13 +79120,13 @@
         <v>90067</v>
       </c>
       <c r="B70" s="2">
-        <v>4600000</v>
+        <v>2500000</v>
       </c>
       <c r="C70" s="2">
-        <v>11000000</v>
+        <v>6100000</v>
       </c>
       <c r="D70" s="2">
-        <v>28000000</v>
+        <v>15000000</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -79149,13 +79149,13 @@
         <v>90068</v>
       </c>
       <c r="B71" s="2">
-        <v>23000000</v>
+        <v>13000000</v>
       </c>
       <c r="C71" s="2">
-        <v>57000000</v>
+        <v>31000000</v>
       </c>
       <c r="D71" s="2">
-        <v>140000000</v>
+        <v>77000000</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -79178,16 +79178,16 @@
         <v>90069</v>
       </c>
       <c r="B72" s="2">
-        <v>81000000</v>
+        <v>45000000</v>
       </c>
       <c r="C72" s="2">
-        <v>300000000</v>
+        <v>160000000</v>
       </c>
       <c r="D72" s="2">
-        <v>1100000000</v>
+        <v>600000000</v>
       </c>
       <c r="E72">
-        <v>4100000000</v>
+        <v>2300000000</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -79207,13 +79207,13 @@
         <v>90070</v>
       </c>
       <c r="B73" s="2">
-        <v>15000000000</v>
+        <v>8300000000</v>
       </c>
       <c r="C73" s="2">
-        <v>57000000000</v>
+        <v>31000000000</v>
       </c>
       <c r="D73" s="2">
-        <v>210000000000</v>
+        <v>120000000000</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -79236,13 +79236,13 @@
         <v>90071</v>
       </c>
       <c r="B74" s="2">
-        <v>260000000000</v>
+        <v>140000000000</v>
       </c>
       <c r="C74" s="2">
-        <v>990000000000</v>
+        <v>540000000000</v>
       </c>
       <c r="D74" s="2">
-        <v>2500000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -79265,10 +79265,10 @@
         <v>90072</v>
       </c>
       <c r="B75" s="2">
-        <v>1800000000000</v>
+        <v>990000000000</v>
       </c>
       <c r="C75" s="2">
-        <v>2500000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="D75" s="2">
         <v>0</v>
@@ -79294,10 +79294,10 @@
         <v>90073</v>
       </c>
       <c r="B76" s="2">
-        <v>1400000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="C76" s="2">
-        <v>1800000000000</v>
+        <v>72000000000</v>
       </c>
       <c r="D76" s="2">
         <v>0</v>
@@ -79323,10 +79323,10 @@
         <v>90074</v>
       </c>
       <c r="B77" s="2">
-        <v>230000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="C77" s="2">
-        <v>850000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D77" s="2">
         <v>0</v>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529870C9-7E70-4ACB-982F-C2B8467411F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0722B07-0035-4E49-A6B2-50ABC1F7F5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10554" uniqueCount="8347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10566" uniqueCount="8352">
   <si>
     <t>Upgrade_Table</t>
   </si>
@@ -28917,6 +28917,24 @@
   </si>
   <si>
     <t>Вирушай по врожай і пройди перший етап!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점수</t>
+  </si>
+  <si>
+    <t>세트 밖이지만 배치한 UI가 쓰는 한·영 전용 폰트 (ONEMobilePOP 등). 한국어·영어에서는 그대로 두고, 그 밖의 언어에서는 그 언어 본문 폰트로 바꾼다 (TextLangFont)</t>
+  </si>
+  <si>
+    <t>Score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>スコア</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Очки</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -33042,7 +33060,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H1548"/>
+  <dimension ref="A1:H1550"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.75" style="2" bestFit="1" customWidth="1"/>
@@ -73010,6 +73028,58 @@
       </c>
       <c r="H1548" s="130" t="s">
         <v>8313</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:8">
+      <c r="A1549">
+        <v>901322</v>
+      </c>
+      <c r="B1549" s="2">
+        <v>91322</v>
+      </c>
+      <c r="C1549" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1549" s="130" t="s">
+        <v>8347</v>
+      </c>
+      <c r="E1549" s="130" t="s">
+        <v>8349</v>
+      </c>
+      <c r="F1549" s="130" t="s">
+        <v>8350</v>
+      </c>
+      <c r="G1549" s="130" t="s">
+        <v>8351</v>
+      </c>
+      <c r="H1549" s="130" t="s">
+        <v>8351</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:8">
+      <c r="A1550">
+        <v>901323</v>
+      </c>
+      <c r="B1550" s="2">
+        <v>91323</v>
+      </c>
+      <c r="C1550" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1550" s="130" t="s">
+        <v>8348</v>
+      </c>
+      <c r="E1550" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1550" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1550" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1550" s="130" t="s">
+        <v>816</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863A55FC-4DCE-4C26-929D-54DE79DCCE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B512C5F6-E258-4CCF-9AFC-10A17EBFFC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4500" yWindow="570" windowWidth="18900" windowHeight="13410" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -76676,7 +76676,7 @@
         <v>2018</v>
       </c>
       <c r="B24">
-        <v>5.5</v>
+        <v>220</v>
       </c>
       <c r="C24" t="s">
         <v>2019</v>
@@ -76804,7 +76804,7 @@
         <v>754</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -76856,7 +76856,7 @@
         <v>762</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -76882,7 +76882,7 @@
         <v>766</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -76908,7 +76908,7 @@
         <v>770</v>
       </c>
       <c r="H8">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -80408,13 +80408,13 @@
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="R54">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S54">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T54">
         <v>4</v>
@@ -84041,16 +84041,16 @@
         <v>90051</v>
       </c>
       <c r="B54" s="1">
-        <v>370</v>
+        <v>65</v>
       </c>
       <c r="C54" s="1">
-        <v>1400</v>
+        <v>240</v>
       </c>
       <c r="D54" s="1">
-        <v>5200</v>
+        <v>920</v>
       </c>
       <c r="E54">
-        <v>20000</v>
+        <v>3500</v>
       </c>
       <c r="F54">
         <v>0</v>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B512C5F6-E258-4CCF-9AFC-10A17EBFFC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4127BEB6-D624-4ADD-9A0F-F4B333F26007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4500" yWindow="570" windowWidth="18900" windowHeight="13410" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29833,46 +29833,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -29881,12 +29881,12 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -30354,29 +30354,29 @@
   <sheetData>
     <row r="1" spans="2:44" ht="12" customHeight="1"/>
     <row r="2" spans="2:44">
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="155"/>
-      <c r="Q2" s="155"/>
-      <c r="R2" s="155"/>
-      <c r="S2" s="155"/>
-      <c r="T2" s="155"/>
-      <c r="U2" s="155"/>
-      <c r="V2" s="156"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="157"/>
+      <c r="U2" s="157"/>
+      <c r="V2" s="158"/>
     </row>
     <row r="3" spans="2:44">
       <c r="B3" s="17"/>
@@ -30433,29 +30433,29 @@
       <c r="V4" s="14"/>
     </row>
     <row r="5" spans="2:44">
-      <c r="B5" s="154" t="s">
+      <c r="B5" s="156" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="155"/>
-      <c r="K5" s="155"/>
-      <c r="L5" s="155"/>
-      <c r="M5" s="155"/>
-      <c r="N5" s="155"/>
-      <c r="O5" s="155"/>
-      <c r="P5" s="155"/>
-      <c r="Q5" s="155"/>
-      <c r="R5" s="155"/>
-      <c r="S5" s="155"/>
-      <c r="T5" s="155"/>
-      <c r="U5" s="155"/>
-      <c r="V5" s="156"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="157"/>
+      <c r="G5" s="157"/>
+      <c r="H5" s="157"/>
+      <c r="I5" s="157"/>
+      <c r="J5" s="157"/>
+      <c r="K5" s="157"/>
+      <c r="L5" s="157"/>
+      <c r="M5" s="157"/>
+      <c r="N5" s="157"/>
+      <c r="O5" s="157"/>
+      <c r="P5" s="157"/>
+      <c r="Q5" s="157"/>
+      <c r="R5" s="157"/>
+      <c r="S5" s="157"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="157"/>
+      <c r="V5" s="158"/>
     </row>
     <row r="6" spans="2:44">
       <c r="B6" s="6"/>
@@ -30585,29 +30585,29 @@
     </row>
     <row r="10" spans="2:44" ht="8.1" customHeight="1"/>
     <row r="11" spans="2:44">
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="156" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155"/>
-      <c r="E11" s="155"/>
-      <c r="F11" s="155"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="155"/>
-      <c r="I11" s="155"/>
-      <c r="J11" s="155"/>
-      <c r="K11" s="155"/>
-      <c r="L11" s="155"/>
-      <c r="M11" s="155"/>
-      <c r="N11" s="155"/>
-      <c r="O11" s="155"/>
-      <c r="P11" s="155"/>
-      <c r="Q11" s="155"/>
-      <c r="R11" s="155"/>
-      <c r="S11" s="155"/>
-      <c r="T11" s="155"/>
-      <c r="U11" s="155"/>
-      <c r="V11" s="156"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="157"/>
+      <c r="F11" s="157"/>
+      <c r="G11" s="157"/>
+      <c r="H11" s="157"/>
+      <c r="I11" s="157"/>
+      <c r="J11" s="157"/>
+      <c r="K11" s="157"/>
+      <c r="L11" s="157"/>
+      <c r="M11" s="157"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="157"/>
+      <c r="Q11" s="157"/>
+      <c r="R11" s="157"/>
+      <c r="S11" s="157"/>
+      <c r="T11" s="157"/>
+      <c r="U11" s="157"/>
+      <c r="V11" s="158"/>
     </row>
     <row r="12" spans="2:44">
       <c r="B12" s="6"/>
@@ -30894,19 +30894,19 @@
       <c r="AF22" s="27"/>
     </row>
     <row r="23" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B23" s="157" t="s">
+      <c r="B23" s="159" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="144"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="143" t="s">
+      <c r="C23" s="146"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="146"/>
+      <c r="H23" s="161" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="144"/>
-      <c r="J23" s="144"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="146"/>
       <c r="K23" s="28" t="s">
         <v>68</v>
       </c>
@@ -30934,18 +30934,18 @@
     </row>
     <row r="24" spans="2:32" s="10" customFormat="1">
       <c r="B24" s="86"/>
-      <c r="C24" s="153" t="s">
+      <c r="C24" s="136" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="151"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
-      <c r="H24" s="150" t="s">
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="137"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="151"/>
-      <c r="J24" s="152"/>
+      <c r="I24" s="137"/>
+      <c r="J24" s="138"/>
       <c r="K24" s="34" t="s">
         <v>70</v>
       </c>
@@ -30973,14 +30973,14 @@
     </row>
     <row r="25" spans="2:32" s="10" customFormat="1">
       <c r="B25" s="22"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="140"/>
-      <c r="G25" s="141"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="140"/>
-      <c r="J25" s="141"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="139"/>
+      <c r="J25" s="140"/>
       <c r="K25" s="19" t="s">
         <v>49</v>
       </c>
@@ -31002,18 +31002,18 @@
     </row>
     <row r="26" spans="2:32" s="10" customFormat="1">
       <c r="B26" s="22"/>
-      <c r="C26" s="139" t="s">
+      <c r="C26" s="144" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="141"/>
-      <c r="H26" s="146" t="s">
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="140"/>
-      <c r="J26" s="141"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="140"/>
       <c r="K26" s="19" t="s">
         <v>74</v>
       </c>
@@ -31033,18 +31033,18 @@
     </row>
     <row r="27" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B27" s="22"/>
-      <c r="C27" s="139" t="s">
+      <c r="C27" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="140"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
-      <c r="G27" s="141"/>
-      <c r="H27" s="146" t="s">
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I27" s="140"/>
-      <c r="J27" s="141"/>
+      <c r="I27" s="139"/>
+      <c r="J27" s="140"/>
       <c r="K27" s="19" t="s">
         <v>75</v>
       </c>
@@ -31064,18 +31064,18 @@
     </row>
     <row r="28" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B28" s="22"/>
-      <c r="C28" s="139" t="s">
+      <c r="C28" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="140"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="141"/>
-      <c r="H28" s="146" t="s">
+      <c r="D28" s="139"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="139"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I28" s="140"/>
-      <c r="J28" s="141"/>
+      <c r="I28" s="139"/>
+      <c r="J28" s="140"/>
       <c r="K28" s="19" t="s">
         <v>77</v>
       </c>
@@ -31095,18 +31095,18 @@
     </row>
     <row r="29" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B29" s="22"/>
-      <c r="C29" s="139" t="s">
+      <c r="C29" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="140"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="140"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="146" t="s">
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I29" s="140"/>
-      <c r="J29" s="141"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="140"/>
       <c r="K29" s="19" t="s">
         <v>78</v>
       </c>
@@ -31126,18 +31126,18 @@
     </row>
     <row r="30" spans="2:32" s="10" customFormat="1">
       <c r="B30" s="22"/>
-      <c r="C30" s="139" t="s">
+      <c r="C30" s="144" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="140"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="140"/>
-      <c r="G30" s="141"/>
-      <c r="H30" s="146" t="s">
+      <c r="D30" s="139"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I30" s="140"/>
-      <c r="J30" s="141"/>
+      <c r="I30" s="139"/>
+      <c r="J30" s="140"/>
       <c r="K30" s="120" t="s">
         <v>421</v>
       </c>
@@ -31157,18 +31157,18 @@
     </row>
     <row r="31" spans="2:32" s="10" customFormat="1">
       <c r="B31" s="22"/>
-      <c r="C31" s="139" t="s">
+      <c r="C31" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="140"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="141"/>
-      <c r="H31" s="146" t="s">
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I31" s="140"/>
-      <c r="J31" s="141"/>
+      <c r="I31" s="139"/>
+      <c r="J31" s="140"/>
       <c r="K31" s="19" t="s">
         <v>80</v>
       </c>
@@ -31188,18 +31188,18 @@
     </row>
     <row r="32" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B32" s="75"/>
-      <c r="C32" s="145" t="s">
+      <c r="C32" s="160" t="s">
         <v>422</v>
       </c>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="138"/>
-      <c r="H32" s="136" t="s">
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
+      <c r="F32" s="149"/>
+      <c r="G32" s="150"/>
+      <c r="H32" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="137"/>
-      <c r="J32" s="138"/>
+      <c r="I32" s="149"/>
+      <c r="J32" s="150"/>
       <c r="K32" s="81" t="s">
         <v>82</v>
       </c>
@@ -31261,19 +31261,19 @@
       <c r="AF33" s="27"/>
     </row>
     <row r="34" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B34" s="148" t="s">
+      <c r="B34" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="144"/>
-      <c r="D34" s="144"/>
-      <c r="E34" s="144"/>
-      <c r="F34" s="144"/>
-      <c r="G34" s="149"/>
-      <c r="H34" s="148" t="s">
+      <c r="C34" s="146"/>
+      <c r="D34" s="146"/>
+      <c r="E34" s="146"/>
+      <c r="F34" s="146"/>
+      <c r="G34" s="147"/>
+      <c r="H34" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I34" s="144"/>
-      <c r="J34" s="149"/>
+      <c r="I34" s="146"/>
+      <c r="J34" s="147"/>
       <c r="K34" s="28" t="s">
         <v>68</v>
       </c>
@@ -31301,18 +31301,18 @@
     </row>
     <row r="35" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B35" s="86"/>
-      <c r="C35" s="153" t="s">
+      <c r="C35" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
-      <c r="G35" s="152"/>
-      <c r="H35" s="150" t="s">
+      <c r="D35" s="137"/>
+      <c r="E35" s="137"/>
+      <c r="F35" s="137"/>
+      <c r="G35" s="138"/>
+      <c r="H35" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I35" s="151"/>
-      <c r="J35" s="152"/>
+      <c r="I35" s="137"/>
+      <c r="J35" s="138"/>
       <c r="K35" s="34" t="s">
         <v>84</v>
       </c>
@@ -31340,18 +31340,18 @@
     </row>
     <row r="36" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B36" s="75"/>
-      <c r="C36" s="145" t="s">
+      <c r="C36" s="160" t="s">
         <v>423</v>
       </c>
-      <c r="D36" s="137"/>
-      <c r="E36" s="137"/>
-      <c r="F36" s="137"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="136" t="s">
+      <c r="D36" s="149"/>
+      <c r="E36" s="149"/>
+      <c r="F36" s="149"/>
+      <c r="G36" s="150"/>
+      <c r="H36" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="I36" s="137"/>
-      <c r="J36" s="138"/>
+      <c r="I36" s="149"/>
+      <c r="J36" s="150"/>
       <c r="K36" s="81" t="s">
         <v>85</v>
       </c>
@@ -31413,19 +31413,19 @@
       <c r="AF37" s="92"/>
     </row>
     <row r="38" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B38" s="148" t="s">
+      <c r="B38" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="144"/>
-      <c r="D38" s="144"/>
-      <c r="E38" s="144"/>
-      <c r="F38" s="144"/>
-      <c r="G38" s="149"/>
-      <c r="H38" s="148" t="s">
+      <c r="C38" s="146"/>
+      <c r="D38" s="146"/>
+      <c r="E38" s="146"/>
+      <c r="F38" s="146"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="144"/>
-      <c r="J38" s="149"/>
+      <c r="I38" s="146"/>
+      <c r="J38" s="147"/>
       <c r="K38" s="28" t="s">
         <v>68</v>
       </c>
@@ -31453,18 +31453,18 @@
     </row>
     <row r="39" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B39" s="21"/>
-      <c r="C39" s="139" t="s">
+      <c r="C39" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="140"/>
-      <c r="E39" s="140"/>
-      <c r="F39" s="140"/>
-      <c r="G39" s="141"/>
-      <c r="H39" s="146" t="s">
+      <c r="D39" s="139"/>
+      <c r="E39" s="139"/>
+      <c r="F39" s="139"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I39" s="140"/>
-      <c r="J39" s="141"/>
+      <c r="I39" s="139"/>
+      <c r="J39" s="140"/>
       <c r="K39" s="19" t="s">
         <v>86</v>
       </c>
@@ -31484,18 +31484,18 @@
     </row>
     <row r="40" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B40" s="22"/>
-      <c r="C40" s="139" t="s">
+      <c r="C40" s="144" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="140"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="140"/>
-      <c r="G40" s="141"/>
-      <c r="H40" s="146" t="s">
+      <c r="D40" s="139"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="139"/>
+      <c r="G40" s="140"/>
+      <c r="H40" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I40" s="140"/>
-      <c r="J40" s="141"/>
+      <c r="I40" s="139"/>
+      <c r="J40" s="140"/>
       <c r="K40" s="19" t="s">
         <v>88</v>
       </c>
@@ -31515,18 +31515,18 @@
     </row>
     <row r="41" spans="2:32" s="10" customFormat="1">
       <c r="B41" s="22"/>
-      <c r="C41" s="139" t="s">
+      <c r="C41" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="140"/>
-      <c r="E41" s="140"/>
-      <c r="F41" s="140"/>
-      <c r="G41" s="141"/>
-      <c r="H41" s="146" t="s">
+      <c r="D41" s="139"/>
+      <c r="E41" s="139"/>
+      <c r="F41" s="139"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="140"/>
-      <c r="J41" s="141"/>
+      <c r="I41" s="139"/>
+      <c r="J41" s="140"/>
       <c r="K41" s="19" t="s">
         <v>89</v>
       </c>
@@ -31546,18 +31546,18 @@
     </row>
     <row r="42" spans="2:32" s="10" customFormat="1">
       <c r="B42" s="22"/>
-      <c r="C42" s="139" t="s">
+      <c r="C42" s="144" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="140"/>
-      <c r="E42" s="140"/>
-      <c r="F42" s="140"/>
-      <c r="G42" s="141"/>
-      <c r="H42" s="146" t="s">
+      <c r="D42" s="139"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I42" s="140"/>
-      <c r="J42" s="141"/>
+      <c r="I42" s="139"/>
+      <c r="J42" s="140"/>
       <c r="K42" s="19" t="s">
         <v>91</v>
       </c>
@@ -31577,18 +31577,18 @@
     </row>
     <row r="43" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B43" s="75"/>
-      <c r="C43" s="142" t="s">
+      <c r="C43" s="152" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="137"/>
-      <c r="E43" s="137"/>
-      <c r="F43" s="137"/>
-      <c r="G43" s="138"/>
-      <c r="H43" s="136" t="s">
+      <c r="D43" s="149"/>
+      <c r="E43" s="149"/>
+      <c r="F43" s="149"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="137"/>
-      <c r="J43" s="138"/>
+      <c r="I43" s="149"/>
+      <c r="J43" s="150"/>
       <c r="K43" s="81" t="s">
         <v>92</v>
       </c>
@@ -31650,19 +31650,19 @@
       <c r="AF44" s="27"/>
     </row>
     <row r="45" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B45" s="148" t="s">
+      <c r="B45" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="144"/>
-      <c r="D45" s="144"/>
-      <c r="E45" s="144"/>
-      <c r="F45" s="144"/>
-      <c r="G45" s="149"/>
-      <c r="H45" s="159" t="s">
+      <c r="C45" s="146"/>
+      <c r="D45" s="146"/>
+      <c r="E45" s="146"/>
+      <c r="F45" s="146"/>
+      <c r="G45" s="147"/>
+      <c r="H45" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="I45" s="160"/>
-      <c r="J45" s="161"/>
+      <c r="I45" s="154"/>
+      <c r="J45" s="155"/>
       <c r="K45" s="83" t="s">
         <v>68</v>
       </c>
@@ -31690,18 +31690,18 @@
     </row>
     <row r="46" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B46" s="21"/>
-      <c r="C46" s="139" t="s">
+      <c r="C46" s="144" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="140"/>
-      <c r="E46" s="140"/>
-      <c r="F46" s="140"/>
-      <c r="G46" s="141"/>
-      <c r="H46" s="150" t="s">
+      <c r="D46" s="139"/>
+      <c r="E46" s="139"/>
+      <c r="F46" s="139"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="I46" s="151"/>
-      <c r="J46" s="152"/>
+      <c r="I46" s="137"/>
+      <c r="J46" s="138"/>
       <c r="K46" s="19" t="s">
         <v>93</v>
       </c>
@@ -31721,18 +31721,18 @@
     </row>
     <row r="47" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B47" s="22"/>
-      <c r="C47" s="139" t="s">
+      <c r="C47" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="140"/>
-      <c r="E47" s="140"/>
-      <c r="F47" s="140"/>
-      <c r="G47" s="141"/>
-      <c r="H47" s="146" t="s">
+      <c r="D47" s="139"/>
+      <c r="E47" s="139"/>
+      <c r="F47" s="139"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="141" t="s">
         <v>81</v>
       </c>
-      <c r="I47" s="140"/>
-      <c r="J47" s="141"/>
+      <c r="I47" s="139"/>
+      <c r="J47" s="140"/>
       <c r="K47" s="19" t="s">
         <v>95</v>
       </c>
@@ -31752,14 +31752,14 @@
     </row>
     <row r="48" spans="2:32" s="10" customFormat="1">
       <c r="B48" s="22"/>
-      <c r="C48" s="140"/>
-      <c r="D48" s="140"/>
-      <c r="E48" s="140"/>
-      <c r="F48" s="140"/>
-      <c r="G48" s="141"/>
-      <c r="H48" s="158"/>
-      <c r="I48" s="140"/>
-      <c r="J48" s="141"/>
+      <c r="C48" s="139"/>
+      <c r="D48" s="139"/>
+      <c r="E48" s="139"/>
+      <c r="F48" s="139"/>
+      <c r="G48" s="140"/>
+      <c r="H48" s="143"/>
+      <c r="I48" s="139"/>
+      <c r="J48" s="140"/>
       <c r="K48" s="19" t="s">
         <v>49</v>
       </c>
@@ -31781,14 +31781,14 @@
     </row>
     <row r="49" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B49" s="22"/>
-      <c r="C49" s="140"/>
-      <c r="D49" s="140"/>
-      <c r="E49" s="140"/>
-      <c r="F49" s="140"/>
-      <c r="G49" s="141"/>
-      <c r="H49" s="158"/>
-      <c r="I49" s="140"/>
-      <c r="J49" s="141"/>
+      <c r="C49" s="139"/>
+      <c r="D49" s="139"/>
+      <c r="E49" s="139"/>
+      <c r="F49" s="139"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="143"/>
+      <c r="I49" s="139"/>
+      <c r="J49" s="140"/>
       <c r="K49" s="19" t="s">
         <v>49</v>
       </c>
@@ -31845,19 +31845,19 @@
       <c r="AG50" s="92"/>
     </row>
     <row r="51" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B51" s="148" t="s">
+      <c r="B51" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="144"/>
-      <c r="D51" s="144"/>
-      <c r="E51" s="144"/>
-      <c r="F51" s="144"/>
-      <c r="G51" s="149"/>
-      <c r="H51" s="148" t="s">
+      <c r="C51" s="146"/>
+      <c r="D51" s="146"/>
+      <c r="E51" s="146"/>
+      <c r="F51" s="146"/>
+      <c r="G51" s="147"/>
+      <c r="H51" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I51" s="144"/>
-      <c r="J51" s="149"/>
+      <c r="I51" s="146"/>
+      <c r="J51" s="147"/>
       <c r="K51" s="28" t="s">
         <v>68</v>
       </c>
@@ -31886,18 +31886,18 @@
     </row>
     <row r="52" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B52" s="21"/>
-      <c r="C52" s="139" t="s">
+      <c r="C52" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="140"/>
-      <c r="E52" s="140"/>
-      <c r="F52" s="140"/>
-      <c r="G52" s="141"/>
-      <c r="H52" s="146" t="s">
+      <c r="D52" s="139"/>
+      <c r="E52" s="139"/>
+      <c r="F52" s="139"/>
+      <c r="G52" s="140"/>
+      <c r="H52" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I52" s="140"/>
-      <c r="J52" s="141"/>
+      <c r="I52" s="139"/>
+      <c r="J52" s="140"/>
       <c r="K52" s="19" t="s">
         <v>99</v>
       </c>
@@ -31917,18 +31917,18 @@
     </row>
     <row r="53" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B53" s="22"/>
-      <c r="C53" s="139" t="s">
+      <c r="C53" s="144" t="s">
         <v>100</v>
       </c>
-      <c r="D53" s="140"/>
-      <c r="E53" s="140"/>
-      <c r="F53" s="140"/>
-      <c r="G53" s="141"/>
-      <c r="H53" s="146" t="s">
+      <c r="D53" s="139"/>
+      <c r="E53" s="139"/>
+      <c r="F53" s="139"/>
+      <c r="G53" s="140"/>
+      <c r="H53" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I53" s="140"/>
-      <c r="J53" s="141"/>
+      <c r="I53" s="139"/>
+      <c r="J53" s="140"/>
       <c r="K53" s="19" t="s">
         <v>101</v>
       </c>
@@ -31948,18 +31948,18 @@
     </row>
     <row r="54" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B54" s="75"/>
-      <c r="C54" s="142" t="s">
+      <c r="C54" s="152" t="s">
         <v>102</v>
       </c>
-      <c r="D54" s="137"/>
-      <c r="E54" s="137"/>
-      <c r="F54" s="137"/>
-      <c r="G54" s="138"/>
-      <c r="H54" s="136" t="s">
+      <c r="D54" s="149"/>
+      <c r="E54" s="149"/>
+      <c r="F54" s="149"/>
+      <c r="G54" s="150"/>
+      <c r="H54" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I54" s="137"/>
-      <c r="J54" s="138"/>
+      <c r="I54" s="149"/>
+      <c r="J54" s="150"/>
       <c r="K54" s="81" t="s">
         <v>103</v>
       </c>
@@ -32023,19 +32023,19 @@
       <c r="AG55" s="92"/>
     </row>
     <row r="56" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B56" s="148" t="s">
+      <c r="B56" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="144"/>
-      <c r="D56" s="144"/>
-      <c r="E56" s="144"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="149"/>
-      <c r="H56" s="148" t="s">
+      <c r="C56" s="146"/>
+      <c r="D56" s="146"/>
+      <c r="E56" s="146"/>
+      <c r="F56" s="146"/>
+      <c r="G56" s="147"/>
+      <c r="H56" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I56" s="144"/>
-      <c r="J56" s="149"/>
+      <c r="I56" s="146"/>
+      <c r="J56" s="147"/>
       <c r="K56" s="28" t="s">
         <v>68</v>
       </c>
@@ -32064,18 +32064,18 @@
     </row>
     <row r="57" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B57" s="21"/>
-      <c r="C57" s="139" t="s">
+      <c r="C57" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="140"/>
-      <c r="E57" s="140"/>
-      <c r="F57" s="140"/>
-      <c r="G57" s="141"/>
-      <c r="H57" s="146" t="s">
+      <c r="D57" s="139"/>
+      <c r="E57" s="139"/>
+      <c r="F57" s="139"/>
+      <c r="G57" s="140"/>
+      <c r="H57" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I57" s="140"/>
-      <c r="J57" s="141"/>
+      <c r="I57" s="139"/>
+      <c r="J57" s="140"/>
       <c r="K57" s="19" t="s">
         <v>104</v>
       </c>
@@ -32095,18 +32095,18 @@
     </row>
     <row r="58" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B58" s="22"/>
-      <c r="C58" s="139" t="s">
+      <c r="C58" s="144" t="s">
         <v>105</v>
       </c>
-      <c r="D58" s="140"/>
-      <c r="E58" s="140"/>
-      <c r="F58" s="140"/>
-      <c r="G58" s="141"/>
-      <c r="H58" s="146" t="s">
+      <c r="D58" s="139"/>
+      <c r="E58" s="139"/>
+      <c r="F58" s="139"/>
+      <c r="G58" s="140"/>
+      <c r="H58" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I58" s="140"/>
-      <c r="J58" s="141"/>
+      <c r="I58" s="139"/>
+      <c r="J58" s="140"/>
       <c r="K58" s="19" t="s">
         <v>106</v>
       </c>
@@ -32126,18 +32126,18 @@
     </row>
     <row r="59" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B59" s="22"/>
-      <c r="C59" s="139" t="s">
+      <c r="C59" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="140"/>
-      <c r="E59" s="140"/>
-      <c r="F59" s="140"/>
-      <c r="G59" s="141"/>
-      <c r="H59" s="146" t="s">
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="140"/>
+      <c r="H59" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I59" s="140"/>
-      <c r="J59" s="141"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="140"/>
       <c r="K59" s="19" t="s">
         <v>107</v>
       </c>
@@ -32157,18 +32157,18 @@
     </row>
     <row r="60" spans="2:33" s="10" customFormat="1">
       <c r="B60" s="22"/>
-      <c r="C60" s="139" t="s">
+      <c r="C60" s="144" t="s">
         <v>108</v>
       </c>
-      <c r="D60" s="140"/>
-      <c r="E60" s="140"/>
-      <c r="F60" s="140"/>
-      <c r="G60" s="141"/>
-      <c r="H60" s="146" t="s">
+      <c r="D60" s="139"/>
+      <c r="E60" s="139"/>
+      <c r="F60" s="139"/>
+      <c r="G60" s="140"/>
+      <c r="H60" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I60" s="140"/>
-      <c r="J60" s="141"/>
+      <c r="I60" s="139"/>
+      <c r="J60" s="140"/>
       <c r="K60" s="19" t="s">
         <v>109</v>
       </c>
@@ -32188,18 +32188,18 @@
     </row>
     <row r="61" spans="2:33" s="10" customFormat="1">
       <c r="B61" s="22"/>
-      <c r="C61" s="139" t="s">
+      <c r="C61" s="144" t="s">
         <v>110</v>
       </c>
-      <c r="D61" s="140"/>
-      <c r="E61" s="140"/>
-      <c r="F61" s="140"/>
-      <c r="G61" s="141"/>
-      <c r="H61" s="146" t="s">
+      <c r="D61" s="139"/>
+      <c r="E61" s="139"/>
+      <c r="F61" s="139"/>
+      <c r="G61" s="140"/>
+      <c r="H61" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I61" s="140"/>
-      <c r="J61" s="141"/>
+      <c r="I61" s="139"/>
+      <c r="J61" s="140"/>
       <c r="K61" s="19" t="s">
         <v>111</v>
       </c>
@@ -32219,18 +32219,18 @@
     </row>
     <row r="62" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B62" s="75"/>
-      <c r="C62" s="142" t="s">
+      <c r="C62" s="152" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="137"/>
-      <c r="E62" s="137"/>
-      <c r="F62" s="137"/>
-      <c r="G62" s="138"/>
-      <c r="H62" s="136" t="s">
+      <c r="D62" s="149"/>
+      <c r="E62" s="149"/>
+      <c r="F62" s="149"/>
+      <c r="G62" s="150"/>
+      <c r="H62" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I62" s="137"/>
-      <c r="J62" s="138"/>
+      <c r="I62" s="149"/>
+      <c r="J62" s="150"/>
       <c r="K62" s="81" t="s">
         <v>113</v>
       </c>
@@ -32294,19 +32294,19 @@
       <c r="AG63" s="92"/>
     </row>
     <row r="64" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B64" s="148" t="s">
+      <c r="B64" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="144"/>
-      <c r="D64" s="144"/>
-      <c r="E64" s="144"/>
-      <c r="F64" s="144"/>
-      <c r="G64" s="149"/>
-      <c r="H64" s="148" t="s">
+      <c r="C64" s="146"/>
+      <c r="D64" s="146"/>
+      <c r="E64" s="146"/>
+      <c r="F64" s="146"/>
+      <c r="G64" s="147"/>
+      <c r="H64" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I64" s="144"/>
-      <c r="J64" s="149"/>
+      <c r="I64" s="146"/>
+      <c r="J64" s="147"/>
       <c r="K64" s="83" t="s">
         <v>68</v>
       </c>
@@ -32335,18 +32335,18 @@
     </row>
     <row r="65" spans="2:33">
       <c r="B65" s="21"/>
-      <c r="C65" s="139" t="s">
+      <c r="C65" s="144" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="147"/>
-      <c r="E65" s="147"/>
-      <c r="F65" s="147"/>
-      <c r="G65" s="141"/>
-      <c r="H65" s="150" t="s">
+      <c r="D65" s="151"/>
+      <c r="E65" s="151"/>
+      <c r="F65" s="151"/>
+      <c r="G65" s="140"/>
+      <c r="H65" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I65" s="151"/>
-      <c r="J65" s="152"/>
+      <c r="I65" s="137"/>
+      <c r="J65" s="138"/>
       <c r="K65" s="19" t="s">
         <v>115</v>
       </c>
@@ -32366,18 +32366,18 @@
     </row>
     <row r="66" spans="2:33">
       <c r="B66" s="22"/>
-      <c r="C66" s="139" t="s">
+      <c r="C66" s="144" t="s">
         <v>116</v>
       </c>
-      <c r="D66" s="147"/>
-      <c r="E66" s="147"/>
-      <c r="F66" s="147"/>
-      <c r="G66" s="141"/>
-      <c r="H66" s="146" t="s">
+      <c r="D66" s="151"/>
+      <c r="E66" s="151"/>
+      <c r="F66" s="151"/>
+      <c r="G66" s="140"/>
+      <c r="H66" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I66" s="147"/>
-      <c r="J66" s="141"/>
+      <c r="I66" s="151"/>
+      <c r="J66" s="140"/>
       <c r="K66" s="19" t="s">
         <v>117</v>
       </c>
@@ -32397,18 +32397,18 @@
     </row>
     <row r="67" spans="2:33">
       <c r="B67" s="22"/>
-      <c r="C67" s="139" t="s">
+      <c r="C67" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D67" s="147"/>
-      <c r="E67" s="147"/>
-      <c r="F67" s="147"/>
-      <c r="G67" s="141"/>
-      <c r="H67" s="146" t="s">
+      <c r="D67" s="151"/>
+      <c r="E67" s="151"/>
+      <c r="F67" s="151"/>
+      <c r="G67" s="140"/>
+      <c r="H67" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I67" s="147"/>
-      <c r="J67" s="141"/>
+      <c r="I67" s="151"/>
+      <c r="J67" s="140"/>
       <c r="K67" s="19" t="s">
         <v>118</v>
       </c>
@@ -32428,18 +32428,18 @@
     </row>
     <row r="68" spans="2:33">
       <c r="B68" s="22"/>
-      <c r="C68" s="139" t="s">
+      <c r="C68" s="144" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="147"/>
-      <c r="E68" s="147"/>
-      <c r="F68" s="147"/>
-      <c r="G68" s="141"/>
-      <c r="H68" s="146" t="s">
+      <c r="D68" s="151"/>
+      <c r="E68" s="151"/>
+      <c r="F68" s="151"/>
+      <c r="G68" s="140"/>
+      <c r="H68" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I68" s="147"/>
-      <c r="J68" s="141"/>
+      <c r="I68" s="151"/>
+      <c r="J68" s="140"/>
       <c r="K68" s="19" t="s">
         <v>120</v>
       </c>
@@ -32459,18 +32459,18 @@
     </row>
     <row r="69" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B69" s="75"/>
-      <c r="C69" s="142" t="s">
+      <c r="C69" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="D69" s="137"/>
-      <c r="E69" s="137"/>
-      <c r="F69" s="137"/>
-      <c r="G69" s="138"/>
-      <c r="H69" s="136" t="s">
+      <c r="D69" s="149"/>
+      <c r="E69" s="149"/>
+      <c r="F69" s="149"/>
+      <c r="G69" s="150"/>
+      <c r="H69" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="I69" s="137"/>
-      <c r="J69" s="138"/>
+      <c r="I69" s="149"/>
+      <c r="J69" s="150"/>
       <c r="K69" s="81" t="s">
         <v>122</v>
       </c>
@@ -32534,19 +32534,19 @@
       <c r="AG70" s="94"/>
     </row>
     <row r="71" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B71" s="148" t="s">
+      <c r="B71" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="144"/>
-      <c r="D71" s="144"/>
-      <c r="E71" s="144"/>
-      <c r="F71" s="144"/>
-      <c r="G71" s="149"/>
-      <c r="H71" s="148" t="s">
+      <c r="C71" s="146"/>
+      <c r="D71" s="146"/>
+      <c r="E71" s="146"/>
+      <c r="F71" s="146"/>
+      <c r="G71" s="147"/>
+      <c r="H71" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I71" s="144"/>
-      <c r="J71" s="149"/>
+      <c r="I71" s="146"/>
+      <c r="J71" s="147"/>
       <c r="K71" s="83" t="s">
         <v>68</v>
       </c>
@@ -32575,18 +32575,18 @@
     </row>
     <row r="72" spans="2:33">
       <c r="B72" s="21"/>
-      <c r="C72" s="139" t="s">
+      <c r="C72" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="147"/>
-      <c r="E72" s="147"/>
-      <c r="F72" s="147"/>
-      <c r="G72" s="141"/>
-      <c r="H72" s="150" t="s">
+      <c r="D72" s="151"/>
+      <c r="E72" s="151"/>
+      <c r="F72" s="151"/>
+      <c r="G72" s="140"/>
+      <c r="H72" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I72" s="151"/>
-      <c r="J72" s="152"/>
+      <c r="I72" s="137"/>
+      <c r="J72" s="138"/>
       <c r="K72" s="19" t="s">
         <v>123</v>
       </c>
@@ -32606,18 +32606,18 @@
     </row>
     <row r="73" spans="2:33">
       <c r="B73" s="22"/>
-      <c r="C73" s="139" t="s">
+      <c r="C73" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D73" s="147"/>
-      <c r="E73" s="147"/>
-      <c r="F73" s="147"/>
-      <c r="G73" s="141"/>
-      <c r="H73" s="146" t="s">
+      <c r="D73" s="151"/>
+      <c r="E73" s="151"/>
+      <c r="F73" s="151"/>
+      <c r="G73" s="140"/>
+      <c r="H73" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I73" s="147"/>
-      <c r="J73" s="141"/>
+      <c r="I73" s="151"/>
+      <c r="J73" s="140"/>
       <c r="K73" s="19" t="s">
         <v>124</v>
       </c>
@@ -32637,18 +32637,18 @@
     </row>
     <row r="74" spans="2:33">
       <c r="B74" s="22"/>
-      <c r="C74" s="139" t="s">
+      <c r="C74" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="D74" s="147"/>
-      <c r="E74" s="147"/>
-      <c r="F74" s="147"/>
-      <c r="G74" s="141"/>
-      <c r="H74" s="146" t="s">
+      <c r="D74" s="151"/>
+      <c r="E74" s="151"/>
+      <c r="F74" s="151"/>
+      <c r="G74" s="140"/>
+      <c r="H74" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I74" s="147"/>
-      <c r="J74" s="141"/>
+      <c r="I74" s="151"/>
+      <c r="J74" s="140"/>
       <c r="K74" s="19" t="s">
         <v>126</v>
       </c>
@@ -32668,18 +32668,18 @@
     </row>
     <row r="75" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B75" s="75"/>
-      <c r="C75" s="142" t="s">
+      <c r="C75" s="152" t="s">
         <v>127</v>
       </c>
-      <c r="D75" s="137"/>
-      <c r="E75" s="137"/>
-      <c r="F75" s="137"/>
-      <c r="G75" s="138"/>
-      <c r="H75" s="136" t="s">
+      <c r="D75" s="149"/>
+      <c r="E75" s="149"/>
+      <c r="F75" s="149"/>
+      <c r="G75" s="150"/>
+      <c r="H75" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I75" s="137"/>
-      <c r="J75" s="138"/>
+      <c r="I75" s="149"/>
+      <c r="J75" s="150"/>
       <c r="K75" s="81" t="s">
         <v>128</v>
       </c>
@@ -32743,19 +32743,19 @@
       <c r="AG76" s="94"/>
     </row>
     <row r="77" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B77" s="148" t="s">
+      <c r="B77" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C77" s="144"/>
-      <c r="D77" s="144"/>
-      <c r="E77" s="144"/>
-      <c r="F77" s="144"/>
-      <c r="G77" s="149"/>
-      <c r="H77" s="148" t="s">
+      <c r="C77" s="146"/>
+      <c r="D77" s="146"/>
+      <c r="E77" s="146"/>
+      <c r="F77" s="146"/>
+      <c r="G77" s="147"/>
+      <c r="H77" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I77" s="144"/>
-      <c r="J77" s="149"/>
+      <c r="I77" s="146"/>
+      <c r="J77" s="147"/>
       <c r="K77" s="83" t="s">
         <v>68</v>
       </c>
@@ -32784,18 +32784,18 @@
     </row>
     <row r="78" spans="2:33">
       <c r="B78" s="21"/>
-      <c r="C78" s="139" t="s">
+      <c r="C78" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="147"/>
-      <c r="E78" s="147"/>
-      <c r="F78" s="147"/>
-      <c r="G78" s="141"/>
-      <c r="H78" s="150" t="s">
+      <c r="D78" s="151"/>
+      <c r="E78" s="151"/>
+      <c r="F78" s="151"/>
+      <c r="G78" s="140"/>
+      <c r="H78" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="I78" s="151"/>
-      <c r="J78" s="152"/>
+      <c r="I78" s="137"/>
+      <c r="J78" s="138"/>
       <c r="K78" s="19" t="s">
         <v>129</v>
       </c>
@@ -32815,18 +32815,18 @@
     </row>
     <row r="79" spans="2:33">
       <c r="B79" s="22"/>
-      <c r="C79" s="139" t="s">
+      <c r="C79" s="144" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="147"/>
-      <c r="E79" s="147"/>
-      <c r="F79" s="147"/>
-      <c r="G79" s="141"/>
-      <c r="H79" s="146" t="s">
+      <c r="D79" s="151"/>
+      <c r="E79" s="151"/>
+      <c r="F79" s="151"/>
+      <c r="G79" s="140"/>
+      <c r="H79" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="I79" s="147"/>
-      <c r="J79" s="141"/>
+      <c r="I79" s="151"/>
+      <c r="J79" s="140"/>
       <c r="K79" s="19" t="s">
         <v>132</v>
       </c>
@@ -32846,18 +32846,18 @@
     </row>
     <row r="80" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B80" s="75"/>
-      <c r="C80" s="142" t="s">
+      <c r="C80" s="152" t="s">
         <v>133</v>
       </c>
-      <c r="D80" s="137"/>
-      <c r="E80" s="137"/>
-      <c r="F80" s="137"/>
-      <c r="G80" s="138"/>
-      <c r="H80" s="136" t="s">
+      <c r="D80" s="149"/>
+      <c r="E80" s="149"/>
+      <c r="F80" s="149"/>
+      <c r="G80" s="150"/>
+      <c r="H80" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I80" s="137"/>
-      <c r="J80" s="138"/>
+      <c r="I80" s="149"/>
+      <c r="J80" s="150"/>
       <c r="K80" s="81" t="s">
         <v>134</v>
       </c>
@@ -32968,12 +32968,81 @@
     </row>
   </sheetData>
   <mergeCells count="97">
-    <mergeCell ref="C24:G25"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="H24:J25"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="H65:J65"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C47:G49"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="B11:V11"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B5:V5"/>
+    <mergeCell ref="H47:J49"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="H40:J40"/>
     <mergeCell ref="H51:J51"/>
     <mergeCell ref="H69:J69"/>
     <mergeCell ref="C29:G29"/>
@@ -32990,81 +33059,12 @@
     <mergeCell ref="C62:G62"/>
     <mergeCell ref="H32:J32"/>
     <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B2:V2"/>
-    <mergeCell ref="B11:V11"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B5:V5"/>
-    <mergeCell ref="H47:J49"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C47:G49"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="H79:J79"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H78:J78"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="H65:J65"/>
-    <mergeCell ref="H71:J71"/>
-    <mergeCell ref="H75:J75"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="C24:G25"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="H24:J25"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:J26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -75056,10 +75056,10 @@
       <c r="B2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
       <c r="G2" s="163"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -75069,10 +75069,10 @@
       <c r="M2" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="149"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="147"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
       <c r="T2" s="11"/>
@@ -75080,10 +75080,10 @@
       <c r="V2" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="W2" s="144"/>
-      <c r="X2" s="144"/>
-      <c r="Y2" s="144"/>
-      <c r="Z2" s="149"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="146"/>
+      <c r="Y2" s="146"/>
+      <c r="Z2" s="147"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
       <c r="AC2" s="10"/>
@@ -75202,10 +75202,10 @@
       <c r="V5" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="W5" s="144"/>
-      <c r="X5" s="144"/>
-      <c r="Y5" s="144"/>
-      <c r="Z5" s="149"/>
+      <c r="W5" s="146"/>
+      <c r="X5" s="146"/>
+      <c r="Y5" s="146"/>
+      <c r="Z5" s="147"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="10"/>
@@ -75251,10 +75251,10 @@
       <c r="B7" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="144"/>
-      <c r="D7" s="144"/>
-      <c r="E7" s="144"/>
-      <c r="F7" s="149"/>
+      <c r="C7" s="146"/>
+      <c r="D7" s="146"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="147"/>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -75263,10 +75263,10 @@
       <c r="L7" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="144"/>
-      <c r="N7" s="144"/>
-      <c r="O7" s="144"/>
-      <c r="P7" s="149"/>
+      <c r="M7" s="146"/>
+      <c r="N7" s="146"/>
+      <c r="O7" s="146"/>
+      <c r="P7" s="147"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
@@ -75475,10 +75475,10 @@
       <c r="AB14" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="AC14" s="144"/>
-      <c r="AD14" s="144"/>
-      <c r="AE14" s="144"/>
-      <c r="AF14" s="149"/>
+      <c r="AC14" s="146"/>
+      <c r="AD14" s="146"/>
+      <c r="AE14" s="146"/>
+      <c r="AF14" s="147"/>
       <c r="AG14" s="100"/>
       <c r="AH14" s="45"/>
       <c r="AI14" s="12"/>
@@ -75552,10 +75552,10 @@
       <c r="AB17" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="AC17" s="144"/>
-      <c r="AD17" s="144"/>
-      <c r="AE17" s="144"/>
-      <c r="AF17" s="149"/>
+      <c r="AC17" s="146"/>
+      <c r="AD17" s="146"/>
+      <c r="AE17" s="146"/>
+      <c r="AF17" s="147"/>
       <c r="AG17" s="102"/>
       <c r="AH17" s="38"/>
       <c r="AI17" s="10"/>
@@ -75673,10 +75673,10 @@
       <c r="AB21" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="AC21" s="144"/>
-      <c r="AD21" s="144"/>
-      <c r="AE21" s="144"/>
-      <c r="AF21" s="149"/>
+      <c r="AC21" s="146"/>
+      <c r="AD21" s="146"/>
+      <c r="AE21" s="146"/>
+      <c r="AF21" s="147"/>
       <c r="AG21" s="116"/>
       <c r="AH21" s="117"/>
     </row>
@@ -76804,7 +76804,7 @@
         <v>754</v>
       </c>
       <c r="H4">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -76830,7 +76830,7 @@
         <v>758</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -76856,7 +76856,7 @@
         <v>762</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -76882,7 +76882,7 @@
         <v>766</v>
       </c>
       <c r="H7">
-        <v>55</v>
+        <v>128.33000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -76908,7 +76908,7 @@
         <v>770</v>
       </c>
       <c r="H8">
-        <v>70</v>
+        <v>163.33000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4127BEB6-D624-4ADD-9A0F-F4B333F26007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814CA4C5-CCDE-4078-992D-A211CB7F6F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="570" windowWidth="18900" windowHeight="13410" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5790" yWindow="1035" windowWidth="18660" windowHeight="13995" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10581" uniqueCount="8357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10695" uniqueCount="8439">
   <si>
     <t>Upgrade_Table</t>
   </si>
@@ -28949,6 +28949,315 @@
   </si>
   <si>
     <t>세트 밖이지만 배치한 UI가 쓰는 한·영 전용 폰트 (ONEMobilePOP 등). 한국어·영어에서는 그대로 두고, 그 밖의 언어에서는 그 언어 본문 폰트로 바꾼다 (TextLangFont)</t>
+  </si>
+  <si>
+    <t>에픽 이상 가중치 ×{0}</t>
+  </si>
+  <si>
+    <t>언어</t>
+  </si>
+  <si>
+    <t>세트 밖이지만 배치한 UI가 쓰는 한·영 전용 폰트 (ONEMobilePOP 등). 한국어·영어에서는 그대로 두고, 그 밖의 언어에서는 그 언어 폰트(koEnTitleFonts면 제목, 아니면 본문)로 바꾼다 (TextLangFont)</t>
+  </si>
+  <si>
+    <t>koEnFonts 가운데 다른 언어에서 제목 폰트(둥글고 굵은 글꼴)로 바꿀 것 (ONEMobilePOP). 나머지는 본문 폰트로</t>
+  </si>
+  <si>
+    <t>소리 설정</t>
+  </si>
+  <si>
+    <t>효과음</t>
+  </si>
+  <si>
+    <t>배경음</t>
+  </si>
+  <si>
+    <t>메인 메뉴</t>
+  </si>
+  <si>
+    <t>음소거: 켜짐</t>
+  </si>
+  <si>
+    <t>음소거: 꺼짐</t>
+  </si>
+  <si>
+    <t>얻은 점수 → 골드 (×{0})</t>
+  </si>
+  <si>
+    <t>신기록! {0} {1}</t>
+  </si>
+  <si>
+    <t>보스 {0} 처치! 스테이지 {1} 열림</t>
+  </si>
+  <si>
+    <t>눌러서 확인해 보세요</t>
+  </si>
+  <si>
+    <t>{0} 완성! 강화 재료로 보관했어요</t>
+  </si>
+  <si>
+    <t>오늘 즉시 완료를 다 썼어요</t>
+  </si>
+  <si>
+    <t>꼬마가 합류하면 열려요</t>
+  </si>
+  <si>
+    <t>{0} 합류 시 해금</t>
+  </si>
+  <si>
+    <t>빈 칸</t>
+  </si>
+  <si>
+    <t>Epic and above weight ×{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>エピック以上の重み ×{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Вес эпических и выше ×{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Вага епічних і вище ×{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Language</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>言語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Язык</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Мова</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound Settings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>サウンド設定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Настройки звука</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Налаштування звуку</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound Effects</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>効果音</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Звуковые эффекты</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Звукові ефекти</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Музыка</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Музика</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Main Menu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>メインメニュー</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Главное меню</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Головне меню</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mute: On</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ミュート:オン</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Без звука: вкл.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Без звуку: увімк.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mute: Off</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ミュート:オフ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Без звука: выкл.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Без звуку: вимк.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Score Earned → Gold (×{0})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>獲得スコア→ゴールド(×{0})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Очки → золото (×{0})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Отримані очки → золото (×{0})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>New record! {0} {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新記録!{0} {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Новый рекорд! {0} {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Новий рекорд! {0} {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss {0} defeated! Stage {1} unlocked</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ボス{0}撃破!ステージ{1}解放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Босс {0} повержен! Открыт этап {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Боса {0} переможено! Відкрито етап {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tap to check it out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>タップして確かめてみましょう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Нажми, чтобы посмотреть</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Натисни, щоб подивитися</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} complete! Stored as an upgrade material</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}完成!強化素材として保管しました</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} готово! Сохранено как материал для улучшения</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} готово! Збережено як матеріал для покращення</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You've used all instant finishes today</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今日の即完了は使い切りました</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unlocks when a little one joins</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちびっこが仲間入りすると解放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Откроется, когда присоединится малыш</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Відкриється, коли приєднається малюк</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unlocks when {0} joins</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}が仲間入りすると解放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Откроется, когда присоединится {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Відкриється, коли приєднається {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空きスロット</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -33073,7 +33382,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H1552"/>
+  <dimension ref="A1:H1571"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.75" style="2" bestFit="1" customWidth="1"/>
@@ -73133,6 +73442,500 @@
       </c>
       <c r="H1552" s="133" t="s">
         <v>816</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:8">
+      <c r="A1553">
+        <v>901324</v>
+      </c>
+      <c r="B1553" s="2">
+        <v>91324</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1553" s="130" t="s">
+        <v>8357</v>
+      </c>
+      <c r="E1553" s="130" t="s">
+        <v>8376</v>
+      </c>
+      <c r="F1553" s="130" t="s">
+        <v>8377</v>
+      </c>
+      <c r="G1553" s="130" t="s">
+        <v>8378</v>
+      </c>
+      <c r="H1553" s="130" t="s">
+        <v>8379</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:8">
+      <c r="A1554">
+        <v>901325</v>
+      </c>
+      <c r="B1554" s="2">
+        <v>91325</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1554" s="130" t="s">
+        <v>8358</v>
+      </c>
+      <c r="E1554" s="130" t="s">
+        <v>8380</v>
+      </c>
+      <c r="F1554" s="130" t="s">
+        <v>8381</v>
+      </c>
+      <c r="G1554" s="130" t="s">
+        <v>8382</v>
+      </c>
+      <c r="H1554" s="130" t="s">
+        <v>8383</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:8">
+      <c r="A1555">
+        <v>901326</v>
+      </c>
+      <c r="B1555" s="2">
+        <v>91326</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1555" s="130" t="s">
+        <v>8359</v>
+      </c>
+      <c r="E1555" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1555" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1555" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1555" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:8">
+      <c r="A1556">
+        <v>901327</v>
+      </c>
+      <c r="B1556" s="2">
+        <v>91327</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1556" s="130" t="s">
+        <v>8360</v>
+      </c>
+      <c r="E1556" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1556" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1556" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1556" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:8">
+      <c r="A1557">
+        <v>901328</v>
+      </c>
+      <c r="B1557" s="2">
+        <v>91328</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1557" s="130" t="s">
+        <v>8361</v>
+      </c>
+      <c r="E1557" s="130" t="s">
+        <v>8384</v>
+      </c>
+      <c r="F1557" s="130" t="s">
+        <v>8385</v>
+      </c>
+      <c r="G1557" s="130" t="s">
+        <v>8386</v>
+      </c>
+      <c r="H1557" s="130" t="s">
+        <v>8387</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:8">
+      <c r="A1558">
+        <v>901329</v>
+      </c>
+      <c r="B1558" s="2">
+        <v>91329</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1558" s="130" t="s">
+        <v>8362</v>
+      </c>
+      <c r="E1558" s="130" t="s">
+        <v>8388</v>
+      </c>
+      <c r="F1558" s="130" t="s">
+        <v>8389</v>
+      </c>
+      <c r="G1558" s="130" t="s">
+        <v>8390</v>
+      </c>
+      <c r="H1558" s="130" t="s">
+        <v>8391</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:8">
+      <c r="A1559">
+        <v>901330</v>
+      </c>
+      <c r="B1559" s="2">
+        <v>91330</v>
+      </c>
+      <c r="C1559" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1559" s="130" t="s">
+        <v>8363</v>
+      </c>
+      <c r="E1559" s="130" t="s">
+        <v>8392</v>
+      </c>
+      <c r="F1559" s="130" t="s">
+        <v>8393</v>
+      </c>
+      <c r="G1559" s="130" t="s">
+        <v>8394</v>
+      </c>
+      <c r="H1559" s="130" t="s">
+        <v>8395</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:8">
+      <c r="A1560">
+        <v>901331</v>
+      </c>
+      <c r="B1560" s="2">
+        <v>91331</v>
+      </c>
+      <c r="C1560" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1560" s="130" t="s">
+        <v>8364</v>
+      </c>
+      <c r="E1560" s="130" t="s">
+        <v>8396</v>
+      </c>
+      <c r="F1560" s="130" t="s">
+        <v>8397</v>
+      </c>
+      <c r="G1560" s="130" t="s">
+        <v>8398</v>
+      </c>
+      <c r="H1560" s="130" t="s">
+        <v>8399</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:8">
+      <c r="A1561">
+        <v>901332</v>
+      </c>
+      <c r="B1561" s="2">
+        <v>91332</v>
+      </c>
+      <c r="C1561" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1561" s="130" t="s">
+        <v>8365</v>
+      </c>
+      <c r="E1561" s="130" t="s">
+        <v>8400</v>
+      </c>
+      <c r="F1561" s="130" t="s">
+        <v>8401</v>
+      </c>
+      <c r="G1561" s="130" t="s">
+        <v>8402</v>
+      </c>
+      <c r="H1561" s="130" t="s">
+        <v>8403</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:8">
+      <c r="A1562">
+        <v>901333</v>
+      </c>
+      <c r="B1562" s="2">
+        <v>91333</v>
+      </c>
+      <c r="C1562" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1562" s="130" t="s">
+        <v>8366</v>
+      </c>
+      <c r="E1562" s="130" t="s">
+        <v>8404</v>
+      </c>
+      <c r="F1562" s="130" t="s">
+        <v>8405</v>
+      </c>
+      <c r="G1562" s="130" t="s">
+        <v>8406</v>
+      </c>
+      <c r="H1562" s="130" t="s">
+        <v>8407</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:8">
+      <c r="A1563">
+        <v>901334</v>
+      </c>
+      <c r="B1563" s="2">
+        <v>91334</v>
+      </c>
+      <c r="C1563" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1563" s="130" t="s">
+        <v>8367</v>
+      </c>
+      <c r="E1563" s="130" t="s">
+        <v>8408</v>
+      </c>
+      <c r="F1563" s="130" t="s">
+        <v>8409</v>
+      </c>
+      <c r="G1563" s="130" t="s">
+        <v>8410</v>
+      </c>
+      <c r="H1563" s="130" t="s">
+        <v>8411</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:8">
+      <c r="A1564">
+        <v>901335</v>
+      </c>
+      <c r="B1564" s="2">
+        <v>91335</v>
+      </c>
+      <c r="C1564" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1564" s="130" t="s">
+        <v>8368</v>
+      </c>
+      <c r="E1564" s="130" t="s">
+        <v>8412</v>
+      </c>
+      <c r="F1564" s="130" t="s">
+        <v>8413</v>
+      </c>
+      <c r="G1564" s="130" t="s">
+        <v>8414</v>
+      </c>
+      <c r="H1564" s="130" t="s">
+        <v>8415</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:8">
+      <c r="A1565">
+        <v>901336</v>
+      </c>
+      <c r="B1565" s="2">
+        <v>91336</v>
+      </c>
+      <c r="C1565" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1565" s="130" t="s">
+        <v>8369</v>
+      </c>
+      <c r="E1565" s="130" t="s">
+        <v>8416</v>
+      </c>
+      <c r="F1565" s="130" t="s">
+        <v>8417</v>
+      </c>
+      <c r="G1565" s="130" t="s">
+        <v>8418</v>
+      </c>
+      <c r="H1565" s="130" t="s">
+        <v>8419</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:8">
+      <c r="A1566">
+        <v>901337</v>
+      </c>
+      <c r="B1566" s="2">
+        <v>91337</v>
+      </c>
+      <c r="C1566" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1566" s="130" t="s">
+        <v>8370</v>
+      </c>
+      <c r="E1566" s="130" t="s">
+        <v>8420</v>
+      </c>
+      <c r="F1566" s="130" t="s">
+        <v>8421</v>
+      </c>
+      <c r="G1566" s="130" t="s">
+        <v>8422</v>
+      </c>
+      <c r="H1566" s="130" t="s">
+        <v>8423</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:8">
+      <c r="A1567">
+        <v>901338</v>
+      </c>
+      <c r="B1567" s="2">
+        <v>91338</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1567" s="130" t="s">
+        <v>8371</v>
+      </c>
+      <c r="E1567" s="130" t="s">
+        <v>8424</v>
+      </c>
+      <c r="F1567" s="130" t="s">
+        <v>8425</v>
+      </c>
+      <c r="G1567" s="130" t="s">
+        <v>8426</v>
+      </c>
+      <c r="H1567" s="130" t="s">
+        <v>8427</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:8">
+      <c r="A1568">
+        <v>901339</v>
+      </c>
+      <c r="B1568" s="2">
+        <v>91339</v>
+      </c>
+      <c r="C1568" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1568" s="130" t="s">
+        <v>8372</v>
+      </c>
+      <c r="E1568" s="130" t="s">
+        <v>8428</v>
+      </c>
+      <c r="F1568" s="130" t="s">
+        <v>8429</v>
+      </c>
+      <c r="G1568" s="130" t="s">
+        <v>8173</v>
+      </c>
+      <c r="H1568" s="130" t="s">
+        <v>8174</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:8">
+      <c r="A1569">
+        <v>901340</v>
+      </c>
+      <c r="B1569" s="2">
+        <v>91340</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1569" s="130" t="s">
+        <v>8373</v>
+      </c>
+      <c r="E1569" s="130" t="s">
+        <v>8430</v>
+      </c>
+      <c r="F1569" s="130" t="s">
+        <v>8431</v>
+      </c>
+      <c r="G1569" s="130" t="s">
+        <v>8432</v>
+      </c>
+      <c r="H1569" s="130" t="s">
+        <v>8433</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:8">
+      <c r="A1570">
+        <v>901341</v>
+      </c>
+      <c r="B1570" s="2">
+        <v>91341</v>
+      </c>
+      <c r="C1570" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1570" s="130" t="s">
+        <v>8374</v>
+      </c>
+      <c r="E1570" s="130" t="s">
+        <v>8434</v>
+      </c>
+      <c r="F1570" s="130" t="s">
+        <v>8435</v>
+      </c>
+      <c r="G1570" s="130" t="s">
+        <v>8436</v>
+      </c>
+      <c r="H1570" s="130" t="s">
+        <v>8437</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:8">
+      <c r="A1571">
+        <v>901342</v>
+      </c>
+      <c r="B1571" s="2">
+        <v>91342</v>
+      </c>
+      <c r="C1571" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1571" s="130" t="s">
+        <v>8375</v>
+      </c>
+      <c r="E1571" s="130" t="s">
+        <v>8209</v>
+      </c>
+      <c r="F1571" s="130" t="s">
+        <v>8438</v>
+      </c>
+      <c r="G1571" s="130" t="s">
+        <v>8211</v>
+      </c>
+      <c r="H1571" s="130" t="s">
+        <v>8212</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A7D5E0-2018-44FE-87B5-AC21C6C2DA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7004AC3-463F-4F71-A084-F38FC1B090FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4500" yWindow="570" windowWidth="18900" windowHeight="13410" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10699" uniqueCount="8463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10777" uniqueCount="8502">
   <si>
     <t>Upgrade_Table</t>
   </si>
@@ -29643,6 +29643,123 @@
   <si>
     <t>Висота смуги {0}, шкода: атака ×{1}</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콤보</t>
+  </si>
+  <si>
+    <t>Combo</t>
+  </si>
+  <si>
+    <t>コンボ</t>
+  </si>
+  <si>
+    <t>Комбо</t>
+  </si>
+  <si>
+    <t>NEW</t>
+  </si>
+  <si>
+    <t>НОВОЕ</t>
+  </si>
+  <si>
+    <t>НОВЕ</t>
+  </si>
+  <si>
+    <t>Lv {0}</t>
+  </si>
+  <si>
+    <t>Ур. {0}</t>
+  </si>
+  <si>
+    <t>Рів. {0}</t>
+  </si>
+  <si>
+    <t>Lv {0}/{1}</t>
+  </si>
+  <si>
+    <t>Ур. {0}/{1}</t>
+  </si>
+  <si>
+    <t>Рів. {0}/{1}</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>МАКС</t>
+  </si>
+  <si>
+    <t>MAX {0}</t>
+  </si>
+  <si>
+    <t>МАКС {0}</t>
+  </si>
+  <si>
+    <t>MAX {0}/{1}</t>
+  </si>
+  <si>
+    <t>МАКС {0}/{1}</t>
+  </si>
+  <si>
+    <t>LVL {0} / {1}</t>
+  </si>
+  <si>
+    <t>Lv {0} / {1}</t>
+  </si>
+  <si>
+    <t>УР. {0} / {1}</t>
+  </si>
+  <si>
+    <t>РІВ. {0} / {1}</t>
+  </si>
+  <si>
+    <t>LVL {0} / ∞</t>
+  </si>
+  <si>
+    <t>Lv {0} / ∞</t>
+  </si>
+  <si>
+    <t>УР. {0} / ∞</t>
+  </si>
+  <si>
+    <t>РІВ. {0} / ∞</t>
+  </si>
+  <si>
+    <t>{0} Lv.{1}</t>
+  </si>
+  <si>
+    <t>{0} ур.{1}</t>
+  </si>
+  <si>
+    <t>{0} рів.{1}</t>
+  </si>
+  <si>
+    <t>{0} {1} Lv.{2}</t>
+  </si>
+  <si>
+    <t>{0} {1} ур.{2}</t>
+  </si>
+  <si>
+    <t>{0} {1} рів.{2}</t>
+  </si>
+  <si>
+    <t>★{0} · Lv.{1}</t>
+  </si>
+  <si>
+    <t>★{0} · ур.{1}</t>
+  </si>
+  <si>
+    <t>★{0} · рів.{1}</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt; &lt;color=#e8a900&gt;{1}&lt;/color&gt;  Lv.{2}/{3}</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt; &lt;color=#e8a900&gt;{1}&lt;/color&gt;  ур.{2}/{3}</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;{0}&lt;/b&gt; &lt;color=#e8a900&gt;{1}&lt;/color&gt;  рів.{2}/{3}</t>
   </si>
 </sst>
 </file>
@@ -30527,46 +30644,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -30575,12 +30692,12 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -31048,29 +31165,29 @@
   <sheetData>
     <row r="1" spans="2:44" ht="12" customHeight="1"/>
     <row r="2" spans="2:44">
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="155"/>
-      <c r="Q2" s="155"/>
-      <c r="R2" s="155"/>
-      <c r="S2" s="155"/>
-      <c r="T2" s="155"/>
-      <c r="U2" s="155"/>
-      <c r="V2" s="156"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="157"/>
+      <c r="U2" s="157"/>
+      <c r="V2" s="158"/>
     </row>
     <row r="3" spans="2:44">
       <c r="B3" s="17"/>
@@ -31127,29 +31244,29 @@
       <c r="V4" s="14"/>
     </row>
     <row r="5" spans="2:44">
-      <c r="B5" s="154" t="s">
+      <c r="B5" s="156" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="155"/>
-      <c r="K5" s="155"/>
-      <c r="L5" s="155"/>
-      <c r="M5" s="155"/>
-      <c r="N5" s="155"/>
-      <c r="O5" s="155"/>
-      <c r="P5" s="155"/>
-      <c r="Q5" s="155"/>
-      <c r="R5" s="155"/>
-      <c r="S5" s="155"/>
-      <c r="T5" s="155"/>
-      <c r="U5" s="155"/>
-      <c r="V5" s="156"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="157"/>
+      <c r="G5" s="157"/>
+      <c r="H5" s="157"/>
+      <c r="I5" s="157"/>
+      <c r="J5" s="157"/>
+      <c r="K5" s="157"/>
+      <c r="L5" s="157"/>
+      <c r="M5" s="157"/>
+      <c r="N5" s="157"/>
+      <c r="O5" s="157"/>
+      <c r="P5" s="157"/>
+      <c r="Q5" s="157"/>
+      <c r="R5" s="157"/>
+      <c r="S5" s="157"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="157"/>
+      <c r="V5" s="158"/>
     </row>
     <row r="6" spans="2:44">
       <c r="B6" s="6"/>
@@ -31279,29 +31396,29 @@
     </row>
     <row r="10" spans="2:44" ht="8.1" customHeight="1"/>
     <row r="11" spans="2:44">
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="156" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155"/>
-      <c r="E11" s="155"/>
-      <c r="F11" s="155"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="155"/>
-      <c r="I11" s="155"/>
-      <c r="J11" s="155"/>
-      <c r="K11" s="155"/>
-      <c r="L11" s="155"/>
-      <c r="M11" s="155"/>
-      <c r="N11" s="155"/>
-      <c r="O11" s="155"/>
-      <c r="P11" s="155"/>
-      <c r="Q11" s="155"/>
-      <c r="R11" s="155"/>
-      <c r="S11" s="155"/>
-      <c r="T11" s="155"/>
-      <c r="U11" s="155"/>
-      <c r="V11" s="156"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="157"/>
+      <c r="F11" s="157"/>
+      <c r="G11" s="157"/>
+      <c r="H11" s="157"/>
+      <c r="I11" s="157"/>
+      <c r="J11" s="157"/>
+      <c r="K11" s="157"/>
+      <c r="L11" s="157"/>
+      <c r="M11" s="157"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="157"/>
+      <c r="Q11" s="157"/>
+      <c r="R11" s="157"/>
+      <c r="S11" s="157"/>
+      <c r="T11" s="157"/>
+      <c r="U11" s="157"/>
+      <c r="V11" s="158"/>
     </row>
     <row r="12" spans="2:44">
       <c r="B12" s="6"/>
@@ -31588,19 +31705,19 @@
       <c r="AF22" s="27"/>
     </row>
     <row r="23" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B23" s="157" t="s">
+      <c r="B23" s="159" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="144"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="143" t="s">
+      <c r="C23" s="146"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="146"/>
+      <c r="H23" s="161" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="144"/>
-      <c r="J23" s="144"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="146"/>
       <c r="K23" s="28" t="s">
         <v>68</v>
       </c>
@@ -31628,18 +31745,18 @@
     </row>
     <row r="24" spans="2:32" s="10" customFormat="1">
       <c r="B24" s="86"/>
-      <c r="C24" s="153" t="s">
+      <c r="C24" s="136" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="151"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
-      <c r="H24" s="150" t="s">
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="137"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="151"/>
-      <c r="J24" s="152"/>
+      <c r="I24" s="137"/>
+      <c r="J24" s="138"/>
       <c r="K24" s="34" t="s">
         <v>70</v>
       </c>
@@ -31667,14 +31784,14 @@
     </row>
     <row r="25" spans="2:32" s="10" customFormat="1">
       <c r="B25" s="22"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="140"/>
-      <c r="G25" s="141"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="140"/>
-      <c r="J25" s="141"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="139"/>
+      <c r="J25" s="140"/>
       <c r="K25" s="19" t="s">
         <v>49</v>
       </c>
@@ -31696,18 +31813,18 @@
     </row>
     <row r="26" spans="2:32" s="10" customFormat="1">
       <c r="B26" s="22"/>
-      <c r="C26" s="139" t="s">
+      <c r="C26" s="144" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="141"/>
-      <c r="H26" s="146" t="s">
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="140"/>
-      <c r="J26" s="141"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="140"/>
       <c r="K26" s="19" t="s">
         <v>74</v>
       </c>
@@ -31727,18 +31844,18 @@
     </row>
     <row r="27" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B27" s="22"/>
-      <c r="C27" s="139" t="s">
+      <c r="C27" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="140"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
-      <c r="G27" s="141"/>
-      <c r="H27" s="146" t="s">
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I27" s="140"/>
-      <c r="J27" s="141"/>
+      <c r="I27" s="139"/>
+      <c r="J27" s="140"/>
       <c r="K27" s="19" t="s">
         <v>75</v>
       </c>
@@ -31758,18 +31875,18 @@
     </row>
     <row r="28" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B28" s="22"/>
-      <c r="C28" s="139" t="s">
+      <c r="C28" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="140"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="141"/>
-      <c r="H28" s="146" t="s">
+      <c r="D28" s="139"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="139"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I28" s="140"/>
-      <c r="J28" s="141"/>
+      <c r="I28" s="139"/>
+      <c r="J28" s="140"/>
       <c r="K28" s="19" t="s">
         <v>77</v>
       </c>
@@ -31789,18 +31906,18 @@
     </row>
     <row r="29" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B29" s="22"/>
-      <c r="C29" s="139" t="s">
+      <c r="C29" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="140"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="140"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="146" t="s">
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I29" s="140"/>
-      <c r="J29" s="141"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="140"/>
       <c r="K29" s="19" t="s">
         <v>78</v>
       </c>
@@ -31820,18 +31937,18 @@
     </row>
     <row r="30" spans="2:32" s="10" customFormat="1">
       <c r="B30" s="22"/>
-      <c r="C30" s="139" t="s">
+      <c r="C30" s="144" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="140"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="140"/>
-      <c r="G30" s="141"/>
-      <c r="H30" s="146" t="s">
+      <c r="D30" s="139"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I30" s="140"/>
-      <c r="J30" s="141"/>
+      <c r="I30" s="139"/>
+      <c r="J30" s="140"/>
       <c r="K30" s="120" t="s">
         <v>421</v>
       </c>
@@ -31851,18 +31968,18 @@
     </row>
     <row r="31" spans="2:32" s="10" customFormat="1">
       <c r="B31" s="22"/>
-      <c r="C31" s="139" t="s">
+      <c r="C31" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="140"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="141"/>
-      <c r="H31" s="146" t="s">
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I31" s="140"/>
-      <c r="J31" s="141"/>
+      <c r="I31" s="139"/>
+      <c r="J31" s="140"/>
       <c r="K31" s="19" t="s">
         <v>80</v>
       </c>
@@ -31882,18 +31999,18 @@
     </row>
     <row r="32" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B32" s="75"/>
-      <c r="C32" s="145" t="s">
+      <c r="C32" s="160" t="s">
         <v>422</v>
       </c>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="138"/>
-      <c r="H32" s="136" t="s">
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
+      <c r="F32" s="149"/>
+      <c r="G32" s="150"/>
+      <c r="H32" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="137"/>
-      <c r="J32" s="138"/>
+      <c r="I32" s="149"/>
+      <c r="J32" s="150"/>
       <c r="K32" s="81" t="s">
         <v>82</v>
       </c>
@@ -31955,19 +32072,19 @@
       <c r="AF33" s="27"/>
     </row>
     <row r="34" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B34" s="148" t="s">
+      <c r="B34" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="144"/>
-      <c r="D34" s="144"/>
-      <c r="E34" s="144"/>
-      <c r="F34" s="144"/>
-      <c r="G34" s="149"/>
-      <c r="H34" s="148" t="s">
+      <c r="C34" s="146"/>
+      <c r="D34" s="146"/>
+      <c r="E34" s="146"/>
+      <c r="F34" s="146"/>
+      <c r="G34" s="147"/>
+      <c r="H34" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I34" s="144"/>
-      <c r="J34" s="149"/>
+      <c r="I34" s="146"/>
+      <c r="J34" s="147"/>
       <c r="K34" s="28" t="s">
         <v>68</v>
       </c>
@@ -31995,18 +32112,18 @@
     </row>
     <row r="35" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B35" s="86"/>
-      <c r="C35" s="153" t="s">
+      <c r="C35" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
-      <c r="G35" s="152"/>
-      <c r="H35" s="150" t="s">
+      <c r="D35" s="137"/>
+      <c r="E35" s="137"/>
+      <c r="F35" s="137"/>
+      <c r="G35" s="138"/>
+      <c r="H35" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I35" s="151"/>
-      <c r="J35" s="152"/>
+      <c r="I35" s="137"/>
+      <c r="J35" s="138"/>
       <c r="K35" s="34" t="s">
         <v>84</v>
       </c>
@@ -32034,18 +32151,18 @@
     </row>
     <row r="36" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B36" s="75"/>
-      <c r="C36" s="145" t="s">
+      <c r="C36" s="160" t="s">
         <v>423</v>
       </c>
-      <c r="D36" s="137"/>
-      <c r="E36" s="137"/>
-      <c r="F36" s="137"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="136" t="s">
+      <c r="D36" s="149"/>
+      <c r="E36" s="149"/>
+      <c r="F36" s="149"/>
+      <c r="G36" s="150"/>
+      <c r="H36" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="I36" s="137"/>
-      <c r="J36" s="138"/>
+      <c r="I36" s="149"/>
+      <c r="J36" s="150"/>
       <c r="K36" s="81" t="s">
         <v>85</v>
       </c>
@@ -32107,19 +32224,19 @@
       <c r="AF37" s="92"/>
     </row>
     <row r="38" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B38" s="148" t="s">
+      <c r="B38" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="144"/>
-      <c r="D38" s="144"/>
-      <c r="E38" s="144"/>
-      <c r="F38" s="144"/>
-      <c r="G38" s="149"/>
-      <c r="H38" s="148" t="s">
+      <c r="C38" s="146"/>
+      <c r="D38" s="146"/>
+      <c r="E38" s="146"/>
+      <c r="F38" s="146"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="144"/>
-      <c r="J38" s="149"/>
+      <c r="I38" s="146"/>
+      <c r="J38" s="147"/>
       <c r="K38" s="28" t="s">
         <v>68</v>
       </c>
@@ -32147,18 +32264,18 @@
     </row>
     <row r="39" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B39" s="21"/>
-      <c r="C39" s="139" t="s">
+      <c r="C39" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="140"/>
-      <c r="E39" s="140"/>
-      <c r="F39" s="140"/>
-      <c r="G39" s="141"/>
-      <c r="H39" s="146" t="s">
+      <c r="D39" s="139"/>
+      <c r="E39" s="139"/>
+      <c r="F39" s="139"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I39" s="140"/>
-      <c r="J39" s="141"/>
+      <c r="I39" s="139"/>
+      <c r="J39" s="140"/>
       <c r="K39" s="19" t="s">
         <v>86</v>
       </c>
@@ -32178,18 +32295,18 @@
     </row>
     <row r="40" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B40" s="22"/>
-      <c r="C40" s="139" t="s">
+      <c r="C40" s="144" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="140"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="140"/>
-      <c r="G40" s="141"/>
-      <c r="H40" s="146" t="s">
+      <c r="D40" s="139"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="139"/>
+      <c r="G40" s="140"/>
+      <c r="H40" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I40" s="140"/>
-      <c r="J40" s="141"/>
+      <c r="I40" s="139"/>
+      <c r="J40" s="140"/>
       <c r="K40" s="19" t="s">
         <v>88</v>
       </c>
@@ -32209,18 +32326,18 @@
     </row>
     <row r="41" spans="2:32" s="10" customFormat="1">
       <c r="B41" s="22"/>
-      <c r="C41" s="139" t="s">
+      <c r="C41" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="140"/>
-      <c r="E41" s="140"/>
-      <c r="F41" s="140"/>
-      <c r="G41" s="141"/>
-      <c r="H41" s="146" t="s">
+      <c r="D41" s="139"/>
+      <c r="E41" s="139"/>
+      <c r="F41" s="139"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="140"/>
-      <c r="J41" s="141"/>
+      <c r="I41" s="139"/>
+      <c r="J41" s="140"/>
       <c r="K41" s="19" t="s">
         <v>89</v>
       </c>
@@ -32240,18 +32357,18 @@
     </row>
     <row r="42" spans="2:32" s="10" customFormat="1">
       <c r="B42" s="22"/>
-      <c r="C42" s="139" t="s">
+      <c r="C42" s="144" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="140"/>
-      <c r="E42" s="140"/>
-      <c r="F42" s="140"/>
-      <c r="G42" s="141"/>
-      <c r="H42" s="146" t="s">
+      <c r="D42" s="139"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I42" s="140"/>
-      <c r="J42" s="141"/>
+      <c r="I42" s="139"/>
+      <c r="J42" s="140"/>
       <c r="K42" s="19" t="s">
         <v>91</v>
       </c>
@@ -32271,18 +32388,18 @@
     </row>
     <row r="43" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B43" s="75"/>
-      <c r="C43" s="142" t="s">
+      <c r="C43" s="152" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="137"/>
-      <c r="E43" s="137"/>
-      <c r="F43" s="137"/>
-      <c r="G43" s="138"/>
-      <c r="H43" s="136" t="s">
+      <c r="D43" s="149"/>
+      <c r="E43" s="149"/>
+      <c r="F43" s="149"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="137"/>
-      <c r="J43" s="138"/>
+      <c r="I43" s="149"/>
+      <c r="J43" s="150"/>
       <c r="K43" s="81" t="s">
         <v>92</v>
       </c>
@@ -32344,19 +32461,19 @@
       <c r="AF44" s="27"/>
     </row>
     <row r="45" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B45" s="148" t="s">
+      <c r="B45" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="144"/>
-      <c r="D45" s="144"/>
-      <c r="E45" s="144"/>
-      <c r="F45" s="144"/>
-      <c r="G45" s="149"/>
-      <c r="H45" s="159" t="s">
+      <c r="C45" s="146"/>
+      <c r="D45" s="146"/>
+      <c r="E45" s="146"/>
+      <c r="F45" s="146"/>
+      <c r="G45" s="147"/>
+      <c r="H45" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="I45" s="160"/>
-      <c r="J45" s="161"/>
+      <c r="I45" s="154"/>
+      <c r="J45" s="155"/>
       <c r="K45" s="83" t="s">
         <v>68</v>
       </c>
@@ -32384,18 +32501,18 @@
     </row>
     <row r="46" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B46" s="21"/>
-      <c r="C46" s="139" t="s">
+      <c r="C46" s="144" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="140"/>
-      <c r="E46" s="140"/>
-      <c r="F46" s="140"/>
-      <c r="G46" s="141"/>
-      <c r="H46" s="150" t="s">
+      <c r="D46" s="139"/>
+      <c r="E46" s="139"/>
+      <c r="F46" s="139"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="I46" s="151"/>
-      <c r="J46" s="152"/>
+      <c r="I46" s="137"/>
+      <c r="J46" s="138"/>
       <c r="K46" s="19" t="s">
         <v>93</v>
       </c>
@@ -32415,18 +32532,18 @@
     </row>
     <row r="47" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B47" s="22"/>
-      <c r="C47" s="139" t="s">
+      <c r="C47" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="140"/>
-      <c r="E47" s="140"/>
-      <c r="F47" s="140"/>
-      <c r="G47" s="141"/>
-      <c r="H47" s="146" t="s">
+      <c r="D47" s="139"/>
+      <c r="E47" s="139"/>
+      <c r="F47" s="139"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="141" t="s">
         <v>81</v>
       </c>
-      <c r="I47" s="140"/>
-      <c r="J47" s="141"/>
+      <c r="I47" s="139"/>
+      <c r="J47" s="140"/>
       <c r="K47" s="19" t="s">
         <v>95</v>
       </c>
@@ -32446,14 +32563,14 @@
     </row>
     <row r="48" spans="2:32" s="10" customFormat="1">
       <c r="B48" s="22"/>
-      <c r="C48" s="140"/>
-      <c r="D48" s="140"/>
-      <c r="E48" s="140"/>
-      <c r="F48" s="140"/>
-      <c r="G48" s="141"/>
-      <c r="H48" s="158"/>
-      <c r="I48" s="140"/>
-      <c r="J48" s="141"/>
+      <c r="C48" s="139"/>
+      <c r="D48" s="139"/>
+      <c r="E48" s="139"/>
+      <c r="F48" s="139"/>
+      <c r="G48" s="140"/>
+      <c r="H48" s="143"/>
+      <c r="I48" s="139"/>
+      <c r="J48" s="140"/>
       <c r="K48" s="19" t="s">
         <v>49</v>
       </c>
@@ -32475,14 +32592,14 @@
     </row>
     <row r="49" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B49" s="22"/>
-      <c r="C49" s="140"/>
-      <c r="D49" s="140"/>
-      <c r="E49" s="140"/>
-      <c r="F49" s="140"/>
-      <c r="G49" s="141"/>
-      <c r="H49" s="158"/>
-      <c r="I49" s="140"/>
-      <c r="J49" s="141"/>
+      <c r="C49" s="139"/>
+      <c r="D49" s="139"/>
+      <c r="E49" s="139"/>
+      <c r="F49" s="139"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="143"/>
+      <c r="I49" s="139"/>
+      <c r="J49" s="140"/>
       <c r="K49" s="19" t="s">
         <v>49</v>
       </c>
@@ -32539,19 +32656,19 @@
       <c r="AG50" s="92"/>
     </row>
     <row r="51" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B51" s="148" t="s">
+      <c r="B51" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="144"/>
-      <c r="D51" s="144"/>
-      <c r="E51" s="144"/>
-      <c r="F51" s="144"/>
-      <c r="G51" s="149"/>
-      <c r="H51" s="148" t="s">
+      <c r="C51" s="146"/>
+      <c r="D51" s="146"/>
+      <c r="E51" s="146"/>
+      <c r="F51" s="146"/>
+      <c r="G51" s="147"/>
+      <c r="H51" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I51" s="144"/>
-      <c r="J51" s="149"/>
+      <c r="I51" s="146"/>
+      <c r="J51" s="147"/>
       <c r="K51" s="28" t="s">
         <v>68</v>
       </c>
@@ -32580,18 +32697,18 @@
     </row>
     <row r="52" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B52" s="21"/>
-      <c r="C52" s="139" t="s">
+      <c r="C52" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="140"/>
-      <c r="E52" s="140"/>
-      <c r="F52" s="140"/>
-      <c r="G52" s="141"/>
-      <c r="H52" s="146" t="s">
+      <c r="D52" s="139"/>
+      <c r="E52" s="139"/>
+      <c r="F52" s="139"/>
+      <c r="G52" s="140"/>
+      <c r="H52" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I52" s="140"/>
-      <c r="J52" s="141"/>
+      <c r="I52" s="139"/>
+      <c r="J52" s="140"/>
       <c r="K52" s="19" t="s">
         <v>99</v>
       </c>
@@ -32611,18 +32728,18 @@
     </row>
     <row r="53" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B53" s="22"/>
-      <c r="C53" s="139" t="s">
+      <c r="C53" s="144" t="s">
         <v>100</v>
       </c>
-      <c r="D53" s="140"/>
-      <c r="E53" s="140"/>
-      <c r="F53" s="140"/>
-      <c r="G53" s="141"/>
-      <c r="H53" s="146" t="s">
+      <c r="D53" s="139"/>
+      <c r="E53" s="139"/>
+      <c r="F53" s="139"/>
+      <c r="G53" s="140"/>
+      <c r="H53" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I53" s="140"/>
-      <c r="J53" s="141"/>
+      <c r="I53" s="139"/>
+      <c r="J53" s="140"/>
       <c r="K53" s="19" t="s">
         <v>101</v>
       </c>
@@ -32642,18 +32759,18 @@
     </row>
     <row r="54" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B54" s="75"/>
-      <c r="C54" s="142" t="s">
+      <c r="C54" s="152" t="s">
         <v>102</v>
       </c>
-      <c r="D54" s="137"/>
-      <c r="E54" s="137"/>
-      <c r="F54" s="137"/>
-      <c r="G54" s="138"/>
-      <c r="H54" s="136" t="s">
+      <c r="D54" s="149"/>
+      <c r="E54" s="149"/>
+      <c r="F54" s="149"/>
+      <c r="G54" s="150"/>
+      <c r="H54" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I54" s="137"/>
-      <c r="J54" s="138"/>
+      <c r="I54" s="149"/>
+      <c r="J54" s="150"/>
       <c r="K54" s="81" t="s">
         <v>103</v>
       </c>
@@ -32717,19 +32834,19 @@
       <c r="AG55" s="92"/>
     </row>
     <row r="56" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B56" s="148" t="s">
+      <c r="B56" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="144"/>
-      <c r="D56" s="144"/>
-      <c r="E56" s="144"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="149"/>
-      <c r="H56" s="148" t="s">
+      <c r="C56" s="146"/>
+      <c r="D56" s="146"/>
+      <c r="E56" s="146"/>
+      <c r="F56" s="146"/>
+      <c r="G56" s="147"/>
+      <c r="H56" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I56" s="144"/>
-      <c r="J56" s="149"/>
+      <c r="I56" s="146"/>
+      <c r="J56" s="147"/>
       <c r="K56" s="28" t="s">
         <v>68</v>
       </c>
@@ -32758,18 +32875,18 @@
     </row>
     <row r="57" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B57" s="21"/>
-      <c r="C57" s="139" t="s">
+      <c r="C57" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="140"/>
-      <c r="E57" s="140"/>
-      <c r="F57" s="140"/>
-      <c r="G57" s="141"/>
-      <c r="H57" s="146" t="s">
+      <c r="D57" s="139"/>
+      <c r="E57" s="139"/>
+      <c r="F57" s="139"/>
+      <c r="G57" s="140"/>
+      <c r="H57" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I57" s="140"/>
-      <c r="J57" s="141"/>
+      <c r="I57" s="139"/>
+      <c r="J57" s="140"/>
       <c r="K57" s="19" t="s">
         <v>104</v>
       </c>
@@ -32789,18 +32906,18 @@
     </row>
     <row r="58" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B58" s="22"/>
-      <c r="C58" s="139" t="s">
+      <c r="C58" s="144" t="s">
         <v>105</v>
       </c>
-      <c r="D58" s="140"/>
-      <c r="E58" s="140"/>
-      <c r="F58" s="140"/>
-      <c r="G58" s="141"/>
-      <c r="H58" s="146" t="s">
+      <c r="D58" s="139"/>
+      <c r="E58" s="139"/>
+      <c r="F58" s="139"/>
+      <c r="G58" s="140"/>
+      <c r="H58" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I58" s="140"/>
-      <c r="J58" s="141"/>
+      <c r="I58" s="139"/>
+      <c r="J58" s="140"/>
       <c r="K58" s="19" t="s">
         <v>106</v>
       </c>
@@ -32820,18 +32937,18 @@
     </row>
     <row r="59" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B59" s="22"/>
-      <c r="C59" s="139" t="s">
+      <c r="C59" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="140"/>
-      <c r="E59" s="140"/>
-      <c r="F59" s="140"/>
-      <c r="G59" s="141"/>
-      <c r="H59" s="146" t="s">
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="140"/>
+      <c r="H59" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I59" s="140"/>
-      <c r="J59" s="141"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="140"/>
       <c r="K59" s="19" t="s">
         <v>107</v>
       </c>
@@ -32851,18 +32968,18 @@
     </row>
     <row r="60" spans="2:33" s="10" customFormat="1">
       <c r="B60" s="22"/>
-      <c r="C60" s="139" t="s">
+      <c r="C60" s="144" t="s">
         <v>108</v>
       </c>
-      <c r="D60" s="140"/>
-      <c r="E60" s="140"/>
-      <c r="F60" s="140"/>
-      <c r="G60" s="141"/>
-      <c r="H60" s="146" t="s">
+      <c r="D60" s="139"/>
+      <c r="E60" s="139"/>
+      <c r="F60" s="139"/>
+      <c r="G60" s="140"/>
+      <c r="H60" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I60" s="140"/>
-      <c r="J60" s="141"/>
+      <c r="I60" s="139"/>
+      <c r="J60" s="140"/>
       <c r="K60" s="19" t="s">
         <v>109</v>
       </c>
@@ -32882,18 +32999,18 @@
     </row>
     <row r="61" spans="2:33" s="10" customFormat="1">
       <c r="B61" s="22"/>
-      <c r="C61" s="139" t="s">
+      <c r="C61" s="144" t="s">
         <v>110</v>
       </c>
-      <c r="D61" s="140"/>
-      <c r="E61" s="140"/>
-      <c r="F61" s="140"/>
-      <c r="G61" s="141"/>
-      <c r="H61" s="146" t="s">
+      <c r="D61" s="139"/>
+      <c r="E61" s="139"/>
+      <c r="F61" s="139"/>
+      <c r="G61" s="140"/>
+      <c r="H61" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I61" s="140"/>
-      <c r="J61" s="141"/>
+      <c r="I61" s="139"/>
+      <c r="J61" s="140"/>
       <c r="K61" s="19" t="s">
         <v>111</v>
       </c>
@@ -32913,18 +33030,18 @@
     </row>
     <row r="62" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B62" s="75"/>
-      <c r="C62" s="142" t="s">
+      <c r="C62" s="152" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="137"/>
-      <c r="E62" s="137"/>
-      <c r="F62" s="137"/>
-      <c r="G62" s="138"/>
-      <c r="H62" s="136" t="s">
+      <c r="D62" s="149"/>
+      <c r="E62" s="149"/>
+      <c r="F62" s="149"/>
+      <c r="G62" s="150"/>
+      <c r="H62" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I62" s="137"/>
-      <c r="J62" s="138"/>
+      <c r="I62" s="149"/>
+      <c r="J62" s="150"/>
       <c r="K62" s="81" t="s">
         <v>113</v>
       </c>
@@ -32988,19 +33105,19 @@
       <c r="AG63" s="92"/>
     </row>
     <row r="64" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B64" s="148" t="s">
+      <c r="B64" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="144"/>
-      <c r="D64" s="144"/>
-      <c r="E64" s="144"/>
-      <c r="F64" s="144"/>
-      <c r="G64" s="149"/>
-      <c r="H64" s="148" t="s">
+      <c r="C64" s="146"/>
+      <c r="D64" s="146"/>
+      <c r="E64" s="146"/>
+      <c r="F64" s="146"/>
+      <c r="G64" s="147"/>
+      <c r="H64" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I64" s="144"/>
-      <c r="J64" s="149"/>
+      <c r="I64" s="146"/>
+      <c r="J64" s="147"/>
       <c r="K64" s="83" t="s">
         <v>68</v>
       </c>
@@ -33029,18 +33146,18 @@
     </row>
     <row r="65" spans="2:33">
       <c r="B65" s="21"/>
-      <c r="C65" s="139" t="s">
+      <c r="C65" s="144" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="147"/>
-      <c r="E65" s="147"/>
-      <c r="F65" s="147"/>
-      <c r="G65" s="141"/>
-      <c r="H65" s="150" t="s">
+      <c r="D65" s="151"/>
+      <c r="E65" s="151"/>
+      <c r="F65" s="151"/>
+      <c r="G65" s="140"/>
+      <c r="H65" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I65" s="151"/>
-      <c r="J65" s="152"/>
+      <c r="I65" s="137"/>
+      <c r="J65" s="138"/>
       <c r="K65" s="19" t="s">
         <v>115</v>
       </c>
@@ -33060,18 +33177,18 @@
     </row>
     <row r="66" spans="2:33">
       <c r="B66" s="22"/>
-      <c r="C66" s="139" t="s">
+      <c r="C66" s="144" t="s">
         <v>116</v>
       </c>
-      <c r="D66" s="147"/>
-      <c r="E66" s="147"/>
-      <c r="F66" s="147"/>
-      <c r="G66" s="141"/>
-      <c r="H66" s="146" t="s">
+      <c r="D66" s="151"/>
+      <c r="E66" s="151"/>
+      <c r="F66" s="151"/>
+      <c r="G66" s="140"/>
+      <c r="H66" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I66" s="147"/>
-      <c r="J66" s="141"/>
+      <c r="I66" s="151"/>
+      <c r="J66" s="140"/>
       <c r="K66" s="19" t="s">
         <v>117</v>
       </c>
@@ -33091,18 +33208,18 @@
     </row>
     <row r="67" spans="2:33">
       <c r="B67" s="22"/>
-      <c r="C67" s="139" t="s">
+      <c r="C67" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D67" s="147"/>
-      <c r="E67" s="147"/>
-      <c r="F67" s="147"/>
-      <c r="G67" s="141"/>
-      <c r="H67" s="146" t="s">
+      <c r="D67" s="151"/>
+      <c r="E67" s="151"/>
+      <c r="F67" s="151"/>
+      <c r="G67" s="140"/>
+      <c r="H67" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I67" s="147"/>
-      <c r="J67" s="141"/>
+      <c r="I67" s="151"/>
+      <c r="J67" s="140"/>
       <c r="K67" s="19" t="s">
         <v>118</v>
       </c>
@@ -33122,18 +33239,18 @@
     </row>
     <row r="68" spans="2:33">
       <c r="B68" s="22"/>
-      <c r="C68" s="139" t="s">
+      <c r="C68" s="144" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="147"/>
-      <c r="E68" s="147"/>
-      <c r="F68" s="147"/>
-      <c r="G68" s="141"/>
-      <c r="H68" s="146" t="s">
+      <c r="D68" s="151"/>
+      <c r="E68" s="151"/>
+      <c r="F68" s="151"/>
+      <c r="G68" s="140"/>
+      <c r="H68" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I68" s="147"/>
-      <c r="J68" s="141"/>
+      <c r="I68" s="151"/>
+      <c r="J68" s="140"/>
       <c r="K68" s="19" t="s">
         <v>120</v>
       </c>
@@ -33153,18 +33270,18 @@
     </row>
     <row r="69" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B69" s="75"/>
-      <c r="C69" s="142" t="s">
+      <c r="C69" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="D69" s="137"/>
-      <c r="E69" s="137"/>
-      <c r="F69" s="137"/>
-      <c r="G69" s="138"/>
-      <c r="H69" s="136" t="s">
+      <c r="D69" s="149"/>
+      <c r="E69" s="149"/>
+      <c r="F69" s="149"/>
+      <c r="G69" s="150"/>
+      <c r="H69" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="I69" s="137"/>
-      <c r="J69" s="138"/>
+      <c r="I69" s="149"/>
+      <c r="J69" s="150"/>
       <c r="K69" s="81" t="s">
         <v>122</v>
       </c>
@@ -33228,19 +33345,19 @@
       <c r="AG70" s="94"/>
     </row>
     <row r="71" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B71" s="148" t="s">
+      <c r="B71" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="144"/>
-      <c r="D71" s="144"/>
-      <c r="E71" s="144"/>
-      <c r="F71" s="144"/>
-      <c r="G71" s="149"/>
-      <c r="H71" s="148" t="s">
+      <c r="C71" s="146"/>
+      <c r="D71" s="146"/>
+      <c r="E71" s="146"/>
+      <c r="F71" s="146"/>
+      <c r="G71" s="147"/>
+      <c r="H71" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I71" s="144"/>
-      <c r="J71" s="149"/>
+      <c r="I71" s="146"/>
+      <c r="J71" s="147"/>
       <c r="K71" s="83" t="s">
         <v>68</v>
       </c>
@@ -33269,18 +33386,18 @@
     </row>
     <row r="72" spans="2:33">
       <c r="B72" s="21"/>
-      <c r="C72" s="139" t="s">
+      <c r="C72" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="147"/>
-      <c r="E72" s="147"/>
-      <c r="F72" s="147"/>
-      <c r="G72" s="141"/>
-      <c r="H72" s="150" t="s">
+      <c r="D72" s="151"/>
+      <c r="E72" s="151"/>
+      <c r="F72" s="151"/>
+      <c r="G72" s="140"/>
+      <c r="H72" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I72" s="151"/>
-      <c r="J72" s="152"/>
+      <c r="I72" s="137"/>
+      <c r="J72" s="138"/>
       <c r="K72" s="19" t="s">
         <v>123</v>
       </c>
@@ -33300,18 +33417,18 @@
     </row>
     <row r="73" spans="2:33">
       <c r="B73" s="22"/>
-      <c r="C73" s="139" t="s">
+      <c r="C73" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D73" s="147"/>
-      <c r="E73" s="147"/>
-      <c r="F73" s="147"/>
-      <c r="G73" s="141"/>
-      <c r="H73" s="146" t="s">
+      <c r="D73" s="151"/>
+      <c r="E73" s="151"/>
+      <c r="F73" s="151"/>
+      <c r="G73" s="140"/>
+      <c r="H73" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I73" s="147"/>
-      <c r="J73" s="141"/>
+      <c r="I73" s="151"/>
+      <c r="J73" s="140"/>
       <c r="K73" s="19" t="s">
         <v>124</v>
       </c>
@@ -33331,18 +33448,18 @@
     </row>
     <row r="74" spans="2:33">
       <c r="B74" s="22"/>
-      <c r="C74" s="139" t="s">
+      <c r="C74" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="D74" s="147"/>
-      <c r="E74" s="147"/>
-      <c r="F74" s="147"/>
-      <c r="G74" s="141"/>
-      <c r="H74" s="146" t="s">
+      <c r="D74" s="151"/>
+      <c r="E74" s="151"/>
+      <c r="F74" s="151"/>
+      <c r="G74" s="140"/>
+      <c r="H74" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I74" s="147"/>
-      <c r="J74" s="141"/>
+      <c r="I74" s="151"/>
+      <c r="J74" s="140"/>
       <c r="K74" s="19" t="s">
         <v>126</v>
       </c>
@@ -33362,18 +33479,18 @@
     </row>
     <row r="75" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B75" s="75"/>
-      <c r="C75" s="142" t="s">
+      <c r="C75" s="152" t="s">
         <v>127</v>
       </c>
-      <c r="D75" s="137"/>
-      <c r="E75" s="137"/>
-      <c r="F75" s="137"/>
-      <c r="G75" s="138"/>
-      <c r="H75" s="136" t="s">
+      <c r="D75" s="149"/>
+      <c r="E75" s="149"/>
+      <c r="F75" s="149"/>
+      <c r="G75" s="150"/>
+      <c r="H75" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I75" s="137"/>
-      <c r="J75" s="138"/>
+      <c r="I75" s="149"/>
+      <c r="J75" s="150"/>
       <c r="K75" s="81" t="s">
         <v>128</v>
       </c>
@@ -33437,19 +33554,19 @@
       <c r="AG76" s="94"/>
     </row>
     <row r="77" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B77" s="148" t="s">
+      <c r="B77" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C77" s="144"/>
-      <c r="D77" s="144"/>
-      <c r="E77" s="144"/>
-      <c r="F77" s="144"/>
-      <c r="G77" s="149"/>
-      <c r="H77" s="148" t="s">
+      <c r="C77" s="146"/>
+      <c r="D77" s="146"/>
+      <c r="E77" s="146"/>
+      <c r="F77" s="146"/>
+      <c r="G77" s="147"/>
+      <c r="H77" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I77" s="144"/>
-      <c r="J77" s="149"/>
+      <c r="I77" s="146"/>
+      <c r="J77" s="147"/>
       <c r="K77" s="83" t="s">
         <v>68</v>
       </c>
@@ -33478,18 +33595,18 @@
     </row>
     <row r="78" spans="2:33">
       <c r="B78" s="21"/>
-      <c r="C78" s="139" t="s">
+      <c r="C78" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="147"/>
-      <c r="E78" s="147"/>
-      <c r="F78" s="147"/>
-      <c r="G78" s="141"/>
-      <c r="H78" s="150" t="s">
+      <c r="D78" s="151"/>
+      <c r="E78" s="151"/>
+      <c r="F78" s="151"/>
+      <c r="G78" s="140"/>
+      <c r="H78" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="I78" s="151"/>
-      <c r="J78" s="152"/>
+      <c r="I78" s="137"/>
+      <c r="J78" s="138"/>
       <c r="K78" s="19" t="s">
         <v>129</v>
       </c>
@@ -33509,18 +33626,18 @@
     </row>
     <row r="79" spans="2:33">
       <c r="B79" s="22"/>
-      <c r="C79" s="139" t="s">
+      <c r="C79" s="144" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="147"/>
-      <c r="E79" s="147"/>
-      <c r="F79" s="147"/>
-      <c r="G79" s="141"/>
-      <c r="H79" s="146" t="s">
+      <c r="D79" s="151"/>
+      <c r="E79" s="151"/>
+      <c r="F79" s="151"/>
+      <c r="G79" s="140"/>
+      <c r="H79" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="I79" s="147"/>
-      <c r="J79" s="141"/>
+      <c r="I79" s="151"/>
+      <c r="J79" s="140"/>
       <c r="K79" s="19" t="s">
         <v>132</v>
       </c>
@@ -33540,18 +33657,18 @@
     </row>
     <row r="80" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B80" s="75"/>
-      <c r="C80" s="142" t="s">
+      <c r="C80" s="152" t="s">
         <v>133</v>
       </c>
-      <c r="D80" s="137"/>
-      <c r="E80" s="137"/>
-      <c r="F80" s="137"/>
-      <c r="G80" s="138"/>
-      <c r="H80" s="136" t="s">
+      <c r="D80" s="149"/>
+      <c r="E80" s="149"/>
+      <c r="F80" s="149"/>
+      <c r="G80" s="150"/>
+      <c r="H80" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I80" s="137"/>
-      <c r="J80" s="138"/>
+      <c r="I80" s="149"/>
+      <c r="J80" s="150"/>
       <c r="K80" s="81" t="s">
         <v>134</v>
       </c>
@@ -33662,12 +33779,81 @@
     </row>
   </sheetData>
   <mergeCells count="97">
-    <mergeCell ref="C24:G25"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="H24:J25"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="H65:J65"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C47:G49"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="B11:V11"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B5:V5"/>
+    <mergeCell ref="H47:J49"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="H40:J40"/>
     <mergeCell ref="H51:J51"/>
     <mergeCell ref="H69:J69"/>
     <mergeCell ref="C29:G29"/>
@@ -33684,81 +33870,12 @@
     <mergeCell ref="C62:G62"/>
     <mergeCell ref="H32:J32"/>
     <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B2:V2"/>
-    <mergeCell ref="B11:V11"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B5:V5"/>
-    <mergeCell ref="H47:J49"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C47:G49"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="H79:J79"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H78:J78"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="H65:J65"/>
-    <mergeCell ref="H71:J71"/>
-    <mergeCell ref="H75:J75"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="C24:G25"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="H24:J25"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:J26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -33767,7 +33884,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H1571"/>
+  <dimension ref="A1:H1584"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.75" style="2" bestFit="1" customWidth="1"/>
@@ -74333,6 +74450,344 @@
       </c>
       <c r="H1571" s="130" t="s">
         <v>7730</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:8">
+      <c r="A1572">
+        <v>901343</v>
+      </c>
+      <c r="B1572" s="2">
+        <v>91343</v>
+      </c>
+      <c r="C1572" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1572" s="130" t="s">
+        <v>8463</v>
+      </c>
+      <c r="E1572" s="130" t="s">
+        <v>8464</v>
+      </c>
+      <c r="F1572" s="130" t="s">
+        <v>8465</v>
+      </c>
+      <c r="G1572" s="130" t="s">
+        <v>8466</v>
+      </c>
+      <c r="H1572" s="130" t="s">
+        <v>8466</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:8">
+      <c r="A1573">
+        <v>901344</v>
+      </c>
+      <c r="B1573" s="2">
+        <v>91344</v>
+      </c>
+      <c r="C1573" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1573" s="130" t="s">
+        <v>8467</v>
+      </c>
+      <c r="E1573" s="130" t="s">
+        <v>8467</v>
+      </c>
+      <c r="F1573" s="130" t="s">
+        <v>8467</v>
+      </c>
+      <c r="G1573" s="130" t="s">
+        <v>8468</v>
+      </c>
+      <c r="H1573" s="130" t="s">
+        <v>8469</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:8">
+      <c r="A1574">
+        <v>901345</v>
+      </c>
+      <c r="B1574" s="2">
+        <v>91345</v>
+      </c>
+      <c r="C1574" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1574" s="130" t="s">
+        <v>8470</v>
+      </c>
+      <c r="E1574" s="130" t="s">
+        <v>8470</v>
+      </c>
+      <c r="F1574" s="130" t="s">
+        <v>8470</v>
+      </c>
+      <c r="G1574" s="130" t="s">
+        <v>8471</v>
+      </c>
+      <c r="H1574" s="130" t="s">
+        <v>8472</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:8">
+      <c r="A1575">
+        <v>901346</v>
+      </c>
+      <c r="B1575" s="2">
+        <v>91346</v>
+      </c>
+      <c r="C1575" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1575" s="130" t="s">
+        <v>8473</v>
+      </c>
+      <c r="E1575" s="130" t="s">
+        <v>8473</v>
+      </c>
+      <c r="F1575" s="130" t="s">
+        <v>8473</v>
+      </c>
+      <c r="G1575" s="130" t="s">
+        <v>8474</v>
+      </c>
+      <c r="H1575" s="130" t="s">
+        <v>8475</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:8">
+      <c r="A1576">
+        <v>901347</v>
+      </c>
+      <c r="B1576" s="2">
+        <v>91347</v>
+      </c>
+      <c r="C1576" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1576" s="130" t="s">
+        <v>8476</v>
+      </c>
+      <c r="E1576" s="130" t="s">
+        <v>8476</v>
+      </c>
+      <c r="F1576" s="130" t="s">
+        <v>8476</v>
+      </c>
+      <c r="G1576" s="130" t="s">
+        <v>8477</v>
+      </c>
+      <c r="H1576" s="130" t="s">
+        <v>8477</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:8">
+      <c r="A1577">
+        <v>901348</v>
+      </c>
+      <c r="B1577" s="2">
+        <v>91348</v>
+      </c>
+      <c r="C1577" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1577" s="130" t="s">
+        <v>8478</v>
+      </c>
+      <c r="E1577" s="130" t="s">
+        <v>8478</v>
+      </c>
+      <c r="F1577" s="130" t="s">
+        <v>8478</v>
+      </c>
+      <c r="G1577" s="130" t="s">
+        <v>8479</v>
+      </c>
+      <c r="H1577" s="130" t="s">
+        <v>8479</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:8">
+      <c r="A1578">
+        <v>901349</v>
+      </c>
+      <c r="B1578" s="2">
+        <v>91349</v>
+      </c>
+      <c r="C1578" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1578" s="130" t="s">
+        <v>8480</v>
+      </c>
+      <c r="E1578" s="130" t="s">
+        <v>8480</v>
+      </c>
+      <c r="F1578" s="130" t="s">
+        <v>8480</v>
+      </c>
+      <c r="G1578" s="130" t="s">
+        <v>8481</v>
+      </c>
+      <c r="H1578" s="130" t="s">
+        <v>8481</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:8">
+      <c r="A1579">
+        <v>901350</v>
+      </c>
+      <c r="B1579" s="2">
+        <v>91350</v>
+      </c>
+      <c r="C1579" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1579" s="130" t="s">
+        <v>8482</v>
+      </c>
+      <c r="E1579" s="130" t="s">
+        <v>8482</v>
+      </c>
+      <c r="F1579" s="130" t="s">
+        <v>8483</v>
+      </c>
+      <c r="G1579" s="130" t="s">
+        <v>8484</v>
+      </c>
+      <c r="H1579" s="130" t="s">
+        <v>8485</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:8">
+      <c r="A1580">
+        <v>901351</v>
+      </c>
+      <c r="B1580" s="2">
+        <v>91351</v>
+      </c>
+      <c r="C1580" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1580" s="130" t="s">
+        <v>8486</v>
+      </c>
+      <c r="E1580" s="130" t="s">
+        <v>8486</v>
+      </c>
+      <c r="F1580" s="130" t="s">
+        <v>8487</v>
+      </c>
+      <c r="G1580" s="130" t="s">
+        <v>8488</v>
+      </c>
+      <c r="H1580" s="130" t="s">
+        <v>8489</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:8">
+      <c r="A1581">
+        <v>901352</v>
+      </c>
+      <c r="B1581" s="2">
+        <v>91352</v>
+      </c>
+      <c r="C1581" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1581" s="130" t="s">
+        <v>8490</v>
+      </c>
+      <c r="E1581" s="130" t="s">
+        <v>8490</v>
+      </c>
+      <c r="F1581" s="130" t="s">
+        <v>8490</v>
+      </c>
+      <c r="G1581" s="130" t="s">
+        <v>8491</v>
+      </c>
+      <c r="H1581" s="130" t="s">
+        <v>8492</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:8">
+      <c r="A1582">
+        <v>901353</v>
+      </c>
+      <c r="B1582" s="2">
+        <v>91353</v>
+      </c>
+      <c r="C1582" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1582" s="130" t="s">
+        <v>8493</v>
+      </c>
+      <c r="E1582" s="130" t="s">
+        <v>8493</v>
+      </c>
+      <c r="F1582" s="130" t="s">
+        <v>8493</v>
+      </c>
+      <c r="G1582" s="130" t="s">
+        <v>8494</v>
+      </c>
+      <c r="H1582" s="130" t="s">
+        <v>8495</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:8">
+      <c r="A1583">
+        <v>901354</v>
+      </c>
+      <c r="B1583" s="2">
+        <v>91354</v>
+      </c>
+      <c r="C1583" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1583" s="130" t="s">
+        <v>8496</v>
+      </c>
+      <c r="E1583" s="130" t="s">
+        <v>8496</v>
+      </c>
+      <c r="F1583" s="130" t="s">
+        <v>8496</v>
+      </c>
+      <c r="G1583" s="130" t="s">
+        <v>8497</v>
+      </c>
+      <c r="H1583" s="130" t="s">
+        <v>8498</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:8">
+      <c r="A1584">
+        <v>901355</v>
+      </c>
+      <c r="B1584" s="2">
+        <v>91355</v>
+      </c>
+      <c r="C1584" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1584" s="130" t="s">
+        <v>8499</v>
+      </c>
+      <c r="E1584" s="130" t="s">
+        <v>8499</v>
+      </c>
+      <c r="F1584" s="130" t="s">
+        <v>8499</v>
+      </c>
+      <c r="G1584" s="130" t="s">
+        <v>8500</v>
+      </c>
+      <c r="H1584" s="130" t="s">
+        <v>8501</v>
       </c>
     </row>
   </sheetData>
@@ -76256,10 +76711,10 @@
       <c r="B2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
       <c r="G2" s="163"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -76269,10 +76724,10 @@
       <c r="M2" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="149"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="147"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
       <c r="T2" s="11"/>
@@ -76280,10 +76735,10 @@
       <c r="V2" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="W2" s="144"/>
-      <c r="X2" s="144"/>
-      <c r="Y2" s="144"/>
-      <c r="Z2" s="149"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="146"/>
+      <c r="Y2" s="146"/>
+      <c r="Z2" s="147"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
       <c r="AC2" s="10"/>
@@ -76402,10 +76857,10 @@
       <c r="V5" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="W5" s="144"/>
-      <c r="X5" s="144"/>
-      <c r="Y5" s="144"/>
-      <c r="Z5" s="149"/>
+      <c r="W5" s="146"/>
+      <c r="X5" s="146"/>
+      <c r="Y5" s="146"/>
+      <c r="Z5" s="147"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="10"/>
@@ -76451,10 +76906,10 @@
       <c r="B7" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="144"/>
-      <c r="D7" s="144"/>
-      <c r="E7" s="144"/>
-      <c r="F7" s="149"/>
+      <c r="C7" s="146"/>
+      <c r="D7" s="146"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="147"/>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -76463,10 +76918,10 @@
       <c r="L7" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="144"/>
-      <c r="N7" s="144"/>
-      <c r="O7" s="144"/>
-      <c r="P7" s="149"/>
+      <c r="M7" s="146"/>
+      <c r="N7" s="146"/>
+      <c r="O7" s="146"/>
+      <c r="P7" s="147"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
@@ -76675,10 +77130,10 @@
       <c r="AB14" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="AC14" s="144"/>
-      <c r="AD14" s="144"/>
-      <c r="AE14" s="144"/>
-      <c r="AF14" s="149"/>
+      <c r="AC14" s="146"/>
+      <c r="AD14" s="146"/>
+      <c r="AE14" s="146"/>
+      <c r="AF14" s="147"/>
       <c r="AG14" s="100"/>
       <c r="AH14" s="45"/>
       <c r="AI14" s="12"/>
@@ -76752,10 +77207,10 @@
       <c r="AB17" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="AC17" s="144"/>
-      <c r="AD17" s="144"/>
-      <c r="AE17" s="144"/>
-      <c r="AF17" s="149"/>
+      <c r="AC17" s="146"/>
+      <c r="AD17" s="146"/>
+      <c r="AE17" s="146"/>
+      <c r="AF17" s="147"/>
       <c r="AG17" s="102"/>
       <c r="AH17" s="38"/>
       <c r="AI17" s="10"/>
@@ -76873,10 +77328,10 @@
       <c r="AB21" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="AC21" s="144"/>
-      <c r="AD21" s="144"/>
-      <c r="AE21" s="144"/>
-      <c r="AF21" s="149"/>
+      <c r="AC21" s="146"/>
+      <c r="AD21" s="146"/>
+      <c r="AE21" s="146"/>
+      <c r="AF21" s="147"/>
       <c r="AG21" s="116"/>
       <c r="AH21" s="117"/>
     </row>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863A55FC-4DCE-4C26-929D-54DE79DCCE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628DA6BB-EF71-4E53-9D11-D4472AADDF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10581" uniqueCount="8357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10677" uniqueCount="8373">
   <si>
     <t>Upgrade_Table</t>
   </si>
@@ -28949,6 +28949,54 @@
   </si>
   <si>
     <t>세트 밖이지만 배치한 UI가 쓰는 한·영 전용 폰트 (ONEMobilePOP 등). 한국어·영어에서는 그대로 두고, 그 밖의 언어에서는 그 언어 본문 폰트로 바꾼다 (TextLangFont)</t>
+  </si>
+  <si>
+    <t>에픽 이상 가중치 ×{0}</t>
+  </si>
+  <si>
+    <t>언어</t>
+  </si>
+  <si>
+    <t>소리 설정</t>
+  </si>
+  <si>
+    <t>효과음</t>
+  </si>
+  <si>
+    <t>배경음</t>
+  </si>
+  <si>
+    <t>메인 메뉴</t>
+  </si>
+  <si>
+    <t>음소거: 켜짐</t>
+  </si>
+  <si>
+    <t>음소거: 꺼짐</t>
+  </si>
+  <si>
+    <t>얻은 점수 → 골드 (×{0})</t>
+  </si>
+  <si>
+    <t>신기록! {0} {1}</t>
+  </si>
+  <si>
+    <t>보스 {0} 처치! 스테이지 {1} 열림</t>
+  </si>
+  <si>
+    <t>{0} 완성! 강화 재료로 보관했어요</t>
+  </si>
+  <si>
+    <t>오늘 즉시 완료를 다 썼어요</t>
+  </si>
+  <si>
+    <t>꼬마가 합류하면 열려요</t>
+  </si>
+  <si>
+    <t>{0} 합류 시 해금</t>
+  </si>
+  <si>
+    <t>빈 칸</t>
   </si>
 </sst>
 </file>
@@ -29833,46 +29881,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -29881,12 +29929,12 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -30354,29 +30402,29 @@
   <sheetData>
     <row r="1" spans="2:44" ht="12" customHeight="1"/>
     <row r="2" spans="2:44">
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="155"/>
-      <c r="Q2" s="155"/>
-      <c r="R2" s="155"/>
-      <c r="S2" s="155"/>
-      <c r="T2" s="155"/>
-      <c r="U2" s="155"/>
-      <c r="V2" s="156"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="157"/>
+      <c r="U2" s="157"/>
+      <c r="V2" s="158"/>
     </row>
     <row r="3" spans="2:44">
       <c r="B3" s="17"/>
@@ -30433,29 +30481,29 @@
       <c r="V4" s="14"/>
     </row>
     <row r="5" spans="2:44">
-      <c r="B5" s="154" t="s">
+      <c r="B5" s="156" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="155"/>
-      <c r="K5" s="155"/>
-      <c r="L5" s="155"/>
-      <c r="M5" s="155"/>
-      <c r="N5" s="155"/>
-      <c r="O5" s="155"/>
-      <c r="P5" s="155"/>
-      <c r="Q5" s="155"/>
-      <c r="R5" s="155"/>
-      <c r="S5" s="155"/>
-      <c r="T5" s="155"/>
-      <c r="U5" s="155"/>
-      <c r="V5" s="156"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="157"/>
+      <c r="G5" s="157"/>
+      <c r="H5" s="157"/>
+      <c r="I5" s="157"/>
+      <c r="J5" s="157"/>
+      <c r="K5" s="157"/>
+      <c r="L5" s="157"/>
+      <c r="M5" s="157"/>
+      <c r="N5" s="157"/>
+      <c r="O5" s="157"/>
+      <c r="P5" s="157"/>
+      <c r="Q5" s="157"/>
+      <c r="R5" s="157"/>
+      <c r="S5" s="157"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="157"/>
+      <c r="V5" s="158"/>
     </row>
     <row r="6" spans="2:44">
       <c r="B6" s="6"/>
@@ -30585,29 +30633,29 @@
     </row>
     <row r="10" spans="2:44" ht="8.1" customHeight="1"/>
     <row r="11" spans="2:44">
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="156" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155"/>
-      <c r="E11" s="155"/>
-      <c r="F11" s="155"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="155"/>
-      <c r="I11" s="155"/>
-      <c r="J11" s="155"/>
-      <c r="K11" s="155"/>
-      <c r="L11" s="155"/>
-      <c r="M11" s="155"/>
-      <c r="N11" s="155"/>
-      <c r="O11" s="155"/>
-      <c r="P11" s="155"/>
-      <c r="Q11" s="155"/>
-      <c r="R11" s="155"/>
-      <c r="S11" s="155"/>
-      <c r="T11" s="155"/>
-      <c r="U11" s="155"/>
-      <c r="V11" s="156"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="157"/>
+      <c r="F11" s="157"/>
+      <c r="G11" s="157"/>
+      <c r="H11" s="157"/>
+      <c r="I11" s="157"/>
+      <c r="J11" s="157"/>
+      <c r="K11" s="157"/>
+      <c r="L11" s="157"/>
+      <c r="M11" s="157"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="157"/>
+      <c r="Q11" s="157"/>
+      <c r="R11" s="157"/>
+      <c r="S11" s="157"/>
+      <c r="T11" s="157"/>
+      <c r="U11" s="157"/>
+      <c r="V11" s="158"/>
     </row>
     <row r="12" spans="2:44">
       <c r="B12" s="6"/>
@@ -30894,19 +30942,19 @@
       <c r="AF22" s="27"/>
     </row>
     <row r="23" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B23" s="157" t="s">
+      <c r="B23" s="159" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="144"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="143" t="s">
+      <c r="C23" s="146"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="146"/>
+      <c r="H23" s="161" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="144"/>
-      <c r="J23" s="144"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="146"/>
       <c r="K23" s="28" t="s">
         <v>68</v>
       </c>
@@ -30934,18 +30982,18 @@
     </row>
     <row r="24" spans="2:32" s="10" customFormat="1">
       <c r="B24" s="86"/>
-      <c r="C24" s="153" t="s">
+      <c r="C24" s="136" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="151"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="152"/>
-      <c r="H24" s="150" t="s">
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="137"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="151"/>
-      <c r="J24" s="152"/>
+      <c r="I24" s="137"/>
+      <c r="J24" s="138"/>
       <c r="K24" s="34" t="s">
         <v>70</v>
       </c>
@@ -30973,14 +31021,14 @@
     </row>
     <row r="25" spans="2:32" s="10" customFormat="1">
       <c r="B25" s="22"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="140"/>
-      <c r="G25" s="141"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="140"/>
-      <c r="J25" s="141"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="139"/>
+      <c r="J25" s="140"/>
       <c r="K25" s="19" t="s">
         <v>49</v>
       </c>
@@ -31002,18 +31050,18 @@
     </row>
     <row r="26" spans="2:32" s="10" customFormat="1">
       <c r="B26" s="22"/>
-      <c r="C26" s="139" t="s">
+      <c r="C26" s="144" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="141"/>
-      <c r="H26" s="146" t="s">
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="140"/>
-      <c r="J26" s="141"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="140"/>
       <c r="K26" s="19" t="s">
         <v>74</v>
       </c>
@@ -31033,18 +31081,18 @@
     </row>
     <row r="27" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B27" s="22"/>
-      <c r="C27" s="139" t="s">
+      <c r="C27" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="140"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
-      <c r="G27" s="141"/>
-      <c r="H27" s="146" t="s">
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I27" s="140"/>
-      <c r="J27" s="141"/>
+      <c r="I27" s="139"/>
+      <c r="J27" s="140"/>
       <c r="K27" s="19" t="s">
         <v>75</v>
       </c>
@@ -31064,18 +31112,18 @@
     </row>
     <row r="28" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B28" s="22"/>
-      <c r="C28" s="139" t="s">
+      <c r="C28" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="140"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="141"/>
-      <c r="H28" s="146" t="s">
+      <c r="D28" s="139"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="139"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I28" s="140"/>
-      <c r="J28" s="141"/>
+      <c r="I28" s="139"/>
+      <c r="J28" s="140"/>
       <c r="K28" s="19" t="s">
         <v>77</v>
       </c>
@@ -31095,18 +31143,18 @@
     </row>
     <row r="29" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B29" s="22"/>
-      <c r="C29" s="139" t="s">
+      <c r="C29" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="140"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="140"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="146" t="s">
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I29" s="140"/>
-      <c r="J29" s="141"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="140"/>
       <c r="K29" s="19" t="s">
         <v>78</v>
       </c>
@@ -31126,18 +31174,18 @@
     </row>
     <row r="30" spans="2:32" s="10" customFormat="1">
       <c r="B30" s="22"/>
-      <c r="C30" s="139" t="s">
+      <c r="C30" s="144" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="140"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="140"/>
-      <c r="G30" s="141"/>
-      <c r="H30" s="146" t="s">
+      <c r="D30" s="139"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I30" s="140"/>
-      <c r="J30" s="141"/>
+      <c r="I30" s="139"/>
+      <c r="J30" s="140"/>
       <c r="K30" s="120" t="s">
         <v>421</v>
       </c>
@@ -31157,18 +31205,18 @@
     </row>
     <row r="31" spans="2:32" s="10" customFormat="1">
       <c r="B31" s="22"/>
-      <c r="C31" s="139" t="s">
+      <c r="C31" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="140"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="141"/>
-      <c r="H31" s="146" t="s">
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I31" s="140"/>
-      <c r="J31" s="141"/>
+      <c r="I31" s="139"/>
+      <c r="J31" s="140"/>
       <c r="K31" s="19" t="s">
         <v>80</v>
       </c>
@@ -31188,18 +31236,18 @@
     </row>
     <row r="32" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B32" s="75"/>
-      <c r="C32" s="145" t="s">
+      <c r="C32" s="160" t="s">
         <v>422</v>
       </c>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="138"/>
-      <c r="H32" s="136" t="s">
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
+      <c r="F32" s="149"/>
+      <c r="G32" s="150"/>
+      <c r="H32" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="137"/>
-      <c r="J32" s="138"/>
+      <c r="I32" s="149"/>
+      <c r="J32" s="150"/>
       <c r="K32" s="81" t="s">
         <v>82</v>
       </c>
@@ -31261,19 +31309,19 @@
       <c r="AF33" s="27"/>
     </row>
     <row r="34" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B34" s="148" t="s">
+      <c r="B34" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="144"/>
-      <c r="D34" s="144"/>
-      <c r="E34" s="144"/>
-      <c r="F34" s="144"/>
-      <c r="G34" s="149"/>
-      <c r="H34" s="148" t="s">
+      <c r="C34" s="146"/>
+      <c r="D34" s="146"/>
+      <c r="E34" s="146"/>
+      <c r="F34" s="146"/>
+      <c r="G34" s="147"/>
+      <c r="H34" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I34" s="144"/>
-      <c r="J34" s="149"/>
+      <c r="I34" s="146"/>
+      <c r="J34" s="147"/>
       <c r="K34" s="28" t="s">
         <v>68</v>
       </c>
@@ -31301,18 +31349,18 @@
     </row>
     <row r="35" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B35" s="86"/>
-      <c r="C35" s="153" t="s">
+      <c r="C35" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
-      <c r="G35" s="152"/>
-      <c r="H35" s="150" t="s">
+      <c r="D35" s="137"/>
+      <c r="E35" s="137"/>
+      <c r="F35" s="137"/>
+      <c r="G35" s="138"/>
+      <c r="H35" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I35" s="151"/>
-      <c r="J35" s="152"/>
+      <c r="I35" s="137"/>
+      <c r="J35" s="138"/>
       <c r="K35" s="34" t="s">
         <v>84</v>
       </c>
@@ -31340,18 +31388,18 @@
     </row>
     <row r="36" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B36" s="75"/>
-      <c r="C36" s="145" t="s">
+      <c r="C36" s="160" t="s">
         <v>423</v>
       </c>
-      <c r="D36" s="137"/>
-      <c r="E36" s="137"/>
-      <c r="F36" s="137"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="136" t="s">
+      <c r="D36" s="149"/>
+      <c r="E36" s="149"/>
+      <c r="F36" s="149"/>
+      <c r="G36" s="150"/>
+      <c r="H36" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="I36" s="137"/>
-      <c r="J36" s="138"/>
+      <c r="I36" s="149"/>
+      <c r="J36" s="150"/>
       <c r="K36" s="81" t="s">
         <v>85</v>
       </c>
@@ -31413,19 +31461,19 @@
       <c r="AF37" s="92"/>
     </row>
     <row r="38" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B38" s="148" t="s">
+      <c r="B38" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="144"/>
-      <c r="D38" s="144"/>
-      <c r="E38" s="144"/>
-      <c r="F38" s="144"/>
-      <c r="G38" s="149"/>
-      <c r="H38" s="148" t="s">
+      <c r="C38" s="146"/>
+      <c r="D38" s="146"/>
+      <c r="E38" s="146"/>
+      <c r="F38" s="146"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="144"/>
-      <c r="J38" s="149"/>
+      <c r="I38" s="146"/>
+      <c r="J38" s="147"/>
       <c r="K38" s="28" t="s">
         <v>68</v>
       </c>
@@ -31453,18 +31501,18 @@
     </row>
     <row r="39" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B39" s="21"/>
-      <c r="C39" s="139" t="s">
+      <c r="C39" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="140"/>
-      <c r="E39" s="140"/>
-      <c r="F39" s="140"/>
-      <c r="G39" s="141"/>
-      <c r="H39" s="146" t="s">
+      <c r="D39" s="139"/>
+      <c r="E39" s="139"/>
+      <c r="F39" s="139"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I39" s="140"/>
-      <c r="J39" s="141"/>
+      <c r="I39" s="139"/>
+      <c r="J39" s="140"/>
       <c r="K39" s="19" t="s">
         <v>86</v>
       </c>
@@ -31484,18 +31532,18 @@
     </row>
     <row r="40" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B40" s="22"/>
-      <c r="C40" s="139" t="s">
+      <c r="C40" s="144" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="140"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="140"/>
-      <c r="G40" s="141"/>
-      <c r="H40" s="146" t="s">
+      <c r="D40" s="139"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="139"/>
+      <c r="G40" s="140"/>
+      <c r="H40" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I40" s="140"/>
-      <c r="J40" s="141"/>
+      <c r="I40" s="139"/>
+      <c r="J40" s="140"/>
       <c r="K40" s="19" t="s">
         <v>88</v>
       </c>
@@ -31515,18 +31563,18 @@
     </row>
     <row r="41" spans="2:32" s="10" customFormat="1">
       <c r="B41" s="22"/>
-      <c r="C41" s="139" t="s">
+      <c r="C41" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="140"/>
-      <c r="E41" s="140"/>
-      <c r="F41" s="140"/>
-      <c r="G41" s="141"/>
-      <c r="H41" s="146" t="s">
+      <c r="D41" s="139"/>
+      <c r="E41" s="139"/>
+      <c r="F41" s="139"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="140"/>
-      <c r="J41" s="141"/>
+      <c r="I41" s="139"/>
+      <c r="J41" s="140"/>
       <c r="K41" s="19" t="s">
         <v>89</v>
       </c>
@@ -31546,18 +31594,18 @@
     </row>
     <row r="42" spans="2:32" s="10" customFormat="1">
       <c r="B42" s="22"/>
-      <c r="C42" s="139" t="s">
+      <c r="C42" s="144" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="140"/>
-      <c r="E42" s="140"/>
-      <c r="F42" s="140"/>
-      <c r="G42" s="141"/>
-      <c r="H42" s="146" t="s">
+      <c r="D42" s="139"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I42" s="140"/>
-      <c r="J42" s="141"/>
+      <c r="I42" s="139"/>
+      <c r="J42" s="140"/>
       <c r="K42" s="19" t="s">
         <v>91</v>
       </c>
@@ -31577,18 +31625,18 @@
     </row>
     <row r="43" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B43" s="75"/>
-      <c r="C43" s="142" t="s">
+      <c r="C43" s="152" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="137"/>
-      <c r="E43" s="137"/>
-      <c r="F43" s="137"/>
-      <c r="G43" s="138"/>
-      <c r="H43" s="136" t="s">
+      <c r="D43" s="149"/>
+      <c r="E43" s="149"/>
+      <c r="F43" s="149"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="137"/>
-      <c r="J43" s="138"/>
+      <c r="I43" s="149"/>
+      <c r="J43" s="150"/>
       <c r="K43" s="81" t="s">
         <v>92</v>
       </c>
@@ -31650,19 +31698,19 @@
       <c r="AF44" s="27"/>
     </row>
     <row r="45" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B45" s="148" t="s">
+      <c r="B45" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="144"/>
-      <c r="D45" s="144"/>
-      <c r="E45" s="144"/>
-      <c r="F45" s="144"/>
-      <c r="G45" s="149"/>
-      <c r="H45" s="159" t="s">
+      <c r="C45" s="146"/>
+      <c r="D45" s="146"/>
+      <c r="E45" s="146"/>
+      <c r="F45" s="146"/>
+      <c r="G45" s="147"/>
+      <c r="H45" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="I45" s="160"/>
-      <c r="J45" s="161"/>
+      <c r="I45" s="154"/>
+      <c r="J45" s="155"/>
       <c r="K45" s="83" t="s">
         <v>68</v>
       </c>
@@ -31690,18 +31738,18 @@
     </row>
     <row r="46" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B46" s="21"/>
-      <c r="C46" s="139" t="s">
+      <c r="C46" s="144" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="140"/>
-      <c r="E46" s="140"/>
-      <c r="F46" s="140"/>
-      <c r="G46" s="141"/>
-      <c r="H46" s="150" t="s">
+      <c r="D46" s="139"/>
+      <c r="E46" s="139"/>
+      <c r="F46" s="139"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="I46" s="151"/>
-      <c r="J46" s="152"/>
+      <c r="I46" s="137"/>
+      <c r="J46" s="138"/>
       <c r="K46" s="19" t="s">
         <v>93</v>
       </c>
@@ -31721,18 +31769,18 @@
     </row>
     <row r="47" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B47" s="22"/>
-      <c r="C47" s="139" t="s">
+      <c r="C47" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="140"/>
-      <c r="E47" s="140"/>
-      <c r="F47" s="140"/>
-      <c r="G47" s="141"/>
-      <c r="H47" s="146" t="s">
+      <c r="D47" s="139"/>
+      <c r="E47" s="139"/>
+      <c r="F47" s="139"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="141" t="s">
         <v>81</v>
       </c>
-      <c r="I47" s="140"/>
-      <c r="J47" s="141"/>
+      <c r="I47" s="139"/>
+      <c r="J47" s="140"/>
       <c r="K47" s="19" t="s">
         <v>95</v>
       </c>
@@ -31752,14 +31800,14 @@
     </row>
     <row r="48" spans="2:32" s="10" customFormat="1">
       <c r="B48" s="22"/>
-      <c r="C48" s="140"/>
-      <c r="D48" s="140"/>
-      <c r="E48" s="140"/>
-      <c r="F48" s="140"/>
-      <c r="G48" s="141"/>
-      <c r="H48" s="158"/>
-      <c r="I48" s="140"/>
-      <c r="J48" s="141"/>
+      <c r="C48" s="139"/>
+      <c r="D48" s="139"/>
+      <c r="E48" s="139"/>
+      <c r="F48" s="139"/>
+      <c r="G48" s="140"/>
+      <c r="H48" s="143"/>
+      <c r="I48" s="139"/>
+      <c r="J48" s="140"/>
       <c r="K48" s="19" t="s">
         <v>49</v>
       </c>
@@ -31781,14 +31829,14 @@
     </row>
     <row r="49" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B49" s="22"/>
-      <c r="C49" s="140"/>
-      <c r="D49" s="140"/>
-      <c r="E49" s="140"/>
-      <c r="F49" s="140"/>
-      <c r="G49" s="141"/>
-      <c r="H49" s="158"/>
-      <c r="I49" s="140"/>
-      <c r="J49" s="141"/>
+      <c r="C49" s="139"/>
+      <c r="D49" s="139"/>
+      <c r="E49" s="139"/>
+      <c r="F49" s="139"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="143"/>
+      <c r="I49" s="139"/>
+      <c r="J49" s="140"/>
       <c r="K49" s="19" t="s">
         <v>49</v>
       </c>
@@ -31845,19 +31893,19 @@
       <c r="AG50" s="92"/>
     </row>
     <row r="51" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B51" s="148" t="s">
+      <c r="B51" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="144"/>
-      <c r="D51" s="144"/>
-      <c r="E51" s="144"/>
-      <c r="F51" s="144"/>
-      <c r="G51" s="149"/>
-      <c r="H51" s="148" t="s">
+      <c r="C51" s="146"/>
+      <c r="D51" s="146"/>
+      <c r="E51" s="146"/>
+      <c r="F51" s="146"/>
+      <c r="G51" s="147"/>
+      <c r="H51" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I51" s="144"/>
-      <c r="J51" s="149"/>
+      <c r="I51" s="146"/>
+      <c r="J51" s="147"/>
       <c r="K51" s="28" t="s">
         <v>68</v>
       </c>
@@ -31886,18 +31934,18 @@
     </row>
     <row r="52" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B52" s="21"/>
-      <c r="C52" s="139" t="s">
+      <c r="C52" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="140"/>
-      <c r="E52" s="140"/>
-      <c r="F52" s="140"/>
-      <c r="G52" s="141"/>
-      <c r="H52" s="146" t="s">
+      <c r="D52" s="139"/>
+      <c r="E52" s="139"/>
+      <c r="F52" s="139"/>
+      <c r="G52" s="140"/>
+      <c r="H52" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I52" s="140"/>
-      <c r="J52" s="141"/>
+      <c r="I52" s="139"/>
+      <c r="J52" s="140"/>
       <c r="K52" s="19" t="s">
         <v>99</v>
       </c>
@@ -31917,18 +31965,18 @@
     </row>
     <row r="53" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B53" s="22"/>
-      <c r="C53" s="139" t="s">
+      <c r="C53" s="144" t="s">
         <v>100</v>
       </c>
-      <c r="D53" s="140"/>
-      <c r="E53" s="140"/>
-      <c r="F53" s="140"/>
-      <c r="G53" s="141"/>
-      <c r="H53" s="146" t="s">
+      <c r="D53" s="139"/>
+      <c r="E53" s="139"/>
+      <c r="F53" s="139"/>
+      <c r="G53" s="140"/>
+      <c r="H53" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I53" s="140"/>
-      <c r="J53" s="141"/>
+      <c r="I53" s="139"/>
+      <c r="J53" s="140"/>
       <c r="K53" s="19" t="s">
         <v>101</v>
       </c>
@@ -31948,18 +31996,18 @@
     </row>
     <row r="54" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B54" s="75"/>
-      <c r="C54" s="142" t="s">
+      <c r="C54" s="152" t="s">
         <v>102</v>
       </c>
-      <c r="D54" s="137"/>
-      <c r="E54" s="137"/>
-      <c r="F54" s="137"/>
-      <c r="G54" s="138"/>
-      <c r="H54" s="136" t="s">
+      <c r="D54" s="149"/>
+      <c r="E54" s="149"/>
+      <c r="F54" s="149"/>
+      <c r="G54" s="150"/>
+      <c r="H54" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I54" s="137"/>
-      <c r="J54" s="138"/>
+      <c r="I54" s="149"/>
+      <c r="J54" s="150"/>
       <c r="K54" s="81" t="s">
         <v>103</v>
       </c>
@@ -32023,19 +32071,19 @@
       <c r="AG55" s="92"/>
     </row>
     <row r="56" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B56" s="148" t="s">
+      <c r="B56" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="144"/>
-      <c r="D56" s="144"/>
-      <c r="E56" s="144"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="149"/>
-      <c r="H56" s="148" t="s">
+      <c r="C56" s="146"/>
+      <c r="D56" s="146"/>
+      <c r="E56" s="146"/>
+      <c r="F56" s="146"/>
+      <c r="G56" s="147"/>
+      <c r="H56" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I56" s="144"/>
-      <c r="J56" s="149"/>
+      <c r="I56" s="146"/>
+      <c r="J56" s="147"/>
       <c r="K56" s="28" t="s">
         <v>68</v>
       </c>
@@ -32064,18 +32112,18 @@
     </row>
     <row r="57" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B57" s="21"/>
-      <c r="C57" s="139" t="s">
+      <c r="C57" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="140"/>
-      <c r="E57" s="140"/>
-      <c r="F57" s="140"/>
-      <c r="G57" s="141"/>
-      <c r="H57" s="146" t="s">
+      <c r="D57" s="139"/>
+      <c r="E57" s="139"/>
+      <c r="F57" s="139"/>
+      <c r="G57" s="140"/>
+      <c r="H57" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I57" s="140"/>
-      <c r="J57" s="141"/>
+      <c r="I57" s="139"/>
+      <c r="J57" s="140"/>
       <c r="K57" s="19" t="s">
         <v>104</v>
       </c>
@@ -32095,18 +32143,18 @@
     </row>
     <row r="58" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B58" s="22"/>
-      <c r="C58" s="139" t="s">
+      <c r="C58" s="144" t="s">
         <v>105</v>
       </c>
-      <c r="D58" s="140"/>
-      <c r="E58" s="140"/>
-      <c r="F58" s="140"/>
-      <c r="G58" s="141"/>
-      <c r="H58" s="146" t="s">
+      <c r="D58" s="139"/>
+      <c r="E58" s="139"/>
+      <c r="F58" s="139"/>
+      <c r="G58" s="140"/>
+      <c r="H58" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I58" s="140"/>
-      <c r="J58" s="141"/>
+      <c r="I58" s="139"/>
+      <c r="J58" s="140"/>
       <c r="K58" s="19" t="s">
         <v>106</v>
       </c>
@@ -32126,18 +32174,18 @@
     </row>
     <row r="59" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B59" s="22"/>
-      <c r="C59" s="139" t="s">
+      <c r="C59" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="140"/>
-      <c r="E59" s="140"/>
-      <c r="F59" s="140"/>
-      <c r="G59" s="141"/>
-      <c r="H59" s="146" t="s">
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="140"/>
+      <c r="H59" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I59" s="140"/>
-      <c r="J59" s="141"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="140"/>
       <c r="K59" s="19" t="s">
         <v>107</v>
       </c>
@@ -32157,18 +32205,18 @@
     </row>
     <row r="60" spans="2:33" s="10" customFormat="1">
       <c r="B60" s="22"/>
-      <c r="C60" s="139" t="s">
+      <c r="C60" s="144" t="s">
         <v>108</v>
       </c>
-      <c r="D60" s="140"/>
-      <c r="E60" s="140"/>
-      <c r="F60" s="140"/>
-      <c r="G60" s="141"/>
-      <c r="H60" s="146" t="s">
+      <c r="D60" s="139"/>
+      <c r="E60" s="139"/>
+      <c r="F60" s="139"/>
+      <c r="G60" s="140"/>
+      <c r="H60" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I60" s="140"/>
-      <c r="J60" s="141"/>
+      <c r="I60" s="139"/>
+      <c r="J60" s="140"/>
       <c r="K60" s="19" t="s">
         <v>109</v>
       </c>
@@ -32188,18 +32236,18 @@
     </row>
     <row r="61" spans="2:33" s="10" customFormat="1">
       <c r="B61" s="22"/>
-      <c r="C61" s="139" t="s">
+      <c r="C61" s="144" t="s">
         <v>110</v>
       </c>
-      <c r="D61" s="140"/>
-      <c r="E61" s="140"/>
-      <c r="F61" s="140"/>
-      <c r="G61" s="141"/>
-      <c r="H61" s="146" t="s">
+      <c r="D61" s="139"/>
+      <c r="E61" s="139"/>
+      <c r="F61" s="139"/>
+      <c r="G61" s="140"/>
+      <c r="H61" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I61" s="140"/>
-      <c r="J61" s="141"/>
+      <c r="I61" s="139"/>
+      <c r="J61" s="140"/>
       <c r="K61" s="19" t="s">
         <v>111</v>
       </c>
@@ -32219,18 +32267,18 @@
     </row>
     <row r="62" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B62" s="75"/>
-      <c r="C62" s="142" t="s">
+      <c r="C62" s="152" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="137"/>
-      <c r="E62" s="137"/>
-      <c r="F62" s="137"/>
-      <c r="G62" s="138"/>
-      <c r="H62" s="136" t="s">
+      <c r="D62" s="149"/>
+      <c r="E62" s="149"/>
+      <c r="F62" s="149"/>
+      <c r="G62" s="150"/>
+      <c r="H62" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="I62" s="137"/>
-      <c r="J62" s="138"/>
+      <c r="I62" s="149"/>
+      <c r="J62" s="150"/>
       <c r="K62" s="81" t="s">
         <v>113</v>
       </c>
@@ -32294,19 +32342,19 @@
       <c r="AG63" s="92"/>
     </row>
     <row r="64" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B64" s="148" t="s">
+      <c r="B64" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="144"/>
-      <c r="D64" s="144"/>
-      <c r="E64" s="144"/>
-      <c r="F64" s="144"/>
-      <c r="G64" s="149"/>
-      <c r="H64" s="148" t="s">
+      <c r="C64" s="146"/>
+      <c r="D64" s="146"/>
+      <c r="E64" s="146"/>
+      <c r="F64" s="146"/>
+      <c r="G64" s="147"/>
+      <c r="H64" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I64" s="144"/>
-      <c r="J64" s="149"/>
+      <c r="I64" s="146"/>
+      <c r="J64" s="147"/>
       <c r="K64" s="83" t="s">
         <v>68</v>
       </c>
@@ -32335,18 +32383,18 @@
     </row>
     <row r="65" spans="2:33">
       <c r="B65" s="21"/>
-      <c r="C65" s="139" t="s">
+      <c r="C65" s="144" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="147"/>
-      <c r="E65" s="147"/>
-      <c r="F65" s="147"/>
-      <c r="G65" s="141"/>
-      <c r="H65" s="150" t="s">
+      <c r="D65" s="151"/>
+      <c r="E65" s="151"/>
+      <c r="F65" s="151"/>
+      <c r="G65" s="140"/>
+      <c r="H65" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I65" s="151"/>
-      <c r="J65" s="152"/>
+      <c r="I65" s="137"/>
+      <c r="J65" s="138"/>
       <c r="K65" s="19" t="s">
         <v>115</v>
       </c>
@@ -32366,18 +32414,18 @@
     </row>
     <row r="66" spans="2:33">
       <c r="B66" s="22"/>
-      <c r="C66" s="139" t="s">
+      <c r="C66" s="144" t="s">
         <v>116</v>
       </c>
-      <c r="D66" s="147"/>
-      <c r="E66" s="147"/>
-      <c r="F66" s="147"/>
-      <c r="G66" s="141"/>
-      <c r="H66" s="146" t="s">
+      <c r="D66" s="151"/>
+      <c r="E66" s="151"/>
+      <c r="F66" s="151"/>
+      <c r="G66" s="140"/>
+      <c r="H66" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I66" s="147"/>
-      <c r="J66" s="141"/>
+      <c r="I66" s="151"/>
+      <c r="J66" s="140"/>
       <c r="K66" s="19" t="s">
         <v>117</v>
       </c>
@@ -32397,18 +32445,18 @@
     </row>
     <row r="67" spans="2:33">
       <c r="B67" s="22"/>
-      <c r="C67" s="139" t="s">
+      <c r="C67" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D67" s="147"/>
-      <c r="E67" s="147"/>
-      <c r="F67" s="147"/>
-      <c r="G67" s="141"/>
-      <c r="H67" s="146" t="s">
+      <c r="D67" s="151"/>
+      <c r="E67" s="151"/>
+      <c r="F67" s="151"/>
+      <c r="G67" s="140"/>
+      <c r="H67" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I67" s="147"/>
-      <c r="J67" s="141"/>
+      <c r="I67" s="151"/>
+      <c r="J67" s="140"/>
       <c r="K67" s="19" t="s">
         <v>118</v>
       </c>
@@ -32428,18 +32476,18 @@
     </row>
     <row r="68" spans="2:33">
       <c r="B68" s="22"/>
-      <c r="C68" s="139" t="s">
+      <c r="C68" s="144" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="147"/>
-      <c r="E68" s="147"/>
-      <c r="F68" s="147"/>
-      <c r="G68" s="141"/>
-      <c r="H68" s="146" t="s">
+      <c r="D68" s="151"/>
+      <c r="E68" s="151"/>
+      <c r="F68" s="151"/>
+      <c r="G68" s="140"/>
+      <c r="H68" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I68" s="147"/>
-      <c r="J68" s="141"/>
+      <c r="I68" s="151"/>
+      <c r="J68" s="140"/>
       <c r="K68" s="19" t="s">
         <v>120</v>
       </c>
@@ -32459,18 +32507,18 @@
     </row>
     <row r="69" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B69" s="75"/>
-      <c r="C69" s="142" t="s">
+      <c r="C69" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="D69" s="137"/>
-      <c r="E69" s="137"/>
-      <c r="F69" s="137"/>
-      <c r="G69" s="138"/>
-      <c r="H69" s="136" t="s">
+      <c r="D69" s="149"/>
+      <c r="E69" s="149"/>
+      <c r="F69" s="149"/>
+      <c r="G69" s="150"/>
+      <c r="H69" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="I69" s="137"/>
-      <c r="J69" s="138"/>
+      <c r="I69" s="149"/>
+      <c r="J69" s="150"/>
       <c r="K69" s="81" t="s">
         <v>122</v>
       </c>
@@ -32534,19 +32582,19 @@
       <c r="AG70" s="94"/>
     </row>
     <row r="71" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B71" s="148" t="s">
+      <c r="B71" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="144"/>
-      <c r="D71" s="144"/>
-      <c r="E71" s="144"/>
-      <c r="F71" s="144"/>
-      <c r="G71" s="149"/>
-      <c r="H71" s="148" t="s">
+      <c r="C71" s="146"/>
+      <c r="D71" s="146"/>
+      <c r="E71" s="146"/>
+      <c r="F71" s="146"/>
+      <c r="G71" s="147"/>
+      <c r="H71" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I71" s="144"/>
-      <c r="J71" s="149"/>
+      <c r="I71" s="146"/>
+      <c r="J71" s="147"/>
       <c r="K71" s="83" t="s">
         <v>68</v>
       </c>
@@ -32575,18 +32623,18 @@
     </row>
     <row r="72" spans="2:33">
       <c r="B72" s="21"/>
-      <c r="C72" s="139" t="s">
+      <c r="C72" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="147"/>
-      <c r="E72" s="147"/>
-      <c r="F72" s="147"/>
-      <c r="G72" s="141"/>
-      <c r="H72" s="150" t="s">
+      <c r="D72" s="151"/>
+      <c r="E72" s="151"/>
+      <c r="F72" s="151"/>
+      <c r="G72" s="140"/>
+      <c r="H72" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="I72" s="151"/>
-      <c r="J72" s="152"/>
+      <c r="I72" s="137"/>
+      <c r="J72" s="138"/>
       <c r="K72" s="19" t="s">
         <v>123</v>
       </c>
@@ -32606,18 +32654,18 @@
     </row>
     <row r="73" spans="2:33">
       <c r="B73" s="22"/>
-      <c r="C73" s="139" t="s">
+      <c r="C73" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="D73" s="147"/>
-      <c r="E73" s="147"/>
-      <c r="F73" s="147"/>
-      <c r="G73" s="141"/>
-      <c r="H73" s="146" t="s">
+      <c r="D73" s="151"/>
+      <c r="E73" s="151"/>
+      <c r="F73" s="151"/>
+      <c r="G73" s="140"/>
+      <c r="H73" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="I73" s="147"/>
-      <c r="J73" s="141"/>
+      <c r="I73" s="151"/>
+      <c r="J73" s="140"/>
       <c r="K73" s="19" t="s">
         <v>124</v>
       </c>
@@ -32637,18 +32685,18 @@
     </row>
     <row r="74" spans="2:33">
       <c r="B74" s="22"/>
-      <c r="C74" s="139" t="s">
+      <c r="C74" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="D74" s="147"/>
-      <c r="E74" s="147"/>
-      <c r="F74" s="147"/>
-      <c r="G74" s="141"/>
-      <c r="H74" s="146" t="s">
+      <c r="D74" s="151"/>
+      <c r="E74" s="151"/>
+      <c r="F74" s="151"/>
+      <c r="G74" s="140"/>
+      <c r="H74" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="I74" s="147"/>
-      <c r="J74" s="141"/>
+      <c r="I74" s="151"/>
+      <c r="J74" s="140"/>
       <c r="K74" s="19" t="s">
         <v>126</v>
       </c>
@@ -32668,18 +32716,18 @@
     </row>
     <row r="75" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B75" s="75"/>
-      <c r="C75" s="142" t="s">
+      <c r="C75" s="152" t="s">
         <v>127</v>
       </c>
-      <c r="D75" s="137"/>
-      <c r="E75" s="137"/>
-      <c r="F75" s="137"/>
-      <c r="G75" s="138"/>
-      <c r="H75" s="136" t="s">
+      <c r="D75" s="149"/>
+      <c r="E75" s="149"/>
+      <c r="F75" s="149"/>
+      <c r="G75" s="150"/>
+      <c r="H75" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I75" s="137"/>
-      <c r="J75" s="138"/>
+      <c r="I75" s="149"/>
+      <c r="J75" s="150"/>
       <c r="K75" s="81" t="s">
         <v>128</v>
       </c>
@@ -32743,19 +32791,19 @@
       <c r="AG76" s="94"/>
     </row>
     <row r="77" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B77" s="148" t="s">
+      <c r="B77" s="145" t="s">
         <v>66</v>
       </c>
-      <c r="C77" s="144"/>
-      <c r="D77" s="144"/>
-      <c r="E77" s="144"/>
-      <c r="F77" s="144"/>
-      <c r="G77" s="149"/>
-      <c r="H77" s="148" t="s">
+      <c r="C77" s="146"/>
+      <c r="D77" s="146"/>
+      <c r="E77" s="146"/>
+      <c r="F77" s="146"/>
+      <c r="G77" s="147"/>
+      <c r="H77" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="I77" s="144"/>
-      <c r="J77" s="149"/>
+      <c r="I77" s="146"/>
+      <c r="J77" s="147"/>
       <c r="K77" s="83" t="s">
         <v>68</v>
       </c>
@@ -32784,18 +32832,18 @@
     </row>
     <row r="78" spans="2:33">
       <c r="B78" s="21"/>
-      <c r="C78" s="139" t="s">
+      <c r="C78" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="147"/>
-      <c r="E78" s="147"/>
-      <c r="F78" s="147"/>
-      <c r="G78" s="141"/>
-      <c r="H78" s="150" t="s">
+      <c r="D78" s="151"/>
+      <c r="E78" s="151"/>
+      <c r="F78" s="151"/>
+      <c r="G78" s="140"/>
+      <c r="H78" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="I78" s="151"/>
-      <c r="J78" s="152"/>
+      <c r="I78" s="137"/>
+      <c r="J78" s="138"/>
       <c r="K78" s="19" t="s">
         <v>129</v>
       </c>
@@ -32815,18 +32863,18 @@
     </row>
     <row r="79" spans="2:33">
       <c r="B79" s="22"/>
-      <c r="C79" s="139" t="s">
+      <c r="C79" s="144" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="147"/>
-      <c r="E79" s="147"/>
-      <c r="F79" s="147"/>
-      <c r="G79" s="141"/>
-      <c r="H79" s="146" t="s">
+      <c r="D79" s="151"/>
+      <c r="E79" s="151"/>
+      <c r="F79" s="151"/>
+      <c r="G79" s="140"/>
+      <c r="H79" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="I79" s="147"/>
-      <c r="J79" s="141"/>
+      <c r="I79" s="151"/>
+      <c r="J79" s="140"/>
       <c r="K79" s="19" t="s">
         <v>132</v>
       </c>
@@ -32846,18 +32894,18 @@
     </row>
     <row r="80" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B80" s="75"/>
-      <c r="C80" s="142" t="s">
+      <c r="C80" s="152" t="s">
         <v>133</v>
       </c>
-      <c r="D80" s="137"/>
-      <c r="E80" s="137"/>
-      <c r="F80" s="137"/>
-      <c r="G80" s="138"/>
-      <c r="H80" s="136" t="s">
+      <c r="D80" s="149"/>
+      <c r="E80" s="149"/>
+      <c r="F80" s="149"/>
+      <c r="G80" s="150"/>
+      <c r="H80" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="I80" s="137"/>
-      <c r="J80" s="138"/>
+      <c r="I80" s="149"/>
+      <c r="J80" s="150"/>
       <c r="K80" s="81" t="s">
         <v>134</v>
       </c>
@@ -32968,12 +33016,81 @@
     </row>
   </sheetData>
   <mergeCells count="97">
-    <mergeCell ref="C24:G25"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="H24:J25"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="H65:J65"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C47:G49"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="B11:V11"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B5:V5"/>
+    <mergeCell ref="H47:J49"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="H40:J40"/>
     <mergeCell ref="H51:J51"/>
     <mergeCell ref="H69:J69"/>
     <mergeCell ref="C29:G29"/>
@@ -32990,81 +33107,12 @@
     <mergeCell ref="C62:G62"/>
     <mergeCell ref="H32:J32"/>
     <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B2:V2"/>
-    <mergeCell ref="B11:V11"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B5:V5"/>
-    <mergeCell ref="H47:J49"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C47:G49"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="H79:J79"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H78:J78"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="H65:J65"/>
-    <mergeCell ref="H71:J71"/>
-    <mergeCell ref="H75:J75"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="C24:G25"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="H24:J25"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:J26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -33073,7 +33121,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H1552"/>
+  <dimension ref="A1:H1568"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.75" style="2" bestFit="1" customWidth="1"/>
@@ -73132,6 +73180,422 @@
         <v>816</v>
       </c>
       <c r="H1552" s="133" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:8">
+      <c r="A1553">
+        <v>901324</v>
+      </c>
+      <c r="B1553" s="2">
+        <v>91324</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1553" s="130" t="s">
+        <v>8357</v>
+      </c>
+      <c r="E1553" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1553" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1553" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1553" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:8">
+      <c r="A1554">
+        <v>901325</v>
+      </c>
+      <c r="B1554" s="2">
+        <v>91325</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1554" s="130" t="s">
+        <v>8358</v>
+      </c>
+      <c r="E1554" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1554" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1554" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1554" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:8">
+      <c r="A1555">
+        <v>901326</v>
+      </c>
+      <c r="B1555" s="2">
+        <v>91326</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1555" s="130" t="s">
+        <v>8359</v>
+      </c>
+      <c r="E1555" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1555" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1555" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1555" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:8">
+      <c r="A1556">
+        <v>901327</v>
+      </c>
+      <c r="B1556" s="2">
+        <v>91327</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1556" s="130" t="s">
+        <v>8360</v>
+      </c>
+      <c r="E1556" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1556" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1556" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1556" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:8">
+      <c r="A1557">
+        <v>901328</v>
+      </c>
+      <c r="B1557" s="2">
+        <v>91328</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1557" s="130" t="s">
+        <v>8361</v>
+      </c>
+      <c r="E1557" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1557" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1557" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1557" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:8">
+      <c r="A1558">
+        <v>901329</v>
+      </c>
+      <c r="B1558" s="2">
+        <v>91329</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1558" s="130" t="s">
+        <v>8362</v>
+      </c>
+      <c r="E1558" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1558" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1558" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1558" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:8">
+      <c r="A1559">
+        <v>901330</v>
+      </c>
+      <c r="B1559" s="2">
+        <v>91330</v>
+      </c>
+      <c r="C1559" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1559" s="130" t="s">
+        <v>8363</v>
+      </c>
+      <c r="E1559" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1559" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1559" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1559" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:8">
+      <c r="A1560">
+        <v>901331</v>
+      </c>
+      <c r="B1560" s="2">
+        <v>91331</v>
+      </c>
+      <c r="C1560" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1560" s="130" t="s">
+        <v>8364</v>
+      </c>
+      <c r="E1560" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1560" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1560" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1560" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:8">
+      <c r="A1561">
+        <v>901332</v>
+      </c>
+      <c r="B1561" s="2">
+        <v>91332</v>
+      </c>
+      <c r="C1561" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1561" s="130" t="s">
+        <v>8365</v>
+      </c>
+      <c r="E1561" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1561" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1561" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1561" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:8">
+      <c r="A1562">
+        <v>901333</v>
+      </c>
+      <c r="B1562" s="2">
+        <v>91333</v>
+      </c>
+      <c r="C1562" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1562" s="130" t="s">
+        <v>8366</v>
+      </c>
+      <c r="E1562" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1562" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1562" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1562" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:8">
+      <c r="A1563">
+        <v>901334</v>
+      </c>
+      <c r="B1563" s="2">
+        <v>91334</v>
+      </c>
+      <c r="C1563" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1563" s="130" t="s">
+        <v>8367</v>
+      </c>
+      <c r="E1563" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1563" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1563" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1563" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:8">
+      <c r="A1564">
+        <v>901335</v>
+      </c>
+      <c r="B1564" s="2">
+        <v>91335</v>
+      </c>
+      <c r="C1564" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1564" s="130" t="s">
+        <v>8368</v>
+      </c>
+      <c r="E1564" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1564" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1564" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1564" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:8">
+      <c r="A1565">
+        <v>901336</v>
+      </c>
+      <c r="B1565" s="2">
+        <v>91336</v>
+      </c>
+      <c r="C1565" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1565" s="130" t="s">
+        <v>8369</v>
+      </c>
+      <c r="E1565" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1565" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1565" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1565" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:8">
+      <c r="A1566">
+        <v>901337</v>
+      </c>
+      <c r="B1566" s="2">
+        <v>91337</v>
+      </c>
+      <c r="C1566" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1566" s="130" t="s">
+        <v>8370</v>
+      </c>
+      <c r="E1566" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1566" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1566" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1566" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:8">
+      <c r="A1567">
+        <v>901338</v>
+      </c>
+      <c r="B1567" s="2">
+        <v>91338</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1567" s="130" t="s">
+        <v>8371</v>
+      </c>
+      <c r="E1567" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1567" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1567" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1567" s="130" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:8">
+      <c r="A1568">
+        <v>901339</v>
+      </c>
+      <c r="B1568" s="2">
+        <v>91339</v>
+      </c>
+      <c r="C1568" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1568" s="130" t="s">
+        <v>8372</v>
+      </c>
+      <c r="E1568" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="F1568" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="G1568" s="130" t="s">
+        <v>816</v>
+      </c>
+      <c r="H1568" s="130" t="s">
         <v>816</v>
       </c>
     </row>
@@ -75056,10 +75520,10 @@
       <c r="B2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
       <c r="G2" s="163"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -75069,10 +75533,10 @@
       <c r="M2" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="149"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="147"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
       <c r="T2" s="11"/>
@@ -75080,10 +75544,10 @@
       <c r="V2" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="W2" s="144"/>
-      <c r="X2" s="144"/>
-      <c r="Y2" s="144"/>
-      <c r="Z2" s="149"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="146"/>
+      <c r="Y2" s="146"/>
+      <c r="Z2" s="147"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
       <c r="AC2" s="10"/>
@@ -75202,10 +75666,10 @@
       <c r="V5" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="W5" s="144"/>
-      <c r="X5" s="144"/>
-      <c r="Y5" s="144"/>
-      <c r="Z5" s="149"/>
+      <c r="W5" s="146"/>
+      <c r="X5" s="146"/>
+      <c r="Y5" s="146"/>
+      <c r="Z5" s="147"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="10"/>
@@ -75251,10 +75715,10 @@
       <c r="B7" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="144"/>
-      <c r="D7" s="144"/>
-      <c r="E7" s="144"/>
-      <c r="F7" s="149"/>
+      <c r="C7" s="146"/>
+      <c r="D7" s="146"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="147"/>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -75263,10 +75727,10 @@
       <c r="L7" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="144"/>
-      <c r="N7" s="144"/>
-      <c r="O7" s="144"/>
-      <c r="P7" s="149"/>
+      <c r="M7" s="146"/>
+      <c r="N7" s="146"/>
+      <c r="O7" s="146"/>
+      <c r="P7" s="147"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
@@ -75475,10 +75939,10 @@
       <c r="AB14" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="AC14" s="144"/>
-      <c r="AD14" s="144"/>
-      <c r="AE14" s="144"/>
-      <c r="AF14" s="149"/>
+      <c r="AC14" s="146"/>
+      <c r="AD14" s="146"/>
+      <c r="AE14" s="146"/>
+      <c r="AF14" s="147"/>
       <c r="AG14" s="100"/>
       <c r="AH14" s="45"/>
       <c r="AI14" s="12"/>
@@ -75552,10 +76016,10 @@
       <c r="AB17" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="AC17" s="144"/>
-      <c r="AD17" s="144"/>
-      <c r="AE17" s="144"/>
-      <c r="AF17" s="149"/>
+      <c r="AC17" s="146"/>
+      <c r="AD17" s="146"/>
+      <c r="AE17" s="146"/>
+      <c r="AF17" s="147"/>
       <c r="AG17" s="102"/>
       <c r="AH17" s="38"/>
       <c r="AI17" s="10"/>
@@ -75673,10 +76137,10 @@
       <c r="AB21" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="AC21" s="144"/>
-      <c r="AD21" s="144"/>
-      <c r="AE21" s="144"/>
-      <c r="AF21" s="149"/>
+      <c r="AC21" s="146"/>
+      <c r="AD21" s="146"/>
+      <c r="AE21" s="146"/>
+      <c r="AF21" s="147"/>
       <c r="AG21" s="116"/>
       <c r="AH21" s="117"/>
     </row>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628DA6BB-EF71-4E53-9D11-D4472AADDF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352C0B71-5F8A-4D04-AEF4-BDBED15795B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10677" uniqueCount="8373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10743" uniqueCount="8422">
   <si>
     <t>Upgrade_Table</t>
   </si>
@@ -28997,6 +28997,191 @@
   </si>
   <si>
     <t>빈 칸</t>
+  </si>
+  <si>
+    <t>아름다움 {0}점</t>
+  </si>
+  <si>
+    <t>설치형 {0}/{1}</t>
+  </si>
+  <si>
+    <t>걸이형 {0}/{1}</t>
+  </si>
+  <si>
+    <t>{0}에 놓이는 장식이 없어요</t>
+  </si>
+  <si>
+    <t>걸이형 자리가 꽉 찼어요 · 다른 장식을 빼 주세요</t>
+  </si>
+  <si>
+    <t>설치형 자리가 꽉 찼어요 · 다른 장식을 빼 주세요</t>
+  </si>
+  <si>
+    <t>{0} 세트</t>
+  </si>
+  <si>
+    <t>공방에서 제작</t>
+  </si>
+  <si>
+    <t>빼기</t>
+  </si>
+  <si>
+    <t>놓기</t>
+  </si>
+  <si>
+    <t>강화 재료 {0}</t>
+  </si>
+  <si>
+    <t>Standing {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>置き型 {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Напольное {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Стоячий {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hanging {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吊り下げ型 {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Подвесное {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Підвісний {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No decor goes on the {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}に置ける飾りはありません</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Для зоны «{0}» нет украшений</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Для зони «{0}» немає декору</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hanging spots are full · Take one down first</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吊り下げ型の枠がいっぱいです・ほかの飾りをはずしてください</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Места для подвесных заняты · Сначала уберите одно</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Місця для підвісних зайняті · Спершу зніміть один</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Standing spots are full · Take one down first</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>置き型の枠がいっぱいです・ほかの飾りをはずしてください</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Места для напольных заняты · Сначала уберите одно</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Місця для стоячих зайняті · Спершу зніміть один</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} Set</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}セット</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Набор: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Набір: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Craft at the Workshop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工房で制作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Создай в Мастерской</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Створи в Майстерні</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Зняти</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Place</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>置く</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Поставить</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Поставити</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>強化材料 {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Материал {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Матеріал {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -33121,7 +33306,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H1568"/>
+  <dimension ref="A1:H1579"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.75" style="2" bestFit="1" customWidth="1"/>
@@ -73597,6 +73782,292 @@
       </c>
       <c r="H1568" s="130" t="s">
         <v>816</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:8">
+      <c r="A1569">
+        <v>901340</v>
+      </c>
+      <c r="B1569" s="2">
+        <v>91340</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1569" s="130" t="s">
+        <v>8373</v>
+      </c>
+      <c r="E1569" s="130" t="s">
+        <v>6873</v>
+      </c>
+      <c r="F1569" s="130" t="s">
+        <v>7499</v>
+      </c>
+      <c r="G1569" s="130" t="s">
+        <v>7500</v>
+      </c>
+      <c r="H1569" s="130" t="s">
+        <v>7501</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:8">
+      <c r="A1570">
+        <v>901341</v>
+      </c>
+      <c r="B1570" s="2">
+        <v>91341</v>
+      </c>
+      <c r="C1570" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1570" s="130" t="s">
+        <v>8374</v>
+      </c>
+      <c r="E1570" s="130" t="s">
+        <v>8384</v>
+      </c>
+      <c r="F1570" s="130" t="s">
+        <v>8385</v>
+      </c>
+      <c r="G1570" s="130" t="s">
+        <v>8386</v>
+      </c>
+      <c r="H1570" s="130" t="s">
+        <v>8387</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:8">
+      <c r="A1571">
+        <v>901342</v>
+      </c>
+      <c r="B1571" s="2">
+        <v>91342</v>
+      </c>
+      <c r="C1571" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1571" s="130" t="s">
+        <v>8375</v>
+      </c>
+      <c r="E1571" s="130" t="s">
+        <v>8388</v>
+      </c>
+      <c r="F1571" s="130" t="s">
+        <v>8389</v>
+      </c>
+      <c r="G1571" s="130" t="s">
+        <v>8390</v>
+      </c>
+      <c r="H1571" s="130" t="s">
+        <v>8391</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:8">
+      <c r="A1572">
+        <v>901343</v>
+      </c>
+      <c r="B1572" s="2">
+        <v>91343</v>
+      </c>
+      <c r="C1572" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1572" s="130" t="s">
+        <v>8376</v>
+      </c>
+      <c r="E1572" s="130" t="s">
+        <v>8392</v>
+      </c>
+      <c r="F1572" s="130" t="s">
+        <v>8393</v>
+      </c>
+      <c r="G1572" s="130" t="s">
+        <v>8394</v>
+      </c>
+      <c r="H1572" s="130" t="s">
+        <v>8395</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:8">
+      <c r="A1573">
+        <v>901344</v>
+      </c>
+      <c r="B1573" s="2">
+        <v>91344</v>
+      </c>
+      <c r="C1573" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1573" s="130" t="s">
+        <v>8377</v>
+      </c>
+      <c r="E1573" s="130" t="s">
+        <v>8396</v>
+      </c>
+      <c r="F1573" s="130" t="s">
+        <v>8397</v>
+      </c>
+      <c r="G1573" s="130" t="s">
+        <v>8398</v>
+      </c>
+      <c r="H1573" s="130" t="s">
+        <v>8399</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:8">
+      <c r="A1574">
+        <v>901345</v>
+      </c>
+      <c r="B1574" s="2">
+        <v>91345</v>
+      </c>
+      <c r="C1574" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1574" s="130" t="s">
+        <v>8378</v>
+      </c>
+      <c r="E1574" s="130" t="s">
+        <v>8400</v>
+      </c>
+      <c r="F1574" s="130" t="s">
+        <v>8401</v>
+      </c>
+      <c r="G1574" s="130" t="s">
+        <v>8402</v>
+      </c>
+      <c r="H1574" s="130" t="s">
+        <v>8403</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:8">
+      <c r="A1575">
+        <v>901346</v>
+      </c>
+      <c r="B1575" s="2">
+        <v>91346</v>
+      </c>
+      <c r="C1575" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1575" s="130" t="s">
+        <v>8379</v>
+      </c>
+      <c r="E1575" s="130" t="s">
+        <v>8404</v>
+      </c>
+      <c r="F1575" s="130" t="s">
+        <v>8405</v>
+      </c>
+      <c r="G1575" s="130" t="s">
+        <v>8406</v>
+      </c>
+      <c r="H1575" s="130" t="s">
+        <v>8407</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:8">
+      <c r="A1576">
+        <v>901347</v>
+      </c>
+      <c r="B1576" s="2">
+        <v>91347</v>
+      </c>
+      <c r="C1576" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1576" s="130" t="s">
+        <v>8380</v>
+      </c>
+      <c r="E1576" s="130" t="s">
+        <v>8408</v>
+      </c>
+      <c r="F1576" s="130" t="s">
+        <v>8409</v>
+      </c>
+      <c r="G1576" s="130" t="s">
+        <v>8410</v>
+      </c>
+      <c r="H1576" s="130" t="s">
+        <v>8411</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:8">
+      <c r="A1577">
+        <v>901348</v>
+      </c>
+      <c r="B1577" s="2">
+        <v>91348</v>
+      </c>
+      <c r="C1577" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1577" s="130" t="s">
+        <v>8381</v>
+      </c>
+      <c r="E1577" s="130" t="s">
+        <v>8412</v>
+      </c>
+      <c r="F1577" s="130" t="s">
+        <v>7532</v>
+      </c>
+      <c r="G1577" s="130" t="s">
+        <v>7533</v>
+      </c>
+      <c r="H1577" s="130" t="s">
+        <v>8413</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:8">
+      <c r="A1578">
+        <v>901349</v>
+      </c>
+      <c r="B1578" s="2">
+        <v>91349</v>
+      </c>
+      <c r="C1578" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1578" s="130" t="s">
+        <v>8382</v>
+      </c>
+      <c r="E1578" s="130" t="s">
+        <v>8414</v>
+      </c>
+      <c r="F1578" s="130" t="s">
+        <v>8415</v>
+      </c>
+      <c r="G1578" s="130" t="s">
+        <v>8416</v>
+      </c>
+      <c r="H1578" s="130" t="s">
+        <v>8417</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:8">
+      <c r="A1579">
+        <v>901350</v>
+      </c>
+      <c r="B1579" s="2">
+        <v>91350</v>
+      </c>
+      <c r="C1579" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1579" s="130" t="s">
+        <v>8383</v>
+      </c>
+      <c r="E1579" s="130" t="s">
+        <v>8418</v>
+      </c>
+      <c r="F1579" s="130" t="s">
+        <v>8419</v>
+      </c>
+      <c r="G1579" s="130" t="s">
+        <v>8420</v>
+      </c>
+      <c r="H1579" s="130" t="s">
+        <v>8421</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352C0B71-5F8A-4D04-AEF4-BDBED15795B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FEE114-585D-4F90-A188-4750FE230E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10743" uniqueCount="8422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11121" uniqueCount="8730">
   <si>
     <t>Upgrade_Table</t>
   </si>
@@ -29181,6 +29181,1175 @@
   </si>
   <si>
     <t>Матеріал {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세계수 성장</t>
+  </si>
+  <si>
+    <t>현재 효과</t>
+  </si>
+  <si>
+    <t>나무버섯 슬롯 {0}개 · 장식 {1}칸</t>
+  </si>
+  <si>
+    <t>세계수 진화 → {0}단계</t>
+  </si>
+  <si>
+    <t>최종 단계</t>
+  </si>
+  <si>
+    <t>나이테</t>
+  </si>
+  <si>
+    <t>공물</t>
+  </si>
+  <si>
+    <t>창고 버섯 {0}개 → 경험치 +{1}</t>
+  </si>
+  <si>
+    <t>바치기</t>
+  </si>
+  <si>
+    <t>다음 {0}단계: {1}</t>
+  </si>
+  <si>
+    <t>모든 가호를 받았어요</t>
+  </si>
+  <si>
+    <t>받은 가호 {0}/{1}</t>
+  </si>
+  <si>
+    <t>확인</t>
+  </si>
+  <si>
+    <t>세계수 {0}단계에 받아요</t>
+  </si>
+  <si>
+    <t>다음 호감도까지 {0}</t>
+  </si>
+  <si>
+    <t>꼬마의 하루</t>
+  </si>
+  <si>
+    <t>부탁 보기</t>
+  </si>
+  <si>
+    <t>꼬마 진화</t>
+  </si>
+  <si>
+    <t>진화</t>
+  </si>
+  <si>
+    <t>{0} ×{1} 모아 줄래?</t>
+  </si>
+  <si>
+    <t>오늘 남은 부탁 {0}</t>
+  </si>
+  <si>
+    <t>오늘 부탁은 다 들어줬어요!</t>
+  </si>
+  <si>
+    <t>지금 진화할 수 있는 꼬마 {0}</t>
+  </si>
+  <si>
+    <t>한 단계 더 자라요!</t>
+  </si>
+  <si>
+    <t>새로운 친구를 초대해요</t>
+  </si>
+  <si>
+    <t>세계수 {0}단계에 만나요</t>
+  </si>
+  <si>
+    <t>합류</t>
+  </si>
+  <si>
+    <t>꼬마 호감도</t>
+  </si>
+  <si>
+    <t>아직 데려온 꼬마가 없어요</t>
+  </si>
+  <si>
+    <t>호감도 최대!</t>
+  </si>
+  <si>
+    <t>호감도 Lv.{0} → Lv.{1}까지 {2} 남음</t>
+  </si>
+  <si>
+    <t>좋아하는 버섯: {0} · 부탁 +{1}</t>
+  </si>
+  <si>
+    <t>꼬마 친구들</t>
+  </si>
+  <si>
+    <t>함께하는 중</t>
+  </si>
+  <si>
+    <t>세계수 {0}단계 {1}가 되면 만나요</t>
+  </si>
+  <si>
+    <t>오늘의 부탁</t>
+  </si>
+  <si>
+    <t>{0} ×{1} 모아 주기</t>
+  </si>
+  <si>
+    <t>이번 주 부탁</t>
+  </si>
+  <si>
+    <t>꼬마의 상자</t>
+  </si>
+  <si>
+    <t>부탁 {0}번 들어주면 {1}</t>
+  </si>
+  <si>
+    <t>매주 월요일에 새로 시작해요</t>
+  </si>
+  <si>
+    <t>마지막 진화까지 마쳤어요</t>
+  </si>
+  <si>
+    <t>세계수 {0}단계</t>
+  </si>
+  <si>
+    <t>진화하면</t>
+  </si>
+  <si>
+    <t>{0}단계 필요</t>
+  </si>
+  <si>
+    <t>작은 제작소</t>
+  </si>
+  <si>
+    <t>제작 목록</t>
+  </si>
+  <si>
+    <t>제작 슬롯</t>
+  </si>
+  <si>
+    <t>제작 {0}/{1} · 즉시 완료 오늘 {2}회</t>
+  </si>
+  <si>
+    <t>필요 재료</t>
+  </si>
+  <si>
+    <t>잠긴 제작 슬롯</t>
+  </si>
+  <si>
+    <t>세계수 {0}단계에 열려요</t>
+  </si>
+  <si>
+    <t>레시피를 골라 제작해요</t>
+  </si>
+  <si>
+    <t>기다리던 장식이 완성됐어요.</t>
+  </si>
+  <si>
+    <t>제작 중…</t>
+  </si>
+  <si>
+    <t>세계수가 {0}단계가 되면 제작 슬롯이 열려요</t>
+  </si>
+  <si>
+    <t>World Tree Growth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹の成長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Рост Мирового древа</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ріст Світового дерева</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Current Effects</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在の効果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Текущие эффекты</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Поточні ефекти</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tree mushroom slots {0} · Decor {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木きのこ枠 {0}・飾り {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Мест для грибов {0} · Декор {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Місць для грибів {0} · Декор {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evolve World Tree → Stage {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹の進化 → {0}段階</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Эволюция древа → этап {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Еволюція дерева → етап {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Final stage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最終段階</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Последний этап</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Останній етап</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tree Rings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年輪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Годичные кольца</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Річні кільця</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Offering</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お供え</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Подношение</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Підношення</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} stored mushrooms → EXP +{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>倉庫のきのこ {0}個 → 経験値 +{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Грибов в запасе: {0} → опыт +{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Грибів у запасі: {0} → досвід +{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Offer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お供えする</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Принести</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Піднести</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Next, stage {0}: {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>次の{0}段階: {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Этап {0}: {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Етап {0}: {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>All blessings received</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>すべての加護を受けました</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Все благословения получены</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Усі благословення отримано</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blessings {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受けた加護 {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Благословения {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Благословення {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>View</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>確認</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Смотреть</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Переглянути</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Received at World Tree stage {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹{0}段階で受けられます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Будет на этапе древа {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Буде на етапі дерева {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} to next affection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>次の好感度まで {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>До следующего уровня симпатии: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>До наступного рівня симпатії: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A Little One's Day</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちびっこの一日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>День малыша</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>День малюка</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>View Favors</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お願いを見る</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Little One Evolution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちびっこ進化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Эволюция малышей</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Еволюція малюків</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Эволюция</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Еволюція</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Could you gather {0} ×{1}?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}を{1}個集めてくれる?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Соберёшь {0} ×{1}?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Збереш {0} ×{1}?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Favors left today {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今日の残りのお願い {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Осталось просьб сегодня: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Залишилось прохань сьогодні: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>All of today's favors are done!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今日のお願いはぜんぶかなえました!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Все просьбы на сегодня выполнены!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Усі прохання на сьогодні виконано!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Little Ones ready to evolve: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今すぐ進化できるちびっこ {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Готовы к эволюции: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Готові до еволюції: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grow one step further!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>もう一段階育ちます!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Вырастем ещё на шаг!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Підростемо ще на крок!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invite a new friend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新しい友だちを招待しよう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Пригласи нового друга</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Запроси нового друга</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Meet at World Tree stage {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹{0}段階で会えます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Встреча на этапе древа {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Зустріч на етапі дерева {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Join</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仲間にする</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Позвать</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Покликати</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Little One Affection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちびっこの好感度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Симпатия малышей</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Симпатія малюків</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No Little Ones have joined yet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>まだ仲間になったちびっこがいません</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Пока нет малышей</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Поки немає малюків</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max affection!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好感度MAX!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Симпатия на максимуме!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Симпатія на максимумі!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Affection Lv.{0} → Lv.{1}: {2} to go</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好感度 Lv.{0} → Lv.{1}まで あと{2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Симпатия ур.{0} → ур.{1}: ещё {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Симпатія рів.{0} → рів.{1}: ще {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Favorite mushrooms: {0} · Favor +{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好きなきのこ: {0}・お願い +{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Любимые грибы: {0} · просьба +{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Улюблені гриби: {0} · прохання +{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Little One Friends</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちびっこの仲間たち</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Друзья-малыши</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Друзі-малюки</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>With you</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いっしょにいます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>С тобой</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>З тобою</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Meet when the World Tree reaches stage {0} {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹が{0}段階 {1}になったら会えます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Встреча, когда древо достигнет этапа {0} «{1}»</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Зустріч, коли дерево досягне етапу {0} «{1}»</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Today's Favors</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今日のお願い</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Просьбы на сегодня</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Прохання на сьогодні</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gather {0} ×{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}を{1}個集める</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Собрать {0} ×{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Зібрати {0} ×{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>This Week's Favors</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今週のお願い</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Просьбы недели</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Прохання тижня</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Little One's Box</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちびっこの箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Коробка малышей</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Скринька малюків</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grant {0} favors for {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お願いを{0}回かなえると {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Выполни {0} просьб: {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Виконай {0} прохань: {1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resets every Monday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毎週月曜日にリセット</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Обновляется каждый понедельник</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Оновлюється щопонеділка</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fully evolved</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最後の進化まで終えました</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Полностью эволюционировал</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Повністю еволюціонував</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>World Tree stage {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹{0}段階</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Этап древа {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Етап дерева {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>When evolved:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進化すると</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>После эволюции:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Після еволюції:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Needs stage {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}段階が必要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Нужен этап {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Потрібен етап {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Little Workshop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小さな工房</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Маленькая мастерская</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Маленька майстерня</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作リスト</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crafting Slots</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作スロット</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ячейки создания</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Комірки створення</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crafting {0}/{1} · Instant finish today {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作 {0}/{1}・今日の即時完了 {2}回</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Создание {0}/{1} · мгновенно сегодня: {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Створення {0}/{1} · миттєво сьогодні: {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Materials</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必要な材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Материалы</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Матеріали</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Locked Slot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ロック中の制作スロット</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Закрытая ячейка</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Закрита комірка</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Opens at World Tree stage {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹{0}段階で開きます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Откроется на этапе древа {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Відкриється на етапі дерева {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pick a recipe to craft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>レシピを選んで制作しよう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Выбери рецепт</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Обери рецепт</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Your decoration is ready.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待っていた飾りが完成しました。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Украшение готово.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Декор готовий.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crafting…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作中…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Создаётся…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Створюється…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crafting slots open when the World Tree reaches stage {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界樹が{0}段階になると制作スロットが開きます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ячейки откроются на этапе древа {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Комірки відкриються на етапі дерева {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>꼬마 {0}명</t>
+  </si>
+  <si>
+    <t>별 {0}/{1}</t>
+  </si>
+  <si>
+    <t>등급</t>
+  </si>
+  <si>
+    <t>매일 세 번, 함께하는 작은 일을 부탁할게요!</t>
+  </si>
+  <si>
+    <t>꼬마 등급</t>
+  </si>
+  <si>
+    <t>아직 합류 전</t>
+  </si>
+  <si>
+    <t>등급 ★{0}/{1} · Lv.{2}/{3}</t>
+  </si>
+  <si>
+    <t>{0} Little Ones</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちびっこ {0}人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Малышей: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Малюків: {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stars {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星 {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Звёзды {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Зірки {0}/{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ランク</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ранг</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Three times a day, I'll ask you for a little favor!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毎日3回、いっしょにする小さなお願いをするね!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Три раза в день я попрошу о маленькой услуге!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Тричі на день я проситиму про маленьку послугу!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Little One Grades</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちびっこのランク</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ранги малышей</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ранги малюків</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not joined yet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>まだ仲間になっていません</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ещё не с тобой</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ще не з тобою</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grade ★{0}/{1} · Lv.{2}/{3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ランク ★{0}/{1}・Lv.{2}/{3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ранг ★{0}/{1} · ур.{2}/{3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ранг ★{0}/{1} · рів.{2}/{3}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -33306,7 +34475,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H1579"/>
+  <dimension ref="A1:H1642"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.75" style="2" bestFit="1" customWidth="1"/>
@@ -74068,6 +75237,1644 @@
       </c>
       <c r="H1579" s="130" t="s">
         <v>8421</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:8">
+      <c r="A1580">
+        <v>901351</v>
+      </c>
+      <c r="B1580" s="2">
+        <v>91351</v>
+      </c>
+      <c r="C1580" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1580" s="130" t="s">
+        <v>8422</v>
+      </c>
+      <c r="E1580" s="130" t="s">
+        <v>8478</v>
+      </c>
+      <c r="F1580" s="130" t="s">
+        <v>8479</v>
+      </c>
+      <c r="G1580" s="130" t="s">
+        <v>8480</v>
+      </c>
+      <c r="H1580" s="130" t="s">
+        <v>8481</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:8">
+      <c r="A1581">
+        <v>901352</v>
+      </c>
+      <c r="B1581" s="2">
+        <v>91352</v>
+      </c>
+      <c r="C1581" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1581" s="130" t="s">
+        <v>8423</v>
+      </c>
+      <c r="E1581" s="130" t="s">
+        <v>8482</v>
+      </c>
+      <c r="F1581" s="130" t="s">
+        <v>8483</v>
+      </c>
+      <c r="G1581" s="130" t="s">
+        <v>8484</v>
+      </c>
+      <c r="H1581" s="130" t="s">
+        <v>8485</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:8">
+      <c r="A1582">
+        <v>901353</v>
+      </c>
+      <c r="B1582" s="2">
+        <v>91353</v>
+      </c>
+      <c r="C1582" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1582" s="130" t="s">
+        <v>8424</v>
+      </c>
+      <c r="E1582" s="130" t="s">
+        <v>8486</v>
+      </c>
+      <c r="F1582" s="130" t="s">
+        <v>8487</v>
+      </c>
+      <c r="G1582" s="130" t="s">
+        <v>8488</v>
+      </c>
+      <c r="H1582" s="130" t="s">
+        <v>8489</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:8">
+      <c r="A1583">
+        <v>901354</v>
+      </c>
+      <c r="B1583" s="2">
+        <v>91354</v>
+      </c>
+      <c r="C1583" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1583" s="130" t="s">
+        <v>8425</v>
+      </c>
+      <c r="E1583" s="130" t="s">
+        <v>8490</v>
+      </c>
+      <c r="F1583" s="130" t="s">
+        <v>8491</v>
+      </c>
+      <c r="G1583" s="130" t="s">
+        <v>8492</v>
+      </c>
+      <c r="H1583" s="130" t="s">
+        <v>8493</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:8">
+      <c r="A1584">
+        <v>901355</v>
+      </c>
+      <c r="B1584" s="2">
+        <v>91355</v>
+      </c>
+      <c r="C1584" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1584" s="130" t="s">
+        <v>8426</v>
+      </c>
+      <c r="E1584" s="130" t="s">
+        <v>8494</v>
+      </c>
+      <c r="F1584" s="130" t="s">
+        <v>8495</v>
+      </c>
+      <c r="G1584" s="130" t="s">
+        <v>8496</v>
+      </c>
+      <c r="H1584" s="130" t="s">
+        <v>8497</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:8">
+      <c r="A1585">
+        <v>901356</v>
+      </c>
+      <c r="B1585" s="2">
+        <v>91356</v>
+      </c>
+      <c r="C1585" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1585" s="130" t="s">
+        <v>8427</v>
+      </c>
+      <c r="E1585" s="130" t="s">
+        <v>8498</v>
+      </c>
+      <c r="F1585" s="130" t="s">
+        <v>8499</v>
+      </c>
+      <c r="G1585" s="130" t="s">
+        <v>8500</v>
+      </c>
+      <c r="H1585" s="130" t="s">
+        <v>8501</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:8">
+      <c r="A1586">
+        <v>901357</v>
+      </c>
+      <c r="B1586" s="2">
+        <v>91357</v>
+      </c>
+      <c r="C1586" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1586" s="130" t="s">
+        <v>8428</v>
+      </c>
+      <c r="E1586" s="130" t="s">
+        <v>8502</v>
+      </c>
+      <c r="F1586" s="130" t="s">
+        <v>8503</v>
+      </c>
+      <c r="G1586" s="130" t="s">
+        <v>8504</v>
+      </c>
+      <c r="H1586" s="130" t="s">
+        <v>8505</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:8">
+      <c r="A1587">
+        <v>901358</v>
+      </c>
+      <c r="B1587" s="2">
+        <v>91358</v>
+      </c>
+      <c r="C1587" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1587" s="130" t="s">
+        <v>8429</v>
+      </c>
+      <c r="E1587" s="130" t="s">
+        <v>8506</v>
+      </c>
+      <c r="F1587" s="130" t="s">
+        <v>8507</v>
+      </c>
+      <c r="G1587" s="130" t="s">
+        <v>8508</v>
+      </c>
+      <c r="H1587" s="130" t="s">
+        <v>8509</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:8">
+      <c r="A1588">
+        <v>901359</v>
+      </c>
+      <c r="B1588" s="2">
+        <v>91359</v>
+      </c>
+      <c r="C1588" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1588" s="130" t="s">
+        <v>8430</v>
+      </c>
+      <c r="E1588" s="130" t="s">
+        <v>8510</v>
+      </c>
+      <c r="F1588" s="130" t="s">
+        <v>8511</v>
+      </c>
+      <c r="G1588" s="130" t="s">
+        <v>8512</v>
+      </c>
+      <c r="H1588" s="130" t="s">
+        <v>8513</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:8">
+      <c r="A1589">
+        <v>901360</v>
+      </c>
+      <c r="B1589" s="2">
+        <v>91360</v>
+      </c>
+      <c r="C1589" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1589" s="130" t="s">
+        <v>8431</v>
+      </c>
+      <c r="E1589" s="130" t="s">
+        <v>8514</v>
+      </c>
+      <c r="F1589" s="130" t="s">
+        <v>8515</v>
+      </c>
+      <c r="G1589" s="130" t="s">
+        <v>8516</v>
+      </c>
+      <c r="H1589" s="130" t="s">
+        <v>8517</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:8">
+      <c r="A1590">
+        <v>901361</v>
+      </c>
+      <c r="B1590" s="2">
+        <v>91361</v>
+      </c>
+      <c r="C1590" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1590" s="130" t="s">
+        <v>8432</v>
+      </c>
+      <c r="E1590" s="130" t="s">
+        <v>8518</v>
+      </c>
+      <c r="F1590" s="130" t="s">
+        <v>8519</v>
+      </c>
+      <c r="G1590" s="130" t="s">
+        <v>8520</v>
+      </c>
+      <c r="H1590" s="130" t="s">
+        <v>8521</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:8">
+      <c r="A1591">
+        <v>901362</v>
+      </c>
+      <c r="B1591" s="2">
+        <v>91362</v>
+      </c>
+      <c r="C1591" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1591" s="130" t="s">
+        <v>8433</v>
+      </c>
+      <c r="E1591" s="130" t="s">
+        <v>8522</v>
+      </c>
+      <c r="F1591" s="130" t="s">
+        <v>8523</v>
+      </c>
+      <c r="G1591" s="130" t="s">
+        <v>8524</v>
+      </c>
+      <c r="H1591" s="130" t="s">
+        <v>8525</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:8">
+      <c r="A1592">
+        <v>901363</v>
+      </c>
+      <c r="B1592" s="2">
+        <v>91363</v>
+      </c>
+      <c r="C1592" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1592" s="130" t="s">
+        <v>8434</v>
+      </c>
+      <c r="E1592" s="130" t="s">
+        <v>8526</v>
+      </c>
+      <c r="F1592" s="130" t="s">
+        <v>8527</v>
+      </c>
+      <c r="G1592" s="130" t="s">
+        <v>8528</v>
+      </c>
+      <c r="H1592" s="130" t="s">
+        <v>8529</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:8">
+      <c r="A1593">
+        <v>901364</v>
+      </c>
+      <c r="B1593" s="2">
+        <v>91364</v>
+      </c>
+      <c r="C1593" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1593" s="130" t="s">
+        <v>8435</v>
+      </c>
+      <c r="E1593" s="130" t="s">
+        <v>8530</v>
+      </c>
+      <c r="F1593" s="130" t="s">
+        <v>8531</v>
+      </c>
+      <c r="G1593" s="130" t="s">
+        <v>8532</v>
+      </c>
+      <c r="H1593" s="130" t="s">
+        <v>8533</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:8">
+      <c r="A1594">
+        <v>901365</v>
+      </c>
+      <c r="B1594" s="2">
+        <v>91365</v>
+      </c>
+      <c r="C1594" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1594" s="130" t="s">
+        <v>8436</v>
+      </c>
+      <c r="E1594" s="130" t="s">
+        <v>8534</v>
+      </c>
+      <c r="F1594" s="130" t="s">
+        <v>8535</v>
+      </c>
+      <c r="G1594" s="130" t="s">
+        <v>8536</v>
+      </c>
+      <c r="H1594" s="130" t="s">
+        <v>8537</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:8">
+      <c r="A1595">
+        <v>901366</v>
+      </c>
+      <c r="B1595" s="2">
+        <v>91366</v>
+      </c>
+      <c r="C1595" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1595" s="130" t="s">
+        <v>8437</v>
+      </c>
+      <c r="E1595" s="130" t="s">
+        <v>8538</v>
+      </c>
+      <c r="F1595" s="130" t="s">
+        <v>8539</v>
+      </c>
+      <c r="G1595" s="130" t="s">
+        <v>8540</v>
+      </c>
+      <c r="H1595" s="130" t="s">
+        <v>8541</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:8">
+      <c r="A1596">
+        <v>901367</v>
+      </c>
+      <c r="B1596" s="2">
+        <v>91367</v>
+      </c>
+      <c r="C1596" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1596" s="130" t="s">
+        <v>8438</v>
+      </c>
+      <c r="E1596" s="130" t="s">
+        <v>8542</v>
+      </c>
+      <c r="F1596" s="130" t="s">
+        <v>8543</v>
+      </c>
+      <c r="G1596" s="130" t="s">
+        <v>7575</v>
+      </c>
+      <c r="H1596" s="130" t="s">
+        <v>7576</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:8">
+      <c r="A1597">
+        <v>901368</v>
+      </c>
+      <c r="B1597" s="2">
+        <v>91368</v>
+      </c>
+      <c r="C1597" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1597" s="130" t="s">
+        <v>8439</v>
+      </c>
+      <c r="E1597" s="130" t="s">
+        <v>8544</v>
+      </c>
+      <c r="F1597" s="130" t="s">
+        <v>8545</v>
+      </c>
+      <c r="G1597" s="130" t="s">
+        <v>8546</v>
+      </c>
+      <c r="H1597" s="130" t="s">
+        <v>8547</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:8">
+      <c r="A1598">
+        <v>901369</v>
+      </c>
+      <c r="B1598" s="2">
+        <v>91369</v>
+      </c>
+      <c r="C1598" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1598" s="130" t="s">
+        <v>8440</v>
+      </c>
+      <c r="E1598" s="130" t="s">
+        <v>3115</v>
+      </c>
+      <c r="F1598" s="130" t="s">
+        <v>8548</v>
+      </c>
+      <c r="G1598" s="130" t="s">
+        <v>8549</v>
+      </c>
+      <c r="H1598" s="130" t="s">
+        <v>8550</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:8">
+      <c r="A1599">
+        <v>901370</v>
+      </c>
+      <c r="B1599" s="2">
+        <v>91370</v>
+      </c>
+      <c r="C1599" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1599" s="130" t="s">
+        <v>8441</v>
+      </c>
+      <c r="E1599" s="130" t="s">
+        <v>8551</v>
+      </c>
+      <c r="F1599" s="130" t="s">
+        <v>8552</v>
+      </c>
+      <c r="G1599" s="130" t="s">
+        <v>8553</v>
+      </c>
+      <c r="H1599" s="130" t="s">
+        <v>8554</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:8">
+      <c r="A1600">
+        <v>901371</v>
+      </c>
+      <c r="B1600" s="2">
+        <v>91371</v>
+      </c>
+      <c r="C1600" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1600" s="130" t="s">
+        <v>8442</v>
+      </c>
+      <c r="E1600" s="130" t="s">
+        <v>8555</v>
+      </c>
+      <c r="F1600" s="130" t="s">
+        <v>8556</v>
+      </c>
+      <c r="G1600" s="130" t="s">
+        <v>8557</v>
+      </c>
+      <c r="H1600" s="130" t="s">
+        <v>8558</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:8">
+      <c r="A1601">
+        <v>901372</v>
+      </c>
+      <c r="B1601" s="2">
+        <v>91372</v>
+      </c>
+      <c r="C1601" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1601" s="130" t="s">
+        <v>8443</v>
+      </c>
+      <c r="E1601" s="130" t="s">
+        <v>8559</v>
+      </c>
+      <c r="F1601" s="130" t="s">
+        <v>8560</v>
+      </c>
+      <c r="G1601" s="130" t="s">
+        <v>8561</v>
+      </c>
+      <c r="H1601" s="130" t="s">
+        <v>8562</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:8">
+      <c r="A1602">
+        <v>901373</v>
+      </c>
+      <c r="B1602" s="2">
+        <v>91373</v>
+      </c>
+      <c r="C1602" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1602" s="130" t="s">
+        <v>8444</v>
+      </c>
+      <c r="E1602" s="130" t="s">
+        <v>8563</v>
+      </c>
+      <c r="F1602" s="130" t="s">
+        <v>8564</v>
+      </c>
+      <c r="G1602" s="130" t="s">
+        <v>8565</v>
+      </c>
+      <c r="H1602" s="130" t="s">
+        <v>8566</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:8">
+      <c r="A1603">
+        <v>901374</v>
+      </c>
+      <c r="B1603" s="2">
+        <v>91374</v>
+      </c>
+      <c r="C1603" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1603" s="130" t="s">
+        <v>8445</v>
+      </c>
+      <c r="E1603" s="130" t="s">
+        <v>8567</v>
+      </c>
+      <c r="F1603" s="130" t="s">
+        <v>8568</v>
+      </c>
+      <c r="G1603" s="130" t="s">
+        <v>8569</v>
+      </c>
+      <c r="H1603" s="130" t="s">
+        <v>8570</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:8">
+      <c r="A1604">
+        <v>901375</v>
+      </c>
+      <c r="B1604" s="2">
+        <v>91375</v>
+      </c>
+      <c r="C1604" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1604" s="130" t="s">
+        <v>8446</v>
+      </c>
+      <c r="E1604" s="130" t="s">
+        <v>8571</v>
+      </c>
+      <c r="F1604" s="130" t="s">
+        <v>8572</v>
+      </c>
+      <c r="G1604" s="130" t="s">
+        <v>8573</v>
+      </c>
+      <c r="H1604" s="130" t="s">
+        <v>8574</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:8">
+      <c r="A1605">
+        <v>901376</v>
+      </c>
+      <c r="B1605" s="2">
+        <v>91376</v>
+      </c>
+      <c r="C1605" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1605" s="130" t="s">
+        <v>8447</v>
+      </c>
+      <c r="E1605" s="130" t="s">
+        <v>8575</v>
+      </c>
+      <c r="F1605" s="130" t="s">
+        <v>8576</v>
+      </c>
+      <c r="G1605" s="130" t="s">
+        <v>8577</v>
+      </c>
+      <c r="H1605" s="130" t="s">
+        <v>8578</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:8">
+      <c r="A1606">
+        <v>901377</v>
+      </c>
+      <c r="B1606" s="2">
+        <v>91377</v>
+      </c>
+      <c r="C1606" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1606" s="130" t="s">
+        <v>8448</v>
+      </c>
+      <c r="E1606" s="130" t="s">
+        <v>8579</v>
+      </c>
+      <c r="F1606" s="130" t="s">
+        <v>8580</v>
+      </c>
+      <c r="G1606" s="130" t="s">
+        <v>8581</v>
+      </c>
+      <c r="H1606" s="130" t="s">
+        <v>8582</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:8">
+      <c r="A1607">
+        <v>901378</v>
+      </c>
+      <c r="B1607" s="2">
+        <v>91378</v>
+      </c>
+      <c r="C1607" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1607" s="130" t="s">
+        <v>8449</v>
+      </c>
+      <c r="E1607" s="130" t="s">
+        <v>8583</v>
+      </c>
+      <c r="F1607" s="130" t="s">
+        <v>8584</v>
+      </c>
+      <c r="G1607" s="130" t="s">
+        <v>8585</v>
+      </c>
+      <c r="H1607" s="130" t="s">
+        <v>8586</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:8">
+      <c r="A1608">
+        <v>901379</v>
+      </c>
+      <c r="B1608" s="2">
+        <v>91379</v>
+      </c>
+      <c r="C1608" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1608" s="130" t="s">
+        <v>8450</v>
+      </c>
+      <c r="E1608" s="130" t="s">
+        <v>8587</v>
+      </c>
+      <c r="F1608" s="130" t="s">
+        <v>8588</v>
+      </c>
+      <c r="G1608" s="130" t="s">
+        <v>8589</v>
+      </c>
+      <c r="H1608" s="130" t="s">
+        <v>8590</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:8">
+      <c r="A1609">
+        <v>901380</v>
+      </c>
+      <c r="B1609" s="2">
+        <v>91380</v>
+      </c>
+      <c r="C1609" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1609" s="130" t="s">
+        <v>8451</v>
+      </c>
+      <c r="E1609" s="130" t="s">
+        <v>8591</v>
+      </c>
+      <c r="F1609" s="130" t="s">
+        <v>8592</v>
+      </c>
+      <c r="G1609" s="130" t="s">
+        <v>8593</v>
+      </c>
+      <c r="H1609" s="130" t="s">
+        <v>8594</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:8">
+      <c r="A1610">
+        <v>901381</v>
+      </c>
+      <c r="B1610" s="2">
+        <v>91381</v>
+      </c>
+      <c r="C1610" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1610" s="130" t="s">
+        <v>8452</v>
+      </c>
+      <c r="E1610" s="130" t="s">
+        <v>8595</v>
+      </c>
+      <c r="F1610" s="130" t="s">
+        <v>8596</v>
+      </c>
+      <c r="G1610" s="130" t="s">
+        <v>8597</v>
+      </c>
+      <c r="H1610" s="130" t="s">
+        <v>8598</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:8">
+      <c r="A1611">
+        <v>901382</v>
+      </c>
+      <c r="B1611" s="2">
+        <v>91382</v>
+      </c>
+      <c r="C1611" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1611" s="130" t="s">
+        <v>8453</v>
+      </c>
+      <c r="E1611" s="130" t="s">
+        <v>8599</v>
+      </c>
+      <c r="F1611" s="130" t="s">
+        <v>8600</v>
+      </c>
+      <c r="G1611" s="130" t="s">
+        <v>8601</v>
+      </c>
+      <c r="H1611" s="130" t="s">
+        <v>8602</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:8">
+      <c r="A1612">
+        <v>901383</v>
+      </c>
+      <c r="B1612" s="2">
+        <v>91383</v>
+      </c>
+      <c r="C1612" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1612" s="130" t="s">
+        <v>8454</v>
+      </c>
+      <c r="E1612" s="130" t="s">
+        <v>8603</v>
+      </c>
+      <c r="F1612" s="130" t="s">
+        <v>8604</v>
+      </c>
+      <c r="G1612" s="130" t="s">
+        <v>8605</v>
+      </c>
+      <c r="H1612" s="130" t="s">
+        <v>8606</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:8">
+      <c r="A1613">
+        <v>901384</v>
+      </c>
+      <c r="B1613" s="2">
+        <v>91384</v>
+      </c>
+      <c r="C1613" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1613" s="130" t="s">
+        <v>8455</v>
+      </c>
+      <c r="E1613" s="130" t="s">
+        <v>8607</v>
+      </c>
+      <c r="F1613" s="130" t="s">
+        <v>8608</v>
+      </c>
+      <c r="G1613" s="130" t="s">
+        <v>8609</v>
+      </c>
+      <c r="H1613" s="130" t="s">
+        <v>8610</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:8">
+      <c r="A1614">
+        <v>901385</v>
+      </c>
+      <c r="B1614" s="2">
+        <v>91385</v>
+      </c>
+      <c r="C1614" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1614" s="130" t="s">
+        <v>8456</v>
+      </c>
+      <c r="E1614" s="130" t="s">
+        <v>8611</v>
+      </c>
+      <c r="F1614" s="130" t="s">
+        <v>8612</v>
+      </c>
+      <c r="G1614" s="130" t="s">
+        <v>8613</v>
+      </c>
+      <c r="H1614" s="130" t="s">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:8">
+      <c r="A1615">
+        <v>901386</v>
+      </c>
+      <c r="B1615" s="2">
+        <v>91386</v>
+      </c>
+      <c r="C1615" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1615" s="130" t="s">
+        <v>8457</v>
+      </c>
+      <c r="E1615" s="130" t="s">
+        <v>8615</v>
+      </c>
+      <c r="F1615" s="130" t="s">
+        <v>8616</v>
+      </c>
+      <c r="G1615" s="130" t="s">
+        <v>8617</v>
+      </c>
+      <c r="H1615" s="130" t="s">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:8">
+      <c r="A1616">
+        <v>901387</v>
+      </c>
+      <c r="B1616" s="2">
+        <v>91387</v>
+      </c>
+      <c r="C1616" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1616" s="130" t="s">
+        <v>8458</v>
+      </c>
+      <c r="E1616" s="130" t="s">
+        <v>8619</v>
+      </c>
+      <c r="F1616" s="130" t="s">
+        <v>8620</v>
+      </c>
+      <c r="G1616" s="130" t="s">
+        <v>8621</v>
+      </c>
+      <c r="H1616" s="130" t="s">
+        <v>8622</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:8">
+      <c r="A1617">
+        <v>901388</v>
+      </c>
+      <c r="B1617" s="2">
+        <v>91388</v>
+      </c>
+      <c r="C1617" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1617" s="130" t="s">
+        <v>8459</v>
+      </c>
+      <c r="E1617" s="130" t="s">
+        <v>8623</v>
+      </c>
+      <c r="F1617" s="130" t="s">
+        <v>8624</v>
+      </c>
+      <c r="G1617" s="130" t="s">
+        <v>8625</v>
+      </c>
+      <c r="H1617" s="130" t="s">
+        <v>8626</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:8">
+      <c r="A1618">
+        <v>901389</v>
+      </c>
+      <c r="B1618" s="2">
+        <v>91389</v>
+      </c>
+      <c r="C1618" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1618" s="130" t="s">
+        <v>8460</v>
+      </c>
+      <c r="E1618" s="130" t="s">
+        <v>8627</v>
+      </c>
+      <c r="F1618" s="130" t="s">
+        <v>8628</v>
+      </c>
+      <c r="G1618" s="130" t="s">
+        <v>8629</v>
+      </c>
+      <c r="H1618" s="130" t="s">
+        <v>8630</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:8">
+      <c r="A1619">
+        <v>901390</v>
+      </c>
+      <c r="B1619" s="2">
+        <v>91390</v>
+      </c>
+      <c r="C1619" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1619" s="130" t="s">
+        <v>8461</v>
+      </c>
+      <c r="E1619" s="130" t="s">
+        <v>8631</v>
+      </c>
+      <c r="F1619" s="130" t="s">
+        <v>8632</v>
+      </c>
+      <c r="G1619" s="130" t="s">
+        <v>8633</v>
+      </c>
+      <c r="H1619" s="130" t="s">
+        <v>8634</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:8">
+      <c r="A1620">
+        <v>901391</v>
+      </c>
+      <c r="B1620" s="2">
+        <v>91391</v>
+      </c>
+      <c r="C1620" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1620" s="130" t="s">
+        <v>8462</v>
+      </c>
+      <c r="E1620" s="130" t="s">
+        <v>8635</v>
+      </c>
+      <c r="F1620" s="130" t="s">
+        <v>8636</v>
+      </c>
+      <c r="G1620" s="130" t="s">
+        <v>8637</v>
+      </c>
+      <c r="H1620" s="130" t="s">
+        <v>8638</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:8">
+      <c r="A1621">
+        <v>901392</v>
+      </c>
+      <c r="B1621" s="2">
+        <v>91392</v>
+      </c>
+      <c r="C1621" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1621" s="130" t="s">
+        <v>8463</v>
+      </c>
+      <c r="E1621" s="130" t="s">
+        <v>8639</v>
+      </c>
+      <c r="F1621" s="130" t="s">
+        <v>8640</v>
+      </c>
+      <c r="G1621" s="130" t="s">
+        <v>8641</v>
+      </c>
+      <c r="H1621" s="130" t="s">
+        <v>8642</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:8">
+      <c r="A1622">
+        <v>901393</v>
+      </c>
+      <c r="B1622" s="2">
+        <v>91393</v>
+      </c>
+      <c r="C1622" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1622" s="130" t="s">
+        <v>8464</v>
+      </c>
+      <c r="E1622" s="130" t="s">
+        <v>8643</v>
+      </c>
+      <c r="F1622" s="130" t="s">
+        <v>8644</v>
+      </c>
+      <c r="G1622" s="130" t="s">
+        <v>8645</v>
+      </c>
+      <c r="H1622" s="130" t="s">
+        <v>8646</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:8">
+      <c r="A1623">
+        <v>901394</v>
+      </c>
+      <c r="B1623" s="2">
+        <v>91394</v>
+      </c>
+      <c r="C1623" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1623" s="130" t="s">
+        <v>8465</v>
+      </c>
+      <c r="E1623" s="130" t="s">
+        <v>8647</v>
+      </c>
+      <c r="F1623" s="130" t="s">
+        <v>8648</v>
+      </c>
+      <c r="G1623" s="130" t="s">
+        <v>8649</v>
+      </c>
+      <c r="H1623" s="130" t="s">
+        <v>8650</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:8">
+      <c r="A1624">
+        <v>901395</v>
+      </c>
+      <c r="B1624" s="2">
+        <v>91395</v>
+      </c>
+      <c r="C1624" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1624" s="130" t="s">
+        <v>8466</v>
+      </c>
+      <c r="E1624" s="130" t="s">
+        <v>8651</v>
+      </c>
+      <c r="F1624" s="130" t="s">
+        <v>8652</v>
+      </c>
+      <c r="G1624" s="130" t="s">
+        <v>8653</v>
+      </c>
+      <c r="H1624" s="130" t="s">
+        <v>8654</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:8">
+      <c r="A1625">
+        <v>901396</v>
+      </c>
+      <c r="B1625" s="2">
+        <v>91396</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1625" s="130" t="s">
+        <v>8467</v>
+      </c>
+      <c r="E1625" s="130" t="s">
+        <v>8655</v>
+      </c>
+      <c r="F1625" s="130" t="s">
+        <v>8656</v>
+      </c>
+      <c r="G1625" s="130" t="s">
+        <v>8657</v>
+      </c>
+      <c r="H1625" s="130" t="s">
+        <v>8658</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:8">
+      <c r="A1626">
+        <v>901397</v>
+      </c>
+      <c r="B1626" s="2">
+        <v>91397</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1626" s="130" t="s">
+        <v>8468</v>
+      </c>
+      <c r="E1626" s="130" t="s">
+        <v>8140</v>
+      </c>
+      <c r="F1626" s="130" t="s">
+        <v>8659</v>
+      </c>
+      <c r="G1626" s="130" t="s">
+        <v>8142</v>
+      </c>
+      <c r="H1626" s="130" t="s">
+        <v>8143</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:8">
+      <c r="A1627">
+        <v>901398</v>
+      </c>
+      <c r="B1627" s="2">
+        <v>91398</v>
+      </c>
+      <c r="C1627" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1627" s="130" t="s">
+        <v>8469</v>
+      </c>
+      <c r="E1627" s="130" t="s">
+        <v>8660</v>
+      </c>
+      <c r="F1627" s="130" t="s">
+        <v>8661</v>
+      </c>
+      <c r="G1627" s="130" t="s">
+        <v>8662</v>
+      </c>
+      <c r="H1627" s="130" t="s">
+        <v>8663</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:8">
+      <c r="A1628">
+        <v>901399</v>
+      </c>
+      <c r="B1628" s="2">
+        <v>91399</v>
+      </c>
+      <c r="C1628" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1628" s="130" t="s">
+        <v>8470</v>
+      </c>
+      <c r="E1628" s="130" t="s">
+        <v>8664</v>
+      </c>
+      <c r="F1628" s="130" t="s">
+        <v>8665</v>
+      </c>
+      <c r="G1628" s="130" t="s">
+        <v>8666</v>
+      </c>
+      <c r="H1628" s="130" t="s">
+        <v>8667</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:8">
+      <c r="A1629">
+        <v>901400</v>
+      </c>
+      <c r="B1629" s="2">
+        <v>91400</v>
+      </c>
+      <c r="C1629" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1629" s="130" t="s">
+        <v>8471</v>
+      </c>
+      <c r="E1629" s="130" t="s">
+        <v>8668</v>
+      </c>
+      <c r="F1629" s="130" t="s">
+        <v>8669</v>
+      </c>
+      <c r="G1629" s="130" t="s">
+        <v>8670</v>
+      </c>
+      <c r="H1629" s="130" t="s">
+        <v>8671</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:8">
+      <c r="A1630">
+        <v>901401</v>
+      </c>
+      <c r="B1630" s="2">
+        <v>91401</v>
+      </c>
+      <c r="C1630" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1630" s="130" t="s">
+        <v>8472</v>
+      </c>
+      <c r="E1630" s="130" t="s">
+        <v>8672</v>
+      </c>
+      <c r="F1630" s="130" t="s">
+        <v>8673</v>
+      </c>
+      <c r="G1630" s="130" t="s">
+        <v>8674</v>
+      </c>
+      <c r="H1630" s="130" t="s">
+        <v>8675</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:8">
+      <c r="A1631">
+        <v>901402</v>
+      </c>
+      <c r="B1631" s="2">
+        <v>91402</v>
+      </c>
+      <c r="C1631" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1631" s="130" t="s">
+        <v>8473</v>
+      </c>
+      <c r="E1631" s="130" t="s">
+        <v>8676</v>
+      </c>
+      <c r="F1631" s="130" t="s">
+        <v>8677</v>
+      </c>
+      <c r="G1631" s="130" t="s">
+        <v>8678</v>
+      </c>
+      <c r="H1631" s="130" t="s">
+        <v>8679</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:8">
+      <c r="A1632">
+        <v>901403</v>
+      </c>
+      <c r="B1632" s="2">
+        <v>91403</v>
+      </c>
+      <c r="C1632" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1632" s="130" t="s">
+        <v>8474</v>
+      </c>
+      <c r="E1632" s="130" t="s">
+        <v>8680</v>
+      </c>
+      <c r="F1632" s="130" t="s">
+        <v>8681</v>
+      </c>
+      <c r="G1632" s="130" t="s">
+        <v>8682</v>
+      </c>
+      <c r="H1632" s="130" t="s">
+        <v>8683</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:8">
+      <c r="A1633">
+        <v>901404</v>
+      </c>
+      <c r="B1633" s="2">
+        <v>91404</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1633" s="130" t="s">
+        <v>8475</v>
+      </c>
+      <c r="E1633" s="130" t="s">
+        <v>8684</v>
+      </c>
+      <c r="F1633" s="130" t="s">
+        <v>8685</v>
+      </c>
+      <c r="G1633" s="130" t="s">
+        <v>8686</v>
+      </c>
+      <c r="H1633" s="130" t="s">
+        <v>8687</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:8">
+      <c r="A1634">
+        <v>901405</v>
+      </c>
+      <c r="B1634" s="2">
+        <v>91405</v>
+      </c>
+      <c r="C1634" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1634" s="130" t="s">
+        <v>8476</v>
+      </c>
+      <c r="E1634" s="130" t="s">
+        <v>8688</v>
+      </c>
+      <c r="F1634" s="130" t="s">
+        <v>8689</v>
+      </c>
+      <c r="G1634" s="130" t="s">
+        <v>8690</v>
+      </c>
+      <c r="H1634" s="130" t="s">
+        <v>8691</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:8">
+      <c r="A1635">
+        <v>901406</v>
+      </c>
+      <c r="B1635" s="2">
+        <v>91406</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1635" s="130" t="s">
+        <v>8477</v>
+      </c>
+      <c r="E1635" s="130" t="s">
+        <v>8692</v>
+      </c>
+      <c r="F1635" s="130" t="s">
+        <v>8693</v>
+      </c>
+      <c r="G1635" s="130" t="s">
+        <v>8694</v>
+      </c>
+      <c r="H1635" s="130" t="s">
+        <v>8695</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:8">
+      <c r="A1636">
+        <v>901407</v>
+      </c>
+      <c r="B1636" s="2">
+        <v>91407</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1636" s="130" t="s">
+        <v>8696</v>
+      </c>
+      <c r="E1636" s="130" t="s">
+        <v>8703</v>
+      </c>
+      <c r="F1636" s="130" t="s">
+        <v>8704</v>
+      </c>
+      <c r="G1636" s="130" t="s">
+        <v>8705</v>
+      </c>
+      <c r="H1636" s="130" t="s">
+        <v>8706</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:8">
+      <c r="A1637">
+        <v>901408</v>
+      </c>
+      <c r="B1637" s="2">
+        <v>91408</v>
+      </c>
+      <c r="C1637" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1637" s="130" t="s">
+        <v>8697</v>
+      </c>
+      <c r="E1637" s="130" t="s">
+        <v>8707</v>
+      </c>
+      <c r="F1637" s="130" t="s">
+        <v>8708</v>
+      </c>
+      <c r="G1637" s="130" t="s">
+        <v>8709</v>
+      </c>
+      <c r="H1637" s="130" t="s">
+        <v>8710</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:8">
+      <c r="A1638">
+        <v>901409</v>
+      </c>
+      <c r="B1638" s="2">
+        <v>91409</v>
+      </c>
+      <c r="C1638" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1638" s="130" t="s">
+        <v>8698</v>
+      </c>
+      <c r="E1638" s="130" t="s">
+        <v>8711</v>
+      </c>
+      <c r="F1638" s="130" t="s">
+        <v>8712</v>
+      </c>
+      <c r="G1638" s="130" t="s">
+        <v>8713</v>
+      </c>
+      <c r="H1638" s="130" t="s">
+        <v>8713</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:8">
+      <c r="A1639">
+        <v>901410</v>
+      </c>
+      <c r="B1639" s="2">
+        <v>91410</v>
+      </c>
+      <c r="C1639" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1639" s="130" t="s">
+        <v>8699</v>
+      </c>
+      <c r="E1639" s="130" t="s">
+        <v>8714</v>
+      </c>
+      <c r="F1639" s="130" t="s">
+        <v>8715</v>
+      </c>
+      <c r="G1639" s="130" t="s">
+        <v>8716</v>
+      </c>
+      <c r="H1639" s="130" t="s">
+        <v>8717</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:8">
+      <c r="A1640">
+        <v>901411</v>
+      </c>
+      <c r="B1640" s="2">
+        <v>91411</v>
+      </c>
+      <c r="C1640" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1640" s="130" t="s">
+        <v>8700</v>
+      </c>
+      <c r="E1640" s="130" t="s">
+        <v>8718</v>
+      </c>
+      <c r="F1640" s="130" t="s">
+        <v>8719</v>
+      </c>
+      <c r="G1640" s="130" t="s">
+        <v>8720</v>
+      </c>
+      <c r="H1640" s="130" t="s">
+        <v>8721</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:8">
+      <c r="A1641">
+        <v>901412</v>
+      </c>
+      <c r="B1641" s="2">
+        <v>91412</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1641" s="130" t="s">
+        <v>8701</v>
+      </c>
+      <c r="E1641" s="130" t="s">
+        <v>8722</v>
+      </c>
+      <c r="F1641" s="130" t="s">
+        <v>8723</v>
+      </c>
+      <c r="G1641" s="130" t="s">
+        <v>8724</v>
+      </c>
+      <c r="H1641" s="130" t="s">
+        <v>8725</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:8">
+      <c r="A1642">
+        <v>901413</v>
+      </c>
+      <c r="B1642" s="2">
+        <v>91413</v>
+      </c>
+      <c r="C1642" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1642" s="130" t="s">
+        <v>8702</v>
+      </c>
+      <c r="E1642" s="130" t="s">
+        <v>8726</v>
+      </c>
+      <c r="F1642" s="130" t="s">
+        <v>8727</v>
+      </c>
+      <c r="G1642" s="130" t="s">
+        <v>8728</v>
+      </c>
+      <c r="H1642" s="130" t="s">
+        <v>8729</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/DB/MMM_DB_Ver.05.xlsx
+++ b/Assets/DB/MMM_DB_Ver.05.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\MoreMustMush\Assets\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FEE114-585D-4F90-A188-4750FE230E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1624DE0E-B32B-4F8A-91B2-DB4450B8F1A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11121" uniqueCount="8730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11125" uniqueCount="8770">
   <si>
     <t>Upgrade_Table</t>
   </si>
@@ -30350,6 +30350,162 @@
   </si>
   <si>
     <t>Ранг ★{0}/{1} · рів.{2}/{3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare Spores</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>レア胞子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Редкие споры</t>
+  </si>
+  <si>
+    <t>Рідкісні спори</t>
+  </si>
+  <si>
+    <t>Epic and higher mushrooms sprout more often. At max level, the forest returns to its natural rate.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>エピック以上のキノコがよく生えるようになります。最大まで上げると森本来の頻度になります。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Эпические и более редкие грибы вырастают чаще. На максимуме лес возвращается к своей обычной частоте.</t>
+  </si>
+  <si>
+    <t>Епічні й рідкісніші гриби з'являються частіше. На максимумі ліс повертається до своєї звичайної частоти.</t>
+  </si>
+  <si>
+    <t>Epic and above weight x{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>エピック以上の重み ×{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Вес эпических и выше x{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Вага епічних і вище ×{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Language</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>言語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Язык</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Мова</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound Settings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>サウンド設定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Настройки звука</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Налаштування звуку</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>効果音</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Эффекты</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ефекти</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Музыка</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Музика</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Main Menu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>メインメニュー</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Главное меню</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Головне меню</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mute: On</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ミュート:オン</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Без звука: вкл.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Без звуку: увімк.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mute: Off</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ミュート:オフ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Без звука: выкл.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Без звуку: вимк.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -31235,46 +31391,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -31283,12 +31439,12 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -31756,29 +31912,29 @@
   <sheetData>
     <row r="1" spans="2:44" ht="12" customHeight="1"/>
     <row r="2" spans="2:44">
-      <c r="B2" s="156" t="s">
+      <c r="B2" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-      <c r="R2" s="157"/>
-      <c r="S2" s="157"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="158"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155"/>
+      <c r="R2" s="155"/>
+      <c r="S2" s="155"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="156"/>
     </row>
     <row r="3" spans="2:44">
       <c r="B3" s="17"/>
@@ -31835,29 +31991,29 @@
       <c r="V4" s="14"/>
     </row>
     <row r="5" spans="2:44">
-      <c r="B5" s="156" t="s">
+      <c r="B5" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="157"/>
-      <c r="N5" s="157"/>
-      <c r="O5" s="157"/>
-      <c r="P5" s="157"/>
-      <c r="Q5" s="157"/>
-      <c r="R5" s="157"/>
-      <c r="S5" s="157"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="157"/>
-      <c r="V5" s="158"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="155"/>
+      <c r="Q5" s="155"/>
+      <c r="R5" s="155"/>
+      <c r="S5" s="155"/>
+      <c r="T5" s="155"/>
+      <c r="U5" s="155"/>
+      <c r="V5" s="156"/>
     </row>
     <row r="6" spans="2:44">
       <c r="B6" s="6"/>
@@ -31987,29 +32143,29 @@
     </row>
     <row r="10" spans="2:44" ht="8.1" customHeight="1"/>
     <row r="11" spans="2:44">
-      <c r="B11" s="156" t="s">
+      <c r="B11" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="157"/>
-      <c r="H11" s="157"/>
-      <c r="I11" s="157"/>
-      <c r="J11" s="157"/>
-      <c r="K11" s="157"/>
-      <c r="L11" s="157"/>
-      <c r="M11" s="157"/>
-      <c r="N11" s="157"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="157"/>
-      <c r="Q11" s="157"/>
-      <c r="R11" s="157"/>
-      <c r="S11" s="157"/>
-      <c r="T11" s="157"/>
-      <c r="U11" s="157"/>
-      <c r="V11" s="158"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="155"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="155"/>
+      <c r="G11" s="155"/>
+      <c r="H11" s="155"/>
+      <c r="I11" s="155"/>
+      <c r="J11" s="155"/>
+      <c r="K11" s="155"/>
+      <c r="L11" s="155"/>
+      <c r="M11" s="155"/>
+      <c r="N11" s="155"/>
+      <c r="O11" s="155"/>
+      <c r="P11" s="155"/>
+      <c r="Q11" s="155"/>
+      <c r="R11" s="155"/>
+      <c r="S11" s="155"/>
+      <c r="T11" s="155"/>
+      <c r="U11" s="155"/>
+      <c r="V11" s="156"/>
     </row>
     <row r="12" spans="2:44">
       <c r="B12" s="6"/>
@@ -32296,19 +32452,19 @@
       <c r="AF22" s="27"/>
     </row>
     <row r="23" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B23" s="159" t="s">
+      <c r="B23" s="157" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="146"/>
-      <c r="D23" s="146"/>
-      <c r="E23" s="146"/>
-      <c r="F23" s="146"/>
-      <c r="G23" s="146"/>
-      <c r="H23" s="161" t="s">
+      <c r="C23" s="144"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="144"/>
+      <c r="G23" s="144"/>
+      <c r="H23" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="146"/>
-      <c r="J23" s="146"/>
+      <c r="I23" s="144"/>
+      <c r="J23" s="144"/>
       <c r="K23" s="28" t="s">
         <v>68</v>
       </c>
@@ -32336,18 +32492,18 @@
     </row>
     <row r="24" spans="2:32" s="10" customFormat="1">
       <c r="B24" s="86"/>
-      <c r="C24" s="136" t="s">
+      <c r="C24" s="153" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="137"/>
-      <c r="E24" s="137"/>
-      <c r="F24" s="137"/>
-      <c r="G24" s="138"/>
-      <c r="H24" s="142" t="s">
+      <c r="D24" s="151"/>
+      <c r="E24" s="151"/>
+      <c r="F24" s="151"/>
+      <c r="G24" s="152"/>
+      <c r="H24" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="137"/>
-      <c r="J24" s="138"/>
+      <c r="I24" s="151"/>
+      <c r="J24" s="152"/>
       <c r="K24" s="34" t="s">
         <v>70</v>
       </c>
@@ -32375,14 +32531,14 @@
     </row>
     <row r="25" spans="2:32" s="10" customFormat="1">
       <c r="B25" s="22"/>
-      <c r="C25" s="139"/>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
-      <c r="G25" s="140"/>
-      <c r="H25" s="143"/>
-      <c r="I25" s="139"/>
-      <c r="J25" s="140"/>
+      <c r="C25" s="140"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="158"/>
+      <c r="I25" s="140"/>
+      <c r="J25" s="141"/>
       <c r="K25" s="19" t="s">
         <v>49</v>
       </c>
@@ -32404,18 +32560,18 @@
     </row>
     <row r="26" spans="2:32" s="10" customFormat="1">
       <c r="B26" s="22"/>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="139" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="141" t="s">
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="141"/>
+      <c r="H26" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="139"/>
-      <c r="J26" s="140"/>
+      <c r="I26" s="140"/>
+      <c r="J26" s="141"/>
       <c r="K26" s="19" t="s">
         <v>74</v>
       </c>
@@ -32435,18 +32591,18 @@
     </row>
     <row r="27" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B27" s="22"/>
-      <c r="C27" s="144" t="s">
+      <c r="C27" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="139"/>
-      <c r="G27" s="140"/>
-      <c r="H27" s="141" t="s">
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="141"/>
+      <c r="H27" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I27" s="139"/>
-      <c r="J27" s="140"/>
+      <c r="I27" s="140"/>
+      <c r="J27" s="141"/>
       <c r="K27" s="19" t="s">
         <v>75</v>
       </c>
@@ -32466,18 +32622,18 @@
     </row>
     <row r="28" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B28" s="22"/>
-      <c r="C28" s="144" t="s">
+      <c r="C28" s="139" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="139"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="141" t="s">
+      <c r="D28" s="140"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I28" s="139"/>
-      <c r="J28" s="140"/>
+      <c r="I28" s="140"/>
+      <c r="J28" s="141"/>
       <c r="K28" s="19" t="s">
         <v>77</v>
       </c>
@@ -32497,18 +32653,18 @@
     </row>
     <row r="29" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B29" s="22"/>
-      <c r="C29" s="144" t="s">
+      <c r="C29" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="140"/>
-      <c r="H29" s="141" t="s">
+      <c r="D29" s="140"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I29" s="139"/>
-      <c r="J29" s="140"/>
+      <c r="I29" s="140"/>
+      <c r="J29" s="141"/>
       <c r="K29" s="19" t="s">
         <v>78</v>
       </c>
@@ -32528,18 +32684,18 @@
     </row>
     <row r="30" spans="2:32" s="10" customFormat="1">
       <c r="B30" s="22"/>
-      <c r="C30" s="144" t="s">
+      <c r="C30" s="139" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="139"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="139"/>
-      <c r="G30" s="140"/>
-      <c r="H30" s="141" t="s">
+      <c r="D30" s="140"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="140"/>
+      <c r="G30" s="141"/>
+      <c r="H30" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I30" s="139"/>
-      <c r="J30" s="140"/>
+      <c r="I30" s="140"/>
+      <c r="J30" s="141"/>
       <c r="K30" s="120" t="s">
         <v>421</v>
       </c>
@@ -32559,18 +32715,18 @@
     </row>
     <row r="31" spans="2:32" s="10" customFormat="1">
       <c r="B31" s="22"/>
-      <c r="C31" s="144" t="s">
+      <c r="C31" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="140"/>
-      <c r="H31" s="141" t="s">
+      <c r="D31" s="140"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="140"/>
+      <c r="G31" s="141"/>
+      <c r="H31" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I31" s="139"/>
-      <c r="J31" s="140"/>
+      <c r="I31" s="140"/>
+      <c r="J31" s="141"/>
       <c r="K31" s="19" t="s">
         <v>80</v>
       </c>
@@ -32590,18 +32746,18 @@
     </row>
     <row r="32" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B32" s="75"/>
-      <c r="C32" s="160" t="s">
+      <c r="C32" s="145" t="s">
         <v>422</v>
       </c>
-      <c r="D32" s="149"/>
-      <c r="E32" s="149"/>
-      <c r="F32" s="149"/>
-      <c r="G32" s="150"/>
-      <c r="H32" s="148" t="s">
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="137"/>
+      <c r="G32" s="138"/>
+      <c r="H32" s="136" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="149"/>
-      <c r="J32" s="150"/>
+      <c r="I32" s="137"/>
+      <c r="J32" s="138"/>
       <c r="K32" s="81" t="s">
         <v>82</v>
       </c>
@@ -32663,19 +32819,19 @@
       <c r="AF33" s="27"/>
     </row>
     <row r="34" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B34" s="145" t="s">
+      <c r="B34" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="146"/>
-      <c r="D34" s="146"/>
-      <c r="E34" s="146"/>
-      <c r="F34" s="146"/>
-      <c r="G34" s="147"/>
-      <c r="H34" s="145" t="s">
+      <c r="C34" s="144"/>
+      <c r="D34" s="144"/>
+      <c r="E34" s="144"/>
+      <c r="F34" s="144"/>
+      <c r="G34" s="149"/>
+      <c r="H34" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I34" s="146"/>
-      <c r="J34" s="147"/>
+      <c r="I34" s="144"/>
+      <c r="J34" s="149"/>
       <c r="K34" s="28" t="s">
         <v>68</v>
       </c>
@@ -32703,18 +32859,18 @@
     </row>
     <row r="35" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B35" s="86"/>
-      <c r="C35" s="136" t="s">
+      <c r="C35" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="137"/>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="138"/>
-      <c r="H35" s="142" t="s">
+      <c r="D35" s="151"/>
+      <c r="E35" s="151"/>
+      <c r="F35" s="151"/>
+      <c r="G35" s="152"/>
+      <c r="H35" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="I35" s="137"/>
-      <c r="J35" s="138"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="152"/>
       <c r="K35" s="34" t="s">
         <v>84</v>
       </c>
@@ -32742,18 +32898,18 @@
     </row>
     <row r="36" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B36" s="75"/>
-      <c r="C36" s="160" t="s">
+      <c r="C36" s="145" t="s">
         <v>423</v>
       </c>
-      <c r="D36" s="149"/>
-      <c r="E36" s="149"/>
-      <c r="F36" s="149"/>
-      <c r="G36" s="150"/>
-      <c r="H36" s="148" t="s">
+      <c r="D36" s="137"/>
+      <c r="E36" s="137"/>
+      <c r="F36" s="137"/>
+      <c r="G36" s="138"/>
+      <c r="H36" s="136" t="s">
         <v>69</v>
       </c>
-      <c r="I36" s="149"/>
-      <c r="J36" s="150"/>
+      <c r="I36" s="137"/>
+      <c r="J36" s="138"/>
       <c r="K36" s="81" t="s">
         <v>85</v>
       </c>
@@ -32815,19 +32971,19 @@
       <c r="AF37" s="92"/>
     </row>
     <row r="38" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B38" s="145" t="s">
+      <c r="B38" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="146"/>
-      <c r="D38" s="146"/>
-      <c r="E38" s="146"/>
-      <c r="F38" s="146"/>
-      <c r="G38" s="147"/>
-      <c r="H38" s="145" t="s">
+      <c r="C38" s="144"/>
+      <c r="D38" s="144"/>
+      <c r="E38" s="144"/>
+      <c r="F38" s="144"/>
+      <c r="G38" s="149"/>
+      <c r="H38" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="146"/>
-      <c r="J38" s="147"/>
+      <c r="I38" s="144"/>
+      <c r="J38" s="149"/>
       <c r="K38" s="28" t="s">
         <v>68</v>
       </c>
@@ -32855,18 +33011,18 @@
     </row>
     <row r="39" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B39" s="21"/>
-      <c r="C39" s="144" t="s">
+      <c r="C39" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="139"/>
-      <c r="E39" s="139"/>
-      <c r="F39" s="139"/>
-      <c r="G39" s="140"/>
-      <c r="H39" s="141" t="s">
+      <c r="D39" s="140"/>
+      <c r="E39" s="140"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="141"/>
+      <c r="H39" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I39" s="139"/>
-      <c r="J39" s="140"/>
+      <c r="I39" s="140"/>
+      <c r="J39" s="141"/>
       <c r="K39" s="19" t="s">
         <v>86</v>
       </c>
@@ -32886,18 +33042,18 @@
     </row>
     <row r="40" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B40" s="22"/>
-      <c r="C40" s="144" t="s">
+      <c r="C40" s="139" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="139"/>
-      <c r="E40" s="139"/>
-      <c r="F40" s="139"/>
-      <c r="G40" s="140"/>
-      <c r="H40" s="141" t="s">
+      <c r="D40" s="140"/>
+      <c r="E40" s="140"/>
+      <c r="F40" s="140"/>
+      <c r="G40" s="141"/>
+      <c r="H40" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I40" s="139"/>
-      <c r="J40" s="140"/>
+      <c r="I40" s="140"/>
+      <c r="J40" s="141"/>
       <c r="K40" s="19" t="s">
         <v>88</v>
       </c>
@@ -32917,18 +33073,18 @@
     </row>
     <row r="41" spans="2:32" s="10" customFormat="1">
       <c r="B41" s="22"/>
-      <c r="C41" s="144" t="s">
+      <c r="C41" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="139"/>
-      <c r="E41" s="139"/>
-      <c r="F41" s="139"/>
-      <c r="G41" s="140"/>
-      <c r="H41" s="141" t="s">
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="140"/>
+      <c r="G41" s="141"/>
+      <c r="H41" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="139"/>
-      <c r="J41" s="140"/>
+      <c r="I41" s="140"/>
+      <c r="J41" s="141"/>
       <c r="K41" s="19" t="s">
         <v>89</v>
       </c>
@@ -32948,18 +33104,18 @@
     </row>
     <row r="42" spans="2:32" s="10" customFormat="1">
       <c r="B42" s="22"/>
-      <c r="C42" s="144" t="s">
+      <c r="C42" s="139" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="139"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="140"/>
-      <c r="H42" s="141" t="s">
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="141"/>
+      <c r="H42" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I42" s="139"/>
-      <c r="J42" s="140"/>
+      <c r="I42" s="140"/>
+      <c r="J42" s="141"/>
       <c r="K42" s="19" t="s">
         <v>91</v>
       </c>
@@ -32979,18 +33135,18 @@
     </row>
     <row r="43" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B43" s="75"/>
-      <c r="C43" s="152" t="s">
+      <c r="C43" s="142" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="149"/>
-      <c r="E43" s="149"/>
-      <c r="F43" s="149"/>
-      <c r="G43" s="150"/>
-      <c r="H43" s="148" t="s">
+      <c r="D43" s="137"/>
+      <c r="E43" s="137"/>
+      <c r="F43" s="137"/>
+      <c r="G43" s="138"/>
+      <c r="H43" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="149"/>
-      <c r="J43" s="150"/>
+      <c r="I43" s="137"/>
+      <c r="J43" s="138"/>
       <c r="K43" s="81" t="s">
         <v>92</v>
       </c>
@@ -33052,19 +33208,19 @@
       <c r="AF44" s="27"/>
     </row>
     <row r="45" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B45" s="145" t="s">
+      <c r="B45" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="146"/>
-      <c r="D45" s="146"/>
-      <c r="E45" s="146"/>
-      <c r="F45" s="146"/>
-      <c r="G45" s="147"/>
-      <c r="H45" s="153" t="s">
+      <c r="C45" s="144"/>
+      <c r="D45" s="144"/>
+      <c r="E45" s="144"/>
+      <c r="F45" s="144"/>
+      <c r="G45" s="149"/>
+      <c r="H45" s="159" t="s">
         <v>67</v>
       </c>
-      <c r="I45" s="154"/>
-      <c r="J45" s="155"/>
+      <c r="I45" s="160"/>
+      <c r="J45" s="161"/>
       <c r="K45" s="83" t="s">
         <v>68</v>
       </c>
@@ -33092,18 +33248,18 @@
     </row>
     <row r="46" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B46" s="21"/>
-      <c r="C46" s="144" t="s">
+      <c r="C46" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="139"/>
-      <c r="E46" s="139"/>
-      <c r="F46" s="139"/>
-      <c r="G46" s="140"/>
-      <c r="H46" s="142" t="s">
+      <c r="D46" s="140"/>
+      <c r="E46" s="140"/>
+      <c r="F46" s="140"/>
+      <c r="G46" s="141"/>
+      <c r="H46" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="I46" s="137"/>
-      <c r="J46" s="138"/>
+      <c r="I46" s="151"/>
+      <c r="J46" s="152"/>
       <c r="K46" s="19" t="s">
         <v>93</v>
       </c>
@@ -33123,18 +33279,18 @@
     </row>
     <row r="47" spans="2:32" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B47" s="22"/>
-      <c r="C47" s="144" t="s">
+      <c r="C47" s="139" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="139"/>
-      <c r="E47" s="139"/>
-      <c r="F47" s="139"/>
-      <c r="G47" s="140"/>
-      <c r="H47" s="141" t="s">
+      <c r="D47" s="140"/>
+      <c r="E47" s="140"/>
+      <c r="F47" s="140"/>
+      <c r="G47" s="141"/>
+      <c r="H47" s="146" t="s">
         <v>81</v>
       </c>
-      <c r="I47" s="139"/>
-      <c r="J47" s="140"/>
+      <c r="I47" s="140"/>
+      <c r="J47" s="141"/>
       <c r="K47" s="19" t="s">
         <v>95</v>
       </c>
@@ -33154,14 +33310,14 @@
     </row>
     <row r="48" spans="2:32" s="10" customFormat="1">
       <c r="B48" s="22"/>
-      <c r="C48" s="139"/>
-      <c r="D48" s="139"/>
-      <c r="E48" s="139"/>
-      <c r="F48" s="139"/>
-      <c r="G48" s="140"/>
-      <c r="H48" s="143"/>
-      <c r="I48" s="139"/>
-      <c r="J48" s="140"/>
+      <c r="C48" s="140"/>
+      <c r="D48" s="140"/>
+      <c r="E48" s="140"/>
+      <c r="F48" s="140"/>
+      <c r="G48" s="141"/>
+      <c r="H48" s="158"/>
+      <c r="I48" s="140"/>
+      <c r="J48" s="141"/>
       <c r="K48" s="19" t="s">
         <v>49</v>
       </c>
@@ -33183,14 +33339,14 @@
     </row>
     <row r="49" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B49" s="22"/>
-      <c r="C49" s="139"/>
-      <c r="D49" s="139"/>
-      <c r="E49" s="139"/>
-      <c r="F49" s="139"/>
-      <c r="G49" s="140"/>
-      <c r="H49" s="143"/>
-      <c r="I49" s="139"/>
-      <c r="J49" s="140"/>
+      <c r="C49" s="140"/>
+      <c r="D49" s="140"/>
+      <c r="E49" s="140"/>
+      <c r="F49" s="140"/>
+      <c r="G49" s="141"/>
+      <c r="H49" s="158"/>
+      <c r="I49" s="140"/>
+      <c r="J49" s="141"/>
       <c r="K49" s="19" t="s">
         <v>49</v>
       </c>
@@ -33247,19 +33403,19 @@
       <c r="AG50" s="92"/>
     </row>
     <row r="51" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B51" s="145" t="s">
+      <c r="B51" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="146"/>
-      <c r="D51" s="146"/>
-      <c r="E51" s="146"/>
-      <c r="F51" s="146"/>
-      <c r="G51" s="147"/>
-      <c r="H51" s="145" t="s">
+      <c r="C51" s="144"/>
+      <c r="D51" s="144"/>
+      <c r="E51" s="144"/>
+      <c r="F51" s="144"/>
+      <c r="G51" s="149"/>
+      <c r="H51" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I51" s="146"/>
-      <c r="J51" s="147"/>
+      <c r="I51" s="144"/>
+      <c r="J51" s="149"/>
       <c r="K51" s="28" t="s">
         <v>68</v>
       </c>
@@ -33288,18 +33444,18 @@
     </row>
     <row r="52" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B52" s="21"/>
-      <c r="C52" s="144" t="s">
+      <c r="C52" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="139"/>
-      <c r="E52" s="139"/>
-      <c r="F52" s="139"/>
-      <c r="G52" s="140"/>
-      <c r="H52" s="141" t="s">
+      <c r="D52" s="140"/>
+      <c r="E52" s="140"/>
+      <c r="F52" s="140"/>
+      <c r="G52" s="141"/>
+      <c r="H52" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I52" s="139"/>
-      <c r="J52" s="140"/>
+      <c r="I52" s="140"/>
+      <c r="J52" s="141"/>
       <c r="K52" s="19" t="s">
         <v>99</v>
       </c>
@@ -33319,18 +33475,18 @@
     </row>
     <row r="53" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B53" s="22"/>
-      <c r="C53" s="144" t="s">
+      <c r="C53" s="139" t="s">
         <v>100</v>
       </c>
-      <c r="D53" s="139"/>
-      <c r="E53" s="139"/>
-      <c r="F53" s="139"/>
-      <c r="G53" s="140"/>
-      <c r="H53" s="141" t="s">
+      <c r="D53" s="140"/>
+      <c r="E53" s="140"/>
+      <c r="F53" s="140"/>
+      <c r="G53" s="141"/>
+      <c r="H53" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I53" s="139"/>
-      <c r="J53" s="140"/>
+      <c r="I53" s="140"/>
+      <c r="J53" s="141"/>
       <c r="K53" s="19" t="s">
         <v>101</v>
       </c>
@@ -33350,18 +33506,18 @@
     </row>
     <row r="54" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B54" s="75"/>
-      <c r="C54" s="152" t="s">
+      <c r="C54" s="142" t="s">
         <v>102</v>
       </c>
-      <c r="D54" s="149"/>
-      <c r="E54" s="149"/>
-      <c r="F54" s="149"/>
-      <c r="G54" s="150"/>
-      <c r="H54" s="148" t="s">
+      <c r="D54" s="137"/>
+      <c r="E54" s="137"/>
+      <c r="F54" s="137"/>
+      <c r="G54" s="138"/>
+      <c r="H54" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="I54" s="149"/>
-      <c r="J54" s="150"/>
+      <c r="I54" s="137"/>
+      <c r="J54" s="138"/>
       <c r="K54" s="81" t="s">
         <v>103</v>
       </c>
@@ -33425,19 +33581,19 @@
       <c r="AG55" s="92"/>
     </row>
     <row r="56" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B56" s="145" t="s">
+      <c r="B56" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="146"/>
-      <c r="D56" s="146"/>
-      <c r="E56" s="146"/>
-      <c r="F56" s="146"/>
-      <c r="G56" s="147"/>
-      <c r="H56" s="145" t="s">
+      <c r="C56" s="144"/>
+      <c r="D56" s="144"/>
+      <c r="E56" s="144"/>
+      <c r="F56" s="144"/>
+      <c r="G56" s="149"/>
+      <c r="H56" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I56" s="146"/>
-      <c r="J56" s="147"/>
+      <c r="I56" s="144"/>
+      <c r="J56" s="149"/>
       <c r="K56" s="28" t="s">
         <v>68</v>
       </c>
@@ -33466,18 +33622,18 @@
     </row>
     <row r="57" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B57" s="21"/>
-      <c r="C57" s="144" t="s">
+      <c r="C57" s="139" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="139"/>
-      <c r="E57" s="139"/>
-      <c r="F57" s="139"/>
-      <c r="G57" s="140"/>
-      <c r="H57" s="141" t="s">
+      <c r="D57" s="140"/>
+      <c r="E57" s="140"/>
+      <c r="F57" s="140"/>
+      <c r="G57" s="141"/>
+      <c r="H57" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I57" s="139"/>
-      <c r="J57" s="140"/>
+      <c r="I57" s="140"/>
+      <c r="J57" s="141"/>
       <c r="K57" s="19" t="s">
         <v>104</v>
       </c>
@@ -33497,18 +33653,18 @@
     </row>
     <row r="58" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B58" s="22"/>
-      <c r="C58" s="144" t="s">
+      <c r="C58" s="139" t="s">
         <v>105</v>
       </c>
-      <c r="D58" s="139"/>
-      <c r="E58" s="139"/>
-      <c r="F58" s="139"/>
-      <c r="G58" s="140"/>
-      <c r="H58" s="141" t="s">
+      <c r="D58" s="140"/>
+      <c r="E58" s="140"/>
+      <c r="F58" s="140"/>
+      <c r="G58" s="141"/>
+      <c r="H58" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I58" s="139"/>
-      <c r="J58" s="140"/>
+      <c r="I58" s="140"/>
+      <c r="J58" s="141"/>
       <c r="K58" s="19" t="s">
         <v>106</v>
       </c>
@@ -33528,18 +33684,18 @@
     </row>
     <row r="59" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1">
       <c r="B59" s="22"/>
-      <c r="C59" s="144" t="s">
+      <c r="C59" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="140"/>
-      <c r="H59" s="141" t="s">
+      <c r="D59" s="140"/>
+      <c r="E59" s="140"/>
+      <c r="F59" s="140"/>
+      <c r="G59" s="141"/>
+      <c r="H59" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I59" s="139"/>
-      <c r="J59" s="140"/>
+      <c r="I59" s="140"/>
+      <c r="J59" s="141"/>
       <c r="K59" s="19" t="s">
         <v>107</v>
       </c>
@@ -33559,18 +33715,18 @@
     </row>
     <row r="60" spans="2:33" s="10" customFormat="1">
       <c r="B60" s="22"/>
-      <c r="C60" s="144" t="s">
+      <c r="C60" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="D60" s="139"/>
-      <c r="E60" s="139"/>
-      <c r="F60" s="139"/>
-      <c r="G60" s="140"/>
-      <c r="H60" s="141" t="s">
+      <c r="D60" s="140"/>
+      <c r="E60" s="140"/>
+      <c r="F60" s="140"/>
+      <c r="G60" s="141"/>
+      <c r="H60" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I60" s="139"/>
-      <c r="J60" s="140"/>
+      <c r="I60" s="140"/>
+      <c r="J60" s="141"/>
       <c r="K60" s="19" t="s">
         <v>109</v>
       </c>
@@ -33590,18 +33746,18 @@
     </row>
     <row r="61" spans="2:33" s="10" customFormat="1">
       <c r="B61" s="22"/>
-      <c r="C61" s="144" t="s">
+      <c r="C61" s="139" t="s">
         <v>110</v>
       </c>
-      <c r="D61" s="139"/>
-      <c r="E61" s="139"/>
-      <c r="F61" s="139"/>
-      <c r="G61" s="140"/>
-      <c r="H61" s="141" t="s">
+      <c r="D61" s="140"/>
+      <c r="E61" s="140"/>
+      <c r="F61" s="140"/>
+      <c r="G61" s="141"/>
+      <c r="H61" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I61" s="139"/>
-      <c r="J61" s="140"/>
+      <c r="I61" s="140"/>
+      <c r="J61" s="141"/>
       <c r="K61" s="19" t="s">
         <v>111</v>
       </c>
@@ -33621,18 +33777,18 @@
     </row>
     <row r="62" spans="2:33" s="10" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B62" s="75"/>
-      <c r="C62" s="152" t="s">
+      <c r="C62" s="142" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="149"/>
-      <c r="E62" s="149"/>
-      <c r="F62" s="149"/>
-      <c r="G62" s="150"/>
-      <c r="H62" s="148" t="s">
+      <c r="D62" s="137"/>
+      <c r="E62" s="137"/>
+      <c r="F62" s="137"/>
+      <c r="G62" s="138"/>
+      <c r="H62" s="136" t="s">
         <v>81</v>
       </c>
-      <c r="I62" s="149"/>
-      <c r="J62" s="150"/>
+      <c r="I62" s="137"/>
+      <c r="J62" s="138"/>
       <c r="K62" s="81" t="s">
         <v>113</v>
       </c>
@@ -33696,19 +33852,19 @@
       <c r="AG63" s="92"/>
     </row>
     <row r="64" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B64" s="145" t="s">
+      <c r="B64" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="146"/>
-      <c r="D64" s="146"/>
-      <c r="E64" s="146"/>
-      <c r="F64" s="146"/>
-      <c r="G64" s="147"/>
-      <c r="H64" s="145" t="s">
+      <c r="C64" s="144"/>
+      <c r="D64" s="144"/>
+      <c r="E64" s="144"/>
+      <c r="F64" s="144"/>
+      <c r="G64" s="149"/>
+      <c r="H64" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I64" s="146"/>
-      <c r="J64" s="147"/>
+      <c r="I64" s="144"/>
+      <c r="J64" s="149"/>
       <c r="K64" s="83" t="s">
         <v>68</v>
       </c>
@@ -33737,18 +33893,18 @@
     </row>
     <row r="65" spans="2:33">
       <c r="B65" s="21"/>
-      <c r="C65" s="144" t="s">
+      <c r="C65" s="139" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="151"/>
-      <c r="E65" s="151"/>
-      <c r="F65" s="151"/>
-      <c r="G65" s="140"/>
-      <c r="H65" s="142" t="s">
+      <c r="D65" s="147"/>
+      <c r="E65" s="147"/>
+      <c r="F65" s="147"/>
+      <c r="G65" s="141"/>
+      <c r="H65" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="I65" s="137"/>
-      <c r="J65" s="138"/>
+      <c r="I65" s="151"/>
+      <c r="J65" s="152"/>
       <c r="K65" s="19" t="s">
         <v>115</v>
       </c>
@@ -33768,18 +33924,18 @@
     </row>
     <row r="66" spans="2:33">
       <c r="B66" s="22"/>
-      <c r="C66" s="144" t="s">
+      <c r="C66" s="139" t="s">
         <v>116</v>
       </c>
-      <c r="D66" s="151"/>
-      <c r="E66" s="151"/>
-      <c r="F66" s="151"/>
-      <c r="G66" s="140"/>
-      <c r="H66" s="141" t="s">
+      <c r="D66" s="147"/>
+      <c r="E66" s="147"/>
+      <c r="F66" s="147"/>
+      <c r="G66" s="141"/>
+      <c r="H66" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I66" s="151"/>
-      <c r="J66" s="140"/>
+      <c r="I66" s="147"/>
+      <c r="J66" s="141"/>
       <c r="K66" s="19" t="s">
         <v>117</v>
       </c>
@@ -33799,18 +33955,18 @@
     </row>
     <row r="67" spans="2:33">
       <c r="B67" s="22"/>
-      <c r="C67" s="144" t="s">
+      <c r="C67" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="D67" s="151"/>
-      <c r="E67" s="151"/>
-      <c r="F67" s="151"/>
-      <c r="G67" s="140"/>
-      <c r="H67" s="141" t="s">
+      <c r="D67" s="147"/>
+      <c r="E67" s="147"/>
+      <c r="F67" s="147"/>
+      <c r="G67" s="141"/>
+      <c r="H67" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I67" s="151"/>
-      <c r="J67" s="140"/>
+      <c r="I67" s="147"/>
+      <c r="J67" s="141"/>
       <c r="K67" s="19" t="s">
         <v>118</v>
       </c>
@@ -33830,18 +33986,18 @@
     </row>
     <row r="68" spans="2:33">
       <c r="B68" s="22"/>
-      <c r="C68" s="144" t="s">
+      <c r="C68" s="139" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="151"/>
-      <c r="E68" s="151"/>
-      <c r="F68" s="151"/>
-      <c r="G68" s="140"/>
-      <c r="H68" s="141" t="s">
+      <c r="D68" s="147"/>
+      <c r="E68" s="147"/>
+      <c r="F68" s="147"/>
+      <c r="G68" s="141"/>
+      <c r="H68" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I68" s="151"/>
-      <c r="J68" s="140"/>
+      <c r="I68" s="147"/>
+      <c r="J68" s="141"/>
       <c r="K68" s="19" t="s">
         <v>120</v>
       </c>
@@ -33861,18 +34017,18 @@
     </row>
     <row r="69" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B69" s="75"/>
-      <c r="C69" s="152" t="s">
+      <c r="C69" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="D69" s="149"/>
-      <c r="E69" s="149"/>
-      <c r="F69" s="149"/>
-      <c r="G69" s="150"/>
-      <c r="H69" s="148" t="s">
+      <c r="D69" s="137"/>
+      <c r="E69" s="137"/>
+      <c r="F69" s="137"/>
+      <c r="G69" s="138"/>
+      <c r="H69" s="136" t="s">
         <v>69</v>
       </c>
-      <c r="I69" s="149"/>
-      <c r="J69" s="150"/>
+      <c r="I69" s="137"/>
+      <c r="J69" s="138"/>
       <c r="K69" s="81" t="s">
         <v>122</v>
       </c>
@@ -33936,19 +34092,19 @@
       <c r="AG70" s="94"/>
     </row>
     <row r="71" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B71" s="145" t="s">
+      <c r="B71" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="146"/>
-      <c r="D71" s="146"/>
-      <c r="E71" s="146"/>
-      <c r="F71" s="146"/>
-      <c r="G71" s="147"/>
-      <c r="H71" s="145" t="s">
+      <c r="C71" s="144"/>
+      <c r="D71" s="144"/>
+      <c r="E71" s="144"/>
+      <c r="F71" s="144"/>
+      <c r="G71" s="149"/>
+      <c r="H71" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I71" s="146"/>
-      <c r="J71" s="147"/>
+      <c r="I71" s="144"/>
+      <c r="J71" s="149"/>
       <c r="K71" s="83" t="s">
         <v>68</v>
       </c>
@@ -33977,18 +34133,18 @@
     </row>
     <row r="72" spans="2:33">
       <c r="B72" s="21"/>
-      <c r="C72" s="144" t="s">
+      <c r="C72" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="151"/>
-      <c r="E72" s="151"/>
-      <c r="F72" s="151"/>
-      <c r="G72" s="140"/>
-      <c r="H72" s="142" t="s">
+      <c r="D72" s="147"/>
+      <c r="E72" s="147"/>
+      <c r="F72" s="147"/>
+      <c r="G72" s="141"/>
+      <c r="H72" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="I72" s="137"/>
-      <c r="J72" s="138"/>
+      <c r="I72" s="151"/>
+      <c r="J72" s="152"/>
       <c r="K72" s="19" t="s">
         <v>123</v>
       </c>
@@ -34008,18 +34164,18 @@
     </row>
     <row r="73" spans="2:33">
       <c r="B73" s="22"/>
-      <c r="C73" s="144" t="s">
+      <c r="C73" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="D73" s="151"/>
-      <c r="E73" s="151"/>
-      <c r="F73" s="151"/>
-      <c r="G73" s="140"/>
-      <c r="H73" s="141" t="s">
+      <c r="D73" s="147"/>
+      <c r="E73" s="147"/>
+      <c r="F73" s="147"/>
+      <c r="G73" s="141"/>
+      <c r="H73" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="I73" s="151"/>
-      <c r="J73" s="140"/>
+      <c r="I73" s="147"/>
+      <c r="J73" s="141"/>
       <c r="K73" s="19" t="s">
         <v>124</v>
       </c>
@@ -34039,18 +34195,18 @@
     </row>
     <row r="74" spans="2:33">
       <c r="B74" s="22"/>
-      <c r="C74" s="144" t="s">
+      <c r="C74" s="139" t="s">
         <v>125</v>
       </c>
-      <c r="D74" s="151"/>
-      <c r="E74" s="151"/>
-      <c r="F74" s="151"/>
-      <c r="G74" s="140"/>
-      <c r="H74" s="141" t="s">
+      <c r="D74" s="147"/>
+      <c r="E74" s="147"/>
+      <c r="F74" s="147"/>
+      <c r="G74" s="141"/>
+      <c r="H74" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="I74" s="151"/>
-      <c r="J74" s="140"/>
+      <c r="I74" s="147"/>
+      <c r="J74" s="141"/>
       <c r="K74" s="19" t="s">
         <v>126</v>
       </c>
@@ -34070,18 +34226,18 @@
     </row>
     <row r="75" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B75" s="75"/>
-      <c r="C75" s="152" t="s">
+      <c r="C75" s="142" t="s">
         <v>127</v>
       </c>
-      <c r="D75" s="149"/>
-      <c r="E75" s="149"/>
-      <c r="F75" s="149"/>
-      <c r="G75" s="150"/>
-      <c r="H75" s="148" t="s">
+      <c r="D75" s="137"/>
+      <c r="E75" s="137"/>
+      <c r="F75" s="137"/>
+      <c r="G75" s="138"/>
+      <c r="H75" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="I75" s="149"/>
-      <c r="J75" s="150"/>
+      <c r="I75" s="137"/>
+      <c r="J75" s="138"/>
       <c r="K75" s="81" t="s">
         <v>128</v>
       </c>
@@ -34145,19 +34301,19 @@
       <c r="AG76" s="94"/>
     </row>
     <row r="77" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B77" s="145" t="s">
+      <c r="B77" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C77" s="146"/>
-      <c r="D77" s="146"/>
-      <c r="E77" s="146"/>
-      <c r="F77" s="146"/>
-      <c r="G77" s="147"/>
-      <c r="H77" s="145" t="s">
+      <c r="C77" s="144"/>
+      <c r="D77" s="144"/>
+      <c r="E77" s="144"/>
+      <c r="F77" s="144"/>
+      <c r="G77" s="149"/>
+      <c r="H77" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="I77" s="146"/>
-      <c r="J77" s="147"/>
+      <c r="I77" s="144"/>
+      <c r="J77" s="149"/>
       <c r="K77" s="83" t="s">
         <v>68</v>
       </c>
@@ -34186,18 +34342,18 @@
     </row>
     <row r="78" spans="2:33">
       <c r="B78" s="21"/>
-      <c r="C78" s="144" t="s">
+      <c r="C78" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="151"/>
-      <c r="E78" s="151"/>
-      <c r="F78" s="151"/>
-      <c r="G78" s="140"/>
-      <c r="H78" s="142" t="s">
+      <c r="D78" s="147"/>
+      <c r="E78" s="147"/>
+      <c r="F78" s="147"/>
+      <c r="G78" s="141"/>
+      <c r="H78" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="I78" s="137"/>
-      <c r="J78" s="138"/>
+      <c r="I78" s="151"/>
+      <c r="J78" s="152"/>
       <c r="K78" s="19" t="s">
         <v>129</v>
       </c>
@@ -34217,18 +34373,18 @@
     </row>
     <row r="79" spans="2:33">
       <c r="B79" s="22"/>
-      <c r="C79" s="144" t="s">
+      <c r="C79" s="139" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="151"/>
-      <c r="E79" s="151"/>
-      <c r="F79" s="151"/>
-      <c r="G79" s="140"/>
-      <c r="H79" s="141" t="s">
+      <c r="D79" s="147"/>
+      <c r="E79" s="147"/>
+      <c r="F79" s="147"/>
+      <c r="G79" s="141"/>
+      <c r="H79" s="146" t="s">
         <v>131</v>
       </c>
-      <c r="I79" s="151"/>
-      <c r="J79" s="140"/>
+      <c r="I79" s="147"/>
+      <c r="J79" s="141"/>
       <c r="K79" s="19" t="s">
         <v>132</v>
       </c>
@@ -34248,18 +34404,18 @@
     </row>
     <row r="80" spans="2:33" ht="18.75" customHeight="1" thickBot="1">
       <c r="B80" s="75"/>
-      <c r="C80" s="152" t="s">
+      <c r="C80" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="D80" s="149"/>
-      <c r="E80" s="149"/>
-      <c r="F80" s="149"/>
-      <c r="G80" s="150"/>
-      <c r="H80" s="148" t="s">
+      <c r="D80" s="137"/>
+      <c r="E80" s="137"/>
+      <c r="F80" s="137"/>
+      <c r="G80" s="138"/>
+      <c r="H80" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="I80" s="149"/>
-      <c r="J80" s="150"/>
+      <c r="I80" s="137"/>
+      <c r="J80" s="138"/>
       <c r="K80" s="81" t="s">
         <v>134</v>
       </c>
@@ -34370,6 +34526,87 @@
     </row>
   </sheetData>
   <mergeCells count="97">
+    <mergeCell ref="C24:G25"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="H24:J25"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="H69:J69"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="H66:J66"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="H64:J64"/>
+    <mergeCell ref="H60:J60"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="B11:V11"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B5:V5"/>
+    <mergeCell ref="H47:J49"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C47:G49"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="H65:J65"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="H36:J36"/>
     <mergeCell ref="H80:J80"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="H62:J62"/>
@@ -34386,87 +34623,6 @@
     <mergeCell ref="H74:J74"/>
     <mergeCell ref="H56:J56"/>
     <mergeCell ref="H68:J68"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="H79:J79"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H78:J78"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="H65:J65"/>
-    <mergeCell ref="H71:J71"/>
-    <mergeCell ref="H75:J75"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C47:G49"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B2:V2"/>
-    <mergeCell ref="B11:V11"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B5:V5"/>
-    <mergeCell ref="H47:J49"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="H51:J51"/>
-    <mergeCell ref="H69:J69"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="H66:J66"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="H64:J64"/>
-    <mergeCell ref="H60:J60"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="C24:G25"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="H24:J25"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:J26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -74459,10 +74615,16 @@
         <v>8348</v>
       </c>
       <c r="E1549" s="133" t="s">
-        <v>816</v>
+        <v>8730</v>
       </c>
       <c r="F1549" s="133" t="s">
-        <v>816</v>
+        <v>8731</v>
+      </c>
+      <c r="G1549" s="130" t="s">
+        <v>8732</v>
+      </c>
+      <c r="H1549" s="130" t="s">
+        <v>8733</v>
       </c>
     </row>
     <row r="1550" spans="1:8">
@@ -74479,10 +74641,16 @@
         <v>8351</v>
       </c>
       <c r="E1550" s="133" t="s">
-        <v>816</v>
+        <v>8734</v>
       </c>
       <c r="F1550" s="133" t="s">
-        <v>816</v>
+        <v>8735</v>
+      </c>
+      <c r="G1550" s="130" t="s">
+        <v>8736</v>
+      </c>
+      <c r="H1550" s="130" t="s">
+        <v>8737</v>
       </c>
     </row>
     <row r="1551" spans="1:8">
@@ -74551,16 +74719,16 @@
         <v>8357</v>
       </c>
       <c r="E1553" s="130" t="s">
-        <v>816</v>
+        <v>8738</v>
       </c>
       <c r="F1553" s="130" t="s">
-        <v>816</v>
+        <v>8739</v>
       </c>
       <c r="G1553" s="130" t="s">
-        <v>816</v>
+        <v>8740</v>
       </c>
       <c r="H1553" s="130" t="s">
-        <v>816</v>
+        <v>8741</v>
       </c>
     </row>
     <row r="1554" spans="1:8">
@@ -74577,16 +74745,16 @@
         <v>8358</v>
       </c>
       <c r="E1554" s="130" t="s">
-        <v>816</v>
+        <v>8742</v>
       </c>
       <c r="F1554" s="130" t="s">
-        <v>816</v>
+        <v>8743</v>
       </c>
       <c r="G1554" s="130" t="s">
-        <v>816</v>
+        <v>8744</v>
       </c>
       <c r="H1554" s="130" t="s">
-        <v>816</v>
+        <v>8745</v>
       </c>
     </row>
     <row r="1555" spans="1:8">
@@ -74603,16 +74771,16 @@
         <v>8359</v>
       </c>
       <c r="E1555" s="130" t="s">
-        <v>816</v>
+        <v>8746</v>
       </c>
       <c r="F1555" s="130" t="s">
-        <v>816</v>
+        <v>8747</v>
       </c>
       <c r="G1555" s="130" t="s">
-        <v>816</v>
+        <v>8748</v>
       </c>
       <c r="H1555" s="130" t="s">
-        <v>816</v>
+        <v>8749</v>
       </c>
     </row>
     <row r="1556" spans="1:8">
@@ -74629,16 +74797,16 @@
         <v>8360</v>
       </c>
       <c r="E1556" s="130" t="s">
-        <v>816</v>
+        <v>8750</v>
       </c>
       <c r="F1556" s="130" t="s">
-        <v>816</v>
+        <v>8751</v>
       </c>
       <c r="G1556" s="130" t="s">
-        <v>816</v>
+        <v>8752</v>
       </c>
       <c r="H1556" s="130" t="s">
-        <v>816</v>
+        <v>8753</v>
       </c>
     </row>
     <row r="1557" spans="1:8">
@@ -74655,16 +74823,16 @@
         <v>8361</v>
       </c>
       <c r="E1557" s="130" t="s">
-        <v>816</v>
+        <v>8754</v>
       </c>
       <c r="F1557" s="130" t="s">
-        <v>816</v>
+        <v>8755</v>
       </c>
       <c r="G1557" s="130" t="s">
-        <v>816</v>
+        <v>8756</v>
       </c>
       <c r="H1557" s="130" t="s">
-        <v>816</v>
+        <v>8757</v>
       </c>
     </row>
     <row r="1558" spans="1:8">
@@ -74681,16 +74849,16 @@
         <v>8362</v>
       </c>
       <c r="E1558" s="130" t="s">
-        <v>816</v>
+        <v>8758</v>
       </c>
       <c r="F1558" s="130" t="s">
-        <v>816</v>
+        <v>8759</v>
       </c>
       <c r="G1558" s="130" t="s">
-        <v>816</v>
+        <v>8760</v>
       </c>
       <c r="H1558" s="130" t="s">
-        <v>816</v>
+        <v>8761</v>
       </c>
     </row>
     <row r="1559" spans="1:8">
@@ -74707,16 +74875,16 @@
         <v>8363</v>
       </c>
       <c r="E1559" s="130" t="s">
-        <v>816</v>
+        <v>8762</v>
       </c>
       <c r="F1559" s="130" t="s">
-        <v>816</v>
+        <v>8763</v>
       </c>
       <c r="G1559" s="130" t="s">
-        <v>816</v>
+        <v>8764</v>
       </c>
       <c r="H1559" s="130" t="s">
-        <v>816</v>
+        <v>8765</v>
       </c>
     </row>
     <row r="1560" spans="1:8">
@@ -74733,16 +74901,16 @@
         <v>8364</v>
       </c>
       <c r="E1560" s="130" t="s">
-        <v>816</v>
+        <v>8766</v>
       </c>
       <c r="F1560" s="130" t="s">
-        <v>816</v>
+        <v>8767</v>
       </c>
       <c r="G1560" s="130" t="s">
-        <v>816</v>
+        <v>8768</v>
       </c>
       <c r="H1560" s="130" t="s">
-        <v>816</v>
+        <v>8769</v>
       </c>
     </row>
     <row r="1561" spans="1:8">
@@ -78798,10 +78966,10 @@
       <c r="B2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
       <c r="G2" s="163"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -78811,10 +78979,10 @@
       <c r="M2" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="146"/>
-      <c r="O2" s="146"/>
-      <c r="P2" s="146"/>
-      <c r="Q2" s="147"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="144"/>
+      <c r="Q2" s="149"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
       <c r="T2" s="11"/>
@@ -78822,10 +78990,10 @@
       <c r="V2" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="W2" s="146"/>
-      <c r="X2" s="146"/>
-      <c r="Y2" s="146"/>
-      <c r="Z2" s="147"/>
+      <c r="W2" s="144"/>
+      <c r="X2" s="144"/>
+      <c r="Y2" s="144"/>
+      <c r="Z2" s="149"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
       <c r="AC2" s="10"/>
@@ -78944,10 +79112,10 @@
       <c r="V5" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="W5" s="146"/>
-      <c r="X5" s="146"/>
-      <c r="Y5" s="146"/>
-      <c r="Z5" s="147"/>
+      <c r="W5" s="144"/>
+      <c r="X5" s="144"/>
+      <c r="Y5" s="144"/>
+      <c r="Z5" s="149"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="10"/>
@@ -78993,10 +79161,10 @@
       <c r="B7" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="146"/>
-      <c r="D7" s="146"/>
-      <c r="E7" s="146"/>
-      <c r="F7" s="147"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="149"/>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -79005,10 +79173,10 @@
       <c r="L7" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="146"/>
-      <c r="N7" s="146"/>
-      <c r="O7" s="146"/>
-      <c r="P7" s="147"/>
+      <c r="M7" s="144"/>
+      <c r="N7" s="144"/>
+      <c r="O7" s="144"/>
+      <c r="P7" s="149"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
@@ -79217,10 +79385,10 @@
       <c r="AB14" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="AC14" s="146"/>
-      <c r="AD14" s="146"/>
-      <c r="AE14" s="146"/>
-      <c r="AF14" s="147"/>
+      <c r="AC14" s="144"/>
+      <c r="AD14" s="144"/>
+      <c r="AE14" s="144"/>
+      <c r="AF14" s="149"/>
       <c r="AG14" s="100"/>
       <c r="AH14" s="45"/>
       <c r="AI14" s="12"/>
@@ -79294,10 +79462,10 @@
       <c r="AB17" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="AC17" s="146"/>
-      <c r="AD17" s="146"/>
-      <c r="AE17" s="146"/>
-      <c r="AF17" s="147"/>
+      <c r="AC17" s="144"/>
+      <c r="AD17" s="144"/>
+      <c r="AE17" s="144"/>
+      <c r="AF17" s="149"/>
       <c r="AG17" s="102"/>
       <c r="AH17" s="38"/>
       <c r="AI17" s="10"/>
@@ -79415,10 +79583,10 @@
       <c r="AB21" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="AC21" s="146"/>
-      <c r="AD21" s="146"/>
-      <c r="AE21" s="146"/>
-      <c r="AF21" s="147"/>
+      <c r="AC21" s="144"/>
+      <c r="AD21" s="144"/>
+      <c r="AE21" s="144"/>
+      <c r="AF21" s="149"/>
       <c r="AG21" s="116"/>
       <c r="AH21" s="117"/>
     </row>
